--- a/セリフ編集/キャラタイプ別/蠱惑×感情的.xlsx
+++ b/セリフ編集/キャラタイプ別/蠱惑×感情的.xlsx
@@ -284,7 +284,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H302"/>
+  <dimension ref="A1:H346"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -1526,7 +1526,7 @@
     <row r="39" ht="40" customHeight="1">
       <c r="A39" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.emotional.seductive[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.ahead.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B39" t="inlineStr" s="2">
@@ -1536,12 +1536,12 @@
       </c>
       <c r="C39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES</t>
         </is>
       </c>
       <c r="D39" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.emotional.seductive[1]</t>
+          <t xml:space="preserve">ahead.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E39" t="inlineStr" s="2">
@@ -1551,14 +1551,14 @@
       </c>
       <c r="F39" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けたわ……っ……でも、もう憎しみは終わり……ふふ、清々しいの……</t>
+          <t xml:space="preserve">済んだ話よ……っ……なのに、まだ手が震えるの</t>
         </is>
       </c>
     </row>
     <row r="40" ht="40" customHeight="1">
       <c r="A40" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.emotional.seductive[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.behind.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B40" t="inlineStr" s="2">
@@ -1568,12 +1568,12 @@
       </c>
       <c r="C40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES</t>
         </is>
       </c>
       <c r="D40" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.emotional.seductive[1]</t>
+          <t xml:space="preserve">behind.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E40" t="inlineStr" s="2">
@@ -1583,14 +1583,14 @@
       </c>
       <c r="F40" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝った……っ……これで全部、過去にできるわね……ふふ、ありがとう……</t>
+          <t xml:space="preserve">終わったの……？ ……嘘よ。まだ、疼いてる</t>
         </is>
       </c>
     </row>
     <row r="41" ht="40" customHeight="1">
       <c r="A41" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser.emotional.seductive[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B41" t="inlineStr" s="2">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="C41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D41" t="inlineStr" s="12">
@@ -1615,14 +1615,14 @@
       </c>
       <c r="F41" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けたわ……っ……でも、あの子相手なら悔いはないの……ふふ……</t>
+          <t xml:space="preserve">負けたわ……っ……でも、もう憎しみは終わり……ふふ、清々しいの……</t>
         </is>
       </c>
     </row>
     <row r="42" ht="40" customHeight="1">
       <c r="A42" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.emotional.seductive[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr" s="2">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="C42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D42" t="inlineStr" s="12">
@@ -1647,14 +1647,14 @@
       </c>
       <c r="F42" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ったわ……っ……ふふ、あの子だからこそ、最高の試合になったの……</t>
+          <t xml:space="preserve">勝った……っ……これで全部、過去にできるわね……ふふ、ありがとう……</t>
         </is>
       </c>
     </row>
     <row r="43" ht="40" customHeight="1">
       <c r="A43" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.emotional.seductive[1]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B43" t="inlineStr" s="2">
@@ -1664,12 +1664,12 @@
       </c>
       <c r="C43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D43" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.emotional.seductive[1]</t>
+          <t xml:space="preserve">loser.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E43" t="inlineStr" s="2">
@@ -1679,14 +1679,14 @@
       </c>
       <c r="F43" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">そろそろ決着ね……っ……ふふ……</t>
+          <t xml:space="preserve">負けたわ……っ……でも、あの子相手なら悔いはないの……ふふ……</t>
         </is>
       </c>
     </row>
     <row r="44" ht="40" customHeight="1">
       <c r="A44" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.emotional.seductive[1]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr" s="2">
@@ -1696,12 +1696,12 @@
       </c>
       <c r="C44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D44" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.emotional.seductive[1]</t>
+          <t xml:space="preserve">winner.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E44" t="inlineStr" s="2">
@@ -1711,14 +1711,14 @@
       </c>
       <c r="F44" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">受けるわ……っ……ふふ、いつでもどうぞ……</t>
+          <t xml:space="preserve">勝ったわ……っ……ふふ、あの子だからこそ、最高の試合になったの……</t>
         </is>
       </c>
     </row>
     <row r="45" ht="40" customHeight="1">
       <c r="A45" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker.emotional.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr" s="2">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="C45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70</t>
         </is>
       </c>
       <c r="D45" t="inlineStr" s="12">
@@ -1743,14 +1743,14 @@
       </c>
       <c r="F45" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……この日を…ずっと待ってた……っ……行くわよ……!</t>
+          <t xml:space="preserve">そろそろ決着ね……っ……ふふ……</t>
         </is>
       </c>
     </row>
     <row r="46" ht="40" customHeight="1">
       <c r="A46" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.emotional.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B46" t="inlineStr" s="2">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="C46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70</t>
         </is>
       </c>
       <c r="D46" t="inlineStr" s="12">
@@ -1775,14 +1775,14 @@
       </c>
       <c r="F46" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ええ……!来なさい、全部受け止めるわ……!</t>
+          <t xml:space="preserve">受けるわ……っ……ふふ、いつでもどうぞ……</t>
         </is>
       </c>
     </row>
     <row r="47" ht="40" customHeight="1">
       <c r="A47" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.emotional.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B47" t="inlineStr" s="2">
@@ -1792,7 +1792,7 @@
       </c>
       <c r="C47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90</t>
         </is>
       </c>
       <c r="D47" t="inlineStr" s="12">
@@ -1807,14 +1807,14 @@
       </c>
       <c r="F47" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決着をつけるわ……っ……ふふ、ずっと待ってたの……</t>
+          <t xml:space="preserve">……この日を…ずっと待ってた……っ……行くわよ……!</t>
         </is>
       </c>
     </row>
     <row r="48" ht="40" customHeight="1">
       <c r="A48" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.emotional.seductive[2]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B48" t="inlineStr" s="2">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="C48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90</t>
         </is>
       </c>
       <c r="D48" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.emotional.seductive[2]</t>
+          <t xml:space="preserve">defender.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E48" t="inlineStr" s="2">
@@ -1839,14 +1839,14 @@
       </c>
       <c r="F48" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう逃がさない……っ……ふふ、覚悟して……</t>
+          <t xml:space="preserve">……ええ……!来なさい、全部受け止めるわ……!</t>
         </is>
       </c>
     </row>
     <row r="49" ht="40" customHeight="1">
       <c r="A49" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.emotional.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B49" t="inlineStr" s="2">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="D49" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.emotional.seductive[1]</t>
+          <t xml:space="preserve">attacker.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E49" t="inlineStr" s="2">
@@ -1871,14 +1871,14 @@
       </c>
       <c r="F49" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">受けて立つわ……っ……ふふ、来なさい……</t>
+          <t xml:space="preserve">決着をつけるわ……っ……ふふ、ずっと待ってたの……</t>
         </is>
       </c>
     </row>
     <row r="50" ht="40" customHeight="1">
       <c r="A50" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateAttacker.emotional.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.emotional.seductive[2]</t>
         </is>
       </c>
       <c r="B50" t="inlineStr" s="2">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="D50" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateAttacker.emotional.seductive[1]</t>
+          <t xml:space="preserve">attacker.emotional.seductive[2]</t>
         </is>
       </c>
       <c r="E50" t="inlineStr" s="2">
@@ -1903,14 +1903,14 @@
       </c>
       <c r="F50" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あなたが運命の相手……っ……ふふ、燃えるわね……</t>
+          <t xml:space="preserve">もう逃がさない……っ……ふふ、覚悟して……</t>
         </is>
       </c>
     </row>
     <row r="51" ht="40" customHeight="1">
       <c r="A51" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateDefender.emotional.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B51" t="inlineStr" s="2">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="D51" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateDefender.emotional.seductive[1]</t>
+          <t xml:space="preserve">defender.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E51" t="inlineStr" s="2">
@@ -1935,14 +1935,14 @@
       </c>
       <c r="F51" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">運命ね……っ……ふふ、その挑戦、受けるわ……</t>
+          <t xml:space="preserve">受けて立つわ……っ……ふふ、来なさい……</t>
         </is>
       </c>
     </row>
     <row r="52" ht="40" customHeight="1">
       <c r="A52" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateLoser.emotional.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateAttacker.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B52" t="inlineStr" s="2">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="C52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES</t>
         </is>
       </c>
       <c r="D52" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateLoser.emotional.seductive[1]</t>
+          <t xml:space="preserve">fateAttacker.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E52" t="inlineStr" s="2">
@@ -1967,14 +1967,14 @@
       </c>
       <c r="F52" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けたわ……っ……でも、運命の試合だったの、悔いはないわ……</t>
+          <t xml:space="preserve">あなたが運命の相手……っ……ふふ、燃えるわね……</t>
         </is>
       </c>
     </row>
     <row r="53" ht="40" customHeight="1">
       <c r="A53" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateWinner.emotional.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateDefender.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B53" t="inlineStr" s="2">
@@ -1984,12 +1984,12 @@
       </c>
       <c r="C53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES</t>
         </is>
       </c>
       <c r="D53" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateWinner.emotional.seductive[1]</t>
+          <t xml:space="preserve">fateDefender.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E53" t="inlineStr" s="2">
@@ -1999,14 +1999,14 @@
       </c>
       <c r="F53" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">運命の戦いに勝った……っ……ふふ、最高の瞬間だったわ……</t>
+          <t xml:space="preserve">運命ね……っ……ふふ、その挑戦、受けるわ……</t>
         </is>
       </c>
     </row>
     <row r="54" ht="40" customHeight="1">
       <c r="A54" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.emotional.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateLoser.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B54" t="inlineStr" s="2">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="D54" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.emotional.seductive[1]</t>
+          <t xml:space="preserve">fateLoser.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E54" t="inlineStr" s="2">
@@ -2031,14 +2031,14 @@
       </c>
       <c r="F54" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けたわ……っ……ふふ、悔しいけど終わりね……</t>
+          <t xml:space="preserve">負けたわ……っ……でも、運命の試合だったの、悔いはないわ……</t>
         </is>
       </c>
     </row>
     <row r="55" ht="40" customHeight="1">
       <c r="A55" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.emotional.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateWinner.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B55" t="inlineStr" s="2">
@@ -2053,7 +2053,7 @@
       </c>
       <c r="D55" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.emotional.seductive[1]</t>
+          <t xml:space="preserve">fateWinner.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E55" t="inlineStr" s="2">
@@ -2063,14 +2063,14 @@
       </c>
       <c r="F55" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ったわ……っ……ふふ、これでお終いね……</t>
+          <t xml:space="preserve">運命の戦いに勝った……っ……ふふ、最高の瞬間だったわ……</t>
         </is>
       </c>
     </row>
     <row r="56" ht="40" customHeight="1">
       <c r="A56" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.emotional.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B56" t="inlineStr" s="2">
@@ -2080,12 +2080,12 @@
       </c>
       <c r="C56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D56" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.emotional.seductive[1]</t>
+          <t xml:space="preserve">loser.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E56" t="inlineStr" s="2">
@@ -2095,14 +2095,14 @@
       </c>
       <c r="F56" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まさか負けるなんて……っ……ふふ、悔しい……</t>
+          <t xml:space="preserve">負けたわ……っ……ふふ、悔しいけど終わりね……</t>
         </is>
       </c>
     </row>
     <row r="57" ht="40" customHeight="1">
       <c r="A57" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.emotional.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B57" t="inlineStr" s="2">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="C57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D57" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.emotional.seductive[1]</t>
+          <t xml:space="preserve">winner.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E57" t="inlineStr" s="2">
@@ -2127,14 +2127,14 @@
       </c>
       <c r="F57" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝っちゃった……っ……ふふ、自分でも信じられないの……</t>
+          <t xml:space="preserve">勝ったわ……っ……ふふ、これでお終いね……</t>
         </is>
       </c>
     </row>
     <row r="58" ht="40" customHeight="1">
       <c r="A58" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.seductive_emotional.lose[1]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B58" t="inlineStr" s="2">
@@ -2144,29 +2144,29 @@
       </c>
       <c r="C58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
         </is>
       </c>
       <c r="D58" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive_emotional.lose[1]</t>
+          <t xml:space="preserve">loserLines.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">03 因縁・絆(Bond/Rivalry)イベント</t>
         </is>
       </c>
       <c r="F58" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……負けたわ。悔しい。ごめんなさい。</t>
+          <t xml:space="preserve">まさか負けるなんて……っ……ふふ、悔しい……</t>
         </is>
       </c>
     </row>
     <row r="59" ht="40" customHeight="1">
       <c r="A59" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.seductive_emotional.lose[2]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B59" t="inlineStr" s="2">
@@ -2176,29 +2176,29 @@
       </c>
       <c r="C59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
         </is>
       </c>
       <c r="D59" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive_emotional.lose[2]</t>
+          <t xml:space="preserve">winnerLines.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">03 因縁・絆(Bond/Rivalry)イベント</t>
         </is>
       </c>
       <c r="F59" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">認めるわ。今日は届かなかった。それだけ。</t>
+          <t xml:space="preserve">勝っちゃった……っ……ふふ、自分でも信じられないの……</t>
         </is>
       </c>
     </row>
     <row r="60" ht="40" customHeight="1">
       <c r="A60" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.seductive_emotional.lose[3]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.seductive_emotional.lose[1]</t>
         </is>
       </c>
       <c r="B60" t="inlineStr" s="2">
@@ -2213,7 +2213,7 @@
       </c>
       <c r="D60" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive_emotional.lose[3]</t>
+          <t xml:space="preserve">seductive_emotional.lose[1]</t>
         </is>
       </c>
       <c r="E60" t="inlineStr" s="2">
@@ -2223,14 +2223,14 @@
       </c>
       <c r="F60" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……勝てなかった。次はこうはいかないわ。</t>
+          <t xml:space="preserve">……負けたわ。悔しい。ごめんなさい。</t>
         </is>
       </c>
     </row>
     <row r="61" ht="40" customHeight="1">
       <c r="A61" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.seductive_emotional.petition[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.seductive_emotional.lose[2]</t>
         </is>
       </c>
       <c r="B61" t="inlineStr" s="2">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="D61" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive_emotional.petition[1]</t>
+          <t xml:space="preserve">seductive_emotional.lose[2]</t>
         </is>
       </c>
       <c r="E61" t="inlineStr" s="2">
@@ -2255,14 +2255,14 @@
       </c>
       <c r="F61" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長。あの人とやりたいの。……いいでしょ?</t>
+          <t xml:space="preserve">認めるわ。今日は届かなかった。それだけ。</t>
         </is>
       </c>
     </row>
     <row r="62" ht="40" customHeight="1">
       <c r="A62" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.seductive_emotional.petition[2]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.seductive_emotional.lose[3]</t>
         </is>
       </c>
       <c r="B62" t="inlineStr" s="2">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="D62" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive_emotional.petition[2]</t>
+          <t xml:space="preserve">seductive_emotional.lose[3]</t>
         </is>
       </c>
       <c r="E62" t="inlineStr" s="2">
@@ -2287,14 +2287,14 @@
       </c>
       <c r="F62" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">我慢が切れたの。あの人と、やらせて。</t>
+          <t xml:space="preserve">……勝てなかった。次はこうはいかないわ。</t>
         </is>
       </c>
     </row>
     <row r="63" ht="40" customHeight="1">
       <c r="A63" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.seductive_emotional.petition[3]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.seductive_emotional.petition[1]</t>
         </is>
       </c>
       <c r="B63" t="inlineStr" s="2">
@@ -2309,7 +2309,7 @@
       </c>
       <c r="D63" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive_emotional.petition[3]</t>
+          <t xml:space="preserve">seductive_emotional.petition[1]</t>
         </is>
       </c>
       <c r="E63" t="inlineStr" s="2">
@@ -2319,14 +2319,14 @@
       </c>
       <c r="F63" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">言うだけ言うわ。あの人と当てて。</t>
+          <t xml:space="preserve">社長。あの人とやりたいの。……いいでしょ?</t>
         </is>
       </c>
     </row>
     <row r="64" ht="40" customHeight="1">
       <c r="A64" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.seductive_emotional.sendoff[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.seductive_emotional.petition[2]</t>
         </is>
       </c>
       <c r="B64" t="inlineStr" s="2">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="D64" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive_emotional.sendoff[1]</t>
+          <t xml:space="preserve">seductive_emotional.petition[2]</t>
         </is>
       </c>
       <c r="E64" t="inlineStr" s="2">
@@ -2351,14 +2351,14 @@
       </c>
       <c r="F64" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふん、話が早いのね。……ありがとう。</t>
+          <t xml:space="preserve">我慢が切れたの。あの人と、やらせて。</t>
         </is>
       </c>
     </row>
     <row r="65" ht="40" customHeight="1">
       <c r="A65" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.seductive_emotional.sendoff[2]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.seductive_emotional.petition[3]</t>
         </is>
       </c>
       <c r="B65" t="inlineStr" s="2">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="D65" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive_emotional.sendoff[2]</t>
+          <t xml:space="preserve">seductive_emotional.petition[3]</t>
         </is>
       </c>
       <c r="E65" t="inlineStr" s="2">
@@ -2383,14 +2383,14 @@
       </c>
       <c r="F65" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">それでいいのよ、社長。行ってくるわ。</t>
+          <t xml:space="preserve">言うだけ言うわ。あの人と当てて。</t>
         </is>
       </c>
     </row>
     <row r="66" ht="40" customHeight="1">
       <c r="A66" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.seductive_emotional.sendoff[3]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.seductive_emotional.sendoff[1]</t>
         </is>
       </c>
       <c r="B66" t="inlineStr" s="2">
@@ -2405,7 +2405,7 @@
       </c>
       <c r="D66" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive_emotional.sendoff[3]</t>
+          <t xml:space="preserve">seductive_emotional.sendoff[1]</t>
         </is>
       </c>
       <c r="E66" t="inlineStr" s="2">
@@ -2415,14 +2415,14 @@
       </c>
       <c r="F66" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">感謝はするわ。……見てなさい。</t>
+          <t xml:space="preserve">ふん、話が早いのね。……ありがとう。</t>
         </is>
       </c>
     </row>
     <row r="67" ht="40" customHeight="1">
       <c r="A67" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.seductive_emotional.win[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.seductive_emotional.sendoff[2]</t>
         </is>
       </c>
       <c r="B67" t="inlineStr" s="2">
@@ -2437,7 +2437,7 @@
       </c>
       <c r="D67" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive_emotional.win[1]</t>
+          <t xml:space="preserve">seductive_emotional.sendoff[2]</t>
         </is>
       </c>
       <c r="E67" t="inlineStr" s="2">
@@ -2447,14 +2447,14 @@
       </c>
       <c r="F67" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ったわ。当たり前でしょ。……ありがと。</t>
+          <t xml:space="preserve">それでいいのよ、社長。行ってくるわ。</t>
         </is>
       </c>
     </row>
     <row r="68" ht="40" customHeight="1">
       <c r="A68" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.seductive_emotional.win[2]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.seductive_emotional.sendoff[3]</t>
         </is>
       </c>
       <c r="B68" t="inlineStr" s="2">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="D68" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive_emotional.win[2]</t>
+          <t xml:space="preserve">seductive_emotional.sendoff[3]</t>
         </is>
       </c>
       <c r="E68" t="inlineStr" s="2">
@@ -2479,14 +2479,14 @@
       </c>
       <c r="F68" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ほら、私の言う通り。いい報告でしょう?</t>
+          <t xml:space="preserve">感謝はするわ。……見てなさい。</t>
         </is>
       </c>
     </row>
     <row r="69" ht="40" customHeight="1">
       <c r="A69" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.seductive_emotional.win[3]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.seductive_emotional.win[1]</t>
         </is>
       </c>
       <c r="B69" t="inlineStr" s="2">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="D69" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive_emotional.win[3]</t>
+          <t xml:space="preserve">seductive_emotional.win[1]</t>
         </is>
       </c>
       <c r="E69" t="inlineStr" s="2">
@@ -2511,14 +2511,14 @@
       </c>
       <c r="F69" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ったわよ。頷いた甲斐、あったでしょ。</t>
+          <t xml:space="preserve">勝ったわ。当たり前でしょ。……ありがと。</t>
         </is>
       </c>
     </row>
     <row r="70" ht="40" customHeight="1">
       <c r="A70" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.seductive_emotional._accept[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.seductive_emotional.win[2]</t>
         </is>
       </c>
       <c r="B70" t="inlineStr" s="2">
@@ -2528,12 +2528,12 @@
       </c>
       <c r="C70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
         </is>
       </c>
       <c r="D70" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive_emotional._accept[1]</t>
+          <t xml:space="preserve">seductive_emotional.win[2]</t>
         </is>
       </c>
       <c r="E70" t="inlineStr" s="2">
@@ -2543,14 +2543,14 @@
       </c>
       <c r="F70" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私を呼んだわね? …後悔させてあげる。</t>
+          <t xml:space="preserve">ほら、私の言う通り。いい報告でしょう?</t>
         </is>
       </c>
     </row>
     <row r="71" ht="40" customHeight="1">
       <c r="A71" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.seductive_emotional._accept[2]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.seductive_emotional.win[3]</t>
         </is>
       </c>
       <c r="B71" t="inlineStr" s="2">
@@ -2560,12 +2560,12 @@
       </c>
       <c r="C71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
         </is>
       </c>
       <c r="D71" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive_emotional._accept[2]</t>
+          <t xml:space="preserve">seductive_emotional.win[3]</t>
         </is>
       </c>
       <c r="E71" t="inlineStr" s="2">
@@ -2575,14 +2575,14 @@
       </c>
       <c r="F71" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふざけてるの? …いいわ、受けるわよ。</t>
+          <t xml:space="preserve">勝ったわよ。頷いた甲斐、あったでしょ。</t>
         </is>
       </c>
     </row>
     <row r="72" ht="40" customHeight="1">
       <c r="A72" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.seductive_emotional._accept[3]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.seductive_emotional._accept[1]</t>
         </is>
       </c>
       <c r="B72" t="inlineStr" s="2">
@@ -2597,7 +2597,7 @@
       </c>
       <c r="D72" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive_emotional._accept[3]</t>
+          <t xml:space="preserve">seductive_emotional._accept[1]</t>
         </is>
       </c>
       <c r="E72" t="inlineStr" s="2">
@@ -2607,14 +2607,14 @@
       </c>
       <c r="F72" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">その目、気に入らないわ。…来なさい。</t>
+          <t xml:space="preserve">私を呼んだわね? …後悔させてあげる。</t>
         </is>
       </c>
     </row>
     <row r="73" ht="40" customHeight="1">
       <c r="A73" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.seductive_emotional.draw[1]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.seductive_emotional._accept[2]</t>
         </is>
       </c>
       <c r="B73" t="inlineStr" s="2">
@@ -2629,7 +2629,7 @@
       </c>
       <c r="D73" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive_emotional.draw[1]</t>
+          <t xml:space="preserve">seductive_emotional._accept[2]</t>
         </is>
       </c>
       <c r="E73" t="inlineStr" s="2">
@@ -2639,14 +2639,14 @@
       </c>
       <c r="F73" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">なによこれ。…全然すっきりしないわ。</t>
+          <t xml:space="preserve">ふざけてるの? …いいわ、受けるわよ。</t>
         </is>
       </c>
     </row>
     <row r="74" ht="40" customHeight="1">
       <c r="A74" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.seductive_emotional.draw[2]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.seductive_emotional._accept[3]</t>
         </is>
       </c>
       <c r="B74" t="inlineStr" s="2">
@@ -2661,7 +2661,7 @@
       </c>
       <c r="D74" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive_emotional.draw[2]</t>
+          <t xml:space="preserve">seductive_emotional._accept[3]</t>
         </is>
       </c>
       <c r="E74" t="inlineStr" s="2">
@@ -2671,14 +2671,14 @@
       </c>
       <c r="F74" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決めさせなさいよ! …ああ、もう。</t>
+          <t xml:space="preserve">その目、気に入らないわ。…来なさい。</t>
         </is>
       </c>
     </row>
     <row r="75" ht="40" customHeight="1">
       <c r="A75" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.seductive_emotional.draw[3]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.seductive_emotional.draw[1]</t>
         </is>
       </c>
       <c r="B75" t="inlineStr" s="2">
@@ -2693,7 +2693,7 @@
       </c>
       <c r="D75" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive_emotional.draw[3]</t>
+          <t xml:space="preserve">seductive_emotional.draw[1]</t>
         </is>
       </c>
       <c r="E75" t="inlineStr" s="2">
@@ -2703,14 +2703,14 @@
       </c>
       <c r="F75" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">中途半端は嫌いなの。…わかるでしょ?</t>
+          <t xml:space="preserve">なによこれ。…全然すっきりしないわ。</t>
         </is>
       </c>
     </row>
     <row r="76" ht="40" customHeight="1">
       <c r="A76" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.seductive_emotional.lose[1]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.seductive_emotional.draw[2]</t>
         </is>
       </c>
       <c r="B76" t="inlineStr" s="2">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="D76" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive_emotional.lose[1]</t>
+          <t xml:space="preserve">seductive_emotional.draw[2]</t>
         </is>
       </c>
       <c r="E76" t="inlineStr" s="2">
@@ -2735,14 +2735,14 @@
       </c>
       <c r="F76" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……っ、なんで。認めたくないわ。</t>
+          <t xml:space="preserve">決めさせなさいよ! …ああ、もう。</t>
         </is>
       </c>
     </row>
     <row r="77" ht="40" customHeight="1">
       <c r="A77" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.seductive_emotional.lose[2]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.seductive_emotional.draw[3]</t>
         </is>
       </c>
       <c r="B77" t="inlineStr" s="2">
@@ -2757,7 +2757,7 @@
       </c>
       <c r="D77" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive_emotional.lose[2]</t>
+          <t xml:space="preserve">seductive_emotional.draw[3]</t>
         </is>
       </c>
       <c r="E77" t="inlineStr" s="2">
@@ -2767,14 +2767,14 @@
       </c>
       <c r="F77" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しい……! 悔しいのよ、私は。</t>
+          <t xml:space="preserve">中途半端は嫌いなの。…わかるでしょ?</t>
         </is>
       </c>
     </row>
     <row r="78" ht="40" customHeight="1">
       <c r="A78" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.seductive_emotional.lose[3]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.seductive_emotional.lose[1]</t>
         </is>
       </c>
       <c r="B78" t="inlineStr" s="2">
@@ -2789,7 +2789,7 @@
       </c>
       <c r="D78" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive_emotional.lose[3]</t>
+          <t xml:space="preserve">seductive_emotional.lose[1]</t>
         </is>
       </c>
       <c r="E78" t="inlineStr" s="2">
@@ -2799,14 +2799,14 @@
       </c>
       <c r="F78" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">笑いなさいよ。……今だけは、許すわ。</t>
+          <t xml:space="preserve">……っ、なんで。認めたくないわ。</t>
         </is>
       </c>
     </row>
     <row r="79" ht="40" customHeight="1">
       <c r="A79" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.seductive_emotional.win[1]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.seductive_emotional.lose[2]</t>
         </is>
       </c>
       <c r="B79" t="inlineStr" s="2">
@@ -2821,7 +2821,7 @@
       </c>
       <c r="D79" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive_emotional.win[1]</t>
+          <t xml:space="preserve">seductive_emotional.lose[2]</t>
         </is>
       </c>
       <c r="E79" t="inlineStr" s="2">
@@ -2831,14 +2831,14 @@
       </c>
       <c r="F79" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">分かった? 二度と私を選ばないで。</t>
+          <t xml:space="preserve">悔しい……! 悔しいのよ、私は。</t>
         </is>
       </c>
     </row>
     <row r="80" ht="40" customHeight="1">
       <c r="A80" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.seductive_emotional.win[2]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.seductive_emotional.lose[3]</t>
         </is>
       </c>
       <c r="B80" t="inlineStr" s="2">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="D80" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive_emotional.win[2]</t>
+          <t xml:space="preserve">seductive_emotional.lose[3]</t>
         </is>
       </c>
       <c r="E80" t="inlineStr" s="2">
@@ -2863,14 +2863,14 @@
       </c>
       <c r="F80" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ……ざまあないわね。</t>
+          <t xml:space="preserve">笑いなさいよ。……今だけは、許すわ。</t>
         </is>
       </c>
     </row>
     <row r="81" ht="40" customHeight="1">
       <c r="A81" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.seductive_emotional.win[3]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.seductive_emotional.win[1]</t>
         </is>
       </c>
       <c r="B81" t="inlineStr" s="2">
@@ -2885,7 +2885,7 @@
       </c>
       <c r="D81" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive_emotional.win[3]</t>
+          <t xml:space="preserve">seductive_emotional.win[1]</t>
         </is>
       </c>
       <c r="E81" t="inlineStr" s="2">
@@ -2895,14 +2895,14 @@
       </c>
       <c r="F81" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もっと吠えてみせなさいよ。ほら。</t>
+          <t xml:space="preserve">分かった? 二度と私を選ばないで。</t>
         </is>
       </c>
     </row>
     <row r="82" ht="40" customHeight="1">
       <c r="A82" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.emotional.seductive[1]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.seductive_emotional.win[2]</t>
         </is>
       </c>
       <c r="B82" t="inlineStr" s="2">
@@ -2912,29 +2912,29 @@
       </c>
       <c r="C82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
         </is>
       </c>
       <c r="D82" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accepted.emotional.seductive[1]</t>
+          <t xml:space="preserve">seductive_emotional.win[2]</t>
         </is>
       </c>
       <c r="E82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
         </is>
       </c>
       <c r="F82" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ごめんね。……新しい舞台で、もっと光ってみせる</t>
+          <t xml:space="preserve">ふふ……ざまあないわね。</t>
         </is>
       </c>
     </row>
     <row r="83" ht="40" customHeight="1">
       <c r="A83" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.emotional.seductive[1]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.seductive_emotional.win[3]</t>
         </is>
       </c>
       <c r="B83" t="inlineStr" s="2">
@@ -2944,29 +2944,29 @@
       </c>
       <c r="C83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
         </is>
       </c>
       <c r="D83" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defended.emotional.seductive[1]</t>
+          <t xml:space="preserve">seductive_emotional.win[3]</t>
         </is>
       </c>
       <c r="E83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
         </is>
       </c>
       <c r="F83" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……必要としてくれるんだ。…うん、残る</t>
+          <t xml:space="preserve">もっと吠えてみせなさいよ。ほら。</t>
         </is>
       </c>
     </row>
     <row r="84" ht="40" customHeight="1">
       <c r="A84" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.emotional.seductive[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B84" t="inlineStr" s="2">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="D84" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defense_failed.emotional.seductive[1]</t>
+          <t xml:space="preserve">accepted.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E84" t="inlineStr" s="2">
@@ -2991,14 +2991,14 @@
       </c>
       <c r="F84" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ごめん。……でも、決めたから</t>
+          <t xml:space="preserve">……ごめんね。……新しい舞台で、もっと光ってみせる</t>
         </is>
       </c>
     </row>
     <row r="85" ht="40" customHeight="1">
       <c r="A85" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.default.emotional.seductive[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B85" t="inlineStr" s="2">
@@ -3008,12 +3008,12 @@
       </c>
       <c r="C85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETAIN_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D85" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">default.emotional.seductive[1]</t>
+          <t xml:space="preserve">defended.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E85" t="inlineStr" s="2">
@@ -3023,14 +3023,14 @@
       </c>
       <c r="F85" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">残らせて……っ……ふふ、まだここでやりたいの……</t>
+          <t xml:space="preserve">……必要としてくれるんだ。…うん、残る</t>
         </is>
       </c>
     </row>
     <row r="86" ht="40" customHeight="1">
       <c r="A86" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.former_champ.emotional.seductive[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B86" t="inlineStr" s="2">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="C86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETAIN_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D86" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">former_champ.emotional.seductive[1]</t>
+          <t xml:space="preserve">defense_failed.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E86" t="inlineStr" s="2">
@@ -3055,14 +3055,14 @@
       </c>
       <c r="F86" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">元チャンピオンとして……っ……ふふ、この場所をまだ守りたいの……</t>
+          <t xml:space="preserve">……ごめん。……でも、決めたから</t>
         </is>
       </c>
     </row>
     <row r="87" ht="40" customHeight="1">
       <c r="A87" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.heel.emotional.seductive[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.default.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B87" t="inlineStr" s="2">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="D87" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heel.emotional.seductive[1]</t>
+          <t xml:space="preserve">default.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E87" t="inlineStr" s="2">
@@ -3087,14 +3087,14 @@
       </c>
       <c r="F87" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">嫌われ者でも……っ……ふふ、ここに居場所が欲しいの……</t>
+          <t xml:space="preserve">残らせて……っ……ふふ、まだここでやりたいの……</t>
         </is>
       </c>
     </row>
     <row r="88" ht="40" customHeight="1">
       <c r="A88" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.high_trust.emotional.seductive[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.former_champ.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B88" t="inlineStr" s="2">
@@ -3109,7 +3109,7 @@
       </c>
       <c r="D88" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">high_trust.emotional.seductive[1]</t>
+          <t xml:space="preserve">former_champ.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E88" t="inlineStr" s="2">
@@ -3119,14 +3119,14 @@
       </c>
       <c r="F88" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ずっとここにいたい……っ……ふふ、あなたのそばが一番なの……</t>
+          <t xml:space="preserve">元チャンピオンとして……っ……ふふ、この場所をまだ守りたいの……</t>
         </is>
       </c>
     </row>
     <row r="89" ht="40" customHeight="1">
       <c r="A89" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ.emotional.seductive[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.heel.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B89" t="inlineStr" s="2">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="C89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
+          <t xml:space="preserve">RETAIN_LINES</t>
         </is>
       </c>
       <c r="D89" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_former_champ.emotional.seductive[1]</t>
+          <t xml:space="preserve">heel.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E89" t="inlineStr" s="2">
@@ -3151,14 +3151,14 @@
       </c>
       <c r="F89" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオンになれた……っ……ふふ、もう思い残しはないわ……</t>
+          <t xml:space="preserve">嫌われ者でも……っ……ふふ、ここに居場所が欲しいの……</t>
         </is>
       </c>
     </row>
     <row r="90" ht="40" customHeight="1">
       <c r="A90" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel.emotional.seductive[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.high_trust.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B90" t="inlineStr" s="2">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="C90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
+          <t xml:space="preserve">RETAIN_LINES</t>
         </is>
       </c>
       <c r="D90" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_heel.emotional.seductive[1]</t>
+          <t xml:space="preserve">high_trust.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E90" t="inlineStr" s="2">
@@ -3183,14 +3183,14 @@
       </c>
       <c r="F90" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悪役のままでも……っ……ふふ、最後まで愛してくれてありがとう……</t>
+          <t xml:space="preserve">ずっとここにいたい……っ……ふふ、あなたのそばが一番なの……</t>
         </is>
       </c>
     </row>
     <row r="91" ht="40" customHeight="1">
       <c r="A91" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title.emotional.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B91" t="inlineStr" s="2">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="D91" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_no_title.emotional.seductive[1]</t>
+          <t xml:space="preserve">accept_former_champ.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E91" t="inlineStr" s="2">
@@ -3215,14 +3215,14 @@
       </c>
       <c r="F91" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">無冠でいいの……っ……ふふ、やりきった気がするから……</t>
+          <t xml:space="preserve">チャンピオンになれた……っ……ふふ、もう思い残しはないわ……</t>
         </is>
       </c>
     </row>
     <row r="92" ht="40" customHeight="1">
       <c r="A92" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.emotional.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B92" t="inlineStr" s="2">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="D92" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_terminal.emotional.seductive[1]</t>
+          <t xml:space="preserve">accept_heel.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E92" t="inlineStr" s="2">
@@ -3247,14 +3247,14 @@
       </c>
       <c r="F92" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう限界なの……っ……ふふ、ごめんなさい……</t>
+          <t xml:space="preserve">悪役のままでも……っ……ふふ、最後まで愛してくれてありがとう……</t>
         </is>
       </c>
     </row>
     <row r="93" ht="40" customHeight="1">
       <c r="A93" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless.emotional.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B93" t="inlineStr" s="2">
@@ -3269,7 +3269,7 @@
       </c>
       <c r="D93" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_winless.emotional.seductive[1]</t>
+          <t xml:space="preserve">accept_no_title.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E93" t="inlineStr" s="2">
@@ -3279,14 +3279,14 @@
       </c>
       <c r="F93" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝てなかったけど……っ……ふふ、戦えただけで満足なの……</t>
+          <t xml:space="preserve">無冠でいいの……っ……ふふ、やりきった気がするから……</t>
         </is>
       </c>
     </row>
     <row r="94" ht="40" customHeight="1">
       <c r="A94" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.emotional.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B94" t="inlineStr" s="2">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="C94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
         </is>
       </c>
       <c r="D94" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_champ.emotional.seductive[1]</t>
+          <t xml:space="preserve">accept_terminal.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E94" t="inlineStr" s="2">
@@ -3311,14 +3311,14 @@
       </c>
       <c r="F94" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだチャンピオンよ……っ……ふふ、降りるわけにはいかないの……</t>
+          <t xml:space="preserve">もう限界なの……っ……ふふ、ごめんなさい……</t>
         </is>
       </c>
     </row>
     <row r="95" ht="40" customHeight="1">
       <c r="A95" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust.emotional.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B95" t="inlineStr" s="2">
@@ -3328,12 +3328,12 @@
       </c>
       <c r="C95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
         </is>
       </c>
       <c r="D95" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_distrust.emotional.seductive[1]</t>
+          <t xml:space="preserve">accept_winless.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E95" t="inlineStr" s="2">
@@ -3343,14 +3343,14 @@
       </c>
       <c r="F95" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">どうして……っ……ふふ、わたしを切り捨てるつもり？……</t>
+          <t xml:space="preserve">勝てなかったけど……っ……ふふ、戦えただけで満足なの……</t>
         </is>
       </c>
     </row>
     <row r="96" ht="40" customHeight="1">
       <c r="A96" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting.emotional.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B96" t="inlineStr" s="2">
@@ -3365,7 +3365,7 @@
       </c>
       <c r="D96" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_fighting.emotional.seductive[1]</t>
+          <t xml:space="preserve">refuse_champ.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E96" t="inlineStr" s="2">
@@ -3375,14 +3375,14 @@
       </c>
       <c r="F96" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ戦えるの……っ……ふふ、わたしを止めないで……</t>
+          <t xml:space="preserve">まだチャンピオンよ……っ……ふふ、降りるわけにはいかないの……</t>
         </is>
       </c>
     </row>
     <row r="97" ht="40" customHeight="1">
       <c r="A97" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel.emotional.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B97" t="inlineStr" s="2">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="D97" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_heel.emotional.seductive[1]</t>
+          <t xml:space="preserve">refuse_distrust.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E97" t="inlineStr" s="2">
@@ -3407,14 +3407,14 @@
       </c>
       <c r="F97" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悪役だってまだやれるわ……っ……ふふ、辞めないわよ……</t>
+          <t xml:space="preserve">どうして……っ……ふふ、わたしを切り捨てるつもり？……</t>
         </is>
       </c>
     </row>
     <row r="98" ht="40" customHeight="1">
       <c r="A98" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.emotional.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B98" t="inlineStr" s="2">
@@ -3424,12 +3424,12 @@
       </c>
       <c r="C98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
         </is>
       </c>
       <c r="D98" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A1_champion.emotional.seductive[1]</t>
+          <t xml:space="preserve">refuse_fighting.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E98" t="inlineStr" s="2">
@@ -3439,14 +3439,14 @@
       </c>
       <c r="F98" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオンのまま降りるわ……っ……ふふ、これ以上ない花道ね……</t>
+          <t xml:space="preserve">まだ戦えるの……っ……ふふ、わたしを止めないで……</t>
         </is>
       </c>
     </row>
     <row r="99" ht="40" customHeight="1">
       <c r="A99" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.emotional.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B99" t="inlineStr" s="2">
@@ -3456,12 +3456,12 @@
       </c>
       <c r="C99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
         </is>
       </c>
       <c r="D99" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A2_uncrowned.emotional.seductive[1]</t>
+          <t xml:space="preserve">refuse_heel.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E99" t="inlineStr" s="2">
@@ -3471,14 +3471,14 @@
       </c>
       <c r="F99" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">無冠で終わるわ……っ……ふふ、それでもやりきったの……</t>
+          <t xml:space="preserve">悪役だってまだやれるわ……っ……ふふ、辞めないわよ……</t>
         </is>
       </c>
     </row>
     <row r="100" ht="40" customHeight="1">
       <c r="A100" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.emotional.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B100" t="inlineStr" s="2">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="D100" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A3_heel.emotional.seductive[1]</t>
+          <t xml:space="preserve">A1_champion.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E100" t="inlineStr" s="2">
@@ -3503,14 +3503,14 @@
       </c>
       <c r="F100" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悪役のまま消えるわ……っ……ふふ、それがわたしらしいの……</t>
+          <t xml:space="preserve">チャンピオンのまま降りるわ……っ……ふふ、これ以上ない花道ね……</t>
         </is>
       </c>
     </row>
     <row r="101" ht="40" customHeight="1">
       <c r="A101" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.emotional.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B101" t="inlineStr" s="2">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="D101" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A4_veteran.emotional.seductive[1]</t>
+          <t xml:space="preserve">A2_uncrowned.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E101" t="inlineStr" s="2">
@@ -3535,14 +3535,14 @@
       </c>
       <c r="F101" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">長かったわ……っ……ふふ、ありがとう、みんな……</t>
+          <t xml:space="preserve">無冠で終わるわ……っ……ふふ、それでもやりきったの……</t>
         </is>
       </c>
     </row>
     <row r="102" ht="40" customHeight="1">
       <c r="A102" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B1_young.emotional.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B102" t="inlineStr" s="2">
@@ -3557,7 +3557,7 @@
       </c>
       <c r="D102" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1_young.emotional.seductive[1]</t>
+          <t xml:space="preserve">A3_heel.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E102" t="inlineStr" s="2">
@@ -3567,14 +3567,14 @@
       </c>
       <c r="F102" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ若いけど……っ……ふふ、わたしには無理だったの……</t>
+          <t xml:space="preserve">悪役のまま消えるわ……っ……ふふ、それがわたしらしいの……</t>
         </is>
       </c>
     </row>
     <row r="103" ht="40" customHeight="1">
       <c r="A103" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.emotional.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B103" t="inlineStr" s="2">
@@ -3589,7 +3589,7 @@
       </c>
       <c r="D103" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_prime.emotional.seductive[1]</t>
+          <t xml:space="preserve">A4_veteran.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E103" t="inlineStr" s="2">
@@ -3599,14 +3599,14 @@
       </c>
       <c r="F103" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今が頂点なのに……っ……ふふ、だからこそ降りるの……</t>
+          <t xml:space="preserve">長かったわ……っ……ふふ、ありがとう、みんな……</t>
         </is>
       </c>
     </row>
     <row r="104" ht="40" customHeight="1">
       <c r="A104" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B3_older.emotional.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B1_young.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B104" t="inlineStr" s="2">
@@ -3621,7 +3621,7 @@
       </c>
       <c r="D104" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B3_older.emotional.seductive[1]</t>
+          <t xml:space="preserve">B1_young.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E104" t="inlineStr" s="2">
@@ -3631,14 +3631,14 @@
       </c>
       <c r="F104" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう体が……っ……ふふ、潮時ね……</t>
+          <t xml:space="preserve">まだ若いけど……っ……ふふ、わたしには無理だったの……</t>
         </is>
       </c>
     </row>
     <row r="105" ht="40" customHeight="1">
       <c r="A105" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.emotional.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B105" t="inlineStr" s="2">
@@ -3653,7 +3653,7 @@
       </c>
       <c r="D105" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_champion_injury.emotional.seductive[1]</t>
+          <t xml:space="preserve">B2_prime.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E105" t="inlineStr" s="2">
@@ -3663,14 +3663,14 @@
       </c>
       <c r="F105" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオンのまま、怪我で……っ……ふふ、悔しいけど仕方ないの……</t>
+          <t xml:space="preserve">今が頂点なのに……っ……ふふ、だからこそ降りるの……</t>
         </is>
       </c>
     </row>
     <row r="106" ht="40" customHeight="1">
       <c r="A106" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VOLUNTARY_STAY_LINES.emotional.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B3_older.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B106" t="inlineStr" s="2">
@@ -3680,12 +3680,12 @@
       </c>
       <c r="C106" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">VOLUNTARY_STAY_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D106" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.seductive[1]</t>
+          <t xml:space="preserve">B3_older.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E106" t="inlineStr" s="2">
@@ -3695,14 +3695,14 @@
       </c>
       <c r="F106" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">残るわ…っ…ここが、わたしの…大切な場所だから…</t>
+          <t xml:space="preserve">もう体が……っ……ふふ、潮時ね……</t>
         </is>
       </c>
     </row>
     <row r="107" ht="40" customHeight="1">
       <c r="A107" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.emotional.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B107" t="inlineStr" s="2">
@@ -3712,29 +3712,29 @@
       </c>
       <c r="C107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D107" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_accept.emotional.seductive[1]</t>
+          <t xml:space="preserve">B4_champion_injury.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F107" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">受けるわ……っ……ふふ、こんなに評価してくれて、嬉しい……</t>
+          <t xml:space="preserve">チャンピオンのまま、怪我で……っ……ふふ、悔しいけど仕方ないの……</t>
         </is>
       </c>
     </row>
     <row r="108" ht="40" customHeight="1">
       <c r="A108" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.emotional.seductive[1]</t>
+          <t xml:space="preserve">VOLUNTARY_STAY_LINES.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B108" t="inlineStr" s="2">
@@ -3744,29 +3744,29 @@
       </c>
       <c r="C108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">VOLUNTARY_STAY_LINES</t>
         </is>
       </c>
       <c r="D108" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_accept.emotional.seductive[1]</t>
+          <t xml:space="preserve">emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F108" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">その条件なら……っ……ふふ、いいわよ、受けてあげる……</t>
+          <t xml:space="preserve">残るわ…っ…ここが、わたしの…大切な場所だから…</t>
         </is>
       </c>
     </row>
     <row r="109" ht="40" customHeight="1">
       <c r="A109" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.emotional.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B109" t="inlineStr" s="2">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="D109" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_refuse.emotional.seductive[1]</t>
+          <t xml:space="preserve">raise_accept.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E109" t="inlineStr" s="2">
@@ -3791,14 +3791,14 @@
       </c>
       <c r="F109" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">考えたけれど……っ……やっぱり、難しいわ、ごめんなさい……</t>
+          <t xml:space="preserve">受けるわ……っ……ふふ、こんなに評価してくれて、嬉しい……</t>
         </is>
       </c>
     </row>
     <row r="110" ht="40" customHeight="1">
       <c r="A110" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.emotional.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B110" t="inlineStr" s="2">
@@ -3813,7 +3813,7 @@
       </c>
       <c r="D110" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.emotional.seductive[1]</t>
+          <t xml:space="preserve">raise_negotiate_accept.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E110" t="inlineStr" s="2">
@@ -3823,14 +3823,14 @@
       </c>
       <c r="F110" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">契約の話……っ……聞いてもらいたいことがあるの……</t>
+          <t xml:space="preserve">その条件なら……っ……ふふ、いいわよ、受けてあげる……</t>
         </is>
       </c>
     </row>
     <row r="111" ht="40" customHeight="1">
       <c r="A111" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.emotional.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B111" t="inlineStr" s="2">
@@ -3845,7 +3845,7 @@
       </c>
       <c r="D111" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_refuse.emotional.seductive[1]</t>
+          <t xml:space="preserve">raise_negotiate_refuse.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E111" t="inlineStr" s="2">
@@ -3855,14 +3855,14 @@
       </c>
       <c r="F111" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……っ……ごめんなさい、その条件では納得できないの……</t>
+          <t xml:space="preserve">考えたけれど……っ……やっぱり、難しいわ、ごめんなさい……</t>
         </is>
       </c>
     </row>
     <row r="112" ht="40" customHeight="1">
       <c r="A112" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.emotional.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B112" t="inlineStr" s="2">
@@ -3877,7 +3877,7 @@
       </c>
       <c r="D112" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_listen.emotional.seductive[1]</t>
+          <t xml:space="preserve">raise_open.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E112" t="inlineStr" s="2">
@@ -3887,14 +3887,14 @@
       </c>
       <c r="F112" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">話だけは聞くわ……っ……それで決めるから……</t>
+          <t xml:space="preserve">契約の話……っ……聞いてもらいたいことがあるの……</t>
         </is>
       </c>
     </row>
     <row r="113" ht="40" customHeight="1">
       <c r="A113" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.emotional.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B113" t="inlineStr" s="2">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="D113" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.emotional.seductive[1]</t>
+          <t xml:space="preserve">raise_refuse.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E113" t="inlineStr" s="2">
@@ -3919,14 +3919,14 @@
       </c>
       <c r="F113" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">他から声がかかってるの……っ……ふふ、どうしようかしら……</t>
+          <t xml:space="preserve">……っ……ごめんなさい、その条件では納得できないの……</t>
         </is>
       </c>
     </row>
     <row r="114" ht="40" customHeight="1">
       <c r="A114" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.emotional.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B114" t="inlineStr" s="2">
@@ -3941,7 +3941,7 @@
       </c>
       <c r="D114" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_release.emotional.seductive[1]</t>
+          <t xml:space="preserve">sudden_departure.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E114" t="inlineStr" s="2">
@@ -3951,14 +3951,14 @@
       </c>
       <c r="F114" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">移籍させて……っ……ふふ、新しい場所で輝きたいの……</t>
+          <t xml:space="preserve">もういいわ。何も言いたくないの。……さよなら。</t>
         </is>
       </c>
     </row>
     <row r="115" ht="40" customHeight="1">
       <c r="A115" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.emotional.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.emotional.seductive[2]</t>
         </is>
       </c>
       <c r="B115" t="inlineStr" s="2">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="D115" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_fail.emotional.seductive[1]</t>
+          <t xml:space="preserve">sudden_departure.emotional.seductive[2]</t>
         </is>
       </c>
       <c r="E115" t="inlineStr" s="2">
@@ -3983,14 +3983,14 @@
       </c>
       <c r="F115" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ごめんなさい……っ……気持ちはもう決まってるの……</t>
+          <t xml:space="preserve">どうして……どうしてこんなことになったの。もう無理よ、辞めるわ。</t>
         </is>
       </c>
     </row>
     <row r="116" ht="40" customHeight="1">
       <c r="A116" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.emotional.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B116" t="inlineStr" s="2">
@@ -4005,7 +4005,7 @@
       </c>
       <c r="D116" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_success.emotional.seductive[1]</t>
+          <t xml:space="preserve">transfer_listen.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E116" t="inlineStr" s="2">
@@ -4015,14 +4015,14 @@
       </c>
       <c r="F116" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">残るわ……っ……ふふ、こんなに引き止められたら、行けないでしょう……</t>
+          <t xml:space="preserve">話だけは聞くわ……っ……それで決めるから……</t>
         </is>
       </c>
     </row>
     <row r="117" ht="40" customHeight="1">
       <c r="A117" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.blocked.emotional.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B117" t="inlineStr" s="2">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="C117" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D117" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">blocked.emotional.seductive[1]</t>
+          <t xml:space="preserve">transfer_open.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E117" t="inlineStr" s="2">
@@ -4047,14 +4047,14 @@
       </c>
       <c r="F117" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">その話は……っ……ふふ、できないの、ごめんなさい……</t>
+          <t xml:space="preserve">他から声がかかってるの……っ……ふふ、どうしようかしら……</t>
         </is>
       </c>
     </row>
     <row r="118" ht="40" customHeight="1">
       <c r="A118" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.fail.emotional.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B118" t="inlineStr" s="2">
@@ -4064,12 +4064,12 @@
       </c>
       <c r="C118" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D118" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fail.emotional.seductive[1]</t>
+          <t xml:space="preserve">transfer_release.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E118" t="inlineStr" s="2">
@@ -4079,14 +4079,14 @@
       </c>
       <c r="F118" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">残念だけど……っ……今回は無理ね、ごめんなさい……</t>
+          <t xml:space="preserve">移籍させて……っ……ふふ、新しい場所で輝きたいの……</t>
         </is>
       </c>
     </row>
     <row r="119" ht="40" customHeight="1">
       <c r="A119" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.start.emotional.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B119" t="inlineStr" s="2">
@@ -4096,12 +4096,12 @@
       </c>
       <c r="C119" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D119" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">start.emotional.seductive[1]</t>
+          <t xml:space="preserve">transfer_retain_fail.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E119" t="inlineStr" s="2">
@@ -4111,14 +4111,14 @@
       </c>
       <c r="F119" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">交渉を始めるわ……っ……ふふ、よろしくね……</t>
+          <t xml:space="preserve">ごめんなさい……っ……気持ちはもう決まってるの……</t>
         </is>
       </c>
     </row>
     <row r="120" ht="40" customHeight="1">
       <c r="A120" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.success.emotional.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B120" t="inlineStr" s="2">
@@ -4128,12 +4128,12 @@
       </c>
       <c r="C120" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D120" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">success.emotional.seductive[1]</t>
+          <t xml:space="preserve">transfer_retain_success.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E120" t="inlineStr" s="2">
@@ -4143,14 +4143,14 @@
       </c>
       <c r="F120" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">これで決まりね……っ……ふふ、いい話し合いだったわ……</t>
+          <t xml:space="preserve">残るわ……っ……ふふ、こんなに引き止められたら、行けないでしょう……</t>
         </is>
       </c>
     </row>
     <row r="121" ht="40" customHeight="1">
       <c r="A121" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_ABSTRACT.seductive.emotional[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.blocked.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B121" t="inlineStr" s="2">
@@ -4160,29 +4160,29 @@
       </c>
       <c r="C121" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
       <c r="D121" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_ABSTRACT.seductive.emotional[1]</t>
+          <t xml:space="preserve">blocked.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E121" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F121" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、お願い、私たちの子たちを置き去りにしないで。</t>
+          <t xml:space="preserve">その話は……っ……ふふ、できないの、ごめんなさい……</t>
         </is>
       </c>
     </row>
     <row r="122" ht="40" customHeight="1">
       <c r="A122" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MAIN.seductive.emotional[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.fail.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B122" t="inlineStr" s="2">
@@ -4192,29 +4192,29 @@
       </c>
       <c r="C122" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
       <c r="D122" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_MAIN.seductive.emotional[1]</t>
+          <t xml:space="preserve">fail.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E122" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F122" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、次のメインは私たちに任せて。中途半端じゃ嫌なの、お願い。</t>
+          <t xml:space="preserve">残念だけど……っ……今回は無理ね、ごめんなさい……</t>
         </is>
       </c>
     </row>
     <row r="123" ht="40" customHeight="1">
       <c r="A123" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MONEY.seductive.emotional[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.start.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B123" t="inlineStr" s="2">
@@ -4224,29 +4224,29 @@
       </c>
       <c r="C123" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
       <c r="D123" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_MONEY.seductive.emotional[1]</t>
+          <t xml:space="preserve">start.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E123" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F123" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、お願い、私たちが何を受け取ってるか、もう一度見て。</t>
+          <t xml:space="preserve">交渉を始めるわ……っ……ふふ、よろしくね……</t>
         </is>
       </c>
     </row>
     <row r="124" ht="40" customHeight="1">
       <c r="A124" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_RECOGNITION.seductive.emotional[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.success.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B124" t="inlineStr" s="2">
@@ -4256,29 +4256,29 @@
       </c>
       <c r="C124" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
       <c r="D124" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_RECOGNITION.seductive.emotional[1]</t>
+          <t xml:space="preserve">success.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E124" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F124" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、私たちが何をしてきたか、ちゃんと見てくれないと寂しいじゃない。</t>
+          <t xml:space="preserve">これで決まりね……っ……ふふ、いい話し合いだったわ……</t>
         </is>
       </c>
     </row>
     <row r="125" ht="40" customHeight="1">
       <c r="A125" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.A.seductive.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_ABSTRACT.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B125" t="inlineStr" s="2">
@@ -4293,7 +4293,7 @@
       </c>
       <c r="D125" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.A.seductive.emotional[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_ABSTRACT.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E125" t="inlineStr" s="2">
@@ -4303,14 +4303,14 @@
       </c>
       <c r="F125" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長…その一言、ずっと欲しかったの。ありがとう。</t>
+          <t xml:space="preserve">社長、お願い、私たちの子たちを置き去りにしないで。</t>
         </is>
       </c>
     </row>
     <row r="126" ht="40" customHeight="1">
       <c r="A126" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.B.seductive.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MAIN.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B126" t="inlineStr" s="2">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="D126" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.B.seductive.emotional[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_MAIN.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E126" t="inlineStr" s="2">
@@ -4335,14 +4335,14 @@
       </c>
       <c r="F126" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そう、ですか。…ちょっと、寂しい。</t>
+          <t xml:space="preserve">社長、次のメインは私たちに任せて。中途半端じゃ嫌なの、お願い。</t>
         </is>
       </c>
     </row>
     <row r="127" ht="40" customHeight="1">
       <c r="A127" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.C.seductive.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MONEY.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B127" t="inlineStr" s="2">
@@ -4357,7 +4357,7 @@
       </c>
       <c r="D127" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.C.seductive.emotional[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_MONEY.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E127" t="inlineStr" s="2">
@@ -4367,14 +4367,14 @@
       </c>
       <c r="F127" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長…そういう形ですか。…嬉しい、です。</t>
+          <t xml:space="preserve">社長、お願い、私たちが何を受け取ってるか、もう一度見て。</t>
         </is>
       </c>
     </row>
     <row r="128" ht="40" customHeight="1">
       <c r="A128" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.A.seductive.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_RECOGNITION.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B128" t="inlineStr" s="2">
@@ -4389,7 +4389,7 @@
       </c>
       <c r="D128" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.A.seductive.emotional[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_RECOGNITION.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E128" t="inlineStr" s="2">
@@ -4399,14 +4399,14 @@
       </c>
       <c r="F128" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長…ありがとう。胸が熱いの、忘れないから。</t>
+          <t xml:space="preserve">社長、私たちが何をしてきたか、ちゃんと見てくれないと寂しいじゃない。</t>
         </is>
       </c>
     </row>
     <row r="129" ht="40" customHeight="1">
       <c r="A129" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.B.seductive.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.A.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B129" t="inlineStr" s="2">
@@ -4421,7 +4421,7 @@
       </c>
       <c r="D129" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.B.seductive.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.A.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E129" t="inlineStr" s="2">
@@ -4431,14 +4431,14 @@
       </c>
       <c r="F129" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そうですか。…ちょっと、寂しいな。</t>
+          <t xml:space="preserve">社長…その一言、ずっと欲しかったの。ありがとう。</t>
         </is>
       </c>
     </row>
     <row r="130" ht="40" customHeight="1">
       <c r="A130" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.C.seductive.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.B.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B130" t="inlineStr" s="2">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="D130" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.C.seductive.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.B.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E130" t="inlineStr" s="2">
@@ -4463,14 +4463,14 @@
       </c>
       <c r="F130" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長…そういう形ですか。…ありがとう。</t>
+          <t xml:space="preserve">…そう、ですか。…ちょっと、寂しい。</t>
         </is>
       </c>
     </row>
     <row r="131" ht="40" customHeight="1">
       <c r="A131" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.A.seductive.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.C.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B131" t="inlineStr" s="2">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="D131" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.A.seductive.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.C.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E131" t="inlineStr" s="2">
@@ -4495,14 +4495,14 @@
       </c>
       <c r="F131" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長…ありがとう。この嬉しさ、忘れない。</t>
+          <t xml:space="preserve">…社長…そういう形ですか。…嬉しい、です。</t>
         </is>
       </c>
     </row>
     <row r="132" ht="40" customHeight="1">
       <c r="A132" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.B.seductive.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.A.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B132" t="inlineStr" s="2">
@@ -4517,7 +4517,7 @@
       </c>
       <c r="D132" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.B.seductive.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.A.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E132" t="inlineStr" s="2">
@@ -4527,14 +4527,14 @@
       </c>
       <c r="F132" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そう、ですか。…ちょっと、寂しいけど。</t>
+          <t xml:space="preserve">社長…ありがとう。胸が熱いの、忘れないから。</t>
         </is>
       </c>
     </row>
     <row r="133" ht="40" customHeight="1">
       <c r="A133" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.C.seductive.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.B.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B133" t="inlineStr" s="2">
@@ -4549,7 +4549,7 @@
       </c>
       <c r="D133" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.C.seductive.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.B.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E133" t="inlineStr" s="2">
@@ -4559,14 +4559,14 @@
       </c>
       <c r="F133" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長…そういう形ですか。…嬉しいです。</t>
+          <t xml:space="preserve">…そうですか。…ちょっと、寂しいな。</t>
         </is>
       </c>
     </row>
     <row r="134" ht="40" customHeight="1">
       <c r="A134" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.A.seductive.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.C.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B134" t="inlineStr" s="2">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="D134" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.A.seductive.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.C.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E134" t="inlineStr" s="2">
@@ -4591,14 +4591,14 @@
       </c>
       <c r="F134" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長…その一言、ずっと欲しかったの。ありがとう。</t>
+          <t xml:space="preserve">…社長…そういう形ですか。…ありがとう。</t>
         </is>
       </c>
     </row>
     <row r="135" ht="40" customHeight="1">
       <c r="A135" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.B.seductive.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.A.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B135" t="inlineStr" s="2">
@@ -4613,7 +4613,7 @@
       </c>
       <c r="D135" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.B.seductive.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.A.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E135" t="inlineStr" s="2">
@@ -4623,14 +4623,14 @@
       </c>
       <c r="F135" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そう、ですか。…ちょっと、寂しい。</t>
+          <t xml:space="preserve">社長…ありがとう。この嬉しさ、忘れない。</t>
         </is>
       </c>
     </row>
     <row r="136" ht="40" customHeight="1">
       <c r="A136" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.C.seductive.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.B.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B136" t="inlineStr" s="2">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="D136" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.C.seductive.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.B.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E136" t="inlineStr" s="2">
@@ -4655,14 +4655,14 @@
       </c>
       <c r="F136" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長…そういう答え方、好き。ありがとう。</t>
+          <t xml:space="preserve">…そう、ですか。…ちょっと、寂しいけど。</t>
         </is>
       </c>
     </row>
     <row r="137" ht="40" customHeight="1">
       <c r="A137" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.A.seductive.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.C.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B137" t="inlineStr" s="2">
@@ -4677,7 +4677,7 @@
       </c>
       <c r="D137" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.A.seductive.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.C.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E137" t="inlineStr" s="2">
@@ -4687,14 +4687,14 @@
       </c>
       <c r="F137" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ああ、…そう、だったんですね。…悪いことをした。</t>
+          <t xml:space="preserve">…社長…そういう形ですか。…嬉しいです。</t>
         </is>
       </c>
     </row>
     <row r="138" ht="40" customHeight="1">
       <c r="A138" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.B.seductive.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.A.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B138" t="inlineStr" s="2">
@@ -4709,7 +4709,7 @@
       </c>
       <c r="D138" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.B.seductive.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.A.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E138" t="inlineStr" s="2">
@@ -4719,14 +4719,14 @@
       </c>
       <c r="F138" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。…でも、誰かを置いてけぼりにはしたくないな。</t>
+          <t xml:space="preserve">社長…その一言、ずっと欲しかったの。ありがとう。</t>
         </is>
       </c>
     </row>
     <row r="139" ht="40" customHeight="1">
       <c r="A139" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.A.seductive.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.B.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B139" t="inlineStr" s="2">
@@ -4741,7 +4741,7 @@
       </c>
       <c r="D139" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.A.seductive.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.B.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E139" t="inlineStr" s="2">
@@ -4751,14 +4751,14 @@
       </c>
       <c r="F139" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そうね、…悪かった。</t>
+          <t xml:space="preserve">…そう、ですか。…ちょっと、寂しい。</t>
         </is>
       </c>
     </row>
     <row r="140" ht="40" customHeight="1">
       <c r="A140" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.B.seductive.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.C.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B140" t="inlineStr" s="2">
@@ -4773,7 +4773,7 @@
       </c>
       <c r="D140" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.B.seductive.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.C.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E140" t="inlineStr" s="2">
@@ -4783,14 +4783,14 @@
       </c>
       <c r="F140" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。</t>
+          <t xml:space="preserve">…社長…そういう答え方、好き。ありがとう。</t>
         </is>
       </c>
     </row>
     <row r="141" ht="40" customHeight="1">
       <c r="A141" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.A.seductive.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.A.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B141" t="inlineStr" s="2">
@@ -4805,7 +4805,7 @@
       </c>
       <c r="D141" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.A.seductive.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.A.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E141" t="inlineStr" s="2">
@@ -4815,14 +4815,14 @@
       </c>
       <c r="F141" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そう、ですか。…私の熱、しまいます。</t>
+          <t xml:space="preserve">…ああ、…そう、だったんですね。…悪いことをした。</t>
         </is>
       </c>
     </row>
     <row r="142" ht="40" customHeight="1">
       <c r="A142" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.B.seductive.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.B.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B142" t="inlineStr" s="2">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="D142" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.B.seductive.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.B.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E142" t="inlineStr" s="2">
@@ -4847,14 +4847,14 @@
       </c>
       <c r="F142" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。…私、止まれないから。</t>
+          <t xml:space="preserve">…ありがとうございます。…でも、誰かを置いてけぼりにはしたくないな。</t>
         </is>
       </c>
     </row>
     <row r="143" ht="40" customHeight="1">
       <c r="A143" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.A.seductive.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.A.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B143" t="inlineStr" s="2">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="D143" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.A.seductive.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.A.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E143" t="inlineStr" s="2">
@@ -4879,14 +4879,14 @@
       </c>
       <c r="F143" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長…ごめんなさい。…言い訳、しないから。</t>
+          <t xml:space="preserve">…そうね、…悪かった。</t>
         </is>
       </c>
     </row>
     <row r="144" ht="40" customHeight="1">
       <c r="A144" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.B.seductive.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.B.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B144" t="inlineStr" s="2">
@@ -4901,7 +4901,7 @@
       </c>
       <c r="D144" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.B.seductive.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.B.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E144" t="inlineStr" s="2">
@@ -4911,14 +4911,14 @@
       </c>
       <c r="F144" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長…ありがとう、本当に優しい。</t>
+          <t xml:space="preserve">…ありがとうございます。</t>
         </is>
       </c>
     </row>
     <row r="145" ht="40" customHeight="1">
       <c r="A145" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.C.seductive.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.A.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B145" t="inlineStr" s="2">
@@ -4933,7 +4933,7 @@
       </c>
       <c r="D145" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.C.seductive.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.A.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E145" t="inlineStr" s="2">
@@ -4943,14 +4943,14 @@
       </c>
       <c r="F145" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長…そういう形ですか。…ありがたい、です。</t>
+          <t xml:space="preserve">…そう、ですか。…私の熱、しまいます。</t>
         </is>
       </c>
     </row>
     <row r="146" ht="40" customHeight="1">
       <c r="A146" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.A.seductive.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.B.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B146" t="inlineStr" s="2">
@@ -4965,7 +4965,7 @@
       </c>
       <c r="D146" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.A.seductive.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.B.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E146" t="inlineStr" s="2">
@@ -4975,14 +4975,14 @@
       </c>
       <c r="F146" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長…見ててくれたんですね。嬉しい。</t>
+          <t xml:space="preserve">…ありがとうございます。…私、止まれないから。</t>
         </is>
       </c>
     </row>
     <row r="147" ht="40" customHeight="1">
       <c r="A147" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.B.seductive.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.A.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="2">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="D147" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.B.seductive.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.A.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E147" t="inlineStr" s="2">
@@ -5007,14 +5007,14 @@
       </c>
       <c r="F147" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…大丈夫です。…まだ、やれる。</t>
+          <t xml:space="preserve">…社長…ごめんなさい。…言い訳、しないから。</t>
         </is>
       </c>
     </row>
     <row r="148" ht="40" customHeight="1">
       <c r="A148" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.C.seductive.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.B.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B148" t="inlineStr" s="2">
@@ -5029,7 +5029,7 @@
       </c>
       <c r="D148" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.C.seductive.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.B.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E148" t="inlineStr" s="2">
@@ -5039,14 +5039,14 @@
       </c>
       <c r="F148" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長…一人じゃなくていいんだね。ありがとう。</t>
+          <t xml:space="preserve">…社長…ありがとう、本当に優しい。</t>
         </is>
       </c>
     </row>
     <row r="149" ht="40" customHeight="1">
       <c r="A149" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.A.seductive.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.C.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="2">
@@ -5061,7 +5061,7 @@
       </c>
       <c r="D149" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.A.seductive.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.C.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E149" t="inlineStr" s="2">
@@ -5071,14 +5071,14 @@
       </c>
       <c r="F149" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そう、ですか。…私のせいだね。</t>
+          <t xml:space="preserve">…社長…そういう形ですか。…ありがたい、です。</t>
         </is>
       </c>
     </row>
     <row r="150" ht="40" customHeight="1">
       <c r="A150" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.B.seductive.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.A.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="2">
@@ -5093,7 +5093,7 @@
       </c>
       <c r="D150" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.B.seductive.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.A.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E150" t="inlineStr" s="2">
@@ -5103,14 +5103,14 @@
       </c>
       <c r="F150" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長、ありがとうございます。</t>
+          <t xml:space="preserve">…社長…見ててくれたんですね。嬉しい。</t>
         </is>
       </c>
     </row>
     <row r="151" ht="40" customHeight="1">
       <c r="A151" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.C.seductive.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.B.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="2">
@@ -5125,7 +5125,7 @@
       </c>
       <c r="D151" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.C.seductive.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.B.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E151" t="inlineStr" s="2">
@@ -5135,14 +5135,14 @@
       </c>
       <c r="F151" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長…そういう形で気にかけてくれるの、嬉しい。</t>
+          <t xml:space="preserve">…大丈夫です。…まだ、やれる。</t>
         </is>
       </c>
     </row>
     <row r="152" ht="40" customHeight="1">
       <c r="A152" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.A.seductive.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.C.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="2">
@@ -5157,7 +5157,7 @@
       </c>
       <c r="D152" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.A.seductive.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.C.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E152" t="inlineStr" s="2">
@@ -5167,14 +5167,14 @@
       </c>
       <c r="F152" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そう、ですか。…私、出ちゃってましたね。</t>
+          <t xml:space="preserve">…社長…一人じゃなくていいんだね。ありがとう。</t>
         </is>
       </c>
     </row>
     <row r="153" ht="40" customHeight="1">
       <c r="A153" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.B.seductive.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.A.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="2">
@@ -5189,7 +5189,7 @@
       </c>
       <c r="D153" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.B.seductive.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.A.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E153" t="inlineStr" s="2">
@@ -5199,14 +5199,14 @@
       </c>
       <c r="F153" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（…睫毛が震えたが、口は開かなかった）</t>
+          <t xml:space="preserve">…そう、ですか。…私のせいだね。</t>
         </is>
       </c>
     </row>
     <row r="154" ht="40" customHeight="1">
       <c r="A154" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.C.seductive.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.B.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="2">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="D154" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.C.seductive.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.B.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E154" t="inlineStr" s="2">
@@ -5231,14 +5231,14 @@
       </c>
       <c r="F154" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長…そういう形ですか。…嬉しい、です。</t>
+          <t xml:space="preserve">…社長、ありがとうございます。</t>
         </is>
       </c>
     </row>
     <row r="155" ht="40" customHeight="1">
       <c r="A155" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.A.seductive.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.C.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="2">
@@ -5253,7 +5253,7 @@
       </c>
       <c r="D155" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.A.seductive.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.C.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E155" t="inlineStr" s="2">
@@ -5263,14 +5263,14 @@
       </c>
       <c r="F155" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長…そう、ですか。…私が追い込みすぎてた。</t>
+          <t xml:space="preserve">…社長…そういう形で気にかけてくれるの、嬉しい。</t>
         </is>
       </c>
     </row>
     <row r="156" ht="40" customHeight="1">
       <c r="A156" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.B.seductive.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.A.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="2">
@@ -5285,7 +5285,7 @@
       </c>
       <c r="D156" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.B.seductive.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.A.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E156" t="inlineStr" s="2">
@@ -5295,14 +5295,14 @@
       </c>
       <c r="F156" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長…ありがとう。やり切らせてください。</t>
+          <t xml:space="preserve">…そう、ですか。…私、出ちゃってましたね。</t>
         </is>
       </c>
     </row>
     <row r="157" ht="40" customHeight="1">
       <c r="A157" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.C.seductive.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.B.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
@@ -5317,7 +5317,7 @@
       </c>
       <c r="D157" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.C.seductive.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.B.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E157" t="inlineStr" s="2">
@@ -5327,14 +5327,14 @@
       </c>
       <c r="F157" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長…ありがとう。私、見えてなかった。</t>
+          <t xml:space="preserve">（…睫毛が震えたが、口は開かなかった）</t>
         </is>
       </c>
     </row>
     <row r="158" ht="40" customHeight="1">
       <c r="A158" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES.emotional.attack.seductive</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.C.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="2">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="C158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D158" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.attack.seductive</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.C.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E158" t="inlineStr" s="2">
@@ -5359,14 +5359,14 @@
       </c>
       <c r="F158" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">許せないのよ、あの子のやり方</t>
+          <t xml:space="preserve">…社長…そういう形ですか。…嬉しい、です。</t>
         </is>
       </c>
     </row>
     <row r="159" ht="40" customHeight="1">
       <c r="A159" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES.emotional.defend.seductive</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.A.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
@@ -5376,12 +5376,12 @@
       </c>
       <c r="C159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D159" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.defend.seductive</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.A.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E159" t="inlineStr" s="2">
@@ -5391,29 +5391,29 @@
       </c>
       <c r="F159" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こっちだって、引けないのよ</t>
+          <t xml:space="preserve">…社長…そう、ですか。…私が追い込みすぎてた。</t>
         </is>
       </c>
     </row>
     <row r="160" ht="40" customHeight="1">
       <c r="A160" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F04_TARGET_LINES.emotional.seductive[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.B.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F04_TARGET_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D160" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.seductive[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.B.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E160" t="inlineStr" s="2">
@@ -5423,29 +5423,29 @@
       </c>
       <c r="F160" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……引き止めないで。わたし、もう向こうへ傾いてるの。</t>
+          <t xml:space="preserve">…社長…ありがとう。やり切らせてください。</t>
         </is>
       </c>
     </row>
     <row r="161" ht="40" customHeight="1">
       <c r="A161" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES.emotional.seductive[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.C.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D161" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.seductive[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.C.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E161" t="inlineStr" s="2">
@@ -5455,29 +5455,29 @@
       </c>
       <c r="F161" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">冷めちゃったのよ、すっかりね……。</t>
+          <t xml:space="preserve">…社長…ありがとう。私、見えてなかった。</t>
         </is>
       </c>
     </row>
     <row r="162" ht="40" customHeight="1">
       <c r="A162" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F06_AMBIENT_LINES.emotional.seductive[1]</t>
+          <t xml:space="preserve">FACTION_F02_LINES.emotional.attack.seductive</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F06_AMBIENT_LINES</t>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
         </is>
       </c>
       <c r="D162" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.seductive[1]</t>
+          <t xml:space="preserve">emotional.attack.seductive</t>
         </is>
       </c>
       <c r="E162" t="inlineStr" s="2">
@@ -5487,29 +5487,29 @@
       </c>
       <c r="F162" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、仲直り……いいものね。</t>
+          <t xml:space="preserve">許せないのよ、あの子のやり方</t>
         </is>
       </c>
     </row>
     <row r="163" ht="40" customHeight="1">
       <c r="A163" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F07_LEADER_LINES.emotional.seductive[1]</t>
+          <t xml:space="preserve">FACTION_F02_LINES.emotional.defend.seductive</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F07_LEADER_LINES</t>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
         </is>
       </c>
       <c r="D163" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.seductive[1]</t>
+          <t xml:space="preserve">emotional.defend.seductive</t>
         </is>
       </c>
       <c r="E163" t="inlineStr" s="2">
@@ -5519,14 +5519,14 @@
       </c>
       <c r="F163" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長さん、うちの子たちに、もうちょっと優しくしてくださらない？</t>
+          <t xml:space="preserve">こっちだって、引けないのよ</t>
         </is>
       </c>
     </row>
     <row r="164" ht="40" customHeight="1">
       <c r="A164" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F08_LEADER_LINES.emotional.seductive[1]</t>
+          <t xml:space="preserve">FACTION_F04_TARGET_LINES.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="C164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F08_LEADER_LINES</t>
+          <t xml:space="preserve">FACTION_F04_TARGET_LINES</t>
         </is>
       </c>
       <c r="D164" t="inlineStr" s="12">
@@ -5551,24 +5551,24 @@
       </c>
       <c r="F164" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……リングでなら、本音で話せるでしょ？</t>
+          <t xml:space="preserve">……引き止めないで。わたし、もう向こうへ傾いてるの。</t>
         </is>
       </c>
     </row>
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES.emotional.seductive[1]</t>
+          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
       <c r="C165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
+          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES</t>
         </is>
       </c>
       <c r="D165" t="inlineStr" s="12">
@@ -5578,29 +5578,29 @@
       </c>
       <c r="E165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F165" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……っ……変わったの、わたし……ふふ、自分でも信じられないくらい……</t>
+          <t xml:space="preserve">冷めちゃったのよ、すっかりね……。</t>
         </is>
       </c>
     </row>
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES.emotional.seductive[1]</t>
+          <t xml:space="preserve">FACTION_F06_AMBIENT_LINES.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
       <c r="C166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES</t>
+          <t xml:space="preserve">FACTION_F06_AMBIENT_LINES</t>
         </is>
       </c>
       <c r="D166" t="inlineStr" s="12">
@@ -5610,83 +5610,83 @@
       </c>
       <c r="E166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F166" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……っ……何か、来そうな予感がするの……ふふ、楽しみだわ……</t>
+          <t xml:space="preserve">ふふ、仲直り……いいものね。</t>
         </is>
       </c>
     </row>
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.cap_reached.emotional.seductive[1]</t>
+          <t xml:space="preserve">FACTION_F07_LEADER_LINES.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
       <c r="C167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">FACTION_F07_LEADER_LINES</t>
         </is>
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cap_reached.emotional.seductive[1]</t>
+          <t xml:space="preserve">emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F167" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまでなのね…少し寂しいけど…胸を張れるわ</t>
+          <t xml:space="preserve">社長さん、うちの子たちに、もうちょっと優しくしてくださらない？</t>
         </is>
       </c>
     </row>
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.emotional.seductive[1]</t>
+          <t xml:space="preserve">FACTION_F08_LEADER_LINES.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
       <c r="C168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">FACTION_F08_LEADER_LINES</t>
         </is>
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_elite.emotional.seductive[1]</t>
+          <t xml:space="preserve">emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F168" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ここまで来ちゃったの…嬉しくて…ちょっと泣きそう</t>
+          <t xml:space="preserve">……リングでなら、本音で話せるでしょ？</t>
         </is>
       </c>
     </row>
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.emotional.seductive[1]</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5696,12 +5696,12 @@
       </c>
       <c r="C169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
         </is>
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_growth.emotional.seductive[1]</t>
+          <t xml:space="preserve">emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr" s="2">
@@ -5711,14 +5711,14 @@
       </c>
       <c r="F169" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ふふっ、強くなっちゃった。嬉しいわ</t>
+          <t xml:space="preserve">……っ……変わったの、わたし……ふふ、自分でも信じられないくらい……</t>
         </is>
       </c>
     </row>
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.emotional.seductive[1]</t>
+          <t xml:space="preserve">BT_HINT_LINES.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -5728,12 +5728,12 @@
       </c>
       <c r="C170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">BT_HINT_LINES</t>
         </is>
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_legend.emotional.seductive[1]</t>
+          <t xml:space="preserve">emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="2">
@@ -5743,14 +5743,14 @@
       </c>
       <c r="F170" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで来ちゃった…もう…涙が止まらないわ…</t>
+          <t xml:space="preserve">……っ……何か、来そうな予感がするの……ふふ、楽しみだわ……</t>
         </is>
       </c>
     </row>
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_growth.emotional.seductive[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.cap_reached.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5765,7 +5765,7 @@
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_growth.emotional.seductive[1]</t>
+          <t xml:space="preserve">cap_reached.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E171" t="inlineStr" s="2">
@@ -5775,14 +5775,14 @@
       </c>
       <c r="F171" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">応援してくれる人が…嬉しいわ…ふふ</t>
+          <t xml:space="preserve">ここまでなのね…少し寂しいけど…胸を張れるわ</t>
         </is>
       </c>
     </row>
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_star.emotional.seductive[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5797,7 +5797,7 @@
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_star.emotional.seductive[1]</t>
+          <t xml:space="preserve">ovr_elite.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E172" t="inlineStr" s="2">
@@ -5807,14 +5807,14 @@
       </c>
       <c r="F172" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんなに…嬉しくて…もう言葉にならないの…</t>
+          <t xml:space="preserve">…ここまで来ちゃったの…嬉しくて…ちょっと泣きそう</t>
         </is>
       </c>
     </row>
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES.emotional.seductive[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="C173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.seductive[1]</t>
+          <t xml:space="preserve">ovr_growth.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
@@ -5839,14 +5839,14 @@
       </c>
       <c r="F173" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……っ……どうしてかしら、力が湧かないの……</t>
+          <t xml:space="preserve">…ふふっ、強くなっちゃった。嬉しいわ</t>
         </is>
       </c>
     </row>
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.emotional.seductive[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="C174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.seductive[1]</t>
+          <t xml:space="preserve">ovr_legend.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E174" t="inlineStr" s="2">
@@ -5871,14 +5871,14 @@
       </c>
       <c r="F174" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……っ……ふふ、また燃えてきたの……</t>
+          <t xml:space="preserve">ここまで来ちゃった…もう…涙が止まらないわ…</t>
         </is>
       </c>
     </row>
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES.emotional.seductive[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_growth.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -5888,12 +5888,12 @@
       </c>
       <c r="C175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.seductive[1]</t>
+          <t xml:space="preserve">pop_growth.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="2">
@@ -5903,14 +5903,14 @@
       </c>
       <c r="F175" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">調子が戻ってきたわ……っ……ふふ、ようやくね……</t>
+          <t xml:space="preserve">応援してくれる人が…嬉しいわ…ふふ</t>
         </is>
       </c>
     </row>
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.defeat.emotional.seductive[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_star.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="C176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defeat.emotional.seductive[1]</t>
+          <t xml:space="preserve">pop_star.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
@@ -5935,14 +5935,14 @@
       </c>
       <c r="F176" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けが続いて……っ……ふふ、自分が分からなくなりそう……</t>
+          <t xml:space="preserve">こんなに…嬉しくて…もう言葉にならないの…</t>
         </is>
       </c>
     </row>
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.emotional.seductive[1]</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="C177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
         </is>
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_moderate_recovery.emotional.seductive[1]</t>
+          <t xml:space="preserve">emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
@@ -5967,14 +5967,14 @@
       </c>
       <c r="F177" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">怪我は治ったけど……っ……ふふ、感覚が戻らないの……</t>
+          <t xml:space="preserve">……っ……どうしてかしら、力が湧かないの……</t>
         </is>
       </c>
     </row>
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.emotional.seductive[1]</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -5984,12 +5984,12 @@
       </c>
       <c r="C178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
         </is>
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_severe_recovery.emotional.seductive[1]</t>
+          <t xml:space="preserve">emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
@@ -5999,14 +5999,14 @@
       </c>
       <c r="F178" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">大怪我から戻ったわ……っ……でも、まだ怖いの……</t>
+          <t xml:space="preserve">……っ……ふふ、また燃えてきたの……</t>
         </is>
       </c>
     </row>
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.emotional.seductive[1]</t>
+          <t xml:space="preserve">SLUMP_END_LINES.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="C179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">SLUMP_END_LINES</t>
         </is>
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">penalty_end.emotional.seductive[1]</t>
+          <t xml:space="preserve">emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
@@ -6031,14 +6031,14 @@
       </c>
       <c r="F179" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">謹慎が明けたわ……っ……ふふ、戻ってきたわよ……</t>
+          <t xml:space="preserve">調子が戻ってきたわ……っ……ふふ、ようやくね……</t>
         </is>
       </c>
     </row>
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.emotional.seductive[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.defeat.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -6048,29 +6048,29 @@
       </c>
       <c r="C180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.emotional.seductive[1]</t>
+          <t xml:space="preserve">defeat.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F180" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高の試合だった…涙が止まらないわ</t>
+          <t xml:space="preserve">負けが続いて……っ……ふふ、自分が分からなくなりそう……</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.emotional.seductive[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -6080,29 +6080,29 @@
       </c>
       <c r="C181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.emotional.seductive[1]</t>
+          <t xml:space="preserve">injury_moderate_recovery.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F181" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオン……っ……ふふ、この重み……愛おしくてたまらないわ……</t>
+          <t xml:space="preserve">怪我は治ったけど……っ……ふふ、感覚が戻らないの……</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.emotional.seductive[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6112,29 +6112,29 @@
       </c>
       <c r="C182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.emotional.seductive[1]</t>
+          <t xml:space="preserve">injury_severe_recovery.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F182" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">殿堂入り…もう言葉にならないわ…（涙を堪える）</t>
+          <t xml:space="preserve">大怪我から戻ったわ……っ……でも、まだ怖いの……</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mediaAward.emotional.seductive[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6144,29 +6144,29 @@
       </c>
       <c r="C183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mediaAward.emotional.seductive[1]</t>
+          <t xml:space="preserve">penalty_end.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F183" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">メディア功労賞……っ……みんなに見てもらえてた証ね、嬉しいわ……</t>
+          <t xml:space="preserve">謹慎が明けたわ……っ……ふふ、戻ってきたわよ……</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.emotional.seductive[1]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6181,7 +6181,7 @@
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.emotional.seductive[1]</t>
+          <t xml:space="preserve">bestMatch.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
@@ -6191,14 +6191,14 @@
       </c>
       <c r="F184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">MVP……っ……ふふ、わたしが一番輝いてたって、そう言ってもらえるのね……</t>
+          <t xml:space="preserve">最高の試合だった…涙が止まらないわ</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.emotional.seductive[1]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6213,7 +6213,7 @@
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.emotional.seductive[1]</t>
+          <t xml:space="preserve">champion.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
@@ -6223,14 +6223,14 @@
       </c>
       <c r="F185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">新人賞……っ……一年目、無我夢中だったの……認めてもらえて嬉しいわ……</t>
+          <t xml:space="preserve">チャンピオン……っ……ふふ、この重み……愛おしくてたまらないわ……</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.emotional.seductive[1]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="C186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.seductive[1]</t>
+          <t xml:space="preserve">hallOfFame.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
@@ -6255,14 +6255,14 @@
       </c>
       <c r="F186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ドームで、あなた方の前で戦える幸せよ…</t>
+          <t xml:space="preserve">殿堂入り…もう言葉にならないわ…（涙を堪える）</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.emotional.seductive[2]</t>
+          <t xml:space="preserve">AWARD_LINES.mediaAward.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6272,12 +6272,12 @@
       </c>
       <c r="C187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.seductive[2]</t>
+          <t xml:space="preserve">mediaAward.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
@@ -6287,14 +6287,14 @@
       </c>
       <c r="F187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">熱い試合を…必ず、約束する</t>
+          <t xml:space="preserve">メディア功労賞……っ……みんなに見てもらえてた証ね、嬉しいわ……</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.emotional.seductive[3]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6304,12 +6304,12 @@
       </c>
       <c r="C188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.seductive[3]</t>
+          <t xml:space="preserve">mvp.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
@@ -6319,14 +6319,14 @@
       </c>
       <c r="F188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この胸の高鳴り…試合で発散させてね</t>
+          <t xml:space="preserve">MVP……っ……ふふ、わたしが一番輝いてたって、そう言ってもらえるのね……</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.emotional.seductive[1]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6336,12 +6336,12 @@
       </c>
       <c r="C189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.seductive[1]</t>
+          <t xml:space="preserve">rookie.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
@@ -6351,14 +6351,14 @@
       </c>
       <c r="F189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…満員、お客様の熱気…忘れられない</t>
+          <t xml:space="preserve">新人王……っ……無我夢中だったの……認めてもらえて嬉しいわ……</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.emotional.seductive[2]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6368,12 +6368,12 @@
       </c>
       <c r="C190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.seductive[2]</t>
+          <t xml:space="preserve">emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
@@ -6383,14 +6383,14 @@
       </c>
       <c r="F190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">胸が熱くて、震えが止まらないの</t>
+          <t xml:space="preserve">…ドームで、あなた方の前で戦える幸せよ…</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.emotional.seductive[3]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.emotional.seductive[2]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6400,12 +6400,12 @@
       </c>
       <c r="C191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.seductive[3]</t>
+          <t xml:space="preserve">emotional.seductive[2]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
@@ -6415,14 +6415,14 @@
       </c>
       <c r="F191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんな素敵な夜、生涯忘れない</t>
+          <t xml:space="preserve">熱い試合を…必ず、約束する</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.emotional.seductive[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.emotional.seductive[3]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6432,29 +6432,29 @@
       </c>
       <c r="C192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.emotional.seductive[1]</t>
+          <t xml:space="preserve">emotional.seductive[3]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お知らせよ……っ……ふふ、聞いて……</t>
+          <t xml:space="preserve">この胸の高鳴り…試合で発散させてね</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.emotional.seductive[2]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6464,29 +6464,29 @@
       </c>
       <c r="C193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.emotional.seductive[2]</t>
+          <t xml:space="preserve">emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ねえ、聞いて……っ……ふふ……</t>
+          <t xml:space="preserve">…満員、お客様の熱気…忘れられない</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.emotional.seductive[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.emotional.seductive[2]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6496,29 +6496,29 @@
       </c>
       <c r="C194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.emotional.seductive[1]</t>
+          <t xml:space="preserve">emotional.seductive[2]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ちょっといいかしら……っ……ふふ……</t>
+          <t xml:space="preserve">胸が熱くて、震えが止まらないの</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.emotional.seductive[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.emotional.seductive[3]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6528,29 +6528,29 @@
       </c>
       <c r="C195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.emotional.seductive[1]</t>
+          <t xml:space="preserve">emotional.seductive[3]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">はぁ……体が、言うこときかないの……ごめんなさい……</t>
+          <t xml:space="preserve">こんな素敵な夜、生涯忘れない</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.emotional.seductive[2]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6565,7 +6565,7 @@
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.emotional.seductive[2]</t>
+          <t xml:space="preserve">N1.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
@@ -6575,14 +6575,14 @@
       </c>
       <c r="F196" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふぅ……ちょっと、休ませて……すぐ、戻るから……</t>
+          <t xml:space="preserve">お知らせよ……っ……ふふ、聞いて……</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.emotional.seductive[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.emotional.seductive[2]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6597,7 +6597,7 @@
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.emotional.seductive[1]</t>
+          <t xml:space="preserve">N1.emotional.seductive[2]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
@@ -6607,14 +6607,14 @@
       </c>
       <c r="F197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">大事な話よ……っ……ふふ、しっかり聞いて……</t>
+          <t xml:space="preserve">ねえ、聞いて……っ……ふふ……</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.emotional.seductive[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6629,7 +6629,7 @@
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.emotional.seductive[1]</t>
+          <t xml:space="preserve">N2.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
@@ -6639,14 +6639,14 @@
       </c>
       <c r="F198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ちょっと心配なの……っ……ふふ……</t>
+          <t xml:space="preserve">ちょっといいかしら……っ……ふふ……</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.emotional.seductive[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6661,7 +6661,7 @@
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_warning.emotional.seductive[1]</t>
+          <t xml:space="preserve">N3.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
@@ -6671,14 +6671,14 @@
       </c>
       <c r="F199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">緊急よ……っ……ふふ、よく聞いて……</t>
+          <t xml:space="preserve">はぁ……体が、言うこときかないの……ごめんなさい……</t>
         </is>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.breakthrough.voice.emotional.seductive[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.emotional.seductive[2]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6688,12 +6688,12 @@
       </c>
       <c r="C200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">breakthrough.voice.emotional.seductive[1]</t>
+          <t xml:space="preserve">N3.emotional.seductive[2]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
@@ -6703,14 +6703,14 @@
       </c>
       <c r="F200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何かが変わった……っ……ふふ……</t>
+          <t xml:space="preserve">ふぅ……ちょっと、休ませて……すぐ、戻るから……</t>
         </is>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.emotional.seductive[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="C201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G1.voice.emotional.seductive[1]</t>
+          <t xml:space="preserve">N4.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
@@ -6735,14 +6735,14 @@
       </c>
       <c r="F201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう少し稼ぎたいわね……っ……</t>
+          <t xml:space="preserve">大事な話よ……っ……ふふ、しっかり聞いて……</t>
         </is>
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice.emotional.seductive[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6752,12 +6752,12 @@
       </c>
       <c r="C202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G2.voice.emotional.seductive[1]</t>
+          <t xml:space="preserve">N5_low.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
@@ -6767,14 +6767,14 @@
       </c>
       <c r="F202" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ひとりは、ちょっと寂しいの……っ……</t>
+          <t xml:space="preserve">ちょっと心配なの……っ……ふふ……</t>
         </is>
       </c>
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice.emotional.seductive[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6784,12 +6784,12 @@
       </c>
       <c r="C203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G3.voice.emotional.seductive[1]</t>
+          <t xml:space="preserve">N5_warning.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
@@ -6799,14 +6799,14 @@
       </c>
       <c r="F203" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もう少し目立たないとダメなのかしら</t>
+          <t xml:space="preserve">緊急よ……っ……ふふ、よく聞いて……</t>
         </is>
       </c>
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G4.voice.emotional.seductive[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.breakthrough.voice.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6821,7 +6821,7 @@
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G4.voice.emotional.seductive[1]</t>
+          <t xml:space="preserve">breakthrough.voice.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
@@ -6831,14 +6831,14 @@
       </c>
       <c r="F204" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もっと強くなりたいの……っ……</t>
+          <t xml:space="preserve">何かが変わった……っ……ふふ……</t>
         </is>
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice.emotional.seductive[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6853,7 +6853,7 @@
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R2.voice.emotional.seductive[1]</t>
+          <t xml:space="preserve">G1.voice.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
@@ -6863,14 +6863,14 @@
       </c>
       <c r="F205" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの子と、もっと話したい……っ……</t>
+          <t xml:space="preserve">もう少し稼ぎたいわね……っ……</t>
         </is>
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice.emotional.seductive[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6885,7 +6885,7 @@
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R4.voice.emotional.seductive[1]</t>
+          <t xml:space="preserve">G2.voice.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
@@ -6895,14 +6895,14 @@
       </c>
       <c r="F206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの子とは、ちょっと距離を置きたいの……っ……</t>
+          <t xml:space="preserve">ひとりは、ちょっと寂しいの……っ……</t>
         </is>
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice.emotional.seductive[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R5.voice.emotional.seductive[1]</t>
+          <t xml:space="preserve">G3.voice.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
@@ -6927,14 +6927,14 @@
       </c>
       <c r="F207" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けたくないの……っ……ふふ……</t>
+          <t xml:space="preserve">…もう少し目立たないとダメなのかしら</t>
         </is>
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.warVictory.voice.emotional.seductive[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G4.voice.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6949,7 +6949,7 @@
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">warVictory.voice.emotional.seductive[1]</t>
+          <t xml:space="preserve">G4.voice.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
@@ -6959,14 +6959,14 @@
       </c>
       <c r="F208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝てた……っ……ふふ、最高の気分……</t>
+          <t xml:space="preserve">もっと強くなりたいの……っ……</t>
         </is>
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_repeat.emotional.seductive[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -6976,29 +6976,29 @@
       </c>
       <c r="C209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus_repeat.emotional.seductive[1]</t>
+          <t xml:space="preserve">R2.voice.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">また……っ……ふふ、こんなに優しくされたら、応えないわけにはいかないわ……</t>
+          <t xml:space="preserve">あの子と、もっと話したい……っ……</t>
         </is>
       </c>
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.emotional.seductive[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -7008,29 +7008,29 @@
       </c>
       <c r="C210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.emotional.seductive[1]</t>
+          <t xml:space="preserve">R4.voice.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ボーナス……っ……気にかけてくれてたのね、嬉しい……ふふ、ありがとう……</t>
+          <t xml:space="preserve">あの子とは、ちょっと距離を置きたいの……っ……</t>
         </is>
       </c>
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.emotional.seductive[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7040,29 +7040,29 @@
       </c>
       <c r="C211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.emotional.seductive[1]</t>
+          <t xml:space="preserve">R5.voice.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">合宿……っ……ふふ、みんなと一緒に過ごせるのね、楽しみ……</t>
+          <t xml:space="preserve">負けたくないの……っ……ふふ……</t>
         </is>
       </c>
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.emotional.seductive[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.warVictory.voice.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7072,29 +7072,29 @@
       </c>
       <c r="C212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage_high_trust.emotional.seductive[1]</t>
+          <t xml:space="preserve">warVictory.voice.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F212" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あなたの言葉だけで……っ……わたし、何でもできちゃいそうなの……ふふ……</t>
+          <t xml:space="preserve">勝てた……っ……ふふ、最高の気分……</t>
         </is>
       </c>
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.emotional.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_repeat.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7109,7 +7109,7 @@
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.emotional.seductive[1]</t>
+          <t xml:space="preserve">bonus_repeat.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
@@ -7119,14 +7119,14 @@
       </c>
       <c r="F213" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">励まし……っ……ふふ、その言葉だけで、力が湧いてくるの……</t>
+          <t xml:space="preserve">また……っ……ふふ、こんなに優しくされたら、応えないわけにはいかないわ……</t>
         </is>
       </c>
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.emotional.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7141,7 +7141,7 @@
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.emotional.seductive[1]</t>
+          <t xml:space="preserve">bonus.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
@@ -7151,14 +7151,14 @@
       </c>
       <c r="F214" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">メディアに……っ……ふふ、わたしを世間に見せたいのね、いいわ……</t>
+          <t xml:space="preserve">ボーナス……っ……気にかけてくれてたのね、嬉しい……ふふ、ありがとう……</t>
         </is>
       </c>
     </row>
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.emotional.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7173,7 +7173,7 @@
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.emotional.seductive[1]</t>
+          <t xml:space="preserve">camp.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
@@ -7183,14 +7183,14 @@
       </c>
       <c r="F215" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">パーティー……っ……ふふ、今夜は思いっきり楽しませてもらうわ……</t>
+          <t xml:space="preserve">合宿……っ……ふふ、みんなと一緒に過ごせるのね、楽しみ……</t>
         </is>
       </c>
     </row>
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.emotional.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7205,7 +7205,7 @@
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.emotional.seductive[1]</t>
+          <t xml:space="preserve">encourage_high_trust.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
@@ -7215,14 +7215,14 @@
       </c>
       <c r="F216" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">休暇……っ……気を遣ってくれたのね、ふふ、嬉しいわ……</t>
+          <t xml:space="preserve">あなたの言葉だけで……っ……わたし、何でもできちゃいそうなの……ふふ……</t>
         </is>
       </c>
     </row>
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.emotional.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7237,7 +7237,7 @@
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.emotional.seductive[1]</t>
+          <t xml:space="preserve">encourage.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
@@ -7247,14 +7247,14 @@
       </c>
       <c r="F217" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">そこまで…してくれるの…っ、嬉しい……早く戻るわ……</t>
+          <t xml:space="preserve">励まし……っ……ふふ、その言葉だけで、力が湧いてくるの……</t>
         </is>
       </c>
     </row>
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.emotional.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7269,7 +7269,7 @@
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.emotional.seductive[1]</t>
+          <t xml:space="preserve">media.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
@@ -7279,14 +7279,14 @@
       </c>
       <c r="F218" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">トレーナーをつけてくれるの……っ……ふふ、本気で育ててくれるのね……</t>
+          <t xml:space="preserve">メディアに……っ……ふふ、わたしを世間に見せたいのね、いいわ……</t>
         </is>
       </c>
     </row>
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.emotional.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="C219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.emotional.seductive[1]</t>
+          <t xml:space="preserve">party.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
@@ -7311,14 +7311,14 @@
       </c>
       <c r="F219" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……っ……どうしようかしら、ふふ、迷っちゃうわね……</t>
+          <t xml:space="preserve">パーティー……っ……ふふ、今夜は思いっきり楽しませてもらうわ……</t>
         </is>
       </c>
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.emotional.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7328,12 +7328,12 @@
       </c>
       <c r="C220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.emotional.seductive[1]</t>
+          <t xml:space="preserve">refresh_leave.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
@@ -7343,14 +7343,14 @@
       </c>
       <c r="F220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いいわよ……っ……ふふ、やってみせるわ……</t>
+          <t xml:space="preserve">休暇……っ……気を遣ってくれたのね、ふふ、嬉しいわ……</t>
         </is>
       </c>
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.emotional.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7360,12 +7360,12 @@
       </c>
       <c r="C221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.emotional.seductive[1]</t>
+          <t xml:space="preserve">special_treatment.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
@@ -7375,14 +7375,14 @@
       </c>
       <c r="F221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……っ……これは認められないわ、悪いけど……</t>
+          <t xml:space="preserve">そこまで…してくれるの…っ、嬉しい……早く戻るわ……</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.emotional.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="C222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_grumble.emotional.seductive[1]</t>
+          <t xml:space="preserve">trainer.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
@@ -7407,14 +7407,14 @@
       </c>
       <c r="F222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">正直に言うわね……っ……ちょっと不満なの……</t>
+          <t xml:space="preserve">トレーナーをつけてくれるの……っ……ふふ、本気で育ててくれるのね……</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.emotional.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7429,7 +7429,7 @@
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_sns.emotional.seductive[1]</t>
+          <t xml:space="preserve">E1.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
@@ -7439,14 +7439,14 @@
       </c>
       <c r="F223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">SNS見たわ……っ……ふふ、勝手な人たちね……</t>
+          <t xml:space="preserve">……っ……どうしようかしら、ふふ、迷っちゃうわね……</t>
         </is>
       </c>
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.emotional.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7461,7 +7461,7 @@
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.emotional.seductive[1]</t>
+          <t xml:space="preserve">E6.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
@@ -7471,14 +7471,14 @@
       </c>
       <c r="F224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ねえ……っ……ちょっと、聞いてほしいの……</t>
+          <t xml:space="preserve">いいわよ……っ……ふふ、やってみせるわ……</t>
         </is>
       </c>
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.emotional.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7493,7 +7493,7 @@
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.emotional.seductive[1]</t>
+          <t xml:space="preserve">S_boycott.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
@@ -7503,14 +7503,14 @@
       </c>
       <c r="F225" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">時間、ある……っ……ふふ、ちょっとだけ付き合って……</t>
+          <t xml:space="preserve">……っ……これは認められないわ、悪いけど……</t>
         </is>
       </c>
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.emotional.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.emotional.seductive[1]</t>
+          <t xml:space="preserve">S_grumble.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
@@ -7535,14 +7535,14 @@
       </c>
       <c r="F226" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……っ……どう答えるのが正解なのかしら、ふふ……</t>
+          <t xml:space="preserve">正直に言うわね……っ……ちょっと不満なの……</t>
         </is>
       </c>
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.emotional.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7557,7 +7557,7 @@
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.emotional.seductive[1]</t>
+          <t xml:space="preserve">S_sns.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
@@ -7567,14 +7567,14 @@
       </c>
       <c r="F227" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">はっきり言うわ……っ……わたしの気持ちは……</t>
+          <t xml:space="preserve">SNS見たわ……っ……ふふ、勝手な人たちね……</t>
         </is>
       </c>
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.emotional.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7589,7 +7589,7 @@
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_silent.emotional.seductive[1]</t>
+          <t xml:space="preserve">S1.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
@@ -7599,14 +7599,14 @@
       </c>
       <c r="F228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………っ……言葉にならないの……ふふ……</t>
+          <t xml:space="preserve">ねえ……っ……ちょっと、聞いてほしいの……</t>
         </is>
       </c>
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.emotional.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7621,7 +7621,7 @@
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.emotional.seductive[1]</t>
+          <t xml:space="preserve">S2.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
@@ -7631,14 +7631,14 @@
       </c>
       <c r="F229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">少し考えさせて……っ……ふふ、すぐには決められないの……</t>
+          <t xml:space="preserve">時間、ある……っ……ふふ、ちょっとだけ付き合って……</t>
         </is>
       </c>
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.emotional.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7653,7 +7653,7 @@
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.emotional.seductive[1]</t>
+          <t xml:space="preserve">S3.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
@@ -7663,14 +7663,14 @@
       </c>
       <c r="F230" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決めたわ……っ……ふふ、これがわたしの答えよ……</t>
+          <t xml:space="preserve">……っ……どう答えるのが正解なのかしら、ふふ……</t>
         </is>
       </c>
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.emotional.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7680,12 +7680,12 @@
       </c>
       <c r="C231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.emotional.seductive[1]</t>
+          <t xml:space="preserve">S4_direct.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
@@ -7695,14 +7695,14 @@
       </c>
       <c r="F231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">これから……っ……やりたいこと、いっぱいあるの……</t>
+          <t xml:space="preserve">はっきり言うわ……っ……わたしの気持ちは……</t>
         </is>
       </c>
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.emotional.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7712,12 +7712,12 @@
       </c>
       <c r="C232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.emotional.seductive[1]</t>
+          <t xml:space="preserve">S4_silent.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
@@ -7727,14 +7727,14 @@
       </c>
       <c r="F232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ねえ……っ……ちょっと話、聞いてくれる？</t>
+          <t xml:space="preserve">………っ……言葉にならないの……ふふ……</t>
         </is>
       </c>
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.emotional.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="C233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.emotional.seductive[1]</t>
+          <t xml:space="preserve">S5.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
@@ -7759,14 +7759,14 @@
       </c>
       <c r="F233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いいわよ……っ……話してみて……</t>
+          <t xml:space="preserve">少し考えさせて……っ……ふふ、すぐには決められないの……</t>
         </is>
       </c>
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.emotional.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7776,12 +7776,12 @@
       </c>
       <c r="C234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.emotional.seductive[1]</t>
+          <t xml:space="preserve">S6.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
@@ -7791,14 +7791,14 @@
       </c>
       <c r="F234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ブランドのお話……っ……ふふ、素敵ね……</t>
+          <t xml:space="preserve">決めたわ……っ……ふふ、これがわたしの答えよ……</t>
         </is>
       </c>
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.emotional.seductive[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7813,7 +7813,7 @@
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.emotional.seductive[1]</t>
+          <t xml:space="preserve">B1.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
@@ -7823,14 +7823,14 @@
       </c>
       <c r="F235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">CMに出るの……っ……ふふ、世間に顔を売るチャンスね……</t>
+          <t xml:space="preserve">これから……っ……やりたいこと、いっぱいあるの……</t>
         </is>
       </c>
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.emotional.seductive[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.emotional.seductive[1]</t>
+          <t xml:space="preserve">B2_fighter1.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
@@ -7855,14 +7855,14 @@
       </c>
       <c r="F236" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ファンに会えるの……っ……ふふ、みんなに直接ありがとうって言えるのね……</t>
+          <t xml:space="preserve">ねえ……っ……ちょっと話、聞いてくれる？</t>
         </is>
       </c>
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.emotional.seductive[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -7877,7 +7877,7 @@
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.emotional.seductive[1]</t>
+          <t xml:space="preserve">B2_fighter2.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
@@ -7887,14 +7887,14 @@
       </c>
       <c r="F237" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ファッションのお仕事……っ……ふふ、おしゃれするのは好きよ……</t>
+          <t xml:space="preserve">いいわよ……っ……話してみて……</t>
         </is>
       </c>
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.emotional.seductive[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -7909,7 +7909,7 @@
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.emotional.seductive[1]</t>
+          <t xml:space="preserve">B4_brand.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
@@ -7919,14 +7919,14 @@
       </c>
       <c r="F238" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">グラビア……っ……ふふ、見られるのは嫌いじゃないの……</t>
+          <t xml:space="preserve">ブランドのお話……っ……ふふ、素敵ね……</t>
         </is>
       </c>
     </row>
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.emotional.seductive[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -7941,7 +7941,7 @@
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.emotional.seductive[1]</t>
+          <t xml:space="preserve">B4_cm.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
@@ -7951,14 +7951,14 @@
       </c>
       <c r="F239" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">バラエティに出るの……っ……ふふ、楽しんでくるわね……</t>
+          <t xml:space="preserve">CMに出るの……っ……ふふ、世間に顔を売るチャンスね……</t>
         </is>
       </c>
     </row>
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.emotional.seductive[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -7973,7 +7973,7 @@
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.emotional.seductive[1]</t>
+          <t xml:space="preserve">B4_fan.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
@@ -7983,14 +7983,14 @@
       </c>
       <c r="F240" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このお仕事……っ……ふふ、面白そうね……</t>
+          <t xml:space="preserve">ファンに会えるの……っ……ふふ、みんなに直接ありがとうって言えるのね……</t>
         </is>
       </c>
     </row>
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.emotional.seductive[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -8000,29 +8000,29 @@
       </c>
       <c r="C241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.seductive[1]</t>
+          <t xml:space="preserve">B4_fashion.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F241" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…夢みたい。精一杯頑張るわ…</t>
+          <t xml:space="preserve">ファッションのお仕事……っ……ふふ、おしゃれするのは好きよ……</t>
         </is>
       </c>
     </row>
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.emotional.seductive[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8032,29 +8032,29 @@
       </c>
       <c r="C242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.seductive[1]</t>
+          <t xml:space="preserve">B4_gravure.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F242" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…悔しい…必ず戻ってやる…</t>
+          <t xml:space="preserve">グラビア……っ……ふふ、見られるのは嫌いじゃないの……</t>
         </is>
       </c>
     </row>
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.emotional.seductive[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8064,29 +8064,29 @@
       </c>
       <c r="C243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.emotional.seductive[1]</t>
+          <t xml:space="preserve">B4_variety.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F243" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…夢みたい。精一杯頑張るわ…</t>
+          <t xml:space="preserve">バラエティに出るの……っ……ふふ、楽しんでくるわね……</t>
         </is>
       </c>
     </row>
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.emotional.seductive[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8096,29 +8096,29 @@
       </c>
       <c r="C244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.emotional.seductive[1]</t>
+          <t xml:space="preserve">B4.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F244" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…悔しい…必ず戻ってやる…</t>
+          <t xml:space="preserve">このお仕事……っ……ふふ、面白そうね……</t>
         </is>
       </c>
     </row>
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.emotional.seductive[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8128,12 +8128,12 @@
       </c>
       <c r="C245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.emotional.seductive[1]</t>
+          <t xml:space="preserve">emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
@@ -8143,14 +8143,14 @@
       </c>
       <c r="F245" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…ありがとう…忘れないわ…</t>
+          <t xml:space="preserve">選んでくれたら…全力で…全力でやるから…！</t>
         </is>
       </c>
     </row>
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.emotional.seductive[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8160,7 +8160,7 @@
       </c>
       <c r="C246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D246" t="inlineStr" s="12">
@@ -8175,14 +8175,14 @@
       </c>
       <c r="F246" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…ありがとう…忘れないわ…</t>
+          <t xml:space="preserve">…っ…夢みたい。精一杯頑張るわ…</t>
         </is>
       </c>
     </row>
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.emotional.seductive[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8192,29 +8192,29 @@
       </c>
       <c r="C247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.emotional.seductive[1]</t>
+          <t xml:space="preserve">emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F247" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">放っておけないの…もう</t>
+          <t xml:space="preserve">ありがとう…っ…嬉しい…。全力で、やるから…</t>
         </is>
       </c>
     </row>
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.emotional.seductive[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8224,29 +8224,29 @@
       </c>
       <c r="C248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.goodLoss.emotional.seductive[1]</t>
+          <t xml:space="preserve">emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F248" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けたけど……っ……ふふ、出し切れたの……</t>
+          <t xml:space="preserve">嬉しい…っ…よろしくね…。頑張るから…</t>
         </is>
       </c>
     </row>
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.emotional.seductive[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8256,29 +8256,29 @@
       </c>
       <c r="C249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.greatWin.emotional.seductive[1]</t>
+          <t xml:space="preserve">emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F249" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高の勝利……っ……ふふ、震えてるの……</t>
+          <t xml:space="preserve">…っ…悔しい…必ず戻ってやる…</t>
         </is>
       </c>
     </row>
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.emotional.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8288,29 +8288,29 @@
       </c>
       <c r="C250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.loss.emotional.seductive[1]</t>
+          <t xml:space="preserve">bitterPrematch.ahead.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F250" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けた……っ……悔しい……</t>
+          <t xml:space="preserve">済んだ話よ……っ……なのに、まだ手が震えるの</t>
         </is>
       </c>
     </row>
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.emotional.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8320,29 +8320,29 @@
       </c>
       <c r="C251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.win.emotional.seductive[1]</t>
+          <t xml:space="preserve">bitterPrematch.behind.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F251" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ったわ……っ……ふふ、嬉しい……</t>
+          <t xml:space="preserve">終わったの……？ ……嘘よ。まだ、疼いてる</t>
         </is>
       </c>
     </row>
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.emotional.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8352,29 +8352,29 @@
       </c>
       <c r="C252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.emotional.seductive[1]</t>
+          <t xml:space="preserve">draftInterest.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F252" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日は……っ……ふふ、よろしくね……</t>
+          <t xml:space="preserve">選んでくれたら…全力で…全力でやるから…！</t>
         </is>
       </c>
     </row>
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.emotional.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8384,29 +8384,29 @@
       </c>
       <c r="C253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.down.emotional.seductive[1]</t>
+          <t xml:space="preserve">draftJoin.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F253" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うまくいかない……っ……どうしてかしら……</t>
+          <t xml:space="preserve">…っ…夢みたい。精一杯頑張るわ…</t>
         </is>
       </c>
     </row>
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.emotional.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8416,29 +8416,29 @@
       </c>
       <c r="C254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.up.emotional.seductive[1]</t>
+          <t xml:space="preserve">faGreeting.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F254" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">なんだか調子いいの……っ……ふふ……</t>
+          <t xml:space="preserve">拾われる側になるなんて…っ…参ったわ</t>
         </is>
       </c>
     </row>
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.emotional.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8448,29 +8448,29 @@
       </c>
       <c r="C255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-04.emotional.seductive[1]</t>
+          <t xml:space="preserve">faSigning.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F255" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習するわ……っ……ふふ……</t>
+          <t xml:space="preserve">ありがとう…っ…嬉しい…。全力で、やるから…</t>
         </is>
       </c>
     </row>
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.emotional.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8480,29 +8480,29 @@
       </c>
       <c r="C256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-05.emotional.seductive[1]</t>
+          <t xml:space="preserve">faWelcome.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F256" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">大丈夫よ……っ……ふふ、心配しないで……</t>
+          <t xml:space="preserve">嬉しい…っ…よろしくね…。頑張るから…</t>
         </is>
       </c>
     </row>
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.emotional.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8512,29 +8512,29 @@
       </c>
       <c r="C257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.emotional.seductive[1]</t>
+          <t xml:space="preserve">injury.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F257" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みんなと一緒だと……っ……ふふ、安心するの……</t>
+          <t xml:space="preserve">…っ…悔しい…必ず戻ってやる…</t>
         </is>
       </c>
     </row>
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.emotional.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8544,29 +8544,29 @@
       </c>
       <c r="C258" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-07.emotional.seductive[1]</t>
+          <t xml:space="preserve">release.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E258" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F258" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お客さんがいっぱい……っ……ふふ、燃えるわね……</t>
+          <t xml:space="preserve">…っ…ありがとう…忘れないわ…</t>
         </is>
       </c>
     </row>
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.emotional.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8576,29 +8576,29 @@
       </c>
       <c r="C259" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.emotional.seductive[1]</t>
+          <t xml:space="preserve">rentalGreeting.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E259" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F259" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">体調は大丈夫よ……っ……ふふ、心配いらない……</t>
+          <t xml:space="preserve">よろしくね…っ…短い間だけど…全力で、やるから…</t>
         </is>
       </c>
     </row>
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.emotional.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8608,29 +8608,29 @@
       </c>
       <c r="C260" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-09.emotional.seductive[1]</t>
+          <t xml:space="preserve">scoutGreeting.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E260" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F260" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次の試合……っ……ふふ、楽しみだわ……</t>
+          <t xml:space="preserve">うふふ♪嬉しい♪</t>
         </is>
       </c>
     </row>
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.emotional.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8640,29 +8640,29 @@
       </c>
       <c r="C261" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.emotional.seductive[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F261" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとう……っ……ふふ、嬉しい……</t>
+          <t xml:space="preserve">悔しい…っ…悔しい…。でも…絶対に、諦めない…</t>
         </is>
       </c>
     </row>
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.emotional.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8672,29 +8672,29 @@
       </c>
       <c r="C262" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.seductive[1]</t>
+          <t xml:space="preserve">titleDefense.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E262" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F262" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勢いが止まったわ……っ……ふふ、また始めればいいのよ……</t>
+          <t xml:space="preserve">守れた…っ…嬉しい…。次も、絶対に守るから…</t>
         </is>
       </c>
     </row>
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.emotional.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8704,29 +8704,29 @@
       </c>
       <c r="C263" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.emotional.seductive[1]</t>
+          <t xml:space="preserve">titleLoss.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E263" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F263" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">身体、もう震えてるの…っ…ふふ、でも最後まで立つわ</t>
+          <t xml:space="preserve">嘘…っ…ベルトが…。でも…でも、諦めない…</t>
         </is>
       </c>
     </row>
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.emotional.seductive[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8736,29 +8736,29 @@
       </c>
       <c r="C264" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.emotional.seductive[2]</t>
+          <t xml:space="preserve">titleWin.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E264" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F264" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで来たのね…っ…最後の舞台、全部ぶつけるわ</t>
+          <t xml:space="preserve">ああ…っ…チャンピオン…。嬉しい…だめ、泣いちゃう…</t>
         </is>
       </c>
     </row>
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.emotional.seductive[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8768,29 +8768,29 @@
       </c>
       <c r="C265" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.emotional.seductive[1]</t>
+          <t xml:space="preserve">emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E265" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F265" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お相手は誰かしら…っ…ふふ、もう身体が疼いてるの</t>
+          <t xml:space="preserve">…っ…ありがとう…忘れないわ…</t>
         </is>
       </c>
     </row>
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.emotional.seductive[2]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8800,29 +8800,29 @@
       </c>
       <c r="C266" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.emotional.seductive[2]</t>
+          <t xml:space="preserve">emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E266" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F266" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">早く来てよ…! この昂り、ぶつける相手が欲しいの…!</t>
+          <t xml:space="preserve">よろしくね…っ…短い間だけど…全力で、やるから…</t>
         </is>
       </c>
     </row>
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.emotional.seductive[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -8832,29 +8832,29 @@
       </c>
       <c r="C267" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.emotional.seductive[1]</t>
+          <t xml:space="preserve">emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E267" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F267" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人、落としたわ…っ…はぁ…まだ疼いてるの。次、早く出してよ</t>
+          <t xml:space="preserve">悔しい…っ…悔しい…。でも…絶対に、諦めない…</t>
         </is>
       </c>
     </row>
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.emotional.seductive[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -8864,29 +8864,29 @@
       </c>
       <c r="C268" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D268" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.emotional.seductive[2]</t>
+          <t xml:space="preserve">emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E268" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F268" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ立ってる…! この身体、まだ終わってないの…! 次、来なさい…!</t>
+          <t xml:space="preserve">守れた…っ…嬉しい…。次も、絶対に守るから…</t>
         </is>
       </c>
     </row>
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.emotional.seductive[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -8896,29 +8896,29 @@
       </c>
       <c r="C269" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D269" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.emotional.seductive[1]</t>
+          <t xml:space="preserve">emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E269" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F269" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">三人で勝ったの……！ この感動は……一人じゃ味わえないわ……</t>
+          <t xml:space="preserve">嘘…っ…ベルトが…。でも…でも、諦めない…</t>
         </is>
       </c>
     </row>
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.emotional.seductive[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -8928,29 +8928,29 @@
       </c>
       <c r="C270" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D270" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.emotional.seductive[2]</t>
+          <t xml:space="preserve">emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E270" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F270" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲間が繋いでくれた想い……最後まで、手放さなかったよ……！</t>
+          <t xml:space="preserve">ああ…っ…チャンピオン…。嬉しい…だめ、泣いちゃう…</t>
         </is>
       </c>
     </row>
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.emotional.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -8960,29 +8960,29 @@
       </c>
       <c r="C271" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D271" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.emotional.seductive[1]</t>
+          <t xml:space="preserve">bond_39_down.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E271" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F271" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この賞じゃ……心は満たされないのよ……！ 次は全部、奪い返すから……</t>
+          <t xml:space="preserve">考えると苦しいの…もう無理…</t>
         </is>
       </c>
     </row>
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.emotional.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -8992,29 +8992,29 @@
       </c>
       <c r="C272" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D272" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.emotional.seductive[2]</t>
+          <t xml:space="preserve">bond_59_down.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E272" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F272" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人で輝いても寂しいだけ……！ 次は……三人で、ね……！</t>
+          <t xml:space="preserve">離れていく…嫌よ…こんなの…</t>
         </is>
       </c>
     </row>
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.emotional.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.emotional.seductive[2]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -9024,29 +9024,29 @@
       </c>
       <c r="C273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.emotional.seductive[1]</t>
+          <t xml:space="preserve">bond_59_down.emotional.seductive[2]</t>
         </is>
       </c>
       <c r="E273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F273" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう身体が動かない……でも、最後に立ってたのは私よ……！ 見届けてくれた？</t>
+          <t xml:space="preserve">どうして…以前のように言葉をくれないの…</t>
         </is>
       </c>
     </row>
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.emotional.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -9056,29 +9056,29 @@
       </c>
       <c r="C274" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.emotional.seductive[2]</t>
+          <t xml:space="preserve">bond_60_up.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E274" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F274" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何人来ても倒れなかった……！ この身体が、全部証明してるでしょ……？</t>
+          <t xml:space="preserve">放っておけないの…もう</t>
         </is>
       </c>
     </row>
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.emotional.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -9088,29 +9088,29 @@
       </c>
       <c r="C275" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.emotional.seductive[1]</t>
+          <t xml:space="preserve">bond_80_up.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E275" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F275" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">優勝……っ……ふふ、わたし、頂点に立ったのね……!</t>
+          <t xml:space="preserve">この人のためなら何でもできるの…！ 絶対に守るわ…！</t>
         </is>
       </c>
     </row>
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.emotional.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.emotional.seductive[2]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -9120,29 +9120,29 @@
       </c>
       <c r="C276" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.emotional.seductive[2]</t>
+          <t xml:space="preserve">bond_80_up.emotional.seductive[2]</t>
         </is>
       </c>
       <c r="E276" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F276" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この景色……っ……ふふ、忘れないわ……</t>
+          <t xml:space="preserve">巡り合えたこと、心から幸せなの…！</t>
         </is>
       </c>
     </row>
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.emotional.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9152,29 +9152,29 @@
       </c>
       <c r="C277" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.emotional.seductive[1]</t>
+          <t xml:space="preserve">rivalry_29_down.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F277" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けたわ……っ……悔しい……でも、いい経験だった……</t>
+          <t xml:space="preserve">因縁…終わっちゃったのね…少し寂しい…</t>
         </is>
       </c>
     </row>
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.emotional.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.emotional.seductive[2]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9184,29 +9184,29 @@
       </c>
       <c r="C278" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.emotional.seductive[2]</t>
+          <t xml:space="preserve">rivalry_29_down.emotional.seductive[2]</t>
         </is>
       </c>
       <c r="E278" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F278" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">リベンジするわ……っ……ふふ、必ず……</t>
+          <t xml:space="preserve">……あの熱さが消えていくわ。これでいいのかしら…</t>
         </is>
       </c>
     </row>
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.emotional.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9216,29 +9216,29 @@
       </c>
       <c r="C279" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.emotional.seductive[1]</t>
+          <t xml:space="preserve">rivalry_30_up.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E279" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F279" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝った……っ……ふふ、まだまだ行けるわ……</t>
+          <t xml:space="preserve">絶対に負けないわ…！ 絶対に…！</t>
         </is>
       </c>
     </row>
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.emotional.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.emotional.seductive[2]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9248,29 +9248,29 @@
       </c>
       <c r="C280" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D280" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.emotional.seductive[2]</t>
+          <t xml:space="preserve">rivalry_30_up.emotional.seductive[2]</t>
         </is>
       </c>
       <c r="E280" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F280" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい感じよ……っ……ふふ……</t>
+          <t xml:space="preserve">考えるだけで胸が熱くなるの…！</t>
         </is>
       </c>
     </row>
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.emotional.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9280,29 +9280,29 @@
       </c>
       <c r="C281" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.emotional.seductive[1]</t>
+          <t xml:space="preserve">rivalry_50_up.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E281" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F281" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ち上がったわ……っ……ふふ、ここまで来られたの……</t>
+          <t xml:space="preserve">くっ…考えると熱くなるの…！</t>
         </is>
       </c>
     </row>
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.emotional.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.emotional.seductive[2]</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -9312,29 +9312,29 @@
       </c>
       <c r="C282" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D282" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.emotional.seductive[2]</t>
+          <t xml:space="preserve">rivalry_50_up.emotional.seductive[2]</t>
         </is>
       </c>
       <c r="E282" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F282" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もっと上を目指すわ……っ……ふふ……</t>
+          <t xml:space="preserve">絶対に…超えてみせるわ…！！</t>
         </is>
       </c>
     </row>
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.emotional.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -9344,29 +9344,29 @@
       </c>
       <c r="C283" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D283" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.emotional.seductive[1]</t>
+          <t xml:space="preserve">rivalry_70_up.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E283" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F283" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決勝戦……っ……ふふ、ここまで来たのね……</t>
+          <t xml:space="preserve">あの出会いがなければ今の私はいなかった…！</t>
         </is>
       </c>
     </row>
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.emotional.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.emotional.seductive[2]</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -9376,29 +9376,29 @@
       </c>
       <c r="C284" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D284" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.emotional.seductive[2]</t>
+          <t xml:space="preserve">rivalry_70_up.emotional.seductive[2]</t>
         </is>
       </c>
       <c r="E284" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F284" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高の舞台ね……っ……ふふ、震えてるの……</t>
+          <t xml:space="preserve">この因縁に終わりなんてないわ…！ 永遠に戦い続けるの…！</t>
         </is>
       </c>
     </row>
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.emotional.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -9408,29 +9408,29 @@
       </c>
       <c r="C285" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D285" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.emotional.seductive[1]</t>
+          <t xml:space="preserve">trust_above_75.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E285" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F285" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">試合前……っ……ふふ、心臓がドキドキしてるの……</t>
+          <t xml:space="preserve">みんなのこと…大好きよ…！ この団体のために全力を尽くすわ…！</t>
         </is>
       </c>
     </row>
     <row r="286" ht="40" customHeight="1">
       <c r="A286" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.emotional.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.emotional.seductive[2]</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -9440,29 +9440,29 @@
       </c>
       <c r="C286" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D286" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.emotional.seductive[2]</t>
+          <t xml:space="preserve">trust_above_75.emotional.seductive[2]</t>
         </is>
       </c>
       <c r="E286" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F286" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">楽しんでくるわね……っ……ふふ……</t>
+          <t xml:space="preserve">ここで出会えた仲間は宝物なの…絶対に裏切らないわ…！</t>
         </is>
       </c>
     </row>
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.emotional.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -9472,29 +9472,29 @@
       </c>
       <c r="C287" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D287" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.emotional.seductive[1]</t>
+          <t xml:space="preserve">trust_below_20.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E287" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F287" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ジュニア大会に……っ……ふふ、わたしを選んでくれたのね、嬉しい……</t>
+          <t xml:space="preserve">もう…信じられないわ…！ どうして…！</t>
         </is>
       </c>
     </row>
     <row r="288" ht="40" customHeight="1">
       <c r="A288" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.emotional.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.emotional.seductive[2]</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
@@ -9504,29 +9504,29 @@
       </c>
       <c r="C288" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D288" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.emotional.seductive[2]</t>
+          <t xml:space="preserve">trust_below_20.emotional.seductive[2]</t>
         </is>
       </c>
       <c r="E288" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F288" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">楽しみだわ……っ……ふふ、燃えてきたの……</t>
+          <t xml:space="preserve">裏切られたのね…全部…偽りだったの…？</t>
         </is>
       </c>
     </row>
     <row r="289" ht="40" customHeight="1">
       <c r="A289" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.emotional.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
@@ -9536,29 +9536,29 @@
       </c>
       <c r="C289" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D289" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.seductive[1]</t>
+          <t xml:space="preserve">trust_below_35.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E289" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F289" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの子が相手……っ……ふふ、燃えてきたわ……</t>
+          <t xml:space="preserve">不安なの…これでいいのかしら…？ 私、忘れられてない…？</t>
         </is>
       </c>
     </row>
     <row r="290" ht="40" customHeight="1">
       <c r="A290" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.emotional.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
@@ -9568,29 +9568,29 @@
       </c>
       <c r="C290" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D290" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.seductive[1]</t>
+          <t xml:space="preserve">GL-01.goodLoss.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E290" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F290" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">嬉しい……っ……!最高の舞台で勝てた……この瞬間を、ずっと忘れないわ……!</t>
+          <t xml:space="preserve">負けたけど……っ……ふふ、出し切れたの……</t>
         </is>
       </c>
     </row>
     <row r="291" ht="40" customHeight="1">
       <c r="A291" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.emotional.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
@@ -9600,29 +9600,29 @@
       </c>
       <c r="C291" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D291" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.seductive[1]</t>
+          <t xml:space="preserve">GL-01.greatWin.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E291" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F291" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">団体として挑むわ……っ……ふふ、燃えるわね……</t>
+          <t xml:space="preserve">最高の勝利……っ……ふふ、震えてるの……</t>
         </is>
       </c>
     </row>
     <row r="292" ht="40" customHeight="1">
       <c r="A292" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.emotional.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
@@ -9632,29 +9632,29 @@
       </c>
       <c r="C292" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D292" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.seductive[2]</t>
+          <t xml:space="preserve">GL-01.loss.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E292" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F292" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みんなで戦うわ……っ……ふふ……</t>
+          <t xml:space="preserve">負けた……っ……悔しい……</t>
         </is>
       </c>
     </row>
     <row r="293" ht="40" customHeight="1">
       <c r="A293" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.emotional.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
@@ -9664,29 +9664,29 @@
       </c>
       <c r="C293" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D293" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.seductive[1]</t>
+          <t xml:space="preserve">GL-01.win.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E293" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F293" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ごめんなさい……っ……今回は遠慮するわ……</t>
+          <t xml:space="preserve">勝ったわ……っ……ふふ、嬉しい……</t>
         </is>
       </c>
     </row>
     <row r="294" ht="40" customHeight="1">
       <c r="A294" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.emotional.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
@@ -9696,29 +9696,29 @@
       </c>
       <c r="C294" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D294" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.seductive[2]</t>
+          <t xml:space="preserve">GL-02.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E294" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F294" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">またの機会に……っ……ふふ……</t>
+          <t xml:space="preserve">今日は……っ……ふふ、よろしくね……</t>
         </is>
       </c>
     </row>
     <row r="295" ht="40" customHeight="1">
       <c r="A295" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.emotional.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="2">
@@ -9728,29 +9728,29 @@
       </c>
       <c r="C295" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D295" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.emotional.seductive[1]</t>
+          <t xml:space="preserve">GL-03.down.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E295" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F295" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けたわ……っ……ふふ、悔しい……</t>
+          <t xml:space="preserve">うまくいかない……っ……どうしてかしら……</t>
         </is>
       </c>
     </row>
     <row r="296" ht="40" customHeight="1">
       <c r="A296" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.emotional.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B296" t="inlineStr" s="2">
@@ -9760,29 +9760,29 @@
       </c>
       <c r="C296" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D296" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.emotional.seductive[2]</t>
+          <t xml:space="preserve">GL-03.up.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E296" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F296" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次は絶対に……っ……ふふ、リベンジするわ……</t>
+          <t xml:space="preserve">なんだか調子いいの……っ……ふふ……</t>
         </is>
       </c>
     </row>
     <row r="297" ht="40" customHeight="1">
       <c r="A297" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.emotional.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B297" t="inlineStr" s="2">
@@ -9792,29 +9792,29 @@
       </c>
       <c r="C297" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D297" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.emotional.seductive[1]</t>
+          <t xml:space="preserve">GL-04.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E297" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F297" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝った……っ……ふふ、団体のために戦えて嬉しい……</t>
+          <t xml:space="preserve">練習するわ……っ……ふふ……</t>
         </is>
       </c>
     </row>
     <row r="298" ht="40" customHeight="1">
       <c r="A298" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.emotional.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B298" t="inlineStr" s="2">
@@ -9824,29 +9824,29 @@
       </c>
       <c r="C298" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D298" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.emotional.seductive[2]</t>
+          <t xml:space="preserve">GL-05.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E298" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F298" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みんなのおかげよ……っ……ふふ……</t>
+          <t xml:space="preserve">大丈夫よ……っ……ふふ、心配しないで……</t>
         </is>
       </c>
     </row>
     <row r="299" ht="40" customHeight="1">
       <c r="A299" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.emotional.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B299" t="inlineStr" s="2">
@@ -9856,29 +9856,29 @@
       </c>
       <c r="C299" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D299" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.seductive[1]</t>
+          <t xml:space="preserve">GL-06.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E299" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F299" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝てた…！ 団体のみんなのおかげ…嬉しい…！</t>
+          <t xml:space="preserve">みんなと一緒だと……っ……ふふ、安心するの……</t>
         </is>
       </c>
     </row>
     <row r="300" ht="40" customHeight="1">
       <c r="A300" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.emotional.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B300" t="inlineStr" s="2">
@@ -9888,29 +9888,29 @@
       </c>
       <c r="C300" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D300" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.seductive[2]</t>
+          <t xml:space="preserve">GL-07.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E300" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F300" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝てた…みんなのおかげ…嬉しい…！</t>
+          <t xml:space="preserve">お客さんがいっぱい……っ……ふふ、燃えるわね……</t>
         </is>
       </c>
     </row>
     <row r="301" ht="40" customHeight="1">
       <c r="A301" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.emotional.seductive[3]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B301" t="inlineStr" s="2">
@@ -9920,59 +9920,1467 @@
       </c>
       <c r="C301" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D301" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.seductive[3]</t>
+          <t xml:space="preserve">GL-08.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E301" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F301" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝てた…嬉しい…！ みんなのために頑張れた…！</t>
+          <t xml:space="preserve">体調は大丈夫よ……っ……ふふ、心配いらない……</t>
         </is>
       </c>
     </row>
     <row r="302" ht="40" customHeight="1">
       <c r="A302" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.emotional.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">GL-09.emotional.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">次の試合……っ……ふふ、楽しみだわ……</t>
+        </is>
+      </c>
+    </row>
+    <row r="303" ht="40" customHeight="1">
+      <c r="A303" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.emotional.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">GL-10.emotional.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ありがとう……っ……ふふ、嬉しい……</t>
+        </is>
+      </c>
+    </row>
+    <row r="304" ht="40" customHeight="1">
+      <c r="A304" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.emotional.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">emotional.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">勢いが止まったわ……っ……ふふ、また始めればいいのよ……</t>
+        </is>
+      </c>
+    </row>
+    <row r="305" ht="40" customHeight="1">
+      <c r="A305" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.emotional.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preFinal.emotional.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">身体、もう震えてるの…っ…ふふ、でも最後まで立つわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="306" ht="40" customHeight="1">
+      <c r="A306" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.emotional.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preFinal.emotional.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ここまで来たのね…っ…最後の舞台、全部ぶつけるわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="307" ht="40" customHeight="1">
+      <c r="A307" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.emotional.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preMatch.emotional.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">お相手は誰かしら…っ…ふふ、もう身体が疼いてるの</t>
+        </is>
+      </c>
+    </row>
+    <row r="308" ht="40" customHeight="1">
+      <c r="A308" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.emotional.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preMatch.emotional.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">早く来てよ…! この昂り、ぶつける相手が欲しいの…!</t>
+        </is>
+      </c>
+    </row>
+    <row r="309" ht="40" customHeight="1">
+      <c r="A309" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.emotional.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">survivor.emotional.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">一人、落としたわ…っ…はぁ…まだ疼いてるの。次、早く出してよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="310" ht="40" customHeight="1">
+      <c r="A310" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.emotional.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">survivor.emotional.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">まだ立ってる…! この身体、まだ終わってないの…! 次、来なさい…!</t>
+        </is>
+      </c>
+    </row>
+    <row r="311" ht="40" customHeight="1">
+      <c r="A311" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.emotional.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">champion.emotional.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">三人で勝ったの……！ この感動は……一人じゃ味わえないわ……</t>
+        </is>
+      </c>
+    </row>
+    <row r="312" ht="40" customHeight="1">
+      <c r="A312" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.emotional.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">champion.emotional.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">仲間が繋いでくれた想い……最後まで、手放さなかったよ……！</t>
+        </is>
+      </c>
+    </row>
+    <row r="313" ht="40" customHeight="1">
+      <c r="A313" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.emotional.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">defiant.emotional.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">この賞じゃ……心は満たされないのよ……！ 次は全部、奪い返すから……</t>
+        </is>
+      </c>
+    </row>
+    <row r="314" ht="40" customHeight="1">
+      <c r="A314" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.emotional.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">defiant.emotional.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">一人で輝いても寂しいだけ……！ 次は……三人で、ね……！</t>
+        </is>
+      </c>
+    </row>
+    <row r="315" ht="40" customHeight="1">
+      <c r="A315" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.emotional.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">gauntlet.emotional.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">もう身体が動かない……でも、最後に立ってたのは私よ……！ 見届けてくれた？</t>
+        </is>
+      </c>
+    </row>
+    <row r="316" ht="40" customHeight="1">
+      <c r="A316" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.emotional.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">gauntlet.emotional.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">何人来ても倒れなかった……！ この身体が、全部証明してるでしょ……？</t>
+        </is>
+      </c>
+    </row>
+    <row r="317" ht="40" customHeight="1">
+      <c r="A317" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.emotional.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">champion.emotional.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">優勝……っ……ふふ、わたし、頂点に立ったのね……!</t>
+        </is>
+      </c>
+    </row>
+    <row r="318" ht="40" customHeight="1">
+      <c r="A318" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.emotional.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">champion.emotional.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">この景色……っ……ふふ、忘れないわ……</t>
+        </is>
+      </c>
+    </row>
+    <row r="319" ht="40" customHeight="1">
+      <c r="A319" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.emotional.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postLose.emotional.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">負けたわ……っ……悔しい……でも、いい経験だった……</t>
+        </is>
+      </c>
+    </row>
+    <row r="320" ht="40" customHeight="1">
+      <c r="A320" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.emotional.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postLose.emotional.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">リベンジするわ……っ……ふふ、必ず……</t>
+        </is>
+      </c>
+    </row>
+    <row r="321" ht="40" customHeight="1">
+      <c r="A321" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.emotional.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postMatchWin.emotional.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">勝った……っ……ふふ、まだまだ行けるわ……</t>
+        </is>
+      </c>
+    </row>
+    <row r="322" ht="40" customHeight="1">
+      <c r="A322" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.emotional.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postMatchWin.emotional.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">いい感じよ……っ……ふふ……</t>
+        </is>
+      </c>
+    </row>
+    <row r="323" ht="40" customHeight="1">
+      <c r="A323" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.emotional.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postWin.emotional.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">勝ち上がったわ……っ……ふふ、ここまで来られたの……</t>
+        </is>
+      </c>
+    </row>
+    <row r="324" ht="40" customHeight="1">
+      <c r="A324" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.emotional.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postWin.emotional.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">もっと上を目指すわ……っ……ふふ……</t>
+        </is>
+      </c>
+    </row>
+    <row r="325" ht="40" customHeight="1">
+      <c r="A325" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.emotional.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preFinal.emotional.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">決勝戦……っ……ふふ、ここまで来たのね……</t>
+        </is>
+      </c>
+    </row>
+    <row r="326" ht="40" customHeight="1">
+      <c r="A326" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.emotional.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preFinal.emotional.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">最高の舞台ね……っ……ふふ、震えてるの……</t>
+        </is>
+      </c>
+    </row>
+    <row r="327" ht="40" customHeight="1">
+      <c r="A327" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.emotional.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preMatch.emotional.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">試合前……っ……ふふ、心臓がドキドキしてるの……</t>
+        </is>
+      </c>
+    </row>
+    <row r="328" ht="40" customHeight="1">
+      <c r="A328" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.emotional.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preMatch.emotional.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">楽しんでくるわね……っ……ふふ……</t>
+        </is>
+      </c>
+    </row>
+    <row r="329" ht="40" customHeight="1">
+      <c r="A329" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.emotional.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">summon.emotional.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ジュニア大会に……っ……ふふ、わたしを選んでくれたのね、嬉しい……</t>
+        </is>
+      </c>
+    </row>
+    <row r="330" ht="40" customHeight="1">
+      <c r="A330" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.emotional.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">summon.emotional.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">楽しみだわ……っ……ふふ、燃えてきたの……</t>
+        </is>
+      </c>
+    </row>
+    <row r="331" ht="40" customHeight="1">
+      <c r="A331" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.emotional.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">emotional.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あの子が相手……っ……ふふ、燃えてきたわ……</t>
+        </is>
+      </c>
+    </row>
+    <row r="332" ht="40" customHeight="1">
+      <c r="A332" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.emotional.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">emotional.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">嬉しい……っ……!最高の舞台で勝てた……この瞬間を、ずっと忘れないわ……!</t>
+        </is>
+      </c>
+    </row>
+    <row r="333" ht="40" customHeight="1">
+      <c r="A333" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.emotional.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">emotional.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">団体として挑むわ……っ……ふふ、燃えるわね……</t>
+        </is>
+      </c>
+    </row>
+    <row r="334" ht="40" customHeight="1">
+      <c r="A334" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.emotional.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">emotional.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">みんなで戦うわ……っ……ふふ……</t>
+        </is>
+      </c>
+    </row>
+    <row r="335" ht="40" customHeight="1">
+      <c r="A335" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.emotional.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">emotional.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ごめんなさい……っ……今回は遠慮するわ……</t>
+        </is>
+      </c>
+    </row>
+    <row r="336" ht="40" customHeight="1">
+      <c r="A336" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.emotional.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">emotional.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">またの機会に……っ……ふふ……</t>
+        </is>
+      </c>
+    </row>
+    <row r="337" ht="40" customHeight="1">
+      <c r="A337" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.emotional.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_lose.emotional.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">負けたわ……っ……ふふ、悔しい……</t>
+        </is>
+      </c>
+    </row>
+    <row r="338" ht="40" customHeight="1">
+      <c r="A338" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.emotional.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_lose.emotional.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">次は絶対に……っ……ふふ、リベンジするわ……</t>
+        </is>
+      </c>
+    </row>
+    <row r="339" ht="40" customHeight="1">
+      <c r="A339" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.emotional.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_win.emotional.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">勝った……っ……ふふ、団体のために戦えて嬉しい……</t>
+        </is>
+      </c>
+    </row>
+    <row r="340" ht="40" customHeight="1">
+      <c r="A340" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.emotional.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_win.emotional.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">みんなのおかげよ……っ……ふふ……</t>
+        </is>
+      </c>
+    </row>
+    <row r="341" ht="40" customHeight="1">
+      <c r="A341" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.emotional.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">emotional.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">勝てた…！ 団体のみんなのおかげ…嬉しい…！</t>
+        </is>
+      </c>
+    </row>
+    <row r="342" ht="40" customHeight="1">
+      <c r="A342" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.emotional.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">emotional.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">勝てた…みんなのおかげ…嬉しい…！</t>
+        </is>
+      </c>
+    </row>
+    <row r="343" ht="40" customHeight="1">
+      <c r="A343" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.emotional.seductive[3]</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">emotional.seductive[3]</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">勝てた…嬉しい…！ みんなのために頑張れた…！</t>
+        </is>
+      </c>
+    </row>
+    <row r="344" ht="40" customHeight="1">
+      <c r="A344" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">ENDING_LINES.fighter.emotional.seductive[1]</t>
         </is>
       </c>
-      <c r="B302" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C302" t="inlineStr" s="2">
+      <c r="B344" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">ENDING_LINES</t>
         </is>
       </c>
-      <c r="D302" t="inlineStr" s="12">
+      <c r="D344" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">fighter.emotional.seductive[1]</t>
         </is>
       </c>
-      <c r="E302" t="inlineStr" s="2">
+      <c r="E344" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">18 経営危機・エンディング</t>
         </is>
       </c>
-      <c r="F302" t="inlineStr" s="3">
+      <c r="F344" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">リングを降りるわ……っ……ふふ、ここで戦えた日々、永遠に忘れない……ありがとう……</t>
         </is>
       </c>
     </row>
+    <row r="345" ht="40" customHeight="1">
+      <c r="A345" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.emotional.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">emotional.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">拾われる側になるなんて…っ…参ったわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="346" ht="40" customHeight="1">
+      <c r="A346" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES.emotional.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">emotional.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">うふふ♪嬉しい♪</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H302"/>
+  <autoFilter ref="A1:H346"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/蠱惑×感情的.xlsx
+++ b/セリフ編集/キャラタイプ別/蠱惑×感情的.xlsx
@@ -284,7 +284,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H346"/>
+  <dimension ref="A1:H344"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -342,7 +342,7 @@
     <row r="2" ht="40" customHeight="1">
       <c r="A2" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.emotional.seductive[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr" s="2">
@@ -357,7 +357,7 @@
       </c>
       <c r="D2" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.emotional.seductive[1]</t>
+          <t xml:space="preserve">atk.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E2" t="inlineStr" s="2">
@@ -374,7 +374,7 @@
     <row r="3" ht="40" customHeight="1">
       <c r="A3" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.emotional.seductive[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr" s="2">
@@ -389,7 +389,7 @@
       </c>
       <c r="D3" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.emotional.seductive[2]</t>
+          <t xml:space="preserve">atk.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E3" t="inlineStr" s="2">
@@ -406,7 +406,7 @@
     <row r="4" ht="40" customHeight="1">
       <c r="A4" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.emotional.seductive[3]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.seductive.emotional[3]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr" s="2">
@@ -421,7 +421,7 @@
       </c>
       <c r="D4" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.emotional.seductive[3]</t>
+          <t xml:space="preserve">atk.seductive.emotional[3]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr" s="2">
@@ -438,7 +438,7 @@
     <row r="5" ht="40" customHeight="1">
       <c r="A5" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.emotional.seductive[4]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.seductive.emotional[4]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr" s="2">
@@ -453,7 +453,7 @@
       </c>
       <c r="D5" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.emotional.seductive[4]</t>
+          <t xml:space="preserve">atk.seductive.emotional[4]</t>
         </is>
       </c>
       <c r="E5" t="inlineStr" s="2">
@@ -470,7 +470,7 @@
     <row r="6" ht="40" customHeight="1">
       <c r="A6" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.emotional.seductive[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr" s="2">
@@ -485,7 +485,7 @@
       </c>
       <c r="D6" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.emotional.seductive[1]</t>
+          <t xml:space="preserve">bigmove.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E6" t="inlineStr" s="2">
@@ -502,7 +502,7 @@
     <row r="7" ht="40" customHeight="1">
       <c r="A7" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.emotional.seductive[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr" s="2">
@@ -517,7 +517,7 @@
       </c>
       <c r="D7" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.emotional.seductive[2]</t>
+          <t xml:space="preserve">bigmove.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E7" t="inlineStr" s="2">
@@ -534,7 +534,7 @@
     <row r="8" ht="40" customHeight="1">
       <c r="A8" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.emotional.seductive[3]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.seductive.emotional[3]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr" s="2">
@@ -549,7 +549,7 @@
       </c>
       <c r="D8" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.emotional.seductive[3]</t>
+          <t xml:space="preserve">bigmove.seductive.emotional[3]</t>
         </is>
       </c>
       <c r="E8" t="inlineStr" s="2">
@@ -566,7 +566,7 @@
     <row r="9" ht="40" customHeight="1">
       <c r="A9" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.climax.emotional.seductive[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.climax.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr" s="2">
@@ -581,7 +581,7 @@
       </c>
       <c r="D9" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">climax.emotional.seductive[1]</t>
+          <t xml:space="preserve">climax.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E9" t="inlineStr" s="2">
@@ -598,7 +598,7 @@
     <row r="10" ht="40" customHeight="1">
       <c r="A10" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.climax.emotional.seductive[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.climax.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr" s="2">
@@ -613,7 +613,7 @@
       </c>
       <c r="D10" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">climax.emotional.seductive[2]</t>
+          <t xml:space="preserve">climax.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E10" t="inlineStr" s="2">
@@ -630,7 +630,7 @@
     <row r="11" ht="40" customHeight="1">
       <c r="A11" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES.emotional.seductive[1]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr" s="2">
@@ -645,7 +645,7 @@
       </c>
       <c r="D11" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.seductive[1]</t>
+          <t xml:space="preserve">seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E11" t="inlineStr" s="2">
@@ -662,7 +662,7 @@
     <row r="12" ht="40" customHeight="1">
       <c r="A12" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES.emotional.seductive[2]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr" s="2">
@@ -677,7 +677,7 @@
       </c>
       <c r="D12" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.seductive[2]</t>
+          <t xml:space="preserve">seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E12" t="inlineStr" s="2">
@@ -694,7 +694,7 @@
     <row r="13" ht="40" customHeight="1">
       <c r="A13" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES.emotional.seductive[3]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.seductive.emotional[3]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr" s="2">
@@ -709,7 +709,7 @@
       </c>
       <c r="D13" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.seductive[3]</t>
+          <t xml:space="preserve">seductive.emotional[3]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr" s="2">
@@ -726,7 +726,7 @@
     <row r="14" ht="40" customHeight="1">
       <c r="A14" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner.emotional.seductive[1]</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr" s="2">
@@ -741,7 +741,7 @@
       </c>
       <c r="D14" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">badWinner.emotional.seductive[1]</t>
+          <t xml:space="preserve">badWinner.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E14" t="inlineStr" s="2">
@@ -758,7 +758,7 @@
     <row r="15" ht="40" customHeight="1">
       <c r="A15" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner.emotional.seductive[1]</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr" s="2">
@@ -773,7 +773,7 @@
       </c>
       <c r="D15" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">goodWinner.emotional.seductive[1]</t>
+          <t xml:space="preserve">goodWinner.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E15" t="inlineStr" s="2">
@@ -790,7 +790,7 @@
     <row r="16" ht="40" customHeight="1">
       <c r="A16" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.emotional.seductive[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr" s="2">
@@ -805,7 +805,7 @@
       </c>
       <c r="D16" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">competition_won.emotional.seductive[1]</t>
+          <t xml:space="preserve">competition_won.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E16" t="inlineStr" s="2">
@@ -822,7 +822,7 @@
     <row r="17" ht="40" customHeight="1">
       <c r="A17" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.emotional.seductive[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr" s="2">
@@ -837,7 +837,7 @@
       </c>
       <c r="D17" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">direct.emotional.seductive[1]</t>
+          <t xml:space="preserve">direct.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E17" t="inlineStr" s="2">
@@ -854,7 +854,7 @@
     <row r="18" ht="40" customHeight="1">
       <c r="A18" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.emotional.seductive[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr" s="2">
@@ -869,7 +869,7 @@
       </c>
       <c r="D18" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fa_signing.emotional.seductive[1]</t>
+          <t xml:space="preserve">fa_signing.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E18" t="inlineStr" s="2">
@@ -886,7 +886,7 @@
     <row r="19" ht="40" customHeight="1">
       <c r="A19" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.emotional.seductive.hit[1]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.seductive.emotional.hit[1]</t>
         </is>
       </c>
       <c r="B19" t="inlineStr" s="2">
@@ -901,7 +901,7 @@
       </c>
       <c r="D19" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.seductive.hit[1]</t>
+          <t xml:space="preserve">seductive.emotional.hit[1]</t>
         </is>
       </c>
       <c r="E19" t="inlineStr" s="2">
@@ -918,7 +918,7 @@
     <row r="20" ht="40" customHeight="1">
       <c r="A20" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.emotional.seductive.hit[2]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.seductive.emotional.hit[2]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr" s="2">
@@ -933,7 +933,7 @@
       </c>
       <c r="D20" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.seductive.hit[2]</t>
+          <t xml:space="preserve">seductive.emotional.hit[2]</t>
         </is>
       </c>
       <c r="E20" t="inlineStr" s="2">
@@ -950,7 +950,7 @@
     <row r="21" ht="40" customHeight="1">
       <c r="A21" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.emotional.seductive.win[1]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.seductive.emotional.win[1]</t>
         </is>
       </c>
       <c r="B21" t="inlineStr" s="2">
@@ -965,7 +965,7 @@
       </c>
       <c r="D21" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.seductive.win[1]</t>
+          <t xml:space="preserve">seductive.emotional.win[1]</t>
         </is>
       </c>
       <c r="E21" t="inlineStr" s="2">
@@ -982,7 +982,7 @@
     <row r="22" ht="40" customHeight="1">
       <c r="A22" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.emotional.seductive.win[2]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.seductive.emotional.win[2]</t>
         </is>
       </c>
       <c r="B22" t="inlineStr" s="2">
@@ -997,7 +997,7 @@
       </c>
       <c r="D22" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.seductive.win[2]</t>
+          <t xml:space="preserve">seductive.emotional.win[2]</t>
         </is>
       </c>
       <c r="E22" t="inlineStr" s="2">
@@ -1014,7 +1014,7 @@
     <row r="23" ht="40" customHeight="1">
       <c r="A23" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BETRAYAL_LINES.emotional.seductive[1]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B23" t="inlineStr" s="2">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="D23" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.seductive[1]</t>
+          <t xml:space="preserve">seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E23" t="inlineStr" s="2">
@@ -1046,7 +1046,7 @@
     <row r="24" ht="40" customHeight="1">
       <c r="A24" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BETRAYAL_LINES.emotional.seductive[2]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B24" t="inlineStr" s="2">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="D24" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.seductive[2]</t>
+          <t xml:space="preserve">seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E24" t="inlineStr" s="2">
@@ -1078,7 +1078,7 @@
     <row r="25" ht="40" customHeight="1">
       <c r="A25" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BETRAYAL_LINES.emotional.seductive[3]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.seductive.emotional[3]</t>
         </is>
       </c>
       <c r="B25" t="inlineStr" s="2">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="D25" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.seductive[3]</t>
+          <t xml:space="preserve">seductive.emotional[3]</t>
         </is>
       </c>
       <c r="E25" t="inlineStr" s="2">
@@ -1110,7 +1110,7 @@
     <row r="26" ht="40" customHeight="1">
       <c r="A26" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_SAVE_LINES.emotional.seductive[1]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B26" t="inlineStr" s="2">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="D26" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.seductive[1]</t>
+          <t xml:space="preserve">seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E26" t="inlineStr" s="2">
@@ -1142,7 +1142,7 @@
     <row r="27" ht="40" customHeight="1">
       <c r="A27" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_SAVE_LINES.emotional.seductive[2]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B27" t="inlineStr" s="2">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="D27" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.seductive[2]</t>
+          <t xml:space="preserve">seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E27" t="inlineStr" s="2">
@@ -1174,7 +1174,7 @@
     <row r="28" ht="40" customHeight="1">
       <c r="A28" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_SAVE_LINES.emotional.seductive[3]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.seductive.emotional[3]</t>
         </is>
       </c>
       <c r="B28" t="inlineStr" s="2">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="D28" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.seductive[3]</t>
+          <t xml:space="preserve">seductive.emotional[3]</t>
         </is>
       </c>
       <c r="E28" t="inlineStr" s="2">
@@ -1206,7 +1206,7 @@
     <row r="29" ht="40" customHeight="1">
       <c r="A29" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_LINES.emotional.seductive[1]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B29" t="inlineStr" s="2">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="D29" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.seductive[1]</t>
+          <t xml:space="preserve">seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E29" t="inlineStr" s="2">
@@ -1238,7 +1238,7 @@
     <row r="30" ht="40" customHeight="1">
       <c r="A30" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_LINES.emotional.seductive[2]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B30" t="inlineStr" s="2">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="D30" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.seductive[2]</t>
+          <t xml:space="preserve">seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E30" t="inlineStr" s="2">
@@ -1270,7 +1270,7 @@
     <row r="31" ht="40" customHeight="1">
       <c r="A31" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_LINES.emotional.seductive[3]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.seductive.emotional[3]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr" s="2">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="D31" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.seductive[3]</t>
+          <t xml:space="preserve">seductive.emotional[3]</t>
         </is>
       </c>
       <c r="E31" t="inlineStr" s="2">
@@ -1302,7 +1302,7 @@
     <row r="32" ht="40" customHeight="1">
       <c r="A32" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HOT_TAG_LINES.emotional.seductive[1]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B32" t="inlineStr" s="2">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="D32" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.seductive[1]</t>
+          <t xml:space="preserve">seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E32" t="inlineStr" s="2">
@@ -1334,7 +1334,7 @@
     <row r="33" ht="40" customHeight="1">
       <c r="A33" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HOT_TAG_LINES.emotional.seductive[2]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B33" t="inlineStr" s="2">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="D33" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.seductive[2]</t>
+          <t xml:space="preserve">seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E33" t="inlineStr" s="2">
@@ -1366,7 +1366,7 @@
     <row r="34" ht="40" customHeight="1">
       <c r="A34" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HOT_TAG_LINES.emotional.seductive[3]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.seductive.emotional[3]</t>
         </is>
       </c>
       <c r="B34" t="inlineStr" s="2">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="D34" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.seductive[3]</t>
+          <t xml:space="preserve">seductive.emotional[3]</t>
         </is>
       </c>
       <c r="E34" t="inlineStr" s="2">
@@ -1398,7 +1398,7 @@
     <row r="35" ht="40" customHeight="1">
       <c r="A35" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.emotional.seductive[1]</t>
+          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B35" t="inlineStr" s="2">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="D35" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.seductive[1]</t>
+          <t xml:space="preserve">seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E35" t="inlineStr" s="2">
@@ -1430,7 +1430,7 @@
     <row r="36" ht="40" customHeight="1">
       <c r="A36" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.emotional.seductive[2]</t>
+          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B36" t="inlineStr" s="2">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="D36" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.seductive[2]</t>
+          <t xml:space="preserve">seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E36" t="inlineStr" s="2">
@@ -1462,7 +1462,7 @@
     <row r="37" ht="40" customHeight="1">
       <c r="A37" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_WIN_LINES.emotional.seductive[1]</t>
+          <t xml:space="preserve">TAG_MATCH_WIN_LINES.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B37" t="inlineStr" s="2">
@@ -1477,7 +1477,7 @@
       </c>
       <c r="D37" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.seductive[1]</t>
+          <t xml:space="preserve">seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E37" t="inlineStr" s="2">
@@ -1494,7 +1494,7 @@
     <row r="38" ht="40" customHeight="1">
       <c r="A38" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_WIN_LINES.emotional.seductive[2]</t>
+          <t xml:space="preserve">TAG_MATCH_WIN_LINES.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B38" t="inlineStr" s="2">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="D38" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.seductive[2]</t>
+          <t xml:space="preserve">seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E38" t="inlineStr" s="2">
@@ -1526,7 +1526,7 @@
     <row r="39" ht="40" customHeight="1">
       <c r="A39" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_PREMATCH_LINES.ahead.emotional.seductive[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.ahead.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B39" t="inlineStr" s="2">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="D39" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ahead.emotional.seductive[1]</t>
+          <t xml:space="preserve">ahead.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E39" t="inlineStr" s="2">
@@ -1558,7 +1558,7 @@
     <row r="40" ht="40" customHeight="1">
       <c r="A40" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_PREMATCH_LINES.behind.emotional.seductive[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.behind.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B40" t="inlineStr" s="2">
@@ -1573,7 +1573,7 @@
       </c>
       <c r="D40" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">behind.emotional.seductive[1]</t>
+          <t xml:space="preserve">behind.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E40" t="inlineStr" s="2">
@@ -1590,7 +1590,7 @@
     <row r="41" ht="40" customHeight="1">
       <c r="A41" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.emotional.seductive[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B41" t="inlineStr" s="2">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="D41" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.emotional.seductive[1]</t>
+          <t xml:space="preserve">loser.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E41" t="inlineStr" s="2">
@@ -1622,7 +1622,7 @@
     <row r="42" ht="40" customHeight="1">
       <c r="A42" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.emotional.seductive[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr" s="2">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="D42" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.emotional.seductive[1]</t>
+          <t xml:space="preserve">winner.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E42" t="inlineStr" s="2">
@@ -1654,7 +1654,7 @@
     <row r="43" ht="40" customHeight="1">
       <c r="A43" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser.emotional.seductive[1]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B43" t="inlineStr" s="2">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="D43" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.emotional.seductive[1]</t>
+          <t xml:space="preserve">loser.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E43" t="inlineStr" s="2">
@@ -1686,7 +1686,7 @@
     <row r="44" ht="40" customHeight="1">
       <c r="A44" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.emotional.seductive[1]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr" s="2">
@@ -1701,7 +1701,7 @@
       </c>
       <c r="D44" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.emotional.seductive[1]</t>
+          <t xml:space="preserve">winner.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E44" t="inlineStr" s="2">
@@ -1718,7 +1718,7 @@
     <row r="45" ht="40" customHeight="1">
       <c r="A45" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.emotional.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr" s="2">
@@ -1733,7 +1733,7 @@
       </c>
       <c r="D45" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.emotional.seductive[1]</t>
+          <t xml:space="preserve">attacker.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E45" t="inlineStr" s="2">
@@ -1750,7 +1750,7 @@
     <row r="46" ht="40" customHeight="1">
       <c r="A46" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.emotional.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B46" t="inlineStr" s="2">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="D46" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.emotional.seductive[1]</t>
+          <t xml:space="preserve">defender.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E46" t="inlineStr" s="2">
@@ -1782,7 +1782,7 @@
     <row r="47" ht="40" customHeight="1">
       <c r="A47" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker.emotional.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B47" t="inlineStr" s="2">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="D47" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.emotional.seductive[1]</t>
+          <t xml:space="preserve">attacker.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E47" t="inlineStr" s="2">
@@ -1814,7 +1814,7 @@
     <row r="48" ht="40" customHeight="1">
       <c r="A48" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.emotional.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B48" t="inlineStr" s="2">
@@ -1829,7 +1829,7 @@
       </c>
       <c r="D48" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.emotional.seductive[1]</t>
+          <t xml:space="preserve">defender.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E48" t="inlineStr" s="2">
@@ -1846,7 +1846,7 @@
     <row r="49" ht="40" customHeight="1">
       <c r="A49" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.emotional.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B49" t="inlineStr" s="2">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="D49" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.emotional.seductive[1]</t>
+          <t xml:space="preserve">attacker.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E49" t="inlineStr" s="2">
@@ -1878,7 +1878,7 @@
     <row r="50" ht="40" customHeight="1">
       <c r="A50" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.emotional.seductive[2]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B50" t="inlineStr" s="2">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="D50" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.emotional.seductive[2]</t>
+          <t xml:space="preserve">attacker.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E50" t="inlineStr" s="2">
@@ -1910,7 +1910,7 @@
     <row r="51" ht="40" customHeight="1">
       <c r="A51" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.emotional.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B51" t="inlineStr" s="2">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="D51" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.emotional.seductive[1]</t>
+          <t xml:space="preserve">defender.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E51" t="inlineStr" s="2">
@@ -1942,7 +1942,7 @@
     <row r="52" ht="40" customHeight="1">
       <c r="A52" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateAttacker.emotional.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateAttacker.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B52" t="inlineStr" s="2">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="D52" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateAttacker.emotional.seductive[1]</t>
+          <t xml:space="preserve">fateAttacker.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E52" t="inlineStr" s="2">
@@ -1974,7 +1974,7 @@
     <row r="53" ht="40" customHeight="1">
       <c r="A53" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateDefender.emotional.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateDefender.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B53" t="inlineStr" s="2">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="D53" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateDefender.emotional.seductive[1]</t>
+          <t xml:space="preserve">fateDefender.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E53" t="inlineStr" s="2">
@@ -2006,7 +2006,7 @@
     <row r="54" ht="40" customHeight="1">
       <c r="A54" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateLoser.emotional.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateLoser.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B54" t="inlineStr" s="2">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="D54" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateLoser.emotional.seductive[1]</t>
+          <t xml:space="preserve">fateLoser.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E54" t="inlineStr" s="2">
@@ -2038,7 +2038,7 @@
     <row r="55" ht="40" customHeight="1">
       <c r="A55" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateWinner.emotional.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateWinner.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B55" t="inlineStr" s="2">
@@ -2053,7 +2053,7 @@
       </c>
       <c r="D55" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateWinner.emotional.seductive[1]</t>
+          <t xml:space="preserve">fateWinner.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E55" t="inlineStr" s="2">
@@ -2070,7 +2070,7 @@
     <row r="56" ht="40" customHeight="1">
       <c r="A56" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.emotional.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B56" t="inlineStr" s="2">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="D56" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.emotional.seductive[1]</t>
+          <t xml:space="preserve">loser.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E56" t="inlineStr" s="2">
@@ -2102,7 +2102,7 @@
     <row r="57" ht="40" customHeight="1">
       <c r="A57" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.emotional.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B57" t="inlineStr" s="2">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="D57" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.emotional.seductive[1]</t>
+          <t xml:space="preserve">winner.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E57" t="inlineStr" s="2">
@@ -2134,7 +2134,7 @@
     <row r="58" ht="40" customHeight="1">
       <c r="A58" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.emotional.seductive[1]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B58" t="inlineStr" s="2">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="D58" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.emotional.seductive[1]</t>
+          <t xml:space="preserve">loserLines.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E58" t="inlineStr" s="2">
@@ -2166,7 +2166,7 @@
     <row r="59" ht="40" customHeight="1">
       <c r="A59" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.emotional.seductive[1]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B59" t="inlineStr" s="2">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="D59" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.emotional.seductive[1]</t>
+          <t xml:space="preserve">winnerLines.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E59" t="inlineStr" s="2">
@@ -2966,7 +2966,7 @@
     <row r="84" ht="40" customHeight="1">
       <c r="A84" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.emotional.seductive[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B84" t="inlineStr" s="2">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="D84" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accepted.emotional.seductive[1]</t>
+          <t xml:space="preserve">accepted.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E84" t="inlineStr" s="2">
@@ -2998,7 +2998,7 @@
     <row r="85" ht="40" customHeight="1">
       <c r="A85" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.emotional.seductive[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B85" t="inlineStr" s="2">
@@ -3013,7 +3013,7 @@
       </c>
       <c r="D85" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defended.emotional.seductive[1]</t>
+          <t xml:space="preserve">defended.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E85" t="inlineStr" s="2">
@@ -3030,7 +3030,7 @@
     <row r="86" ht="40" customHeight="1">
       <c r="A86" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.emotional.seductive[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B86" t="inlineStr" s="2">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="D86" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defense_failed.emotional.seductive[1]</t>
+          <t xml:space="preserve">defense_failed.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E86" t="inlineStr" s="2">
@@ -3062,7 +3062,7 @@
     <row r="87" ht="40" customHeight="1">
       <c r="A87" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.default.emotional.seductive[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.default.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B87" t="inlineStr" s="2">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="D87" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">default.emotional.seductive[1]</t>
+          <t xml:space="preserve">default.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E87" t="inlineStr" s="2">
@@ -3094,7 +3094,7 @@
     <row r="88" ht="40" customHeight="1">
       <c r="A88" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.former_champ.emotional.seductive[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.former_champ.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B88" t="inlineStr" s="2">
@@ -3109,7 +3109,7 @@
       </c>
       <c r="D88" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">former_champ.emotional.seductive[1]</t>
+          <t xml:space="preserve">former_champ.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E88" t="inlineStr" s="2">
@@ -3126,7 +3126,7 @@
     <row r="89" ht="40" customHeight="1">
       <c r="A89" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.heel.emotional.seductive[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.heel.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B89" t="inlineStr" s="2">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="D89" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heel.emotional.seductive[1]</t>
+          <t xml:space="preserve">heel.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E89" t="inlineStr" s="2">
@@ -3158,7 +3158,7 @@
     <row r="90" ht="40" customHeight="1">
       <c r="A90" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.high_trust.emotional.seductive[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.high_trust.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B90" t="inlineStr" s="2">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="D90" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">high_trust.emotional.seductive[1]</t>
+          <t xml:space="preserve">high_trust.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E90" t="inlineStr" s="2">
@@ -3190,7 +3190,7 @@
     <row r="91" ht="40" customHeight="1">
       <c r="A91" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ.emotional.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B91" t="inlineStr" s="2">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="D91" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_former_champ.emotional.seductive[1]</t>
+          <t xml:space="preserve">accept_former_champ.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E91" t="inlineStr" s="2">
@@ -3222,7 +3222,7 @@
     <row r="92" ht="40" customHeight="1">
       <c r="A92" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel.emotional.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B92" t="inlineStr" s="2">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="D92" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_heel.emotional.seductive[1]</t>
+          <t xml:space="preserve">accept_heel.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E92" t="inlineStr" s="2">
@@ -3254,7 +3254,7 @@
     <row r="93" ht="40" customHeight="1">
       <c r="A93" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title.emotional.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B93" t="inlineStr" s="2">
@@ -3269,7 +3269,7 @@
       </c>
       <c r="D93" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_no_title.emotional.seductive[1]</t>
+          <t xml:space="preserve">accept_no_title.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E93" t="inlineStr" s="2">
@@ -3286,7 +3286,7 @@
     <row r="94" ht="40" customHeight="1">
       <c r="A94" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.emotional.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B94" t="inlineStr" s="2">
@@ -3301,7 +3301,7 @@
       </c>
       <c r="D94" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_terminal.emotional.seductive[1]</t>
+          <t xml:space="preserve">accept_terminal.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E94" t="inlineStr" s="2">
@@ -3318,7 +3318,7 @@
     <row r="95" ht="40" customHeight="1">
       <c r="A95" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless.emotional.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B95" t="inlineStr" s="2">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="D95" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_winless.emotional.seductive[1]</t>
+          <t xml:space="preserve">accept_winless.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E95" t="inlineStr" s="2">
@@ -3350,7 +3350,7 @@
     <row r="96" ht="40" customHeight="1">
       <c r="A96" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.emotional.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B96" t="inlineStr" s="2">
@@ -3365,7 +3365,7 @@
       </c>
       <c r="D96" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_champ.emotional.seductive[1]</t>
+          <t xml:space="preserve">refuse_champ.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E96" t="inlineStr" s="2">
@@ -3382,7 +3382,7 @@
     <row r="97" ht="40" customHeight="1">
       <c r="A97" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust.emotional.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B97" t="inlineStr" s="2">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="D97" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_distrust.emotional.seductive[1]</t>
+          <t xml:space="preserve">refuse_distrust.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E97" t="inlineStr" s="2">
@@ -3414,7 +3414,7 @@
     <row r="98" ht="40" customHeight="1">
       <c r="A98" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting.emotional.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B98" t="inlineStr" s="2">
@@ -3429,7 +3429,7 @@
       </c>
       <c r="D98" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_fighting.emotional.seductive[1]</t>
+          <t xml:space="preserve">refuse_fighting.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E98" t="inlineStr" s="2">
@@ -3446,7 +3446,7 @@
     <row r="99" ht="40" customHeight="1">
       <c r="A99" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel.emotional.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B99" t="inlineStr" s="2">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="D99" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_heel.emotional.seductive[1]</t>
+          <t xml:space="preserve">refuse_heel.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E99" t="inlineStr" s="2">
@@ -3478,7 +3478,7 @@
     <row r="100" ht="40" customHeight="1">
       <c r="A100" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.emotional.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B100" t="inlineStr" s="2">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="D100" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A1_champion.emotional.seductive[1]</t>
+          <t xml:space="preserve">A1_champion.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E100" t="inlineStr" s="2">
@@ -3510,7 +3510,7 @@
     <row r="101" ht="40" customHeight="1">
       <c r="A101" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.emotional.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B101" t="inlineStr" s="2">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="D101" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A2_uncrowned.emotional.seductive[1]</t>
+          <t xml:space="preserve">A2_uncrowned.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E101" t="inlineStr" s="2">
@@ -3542,7 +3542,7 @@
     <row r="102" ht="40" customHeight="1">
       <c r="A102" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.emotional.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B102" t="inlineStr" s="2">
@@ -3557,7 +3557,7 @@
       </c>
       <c r="D102" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A3_heel.emotional.seductive[1]</t>
+          <t xml:space="preserve">A3_heel.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E102" t="inlineStr" s="2">
@@ -3574,7 +3574,7 @@
     <row r="103" ht="40" customHeight="1">
       <c r="A103" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.emotional.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B103" t="inlineStr" s="2">
@@ -3589,7 +3589,7 @@
       </c>
       <c r="D103" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A4_veteran.emotional.seductive[1]</t>
+          <t xml:space="preserve">A4_veteran.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E103" t="inlineStr" s="2">
@@ -3606,7 +3606,7 @@
     <row r="104" ht="40" customHeight="1">
       <c r="A104" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B1_young.emotional.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B1_young.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B104" t="inlineStr" s="2">
@@ -3621,7 +3621,7 @@
       </c>
       <c r="D104" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1_young.emotional.seductive[1]</t>
+          <t xml:space="preserve">B1_young.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E104" t="inlineStr" s="2">
@@ -3638,7 +3638,7 @@
     <row r="105" ht="40" customHeight="1">
       <c r="A105" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.emotional.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B105" t="inlineStr" s="2">
@@ -3653,7 +3653,7 @@
       </c>
       <c r="D105" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_prime.emotional.seductive[1]</t>
+          <t xml:space="preserve">B2_prime.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E105" t="inlineStr" s="2">
@@ -3670,7 +3670,7 @@
     <row r="106" ht="40" customHeight="1">
       <c r="A106" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B3_older.emotional.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B3_older.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B106" t="inlineStr" s="2">
@@ -3685,7 +3685,7 @@
       </c>
       <c r="D106" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B3_older.emotional.seductive[1]</t>
+          <t xml:space="preserve">B3_older.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E106" t="inlineStr" s="2">
@@ -3702,7 +3702,7 @@
     <row r="107" ht="40" customHeight="1">
       <c r="A107" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.emotional.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B107" t="inlineStr" s="2">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="D107" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_champion_injury.emotional.seductive[1]</t>
+          <t xml:space="preserve">B4_champion_injury.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E107" t="inlineStr" s="2">
@@ -3734,7 +3734,7 @@
     <row r="108" ht="40" customHeight="1">
       <c r="A108" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VOLUNTARY_STAY_LINES.emotional.seductive[1]</t>
+          <t xml:space="preserve">VOLUNTARY_STAY_LINES.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B108" t="inlineStr" s="2">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="D108" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.seductive[1]</t>
+          <t xml:space="preserve">seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E108" t="inlineStr" s="2">
@@ -3766,7 +3766,7 @@
     <row r="109" ht="40" customHeight="1">
       <c r="A109" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.emotional.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B109" t="inlineStr" s="2">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="D109" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_accept.emotional.seductive[1]</t>
+          <t xml:space="preserve">raise_accept.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E109" t="inlineStr" s="2">
@@ -3798,7 +3798,7 @@
     <row r="110" ht="40" customHeight="1">
       <c r="A110" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.emotional.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B110" t="inlineStr" s="2">
@@ -3813,7 +3813,7 @@
       </c>
       <c r="D110" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_accept.emotional.seductive[1]</t>
+          <t xml:space="preserve">raise_negotiate_accept.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E110" t="inlineStr" s="2">
@@ -3830,7 +3830,7 @@
     <row r="111" ht="40" customHeight="1">
       <c r="A111" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.emotional.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B111" t="inlineStr" s="2">
@@ -3845,7 +3845,7 @@
       </c>
       <c r="D111" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_refuse.emotional.seductive[1]</t>
+          <t xml:space="preserve">raise_negotiate_refuse.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E111" t="inlineStr" s="2">
@@ -3862,7 +3862,7 @@
     <row r="112" ht="40" customHeight="1">
       <c r="A112" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.emotional.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B112" t="inlineStr" s="2">
@@ -3877,7 +3877,7 @@
       </c>
       <c r="D112" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.emotional.seductive[1]</t>
+          <t xml:space="preserve">raise_open.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E112" t="inlineStr" s="2">
@@ -3894,7 +3894,7 @@
     <row r="113" ht="40" customHeight="1">
       <c r="A113" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.emotional.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B113" t="inlineStr" s="2">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="D113" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_refuse.emotional.seductive[1]</t>
+          <t xml:space="preserve">raise_refuse.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E113" t="inlineStr" s="2">
@@ -3926,7 +3926,7 @@
     <row r="114" ht="40" customHeight="1">
       <c r="A114" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.emotional.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B114" t="inlineStr" s="2">
@@ -3941,7 +3941,7 @@
       </c>
       <c r="D114" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.emotional.seductive[1]</t>
+          <t xml:space="preserve">sudden_departure.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E114" t="inlineStr" s="2">
@@ -3958,7 +3958,7 @@
     <row r="115" ht="40" customHeight="1">
       <c r="A115" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.emotional.seductive[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B115" t="inlineStr" s="2">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="D115" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.emotional.seductive[2]</t>
+          <t xml:space="preserve">sudden_departure.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E115" t="inlineStr" s="2">
@@ -3990,7 +3990,7 @@
     <row r="116" ht="40" customHeight="1">
       <c r="A116" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.emotional.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B116" t="inlineStr" s="2">
@@ -4005,7 +4005,7 @@
       </c>
       <c r="D116" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_listen.emotional.seductive[1]</t>
+          <t xml:space="preserve">transfer_listen.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E116" t="inlineStr" s="2">
@@ -4022,7 +4022,7 @@
     <row r="117" ht="40" customHeight="1">
       <c r="A117" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.emotional.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B117" t="inlineStr" s="2">
@@ -4037,7 +4037,7 @@
       </c>
       <c r="D117" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.emotional.seductive[1]</t>
+          <t xml:space="preserve">transfer_open.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E117" t="inlineStr" s="2">
@@ -4054,7 +4054,7 @@
     <row r="118" ht="40" customHeight="1">
       <c r="A118" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.emotional.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B118" t="inlineStr" s="2">
@@ -4069,7 +4069,7 @@
       </c>
       <c r="D118" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_release.emotional.seductive[1]</t>
+          <t xml:space="preserve">transfer_release.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E118" t="inlineStr" s="2">
@@ -4086,7 +4086,7 @@
     <row r="119" ht="40" customHeight="1">
       <c r="A119" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.emotional.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B119" t="inlineStr" s="2">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="D119" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_fail.emotional.seductive[1]</t>
+          <t xml:space="preserve">transfer_retain_fail.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E119" t="inlineStr" s="2">
@@ -4118,7 +4118,7 @@
     <row r="120" ht="40" customHeight="1">
       <c r="A120" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.emotional.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B120" t="inlineStr" s="2">
@@ -4133,7 +4133,7 @@
       </c>
       <c r="D120" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_success.emotional.seductive[1]</t>
+          <t xml:space="preserve">transfer_retain_success.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E120" t="inlineStr" s="2">
@@ -4150,7 +4150,7 @@
     <row r="121" ht="40" customHeight="1">
       <c r="A121" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.blocked.emotional.seductive[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.blocked.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B121" t="inlineStr" s="2">
@@ -4165,7 +4165,7 @@
       </c>
       <c r="D121" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">blocked.emotional.seductive[1]</t>
+          <t xml:space="preserve">blocked.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E121" t="inlineStr" s="2">
@@ -4182,7 +4182,7 @@
     <row r="122" ht="40" customHeight="1">
       <c r="A122" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.fail.emotional.seductive[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.fail.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B122" t="inlineStr" s="2">
@@ -4197,7 +4197,7 @@
       </c>
       <c r="D122" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fail.emotional.seductive[1]</t>
+          <t xml:space="preserve">fail.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E122" t="inlineStr" s="2">
@@ -4214,7 +4214,7 @@
     <row r="123" ht="40" customHeight="1">
       <c r="A123" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.start.emotional.seductive[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.start.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B123" t="inlineStr" s="2">
@@ -4229,7 +4229,7 @@
       </c>
       <c r="D123" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">start.emotional.seductive[1]</t>
+          <t xml:space="preserve">start.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E123" t="inlineStr" s="2">
@@ -4246,7 +4246,7 @@
     <row r="124" ht="40" customHeight="1">
       <c r="A124" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.success.emotional.seductive[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.success.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B124" t="inlineStr" s="2">
@@ -4261,7 +4261,7 @@
       </c>
       <c r="D124" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">success.emotional.seductive[1]</t>
+          <t xml:space="preserve">success.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E124" t="inlineStr" s="2">
@@ -5526,7 +5526,7 @@
     <row r="164" ht="40" customHeight="1">
       <c r="A164" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F04_TARGET_LINES.emotional.seductive[1]</t>
+          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
@@ -5536,12 +5536,12 @@
       </c>
       <c r="C164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F04_TARGET_LINES</t>
+          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES</t>
         </is>
       </c>
       <c r="D164" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.seductive[1]</t>
+          <t xml:space="preserve">seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E164" t="inlineStr" s="2">
@@ -5551,14 +5551,14 @@
       </c>
       <c r="F164" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……引き止めないで。わたし、もう向こうへ傾いてるの。</t>
+          <t xml:space="preserve">冷めちゃったのよ、すっかりね……。</t>
         </is>
       </c>
     </row>
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES.emotional.seductive[1]</t>
+          <t xml:space="preserve">FACTION_F06_AMBIENT_LINES.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
@@ -5568,12 +5568,12 @@
       </c>
       <c r="C165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES</t>
+          <t xml:space="preserve">FACTION_F06_AMBIENT_LINES</t>
         </is>
       </c>
       <c r="D165" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.seductive[1]</t>
+          <t xml:space="preserve">seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E165" t="inlineStr" s="2">
@@ -5583,14 +5583,14 @@
       </c>
       <c r="F165" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">冷めちゃったのよ、すっかりね……。</t>
+          <t xml:space="preserve">ふふ、仲直り……いいものね。</t>
         </is>
       </c>
     </row>
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F06_AMBIENT_LINES.emotional.seductive[1]</t>
+          <t xml:space="preserve">FACTION_F08_LEADER_LINES.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -5600,12 +5600,12 @@
       </c>
       <c r="C166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F06_AMBIENT_LINES</t>
+          <t xml:space="preserve">FACTION_F08_LEADER_LINES</t>
         </is>
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.seductive[1]</t>
+          <t xml:space="preserve">seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E166" t="inlineStr" s="2">
@@ -5615,78 +5615,78 @@
       </c>
       <c r="F166" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、仲直り……いいものね。</t>
+          <t xml:space="preserve">……リングでなら、本音で話せるでしょ？</t>
         </is>
       </c>
     </row>
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F07_LEADER_LINES.emotional.seductive[1]</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F07_LEADER_LINES</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
         </is>
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.seductive[1]</t>
+          <t xml:space="preserve">seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F167" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長さん、うちの子たちに、もうちょっと優しくしてくださらない？</t>
+          <t xml:space="preserve">……っ……変わったの、わたし……ふふ、自分でも信じられないくらい……</t>
         </is>
       </c>
     </row>
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F08_LEADER_LINES.emotional.seductive[1]</t>
+          <t xml:space="preserve">BT_HINT_LINES.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F08_LEADER_LINES</t>
+          <t xml:space="preserve">BT_HINT_LINES</t>
         </is>
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.seductive[1]</t>
+          <t xml:space="preserve">seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F168" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……リングでなら、本音で話せるでしょ？</t>
+          <t xml:space="preserve">……っ……何か、来そうな予感がするの……ふふ、楽しみだわ……</t>
         </is>
       </c>
     </row>
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES.emotional.seductive[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.cap_reached.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5696,12 +5696,12 @@
       </c>
       <c r="C169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.seductive[1]</t>
+          <t xml:space="preserve">cap_reached.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr" s="2">
@@ -5711,14 +5711,14 @@
       </c>
       <c r="F169" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……っ……変わったの、わたし……ふふ、自分でも信じられないくらい……</t>
+          <t xml:space="preserve">ここまでなのね…少し寂しいけど…胸を張れるわ</t>
         </is>
       </c>
     </row>
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES.emotional.seductive[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -5728,12 +5728,12 @@
       </c>
       <c r="C170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.seductive[1]</t>
+          <t xml:space="preserve">ovr_elite.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="2">
@@ -5743,14 +5743,14 @@
       </c>
       <c r="F170" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……っ……何か、来そうな予感がするの……ふふ、楽しみだわ……</t>
+          <t xml:space="preserve">…ここまで来ちゃったの…嬉しくて…ちょっと泣きそう</t>
         </is>
       </c>
     </row>
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.cap_reached.emotional.seductive[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5765,7 +5765,7 @@
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cap_reached.emotional.seductive[1]</t>
+          <t xml:space="preserve">ovr_growth.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E171" t="inlineStr" s="2">
@@ -5775,14 +5775,14 @@
       </c>
       <c r="F171" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまでなのね…少し寂しいけど…胸を張れるわ</t>
+          <t xml:space="preserve">…ふふっ、強くなっちゃった。嬉しいわ</t>
         </is>
       </c>
     </row>
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.emotional.seductive[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5797,7 +5797,7 @@
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_elite.emotional.seductive[1]</t>
+          <t xml:space="preserve">ovr_legend.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E172" t="inlineStr" s="2">
@@ -5807,14 +5807,14 @@
       </c>
       <c r="F172" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ここまで来ちゃったの…嬉しくて…ちょっと泣きそう</t>
+          <t xml:space="preserve">ここまで来ちゃった…もう…涙が止まらないわ…</t>
         </is>
       </c>
     </row>
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.emotional.seductive[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_growth.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5829,7 +5829,7 @@
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_growth.emotional.seductive[1]</t>
+          <t xml:space="preserve">pop_growth.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
@@ -5839,14 +5839,14 @@
       </c>
       <c r="F173" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ふふっ、強くなっちゃった。嬉しいわ</t>
+          <t xml:space="preserve">応援してくれる人が…嬉しいわ…ふふ</t>
         </is>
       </c>
     </row>
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.emotional.seductive[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_star.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5861,7 +5861,7 @@
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_legend.emotional.seductive[1]</t>
+          <t xml:space="preserve">pop_star.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E174" t="inlineStr" s="2">
@@ -5871,14 +5871,14 @@
       </c>
       <c r="F174" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで来ちゃった…もう…涙が止まらないわ…</t>
+          <t xml:space="preserve">こんなに…嬉しくて…もう言葉にならないの…</t>
         </is>
       </c>
     </row>
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_growth.emotional.seductive[1]</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -5888,12 +5888,12 @@
       </c>
       <c r="C175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
         </is>
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_growth.emotional.seductive[1]</t>
+          <t xml:space="preserve">seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="2">
@@ -5903,14 +5903,14 @@
       </c>
       <c r="F175" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">応援してくれる人が…嬉しいわ…ふふ</t>
+          <t xml:space="preserve">……っ……どうしてかしら、力が湧かないの……</t>
         </is>
       </c>
     </row>
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_star.emotional.seductive[1]</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="C176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
         </is>
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_star.emotional.seductive[1]</t>
+          <t xml:space="preserve">seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
@@ -5935,14 +5935,14 @@
       </c>
       <c r="F176" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんなに…嬉しくて…もう言葉にならないの…</t>
+          <t xml:space="preserve">……っ……ふふ、また燃えてきたの……</t>
         </is>
       </c>
     </row>
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES.emotional.seductive[1]</t>
+          <t xml:space="preserve">SLUMP_END_LINES.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="C177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
+          <t xml:space="preserve">SLUMP_END_LINES</t>
         </is>
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.seductive[1]</t>
+          <t xml:space="preserve">seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
@@ -5967,14 +5967,14 @@
       </c>
       <c r="F177" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……っ……どうしてかしら、力が湧かないの……</t>
+          <t xml:space="preserve">調子が戻ってきたわ……っ……ふふ、ようやくね……</t>
         </is>
       </c>
     </row>
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.emotional.seductive[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.defeat.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -5984,12 +5984,12 @@
       </c>
       <c r="C178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.seductive[1]</t>
+          <t xml:space="preserve">defeat.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
@@ -5999,14 +5999,14 @@
       </c>
       <c r="F178" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……っ……ふふ、また燃えてきたの……</t>
+          <t xml:space="preserve">負けが続いて……っ……ふふ、自分が分からなくなりそう……</t>
         </is>
       </c>
     </row>
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES.emotional.seductive[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="C179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.seductive[1]</t>
+          <t xml:space="preserve">injury_moderate_recovery.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
@@ -6031,14 +6031,14 @@
       </c>
       <c r="F179" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">調子が戻ってきたわ……っ……ふふ、ようやくね……</t>
+          <t xml:space="preserve">怪我は治ったけど……っ……ふふ、感覚が戻らないの……</t>
         </is>
       </c>
     </row>
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.defeat.emotional.seductive[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -6053,7 +6053,7 @@
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defeat.emotional.seductive[1]</t>
+          <t xml:space="preserve">injury_severe_recovery.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
@@ -6063,14 +6063,14 @@
       </c>
       <c r="F180" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けが続いて……っ……ふふ、自分が分からなくなりそう……</t>
+          <t xml:space="preserve">大怪我から戻ったわ……っ……でも、まだ怖いの……</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.emotional.seductive[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -6085,7 +6085,7 @@
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_moderate_recovery.emotional.seductive[1]</t>
+          <t xml:space="preserve">penalty_end.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
@@ -6095,14 +6095,14 @@
       </c>
       <c r="F181" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">怪我は治ったけど……っ……ふふ、感覚が戻らないの……</t>
+          <t xml:space="preserve">謹慎が明けたわ……っ……ふふ、戻ってきたわよ……</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.emotional.seductive[1]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6112,29 +6112,29 @@
       </c>
       <c r="C182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_severe_recovery.emotional.seductive[1]</t>
+          <t xml:space="preserve">bestMatch.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F182" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">大怪我から戻ったわ……っ……でも、まだ怖いの……</t>
+          <t xml:space="preserve">最高の試合だった…涙が止まらないわ</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.emotional.seductive[1]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6144,29 +6144,29 @@
       </c>
       <c r="C183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">penalty_end.emotional.seductive[1]</t>
+          <t xml:space="preserve">champion.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F183" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">謹慎が明けたわ……っ……ふふ、戻ってきたわよ……</t>
+          <t xml:space="preserve">チャンピオン……っ……ふふ、この重み……愛おしくてたまらないわ……</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.emotional.seductive[1]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6181,7 +6181,7 @@
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.emotional.seductive[1]</t>
+          <t xml:space="preserve">hallOfFame.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
@@ -6191,14 +6191,14 @@
       </c>
       <c r="F184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高の試合だった…涙が止まらないわ</t>
+          <t xml:space="preserve">殿堂入り…もう言葉にならないわ…（涙を堪える）</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.emotional.seductive[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mediaAward.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6213,7 +6213,7 @@
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.emotional.seductive[1]</t>
+          <t xml:space="preserve">mediaAward.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
@@ -6223,14 +6223,14 @@
       </c>
       <c r="F185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオン……っ……ふふ、この重み……愛おしくてたまらないわ……</t>
+          <t xml:space="preserve">メディア功労賞……っ……みんなに見てもらえてた証ね、嬉しいわ……</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.emotional.seductive[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6245,7 +6245,7 @@
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.emotional.seductive[1]</t>
+          <t xml:space="preserve">mvp.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
@@ -6255,14 +6255,14 @@
       </c>
       <c r="F186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">殿堂入り…もう言葉にならないわ…（涙を堪える）</t>
+          <t xml:space="preserve">MVP……っ……ふふ、わたしが一番輝いてたって、そう言ってもらえるのね……</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mediaAward.emotional.seductive[1]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6277,7 +6277,7 @@
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mediaAward.emotional.seductive[1]</t>
+          <t xml:space="preserve">rookie.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
@@ -6287,14 +6287,14 @@
       </c>
       <c r="F187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">メディア功労賞……っ……みんなに見てもらえてた証ね、嬉しいわ……</t>
+          <t xml:space="preserve">新人王……っ……無我夢中だったの……認めてもらえて嬉しいわ……</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.emotional.seductive[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6304,12 +6304,12 @@
       </c>
       <c r="C188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.emotional.seductive[1]</t>
+          <t xml:space="preserve">seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
@@ -6319,14 +6319,14 @@
       </c>
       <c r="F188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">MVP……っ……ふふ、わたしが一番輝いてたって、そう言ってもらえるのね……</t>
+          <t xml:space="preserve">…ドームで、あなた方の前で戦える幸せよ…</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.emotional.seductive[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6336,12 +6336,12 @@
       </c>
       <c r="C189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.emotional.seductive[1]</t>
+          <t xml:space="preserve">seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
@@ -6351,14 +6351,14 @@
       </c>
       <c r="F189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">新人王……っ……無我夢中だったの……認めてもらえて嬉しいわ……</t>
+          <t xml:space="preserve">熱い試合を…必ず、約束する</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.emotional.seductive[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.seductive.emotional[3]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6373,7 +6373,7 @@
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.seductive[1]</t>
+          <t xml:space="preserve">seductive.emotional[3]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
@@ -6383,14 +6383,14 @@
       </c>
       <c r="F190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ドームで、あなた方の前で戦える幸せよ…</t>
+          <t xml:space="preserve">この胸の高鳴り…試合で発散させてね</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.emotional.seductive[2]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6400,12 +6400,12 @@
       </c>
       <c r="C191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.seductive[2]</t>
+          <t xml:space="preserve">seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
@@ -6415,14 +6415,14 @@
       </c>
       <c r="F191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">熱い試合を…必ず、約束する</t>
+          <t xml:space="preserve">…満員、お客様の熱気…忘れられない</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.emotional.seductive[3]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6432,12 +6432,12 @@
       </c>
       <c r="C192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.seductive[3]</t>
+          <t xml:space="preserve">seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
@@ -6447,14 +6447,14 @@
       </c>
       <c r="F192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この胸の高鳴り…試合で発散させてね</t>
+          <t xml:space="preserve">胸が熱くて、震えが止まらないの</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.emotional.seductive[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.seductive.emotional[3]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6469,7 +6469,7 @@
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.seductive[1]</t>
+          <t xml:space="preserve">seductive.emotional[3]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
@@ -6479,14 +6479,14 @@
       </c>
       <c r="F193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…満員、お客様の熱気…忘れられない</t>
+          <t xml:space="preserve">こんな素敵な夜、生涯忘れない</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.emotional.seductive[2]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6496,29 +6496,29 @@
       </c>
       <c r="C194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.seductive[2]</t>
+          <t xml:space="preserve">N1.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">胸が熱くて、震えが止まらないの</t>
+          <t xml:space="preserve">お知らせよ……っ……ふふ、聞いて……</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.emotional.seductive[3]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6528,29 +6528,29 @@
       </c>
       <c r="C195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.seductive[3]</t>
+          <t xml:space="preserve">N1.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんな素敵な夜、生涯忘れない</t>
+          <t xml:space="preserve">ねえ、聞いて……っ……ふふ……</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.emotional.seductive[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6565,7 +6565,7 @@
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.emotional.seductive[1]</t>
+          <t xml:space="preserve">N2.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
@@ -6575,14 +6575,14 @@
       </c>
       <c r="F196" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お知らせよ……っ……ふふ、聞いて……</t>
+          <t xml:space="preserve">ちょっといいかしら……っ……ふふ……</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.emotional.seductive[2]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6597,7 +6597,7 @@
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.emotional.seductive[2]</t>
+          <t xml:space="preserve">N3.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
@@ -6607,14 +6607,14 @@
       </c>
       <c r="F197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ねえ、聞いて……っ……ふふ……</t>
+          <t xml:space="preserve">はぁ……体が、言うこときかないの……ごめんなさい……</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.emotional.seductive[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6629,7 +6629,7 @@
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.emotional.seductive[1]</t>
+          <t xml:space="preserve">N3.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
@@ -6639,14 +6639,14 @@
       </c>
       <c r="F198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ちょっといいかしら……っ……ふふ……</t>
+          <t xml:space="preserve">ふぅ……ちょっと、休ませて……すぐ、戻るから……</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.emotional.seductive[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6661,7 +6661,7 @@
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.emotional.seductive[1]</t>
+          <t xml:space="preserve">N4.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
@@ -6671,14 +6671,14 @@
       </c>
       <c r="F199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">はぁ……体が、言うこときかないの……ごめんなさい……</t>
+          <t xml:space="preserve">大事な話よ……っ……ふふ、しっかり聞いて……</t>
         </is>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.emotional.seductive[2]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6693,7 +6693,7 @@
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.emotional.seductive[2]</t>
+          <t xml:space="preserve">N5_low.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
@@ -6703,14 +6703,14 @@
       </c>
       <c r="F200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふぅ……ちょっと、休ませて……すぐ、戻るから……</t>
+          <t xml:space="preserve">ちょっと心配なの……っ……ふふ……</t>
         </is>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.emotional.seductive[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.emotional.seductive[1]</t>
+          <t xml:space="preserve">N5_warning.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
@@ -6735,14 +6735,14 @@
       </c>
       <c r="F201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">大事な話よ……っ……ふふ、しっかり聞いて……</t>
+          <t xml:space="preserve">緊急よ……っ……ふふ、よく聞いて……</t>
         </is>
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.emotional.seductive[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.breakthrough.voice.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6752,12 +6752,12 @@
       </c>
       <c r="C202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.emotional.seductive[1]</t>
+          <t xml:space="preserve">breakthrough.voice.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
@@ -6767,14 +6767,14 @@
       </c>
       <c r="F202" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ちょっと心配なの……っ……ふふ……</t>
+          <t xml:space="preserve">何かが変わった……っ……ふふ……</t>
         </is>
       </c>
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.emotional.seductive[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6784,12 +6784,12 @@
       </c>
       <c r="C203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_warning.emotional.seductive[1]</t>
+          <t xml:space="preserve">G1.voice.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
@@ -6799,14 +6799,14 @@
       </c>
       <c r="F203" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">緊急よ……っ……ふふ、よく聞いて……</t>
+          <t xml:space="preserve">もう少し稼ぎたいわね……っ……</t>
         </is>
       </c>
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.breakthrough.voice.emotional.seductive[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6821,7 +6821,7 @@
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">breakthrough.voice.emotional.seductive[1]</t>
+          <t xml:space="preserve">G2.voice.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
@@ -6831,14 +6831,14 @@
       </c>
       <c r="F204" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何かが変わった……っ……ふふ……</t>
+          <t xml:space="preserve">ひとりは、ちょっと寂しいの……っ……</t>
         </is>
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.emotional.seductive[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6853,7 +6853,7 @@
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G1.voice.emotional.seductive[1]</t>
+          <t xml:space="preserve">G3.voice.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
@@ -6863,14 +6863,14 @@
       </c>
       <c r="F205" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう少し稼ぎたいわね……っ……</t>
+          <t xml:space="preserve">…もう少し目立たないとダメなのかしら</t>
         </is>
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice.emotional.seductive[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G4.voice.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6885,7 +6885,7 @@
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G2.voice.emotional.seductive[1]</t>
+          <t xml:space="preserve">G4.voice.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
@@ -6895,14 +6895,14 @@
       </c>
       <c r="F206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ひとりは、ちょっと寂しいの……っ……</t>
+          <t xml:space="preserve">もっと強くなりたいの……っ……</t>
         </is>
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice.emotional.seductive[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G3.voice.emotional.seductive[1]</t>
+          <t xml:space="preserve">R2.voice.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
@@ -6927,14 +6927,14 @@
       </c>
       <c r="F207" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もう少し目立たないとダメなのかしら</t>
+          <t xml:space="preserve">あの子と、もっと話したい……っ……</t>
         </is>
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G4.voice.emotional.seductive[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6949,7 +6949,7 @@
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G4.voice.emotional.seductive[1]</t>
+          <t xml:space="preserve">R4.voice.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
@@ -6959,14 +6959,14 @@
       </c>
       <c r="F208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もっと強くなりたいの……っ……</t>
+          <t xml:space="preserve">あの子とは、ちょっと距離を置きたいの……っ……</t>
         </is>
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice.emotional.seductive[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -6981,7 +6981,7 @@
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R2.voice.emotional.seductive[1]</t>
+          <t xml:space="preserve">R5.voice.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
@@ -6991,14 +6991,14 @@
       </c>
       <c r="F209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの子と、もっと話したい……っ……</t>
+          <t xml:space="preserve">負けたくないの……っ……ふふ……</t>
         </is>
       </c>
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice.emotional.seductive[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.warVictory.voice.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -7013,7 +7013,7 @@
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R4.voice.emotional.seductive[1]</t>
+          <t xml:space="preserve">warVictory.voice.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
@@ -7023,14 +7023,14 @@
       </c>
       <c r="F210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの子とは、ちょっと距離を置きたいの……っ……</t>
+          <t xml:space="preserve">勝てた……っ……ふふ、最高の気分……</t>
         </is>
       </c>
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice.emotional.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_repeat.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7040,29 +7040,29 @@
       </c>
       <c r="C211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R5.voice.emotional.seductive[1]</t>
+          <t xml:space="preserve">bonus_repeat.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けたくないの……っ……ふふ……</t>
+          <t xml:space="preserve">また……っ……ふふ、こんなに優しくされたら、応えないわけにはいかないわ……</t>
         </is>
       </c>
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.warVictory.voice.emotional.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7072,29 +7072,29 @@
       </c>
       <c r="C212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">warVictory.voice.emotional.seductive[1]</t>
+          <t xml:space="preserve">bonus.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F212" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝てた……っ……ふふ、最高の気分……</t>
+          <t xml:space="preserve">ボーナス……っ……気にかけてくれてたのね、嬉しい……ふふ、ありがとう……</t>
         </is>
       </c>
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_repeat.emotional.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7109,7 +7109,7 @@
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus_repeat.emotional.seductive[1]</t>
+          <t xml:space="preserve">camp.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
@@ -7119,14 +7119,14 @@
       </c>
       <c r="F213" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">また……っ……ふふ、こんなに優しくされたら、応えないわけにはいかないわ……</t>
+          <t xml:space="preserve">合宿……っ……ふふ、みんなと一緒に過ごせるのね、楽しみ……</t>
         </is>
       </c>
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.emotional.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7141,7 +7141,7 @@
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.emotional.seductive[1]</t>
+          <t xml:space="preserve">encourage_high_trust.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
@@ -7151,14 +7151,14 @@
       </c>
       <c r="F214" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ボーナス……っ……気にかけてくれてたのね、嬉しい……ふふ、ありがとう……</t>
+          <t xml:space="preserve">あなたの言葉だけで……っ……わたし、何でもできちゃいそうなの……ふふ……</t>
         </is>
       </c>
     </row>
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.emotional.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7173,7 +7173,7 @@
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.emotional.seductive[1]</t>
+          <t xml:space="preserve">encourage.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
@@ -7183,14 +7183,14 @@
       </c>
       <c r="F215" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">合宿……っ……ふふ、みんなと一緒に過ごせるのね、楽しみ……</t>
+          <t xml:space="preserve">励まし……っ……ふふ、その言葉だけで、力が湧いてくるの……</t>
         </is>
       </c>
     </row>
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.emotional.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7205,7 +7205,7 @@
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage_high_trust.emotional.seductive[1]</t>
+          <t xml:space="preserve">media.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
@@ -7215,14 +7215,14 @@
       </c>
       <c r="F216" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あなたの言葉だけで……っ……わたし、何でもできちゃいそうなの……ふふ……</t>
+          <t xml:space="preserve">メディアに……っ……ふふ、わたしを世間に見せたいのね、いいわ……</t>
         </is>
       </c>
     </row>
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.emotional.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7237,7 +7237,7 @@
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.emotional.seductive[1]</t>
+          <t xml:space="preserve">party.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
@@ -7247,14 +7247,14 @@
       </c>
       <c r="F217" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">励まし……っ……ふふ、その言葉だけで、力が湧いてくるの……</t>
+          <t xml:space="preserve">パーティー……っ……ふふ、今夜は思いっきり楽しませてもらうわ……</t>
         </is>
       </c>
     </row>
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.emotional.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7269,7 +7269,7 @@
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.emotional.seductive[1]</t>
+          <t xml:space="preserve">refresh_leave.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
@@ -7279,14 +7279,14 @@
       </c>
       <c r="F218" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">メディアに……っ……ふふ、わたしを世間に見せたいのね、いいわ……</t>
+          <t xml:space="preserve">休暇……っ……気を遣ってくれたのね、ふふ、嬉しいわ……</t>
         </is>
       </c>
     </row>
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.emotional.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7301,7 +7301,7 @@
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.emotional.seductive[1]</t>
+          <t xml:space="preserve">special_treatment.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
@@ -7311,14 +7311,14 @@
       </c>
       <c r="F219" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">パーティー……っ……ふふ、今夜は思いっきり楽しませてもらうわ……</t>
+          <t xml:space="preserve">そこまで…してくれるの…っ、嬉しい……早く戻るわ……</t>
         </is>
       </c>
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.emotional.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7333,7 +7333,7 @@
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.emotional.seductive[1]</t>
+          <t xml:space="preserve">trainer.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
@@ -7343,14 +7343,14 @@
       </c>
       <c r="F220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">休暇……っ……気を遣ってくれたのね、ふふ、嬉しいわ……</t>
+          <t xml:space="preserve">トレーナーをつけてくれるの……っ……ふふ、本気で育ててくれるのね……</t>
         </is>
       </c>
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.emotional.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7360,12 +7360,12 @@
       </c>
       <c r="C221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.emotional.seductive[1]</t>
+          <t xml:space="preserve">E1.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
@@ -7375,14 +7375,14 @@
       </c>
       <c r="F221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">そこまで…してくれるの…っ、嬉しい……早く戻るわ……</t>
+          <t xml:space="preserve">……っ……どうしようかしら、ふふ、迷っちゃうわね……</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.emotional.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="C222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.emotional.seductive[1]</t>
+          <t xml:space="preserve">E6.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
@@ -7407,14 +7407,14 @@
       </c>
       <c r="F222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">トレーナーをつけてくれるの……っ……ふふ、本気で育ててくれるのね……</t>
+          <t xml:space="preserve">いいわよ……っ……ふふ、やってみせるわ……</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.emotional.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7429,7 +7429,7 @@
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.emotional.seductive[1]</t>
+          <t xml:space="preserve">S_boycott.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
@@ -7439,14 +7439,14 @@
       </c>
       <c r="F223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……っ……どうしようかしら、ふふ、迷っちゃうわね……</t>
+          <t xml:space="preserve">……っ……これは認められないわ、悪いけど……</t>
         </is>
       </c>
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.emotional.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7461,7 +7461,7 @@
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.emotional.seductive[1]</t>
+          <t xml:space="preserve">S_grumble.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
@@ -7471,14 +7471,14 @@
       </c>
       <c r="F224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いいわよ……っ……ふふ、やってみせるわ……</t>
+          <t xml:space="preserve">正直に言うわね……っ……ちょっと不満なの……</t>
         </is>
       </c>
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.emotional.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7493,7 +7493,7 @@
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.emotional.seductive[1]</t>
+          <t xml:space="preserve">S_sns.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
@@ -7503,14 +7503,14 @@
       </c>
       <c r="F225" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……っ……これは認められないわ、悪いけど……</t>
+          <t xml:space="preserve">SNS見たわ……っ……ふふ、勝手な人たちね……</t>
         </is>
       </c>
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.emotional.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_grumble.emotional.seductive[1]</t>
+          <t xml:space="preserve">S1.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
@@ -7535,14 +7535,14 @@
       </c>
       <c r="F226" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">正直に言うわね……っ……ちょっと不満なの……</t>
+          <t xml:space="preserve">ねえ……っ……ちょっと、聞いてほしいの……</t>
         </is>
       </c>
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.emotional.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7557,7 +7557,7 @@
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_sns.emotional.seductive[1]</t>
+          <t xml:space="preserve">S2.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
@@ -7567,14 +7567,14 @@
       </c>
       <c r="F227" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">SNS見たわ……っ……ふふ、勝手な人たちね……</t>
+          <t xml:space="preserve">時間、ある……っ……ふふ、ちょっとだけ付き合って……</t>
         </is>
       </c>
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.emotional.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7589,7 +7589,7 @@
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.emotional.seductive[1]</t>
+          <t xml:space="preserve">S3.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
@@ -7599,14 +7599,14 @@
       </c>
       <c r="F228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ねえ……っ……ちょっと、聞いてほしいの……</t>
+          <t xml:space="preserve">……っ……どう答えるのが正解なのかしら、ふふ……</t>
         </is>
       </c>
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.emotional.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7621,7 +7621,7 @@
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.emotional.seductive[1]</t>
+          <t xml:space="preserve">S4_direct.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
@@ -7631,14 +7631,14 @@
       </c>
       <c r="F229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">時間、ある……っ……ふふ、ちょっとだけ付き合って……</t>
+          <t xml:space="preserve">はっきり言うわ……っ……わたしの気持ちは……</t>
         </is>
       </c>
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.emotional.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7653,7 +7653,7 @@
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.emotional.seductive[1]</t>
+          <t xml:space="preserve">S4_silent.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
@@ -7663,14 +7663,14 @@
       </c>
       <c r="F230" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……っ……どう答えるのが正解なのかしら、ふふ……</t>
+          <t xml:space="preserve">………っ……言葉にならないの……ふふ……</t>
         </is>
       </c>
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.emotional.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7685,7 +7685,7 @@
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.emotional.seductive[1]</t>
+          <t xml:space="preserve">S5.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
@@ -7695,14 +7695,14 @@
       </c>
       <c r="F231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">はっきり言うわ……っ……わたしの気持ちは……</t>
+          <t xml:space="preserve">少し考えさせて……っ……ふふ、すぐには決められないの……</t>
         </is>
       </c>
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.emotional.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7717,7 +7717,7 @@
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_silent.emotional.seductive[1]</t>
+          <t xml:space="preserve">S6.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
@@ -7727,14 +7727,14 @@
       </c>
       <c r="F232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………っ……言葉にならないの……ふふ……</t>
+          <t xml:space="preserve">決めたわ……っ……ふふ、これがわたしの答えよ……</t>
         </is>
       </c>
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.emotional.seductive[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="C233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.emotional.seductive[1]</t>
+          <t xml:space="preserve">B1.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
@@ -7759,14 +7759,14 @@
       </c>
       <c r="F233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">少し考えさせて……っ……ふふ、すぐには決められないの……</t>
+          <t xml:space="preserve">これから……っ……やりたいこと、いっぱいあるの……</t>
         </is>
       </c>
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.emotional.seductive[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7776,12 +7776,12 @@
       </c>
       <c r="C234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.emotional.seductive[1]</t>
+          <t xml:space="preserve">B2_fighter1.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
@@ -7791,14 +7791,14 @@
       </c>
       <c r="F234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決めたわ……っ……ふふ、これがわたしの答えよ……</t>
+          <t xml:space="preserve">ねえ……っ……ちょっと話、聞いてくれる？</t>
         </is>
       </c>
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.emotional.seductive[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7813,7 +7813,7 @@
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.emotional.seductive[1]</t>
+          <t xml:space="preserve">B2_fighter2.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
@@ -7823,14 +7823,14 @@
       </c>
       <c r="F235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">これから……っ……やりたいこと、いっぱいあるの……</t>
+          <t xml:space="preserve">いいわよ……っ……話してみて……</t>
         </is>
       </c>
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.emotional.seductive[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.emotional.seductive[1]</t>
+          <t xml:space="preserve">B4_brand.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
@@ -7855,14 +7855,14 @@
       </c>
       <c r="F236" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ねえ……っ……ちょっと話、聞いてくれる？</t>
+          <t xml:space="preserve">ブランドのお話……っ……ふふ、素敵ね……</t>
         </is>
       </c>
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.emotional.seductive[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -7877,7 +7877,7 @@
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.emotional.seductive[1]</t>
+          <t xml:space="preserve">B4_cm.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
@@ -7887,14 +7887,14 @@
       </c>
       <c r="F237" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いいわよ……っ……話してみて……</t>
+          <t xml:space="preserve">CMに出るの……っ……ふふ、世間に顔を売るチャンスね……</t>
         </is>
       </c>
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.emotional.seductive[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -7909,7 +7909,7 @@
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.emotional.seductive[1]</t>
+          <t xml:space="preserve">B4_fan.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
@@ -7919,14 +7919,14 @@
       </c>
       <c r="F238" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ブランドのお話……っ……ふふ、素敵ね……</t>
+          <t xml:space="preserve">ファンに会えるの……っ……ふふ、みんなに直接ありがとうって言えるのね……</t>
         </is>
       </c>
     </row>
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.emotional.seductive[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -7941,7 +7941,7 @@
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.emotional.seductive[1]</t>
+          <t xml:space="preserve">B4_fashion.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
@@ -7951,14 +7951,14 @@
       </c>
       <c r="F239" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">CMに出るの……っ……ふふ、世間に顔を売るチャンスね……</t>
+          <t xml:space="preserve">ファッションのお仕事……っ……ふふ、おしゃれするのは好きよ……</t>
         </is>
       </c>
     </row>
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.emotional.seductive[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -7973,7 +7973,7 @@
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.emotional.seductive[1]</t>
+          <t xml:space="preserve">B4_gravure.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
@@ -7983,14 +7983,14 @@
       </c>
       <c r="F240" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ファンに会えるの……っ……ふふ、みんなに直接ありがとうって言えるのね……</t>
+          <t xml:space="preserve">グラビア……っ……ふふ、見られるのは嫌いじゃないの……</t>
         </is>
       </c>
     </row>
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.emotional.seductive[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -8005,7 +8005,7 @@
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.emotional.seductive[1]</t>
+          <t xml:space="preserve">B4_variety.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
@@ -8015,14 +8015,14 @@
       </c>
       <c r="F241" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ファッションのお仕事……っ……ふふ、おしゃれするのは好きよ……</t>
+          <t xml:space="preserve">バラエティに出るの……っ……ふふ、楽しんでくるわね……</t>
         </is>
       </c>
     </row>
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.emotional.seductive[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8037,7 +8037,7 @@
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.emotional.seductive[1]</t>
+          <t xml:space="preserve">B4.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
@@ -8047,14 +8047,14 @@
       </c>
       <c r="F242" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">グラビア……っ……ふふ、見られるのは嫌いじゃないの……</t>
+          <t xml:space="preserve">このお仕事……っ……ふふ、面白そうね……</t>
         </is>
       </c>
     </row>
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.emotional.seductive[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8064,29 +8064,29 @@
       </c>
       <c r="C243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.emotional.seductive[1]</t>
+          <t xml:space="preserve">seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F243" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">バラエティに出るの……っ……ふふ、楽しんでくるわね……</t>
+          <t xml:space="preserve">選んでくれたら…全力で…全力でやるから…！</t>
         </is>
       </c>
     </row>
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.emotional.seductive[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8096,29 +8096,29 @@
       </c>
       <c r="C244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.emotional.seductive[1]</t>
+          <t xml:space="preserve">seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F244" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このお仕事……っ……ふふ、面白そうね……</t>
+          <t xml:space="preserve">…っ…夢みたい。精一杯頑張るわ…</t>
         </is>
       </c>
     </row>
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.emotional.seductive[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8128,12 +8128,12 @@
       </c>
       <c r="C245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.seductive[1]</t>
+          <t xml:space="preserve">seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
@@ -8143,14 +8143,14 @@
       </c>
       <c r="F245" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">選んでくれたら…全力で…全力でやるから…！</t>
+          <t xml:space="preserve">ありがとう…っ…嬉しい…。全力で、やるから…</t>
         </is>
       </c>
     </row>
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.emotional.seductive[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8160,12 +8160,12 @@
       </c>
       <c r="C246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.seductive[1]</t>
+          <t xml:space="preserve">seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
@@ -8175,14 +8175,14 @@
       </c>
       <c r="F246" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…夢みたい。精一杯頑張るわ…</t>
+          <t xml:space="preserve">嬉しい…っ…よろしくね…。頑張るから…</t>
         </is>
       </c>
     </row>
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.emotional.seductive[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8192,12 +8192,12 @@
       </c>
       <c r="C247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.seductive[1]</t>
+          <t xml:space="preserve">seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr" s="2">
@@ -8207,14 +8207,14 @@
       </c>
       <c r="F247" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとう…っ…嬉しい…。全力で、やるから…</t>
+          <t xml:space="preserve">…っ…悔しい…必ず戻ってやる…</t>
         </is>
       </c>
     </row>
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.emotional.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="C248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.seductive[1]</t>
+          <t xml:space="preserve">bitterPrematch.ahead.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E248" t="inlineStr" s="2">
@@ -8239,14 +8239,14 @@
       </c>
       <c r="F248" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">嬉しい…っ…よろしくね…。頑張るから…</t>
+          <t xml:space="preserve">済んだ話よ……っ……なのに、まだ手が震えるの</t>
         </is>
       </c>
     </row>
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.emotional.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8256,12 +8256,12 @@
       </c>
       <c r="C249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.seductive[1]</t>
+          <t xml:space="preserve">bitterPrematch.behind.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E249" t="inlineStr" s="2">
@@ -8271,14 +8271,14 @@
       </c>
       <c r="F249" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…悔しい…必ず戻ってやる…</t>
+          <t xml:space="preserve">終わったの……？ ……嘘よ。まだ、疼いてる</t>
         </is>
       </c>
     </row>
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.emotional.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.ahead.emotional.seductive[1]</t>
+          <t xml:space="preserve">draftInterest.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
@@ -8303,14 +8303,14 @@
       </c>
       <c r="F250" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">済んだ話よ……っ……なのに、まだ手が震えるの</t>
+          <t xml:space="preserve">選んでくれたら…全力で…全力でやるから…！</t>
         </is>
       </c>
     </row>
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.emotional.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8325,7 +8325,7 @@
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.behind.emotional.seductive[1]</t>
+          <t xml:space="preserve">draftJoin.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
@@ -8335,14 +8335,14 @@
       </c>
       <c r="F251" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">終わったの……？ ……嘘よ。まだ、疼いてる</t>
+          <t xml:space="preserve">…っ…夢みたい。精一杯頑張るわ…</t>
         </is>
       </c>
     </row>
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.emotional.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8357,7 +8357,7 @@
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.emotional.seductive[1]</t>
+          <t xml:space="preserve">faGreeting.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
@@ -8367,14 +8367,14 @@
       </c>
       <c r="F252" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">選んでくれたら…全力で…全力でやるから…！</t>
+          <t xml:space="preserve">拾われる側になるなんて…っ…参ったわ</t>
         </is>
       </c>
     </row>
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.emotional.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8389,7 +8389,7 @@
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.emotional.seductive[1]</t>
+          <t xml:space="preserve">faSigning.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
@@ -8399,14 +8399,14 @@
       </c>
       <c r="F253" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…夢みたい。精一杯頑張るわ…</t>
+          <t xml:space="preserve">ありがとう…っ…嬉しい…。全力で、やるから…</t>
         </is>
       </c>
     </row>
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.emotional.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8421,7 +8421,7 @@
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.emotional.seductive[1]</t>
+          <t xml:space="preserve">faWelcome.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
@@ -8431,14 +8431,14 @@
       </c>
       <c r="F254" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">拾われる側になるなんて…っ…参ったわ</t>
+          <t xml:space="preserve">嬉しい…っ…よろしくね…。頑張るから…</t>
         </is>
       </c>
     </row>
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.emotional.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8453,7 +8453,7 @@
       </c>
       <c r="D255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.emotional.seductive[1]</t>
+          <t xml:space="preserve">injury.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E255" t="inlineStr" s="2">
@@ -8463,14 +8463,14 @@
       </c>
       <c r="F255" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとう…っ…嬉しい…。全力で、やるから…</t>
+          <t xml:space="preserve">…っ…悔しい…必ず戻ってやる…</t>
         </is>
       </c>
     </row>
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.emotional.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8485,7 +8485,7 @@
       </c>
       <c r="D256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.emotional.seductive[1]</t>
+          <t xml:space="preserve">release.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E256" t="inlineStr" s="2">
@@ -8495,14 +8495,14 @@
       </c>
       <c r="F256" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">嬉しい…っ…よろしくね…。頑張るから…</t>
+          <t xml:space="preserve">…っ…ありがとう…忘れないわ…</t>
         </is>
       </c>
     </row>
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.emotional.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8517,7 +8517,7 @@
       </c>
       <c r="D257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.emotional.seductive[1]</t>
+          <t xml:space="preserve">rentalGreeting.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E257" t="inlineStr" s="2">
@@ -8527,14 +8527,14 @@
       </c>
       <c r="F257" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…悔しい…必ず戻ってやる…</t>
+          <t xml:space="preserve">よろしくね…っ…短い間だけど…全力で、やるから…</t>
         </is>
       </c>
     </row>
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.emotional.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="D258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.emotional.seductive[1]</t>
+          <t xml:space="preserve">scoutGreeting.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E258" t="inlineStr" s="2">
@@ -8559,14 +8559,14 @@
       </c>
       <c r="F258" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…ありがとう…忘れないわ…</t>
+          <t xml:space="preserve">うふふ♪嬉しい♪</t>
         </is>
       </c>
     </row>
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.emotional.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8581,7 +8581,7 @@
       </c>
       <c r="D259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.emotional.seductive[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E259" t="inlineStr" s="2">
@@ -8591,14 +8591,14 @@
       </c>
       <c r="F259" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくね…っ…短い間だけど…全力で、やるから…</t>
+          <t xml:space="preserve">悔しい…っ…悔しい…。でも…絶対に、諦めない…</t>
         </is>
       </c>
     </row>
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.emotional.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8613,7 +8613,7 @@
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.emotional.seductive[1]</t>
+          <t xml:space="preserve">titleDefense.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E260" t="inlineStr" s="2">
@@ -8623,14 +8623,14 @@
       </c>
       <c r="F260" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うふふ♪嬉しい♪</t>
+          <t xml:space="preserve">守れた…っ…嬉しい…。次も、絶対に守るから…</t>
         </is>
       </c>
     </row>
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.emotional.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8645,7 +8645,7 @@
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.emotional.seductive[1]</t>
+          <t xml:space="preserve">titleLoss.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
@@ -8655,14 +8655,14 @@
       </c>
       <c r="F261" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しい…っ…悔しい…。でも…絶対に、諦めない…</t>
+          <t xml:space="preserve">嘘…っ…ベルトが…。でも…でも、諦めない…</t>
         </is>
       </c>
     </row>
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.emotional.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8677,7 +8677,7 @@
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.emotional.seductive[1]</t>
+          <t xml:space="preserve">titleWin.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E262" t="inlineStr" s="2">
@@ -8687,14 +8687,14 @@
       </c>
       <c r="F262" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">守れた…っ…嬉しい…。次も、絶対に守るから…</t>
+          <t xml:space="preserve">ああ…っ…チャンピオン…。嬉しい…だめ、泣いちゃう…</t>
         </is>
       </c>
     </row>
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.emotional.seductive[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8704,12 +8704,12 @@
       </c>
       <c r="C263" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.emotional.seductive[1]</t>
+          <t xml:space="preserve">seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E263" t="inlineStr" s="2">
@@ -8719,14 +8719,14 @@
       </c>
       <c r="F263" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">嘘…っ…ベルトが…。でも…でも、諦めない…</t>
+          <t xml:space="preserve">…っ…ありがとう…忘れないわ…</t>
         </is>
       </c>
     </row>
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.emotional.seductive[1]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8736,12 +8736,12 @@
       </c>
       <c r="C264" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.emotional.seductive[1]</t>
+          <t xml:space="preserve">seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E264" t="inlineStr" s="2">
@@ -8751,14 +8751,14 @@
       </c>
       <c r="F264" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ああ…っ…チャンピオン…。嬉しい…だめ、泣いちゃう…</t>
+          <t xml:space="preserve">よろしくね…っ…短い間だけど…全力で、やるから…</t>
         </is>
       </c>
     </row>
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.emotional.seductive[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="C265" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.seductive[1]</t>
+          <t xml:space="preserve">seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E265" t="inlineStr" s="2">
@@ -8783,14 +8783,14 @@
       </c>
       <c r="F265" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…ありがとう…忘れないわ…</t>
+          <t xml:space="preserve">悔しい…っ…悔しい…。でも…絶対に、諦めない…</t>
         </is>
       </c>
     </row>
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.emotional.seductive[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8800,12 +8800,12 @@
       </c>
       <c r="C266" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.seductive[1]</t>
+          <t xml:space="preserve">seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E266" t="inlineStr" s="2">
@@ -8815,14 +8815,14 @@
       </c>
       <c r="F266" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくね…っ…短い間だけど…全力で、やるから…</t>
+          <t xml:space="preserve">守れた…っ…嬉しい…。次も、絶対に守るから…</t>
         </is>
       </c>
     </row>
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.emotional.seductive[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -8832,12 +8832,12 @@
       </c>
       <c r="C267" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.seductive[1]</t>
+          <t xml:space="preserve">seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E267" t="inlineStr" s="2">
@@ -8847,14 +8847,14 @@
       </c>
       <c r="F267" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しい…っ…悔しい…。でも…絶対に、諦めない…</t>
+          <t xml:space="preserve">嘘…っ…ベルトが…。でも…でも、諦めない…</t>
         </is>
       </c>
     </row>
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.emotional.seductive[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -8864,12 +8864,12 @@
       </c>
       <c r="C268" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D268" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.seductive[1]</t>
+          <t xml:space="preserve">seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E268" t="inlineStr" s="2">
@@ -8879,14 +8879,14 @@
       </c>
       <c r="F268" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">守れた…っ…嬉しい…。次も、絶対に守るから…</t>
+          <t xml:space="preserve">ああ…っ…チャンピオン…。嬉しい…だめ、泣いちゃう…</t>
         </is>
       </c>
     </row>
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.emotional.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -8896,29 +8896,29 @@
       </c>
       <c r="C269" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D269" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.seductive[1]</t>
+          <t xml:space="preserve">bond_39_down.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E269" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F269" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">嘘…っ…ベルトが…。でも…でも、諦めない…</t>
+          <t xml:space="preserve">考えると苦しいの…もう無理…</t>
         </is>
       </c>
     </row>
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.emotional.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -8928,29 +8928,29 @@
       </c>
       <c r="C270" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D270" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.seductive[1]</t>
+          <t xml:space="preserve">bond_59_down.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E270" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F270" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ああ…っ…チャンピオン…。嬉しい…だめ、泣いちゃう…</t>
+          <t xml:space="preserve">離れていく…嫌よ…こんなの…</t>
         </is>
       </c>
     </row>
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.emotional.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.emotional.seductive[2]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -8965,7 +8965,7 @@
       </c>
       <c r="D271" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.emotional.seductive[1]</t>
+          <t xml:space="preserve">bond_59_down.emotional.seductive[2]</t>
         </is>
       </c>
       <c r="E271" t="inlineStr" s="2">
@@ -8975,14 +8975,14 @@
       </c>
       <c r="F271" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">考えると苦しいの…もう無理…</t>
+          <t xml:space="preserve">どうして…以前のように言葉をくれないの…</t>
         </is>
       </c>
     </row>
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.emotional.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -8997,7 +8997,7 @@
       </c>
       <c r="D272" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.emotional.seductive[1]</t>
+          <t xml:space="preserve">bond_60_up.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E272" t="inlineStr" s="2">
@@ -9007,14 +9007,14 @@
       </c>
       <c r="F272" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">離れていく…嫌よ…こんなの…</t>
+          <t xml:space="preserve">放っておけないの…もう</t>
         </is>
       </c>
     </row>
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.emotional.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -9029,7 +9029,7 @@
       </c>
       <c r="D273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.emotional.seductive[2]</t>
+          <t xml:space="preserve">bond_80_up.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E273" t="inlineStr" s="2">
@@ -9039,14 +9039,14 @@
       </c>
       <c r="F273" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">どうして…以前のように言葉をくれないの…</t>
+          <t xml:space="preserve">この人のためなら何でもできるの…！ 絶対に守るわ…！</t>
         </is>
       </c>
     </row>
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.emotional.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.emotional.seductive[2]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -9061,7 +9061,7 @@
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.emotional.seductive[1]</t>
+          <t xml:space="preserve">bond_80_up.emotional.seductive[2]</t>
         </is>
       </c>
       <c r="E274" t="inlineStr" s="2">
@@ -9071,14 +9071,14 @@
       </c>
       <c r="F274" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">放っておけないの…もう</t>
+          <t xml:space="preserve">巡り合えたこと、心から幸せなの…！</t>
         </is>
       </c>
     </row>
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.emotional.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -9093,7 +9093,7 @@
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.emotional.seductive[1]</t>
+          <t xml:space="preserve">rivalry_29_down.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E275" t="inlineStr" s="2">
@@ -9103,14 +9103,14 @@
       </c>
       <c r="F275" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この人のためなら何でもできるの…！ 絶対に守るわ…！</t>
+          <t xml:space="preserve">因縁…終わっちゃったのね…少し寂しい…</t>
         </is>
       </c>
     </row>
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.emotional.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.emotional.seductive[2]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -9125,7 +9125,7 @@
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.emotional.seductive[2]</t>
+          <t xml:space="preserve">rivalry_29_down.emotional.seductive[2]</t>
         </is>
       </c>
       <c r="E276" t="inlineStr" s="2">
@@ -9135,14 +9135,14 @@
       </c>
       <c r="F276" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">巡り合えたこと、心から幸せなの…！</t>
+          <t xml:space="preserve">……あの熱さが消えていくわ。これでいいのかしら…</t>
         </is>
       </c>
     </row>
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.emotional.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9157,7 +9157,7 @@
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.emotional.seductive[1]</t>
+          <t xml:space="preserve">rivalry_30_up.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="2">
@@ -9167,14 +9167,14 @@
       </c>
       <c r="F277" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">因縁…終わっちゃったのね…少し寂しい…</t>
+          <t xml:space="preserve">絶対に負けないわ…！ 絶対に…！</t>
         </is>
       </c>
     </row>
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.emotional.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.emotional.seductive[2]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9189,7 +9189,7 @@
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.emotional.seductive[2]</t>
+          <t xml:space="preserve">rivalry_30_up.emotional.seductive[2]</t>
         </is>
       </c>
       <c r="E278" t="inlineStr" s="2">
@@ -9199,14 +9199,14 @@
       </c>
       <c r="F278" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……あの熱さが消えていくわ。これでいいのかしら…</t>
+          <t xml:space="preserve">考えるだけで胸が熱くなるの…！</t>
         </is>
       </c>
     </row>
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.emotional.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9221,7 +9221,7 @@
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.emotional.seductive[1]</t>
+          <t xml:space="preserve">rivalry_50_up.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E279" t="inlineStr" s="2">
@@ -9231,14 +9231,14 @@
       </c>
       <c r="F279" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">絶対に負けないわ…！ 絶対に…！</t>
+          <t xml:space="preserve">くっ…考えると熱くなるの…！</t>
         </is>
       </c>
     </row>
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.emotional.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.emotional.seductive[2]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9253,7 +9253,7 @@
       </c>
       <c r="D280" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.emotional.seductive[2]</t>
+          <t xml:space="preserve">rivalry_50_up.emotional.seductive[2]</t>
         </is>
       </c>
       <c r="E280" t="inlineStr" s="2">
@@ -9263,14 +9263,14 @@
       </c>
       <c r="F280" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">考えるだけで胸が熱くなるの…！</t>
+          <t xml:space="preserve">絶対に…超えてみせるわ…！！</t>
         </is>
       </c>
     </row>
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.emotional.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9285,7 +9285,7 @@
       </c>
       <c r="D281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.emotional.seductive[1]</t>
+          <t xml:space="preserve">rivalry_70_up.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E281" t="inlineStr" s="2">
@@ -9295,14 +9295,14 @@
       </c>
       <c r="F281" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くっ…考えると熱くなるの…！</t>
+          <t xml:space="preserve">あの出会いがなければ今の私はいなかった…！</t>
         </is>
       </c>
     </row>
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.emotional.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.emotional.seductive[2]</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -9317,7 +9317,7 @@
       </c>
       <c r="D282" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.emotional.seductive[2]</t>
+          <t xml:space="preserve">rivalry_70_up.emotional.seductive[2]</t>
         </is>
       </c>
       <c r="E282" t="inlineStr" s="2">
@@ -9327,14 +9327,14 @@
       </c>
       <c r="F282" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">絶対に…超えてみせるわ…！！</t>
+          <t xml:space="preserve">この因縁に終わりなんてないわ…！ 永遠に戦い続けるの…！</t>
         </is>
       </c>
     </row>
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.emotional.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -9349,7 +9349,7 @@
       </c>
       <c r="D283" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.emotional.seductive[1]</t>
+          <t xml:space="preserve">trust_above_75.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E283" t="inlineStr" s="2">
@@ -9359,14 +9359,14 @@
       </c>
       <c r="F283" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの出会いがなければ今の私はいなかった…！</t>
+          <t xml:space="preserve">みんなのこと…大好きよ…！ この団体のために全力を尽くすわ…！</t>
         </is>
       </c>
     </row>
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.emotional.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.emotional.seductive[2]</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -9381,7 +9381,7 @@
       </c>
       <c r="D284" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.emotional.seductive[2]</t>
+          <t xml:space="preserve">trust_above_75.emotional.seductive[2]</t>
         </is>
       </c>
       <c r="E284" t="inlineStr" s="2">
@@ -9391,14 +9391,14 @@
       </c>
       <c r="F284" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この因縁に終わりなんてないわ…！ 永遠に戦い続けるの…！</t>
+          <t xml:space="preserve">ここで出会えた仲間は宝物なの…絶対に裏切らないわ…！</t>
         </is>
       </c>
     </row>
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.emotional.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -9413,7 +9413,7 @@
       </c>
       <c r="D285" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.emotional.seductive[1]</t>
+          <t xml:space="preserve">trust_below_20.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E285" t="inlineStr" s="2">
@@ -9423,14 +9423,14 @@
       </c>
       <c r="F285" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みんなのこと…大好きよ…！ この団体のために全力を尽くすわ…！</t>
+          <t xml:space="preserve">もう…信じられないわ…！ どうして…！</t>
         </is>
       </c>
     </row>
     <row r="286" ht="40" customHeight="1">
       <c r="A286" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.emotional.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.emotional.seductive[2]</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -9445,7 +9445,7 @@
       </c>
       <c r="D286" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.emotional.seductive[2]</t>
+          <t xml:space="preserve">trust_below_20.emotional.seductive[2]</t>
         </is>
       </c>
       <c r="E286" t="inlineStr" s="2">
@@ -9455,14 +9455,14 @@
       </c>
       <c r="F286" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここで出会えた仲間は宝物なの…絶対に裏切らないわ…！</t>
+          <t xml:space="preserve">裏切られたのね…全部…偽りだったの…？</t>
         </is>
       </c>
     </row>
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.emotional.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -9477,7 +9477,7 @@
       </c>
       <c r="D287" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.emotional.seductive[1]</t>
+          <t xml:space="preserve">trust_below_35.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E287" t="inlineStr" s="2">
@@ -9487,14 +9487,14 @@
       </c>
       <c r="F287" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう…信じられないわ…！ どうして…！</t>
+          <t xml:space="preserve">不安なの…これでいいのかしら…？ 私、忘れられてない…？</t>
         </is>
       </c>
     </row>
     <row r="288" ht="40" customHeight="1">
       <c r="A288" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.emotional.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
@@ -9504,12 +9504,12 @@
       </c>
       <c r="C288" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D288" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.emotional.seductive[2]</t>
+          <t xml:space="preserve">GL-01.goodLoss.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E288" t="inlineStr" s="2">
@@ -9519,14 +9519,14 @@
       </c>
       <c r="F288" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">裏切られたのね…全部…偽りだったの…？</t>
+          <t xml:space="preserve">負けたけど……っ……ふふ、出し切れたの……</t>
         </is>
       </c>
     </row>
     <row r="289" ht="40" customHeight="1">
       <c r="A289" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.emotional.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
@@ -9536,12 +9536,12 @@
       </c>
       <c r="C289" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D289" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.emotional.seductive[1]</t>
+          <t xml:space="preserve">GL-01.greatWin.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E289" t="inlineStr" s="2">
@@ -9551,14 +9551,14 @@
       </c>
       <c r="F289" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">不安なの…これでいいのかしら…？ 私、忘れられてない…？</t>
+          <t xml:space="preserve">最高の勝利……っ……ふふ、震えてるの……</t>
         </is>
       </c>
     </row>
     <row r="290" ht="40" customHeight="1">
       <c r="A290" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.emotional.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
@@ -9573,7 +9573,7 @@
       </c>
       <c r="D290" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.goodLoss.emotional.seductive[1]</t>
+          <t xml:space="preserve">GL-01.loss.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E290" t="inlineStr" s="2">
@@ -9583,14 +9583,14 @@
       </c>
       <c r="F290" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けたけど……っ……ふふ、出し切れたの……</t>
+          <t xml:space="preserve">負けた……っ……悔しい……</t>
         </is>
       </c>
     </row>
     <row r="291" ht="40" customHeight="1">
       <c r="A291" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.emotional.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
@@ -9605,7 +9605,7 @@
       </c>
       <c r="D291" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.greatWin.emotional.seductive[1]</t>
+          <t xml:space="preserve">GL-01.win.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E291" t="inlineStr" s="2">
@@ -9615,14 +9615,14 @@
       </c>
       <c r="F291" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高の勝利……っ……ふふ、震えてるの……</t>
+          <t xml:space="preserve">勝ったわ……っ……ふふ、嬉しい……</t>
         </is>
       </c>
     </row>
     <row r="292" ht="40" customHeight="1">
       <c r="A292" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.emotional.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
@@ -9637,7 +9637,7 @@
       </c>
       <c r="D292" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.loss.emotional.seductive[1]</t>
+          <t xml:space="preserve">GL-02.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E292" t="inlineStr" s="2">
@@ -9647,14 +9647,14 @@
       </c>
       <c r="F292" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けた……っ……悔しい……</t>
+          <t xml:space="preserve">今日は……っ……ふふ、よろしくね……</t>
         </is>
       </c>
     </row>
     <row r="293" ht="40" customHeight="1">
       <c r="A293" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.emotional.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
@@ -9669,7 +9669,7 @@
       </c>
       <c r="D293" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.win.emotional.seductive[1]</t>
+          <t xml:space="preserve">GL-03.down.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E293" t="inlineStr" s="2">
@@ -9679,14 +9679,14 @@
       </c>
       <c r="F293" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ったわ……っ……ふふ、嬉しい……</t>
+          <t xml:space="preserve">うまくいかない……っ……どうしてかしら……</t>
         </is>
       </c>
     </row>
     <row r="294" ht="40" customHeight="1">
       <c r="A294" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.emotional.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
@@ -9701,7 +9701,7 @@
       </c>
       <c r="D294" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.emotional.seductive[1]</t>
+          <t xml:space="preserve">GL-03.up.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E294" t="inlineStr" s="2">
@@ -9711,14 +9711,14 @@
       </c>
       <c r="F294" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日は……っ……ふふ、よろしくね……</t>
+          <t xml:space="preserve">なんだか調子いいの……っ……ふふ……</t>
         </is>
       </c>
     </row>
     <row r="295" ht="40" customHeight="1">
       <c r="A295" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.emotional.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="2">
@@ -9733,7 +9733,7 @@
       </c>
       <c r="D295" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.down.emotional.seductive[1]</t>
+          <t xml:space="preserve">GL-04.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E295" t="inlineStr" s="2">
@@ -9743,14 +9743,14 @@
       </c>
       <c r="F295" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うまくいかない……っ……どうしてかしら……</t>
+          <t xml:space="preserve">練習するわ……っ……ふふ……</t>
         </is>
       </c>
     </row>
     <row r="296" ht="40" customHeight="1">
       <c r="A296" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.emotional.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B296" t="inlineStr" s="2">
@@ -9765,7 +9765,7 @@
       </c>
       <c r="D296" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.up.emotional.seductive[1]</t>
+          <t xml:space="preserve">GL-05.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E296" t="inlineStr" s="2">
@@ -9775,14 +9775,14 @@
       </c>
       <c r="F296" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">なんだか調子いいの……っ……ふふ……</t>
+          <t xml:space="preserve">大丈夫よ……っ……ふふ、心配しないで……</t>
         </is>
       </c>
     </row>
     <row r="297" ht="40" customHeight="1">
       <c r="A297" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.emotional.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B297" t="inlineStr" s="2">
@@ -9797,7 +9797,7 @@
       </c>
       <c r="D297" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-04.emotional.seductive[1]</t>
+          <t xml:space="preserve">GL-06.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E297" t="inlineStr" s="2">
@@ -9807,14 +9807,14 @@
       </c>
       <c r="F297" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習するわ……っ……ふふ……</t>
+          <t xml:space="preserve">みんなと一緒だと……っ……ふふ、安心するの……</t>
         </is>
       </c>
     </row>
     <row r="298" ht="40" customHeight="1">
       <c r="A298" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.emotional.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B298" t="inlineStr" s="2">
@@ -9829,7 +9829,7 @@
       </c>
       <c r="D298" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-05.emotional.seductive[1]</t>
+          <t xml:space="preserve">GL-07.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E298" t="inlineStr" s="2">
@@ -9839,14 +9839,14 @@
       </c>
       <c r="F298" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">大丈夫よ……っ……ふふ、心配しないで……</t>
+          <t xml:space="preserve">お客さんがいっぱい……っ……ふふ、燃えるわね……</t>
         </is>
       </c>
     </row>
     <row r="299" ht="40" customHeight="1">
       <c r="A299" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.emotional.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B299" t="inlineStr" s="2">
@@ -9861,7 +9861,7 @@
       </c>
       <c r="D299" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.emotional.seductive[1]</t>
+          <t xml:space="preserve">GL-08.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E299" t="inlineStr" s="2">
@@ -9871,14 +9871,14 @@
       </c>
       <c r="F299" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みんなと一緒だと……っ……ふふ、安心するの……</t>
+          <t xml:space="preserve">体調は大丈夫よ……っ……ふふ、心配いらない……</t>
         </is>
       </c>
     </row>
     <row r="300" ht="40" customHeight="1">
       <c r="A300" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.emotional.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B300" t="inlineStr" s="2">
@@ -9893,7 +9893,7 @@
       </c>
       <c r="D300" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-07.emotional.seductive[1]</t>
+          <t xml:space="preserve">GL-09.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E300" t="inlineStr" s="2">
@@ -9903,14 +9903,14 @@
       </c>
       <c r="F300" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お客さんがいっぱい……っ……ふふ、燃えるわね……</t>
+          <t xml:space="preserve">次の試合……っ……ふふ、楽しみだわ……</t>
         </is>
       </c>
     </row>
     <row r="301" ht="40" customHeight="1">
       <c r="A301" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.emotional.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B301" t="inlineStr" s="2">
@@ -9925,7 +9925,7 @@
       </c>
       <c r="D301" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.emotional.seductive[1]</t>
+          <t xml:space="preserve">GL-10.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E301" t="inlineStr" s="2">
@@ -9935,14 +9935,14 @@
       </c>
       <c r="F301" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">体調は大丈夫よ……っ……ふふ、心配いらない……</t>
+          <t xml:space="preserve">ありがとう……っ……ふふ、嬉しい……</t>
         </is>
       </c>
     </row>
     <row r="302" ht="40" customHeight="1">
       <c r="A302" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.emotional.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B302" t="inlineStr" s="2">
@@ -9952,12 +9952,12 @@
       </c>
       <c r="C302" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D302" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-09.emotional.seductive[1]</t>
+          <t xml:space="preserve">seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E302" t="inlineStr" s="2">
@@ -9967,14 +9967,14 @@
       </c>
       <c r="F302" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次の試合……っ……ふふ、楽しみだわ……</t>
+          <t xml:space="preserve">勢いが止まったわ……っ……ふふ、また始めればいいのよ……</t>
         </is>
       </c>
     </row>
     <row r="303" ht="40" customHeight="1">
       <c r="A303" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.emotional.seductive[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B303" t="inlineStr" s="2">
@@ -9984,29 +9984,29 @@
       </c>
       <c r="C303" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D303" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.emotional.seductive[1]</t>
+          <t xml:space="preserve">preFinal.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E303" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F303" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとう……っ……ふふ、嬉しい……</t>
+          <t xml:space="preserve">身体、もう震えてるの…っ…ふふ、でも最後まで立つわ</t>
         </is>
       </c>
     </row>
     <row r="304" ht="40" customHeight="1">
       <c r="A304" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.emotional.seductive[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B304" t="inlineStr" s="2">
@@ -10016,29 +10016,29 @@
       </c>
       <c r="C304" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D304" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.seductive[1]</t>
+          <t xml:space="preserve">preFinal.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E304" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F304" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勢いが止まったわ……っ……ふふ、また始めればいいのよ……</t>
+          <t xml:space="preserve">ここまで来たのね…っ…最後の舞台、全部ぶつけるわ</t>
         </is>
       </c>
     </row>
     <row r="305" ht="40" customHeight="1">
       <c r="A305" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.emotional.seductive[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B305" t="inlineStr" s="2">
@@ -10053,7 +10053,7 @@
       </c>
       <c r="D305" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.emotional.seductive[1]</t>
+          <t xml:space="preserve">preMatch.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E305" t="inlineStr" s="2">
@@ -10063,14 +10063,14 @@
       </c>
       <c r="F305" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">身体、もう震えてるの…っ…ふふ、でも最後まで立つわ</t>
+          <t xml:space="preserve">お相手は誰かしら…っ…ふふ、もう身体が疼いてるの</t>
         </is>
       </c>
     </row>
     <row r="306" ht="40" customHeight="1">
       <c r="A306" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.emotional.seductive[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B306" t="inlineStr" s="2">
@@ -10085,7 +10085,7 @@
       </c>
       <c r="D306" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.emotional.seductive[2]</t>
+          <t xml:space="preserve">preMatch.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E306" t="inlineStr" s="2">
@@ -10095,14 +10095,14 @@
       </c>
       <c r="F306" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで来たのね…っ…最後の舞台、全部ぶつけるわ</t>
+          <t xml:space="preserve">早く来てよ…! この昂り、ぶつける相手が欲しいの…!</t>
         </is>
       </c>
     </row>
     <row r="307" ht="40" customHeight="1">
       <c r="A307" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.emotional.seductive[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B307" t="inlineStr" s="2">
@@ -10117,7 +10117,7 @@
       </c>
       <c r="D307" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.emotional.seductive[1]</t>
+          <t xml:space="preserve">survivor.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E307" t="inlineStr" s="2">
@@ -10127,14 +10127,14 @@
       </c>
       <c r="F307" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お相手は誰かしら…っ…ふふ、もう身体が疼いてるの</t>
+          <t xml:space="preserve">一人、落としたわ…っ…はぁ…まだ疼いてるの。次、早く出してよ</t>
         </is>
       </c>
     </row>
     <row r="308" ht="40" customHeight="1">
       <c r="A308" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.emotional.seductive[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B308" t="inlineStr" s="2">
@@ -10149,7 +10149,7 @@
       </c>
       <c r="D308" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.emotional.seductive[2]</t>
+          <t xml:space="preserve">survivor.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E308" t="inlineStr" s="2">
@@ -10159,14 +10159,14 @@
       </c>
       <c r="F308" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">早く来てよ…! この昂り、ぶつける相手が欲しいの…!</t>
+          <t xml:space="preserve">まだ立ってる…! この身体、まだ終わってないの…! 次、来なさい…!</t>
         </is>
       </c>
     </row>
     <row r="309" ht="40" customHeight="1">
       <c r="A309" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.emotional.seductive[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B309" t="inlineStr" s="2">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="C309" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D309" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.emotional.seductive[1]</t>
+          <t xml:space="preserve">champion.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E309" t="inlineStr" s="2">
@@ -10191,14 +10191,14 @@
       </c>
       <c r="F309" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人、落としたわ…っ…はぁ…まだ疼いてるの。次、早く出してよ</t>
+          <t xml:space="preserve">三人で勝ったの……！ この感動は……一人じゃ味わえないわ……</t>
         </is>
       </c>
     </row>
     <row r="310" ht="40" customHeight="1">
       <c r="A310" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.emotional.seductive[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B310" t="inlineStr" s="2">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="C310" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D310" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.emotional.seductive[2]</t>
+          <t xml:space="preserve">champion.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E310" t="inlineStr" s="2">
@@ -10223,14 +10223,14 @@
       </c>
       <c r="F310" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ立ってる…! この身体、まだ終わってないの…! 次、来なさい…!</t>
+          <t xml:space="preserve">仲間が繋いでくれた想い……最後まで、手放さなかったよ……！</t>
         </is>
       </c>
     </row>
     <row r="311" ht="40" customHeight="1">
       <c r="A311" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.emotional.seductive[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B311" t="inlineStr" s="2">
@@ -10245,7 +10245,7 @@
       </c>
       <c r="D311" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.emotional.seductive[1]</t>
+          <t xml:space="preserve">defiant.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E311" t="inlineStr" s="2">
@@ -10255,14 +10255,14 @@
       </c>
       <c r="F311" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">三人で勝ったの……！ この感動は……一人じゃ味わえないわ……</t>
+          <t xml:space="preserve">この賞じゃ……心は満たされないのよ……！ 次は全部、奪い返すから……</t>
         </is>
       </c>
     </row>
     <row r="312" ht="40" customHeight="1">
       <c r="A312" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.emotional.seductive[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B312" t="inlineStr" s="2">
@@ -10277,7 +10277,7 @@
       </c>
       <c r="D312" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.emotional.seductive[2]</t>
+          <t xml:space="preserve">defiant.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E312" t="inlineStr" s="2">
@@ -10287,14 +10287,14 @@
       </c>
       <c r="F312" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲間が繋いでくれた想い……最後まで、手放さなかったよ……！</t>
+          <t xml:space="preserve">一人で輝いても寂しいだけ……！ 次は……三人で、ね……！</t>
         </is>
       </c>
     </row>
     <row r="313" ht="40" customHeight="1">
       <c r="A313" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.emotional.seductive[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B313" t="inlineStr" s="2">
@@ -10309,7 +10309,7 @@
       </c>
       <c r="D313" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.emotional.seductive[1]</t>
+          <t xml:space="preserve">gauntlet.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E313" t="inlineStr" s="2">
@@ -10319,14 +10319,14 @@
       </c>
       <c r="F313" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この賞じゃ……心は満たされないのよ……！ 次は全部、奪い返すから……</t>
+          <t xml:space="preserve">もう身体が動かない……でも、最後に立ってたのは私よ……！ 見届けてくれた？</t>
         </is>
       </c>
     </row>
     <row r="314" ht="40" customHeight="1">
       <c r="A314" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.emotional.seductive[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B314" t="inlineStr" s="2">
@@ -10341,7 +10341,7 @@
       </c>
       <c r="D314" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.emotional.seductive[2]</t>
+          <t xml:space="preserve">gauntlet.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E314" t="inlineStr" s="2">
@@ -10351,14 +10351,14 @@
       </c>
       <c r="F314" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人で輝いても寂しいだけ……！ 次は……三人で、ね……！</t>
+          <t xml:space="preserve">何人来ても倒れなかった……！ この身体が、全部証明してるでしょ……？</t>
         </is>
       </c>
     </row>
     <row r="315" ht="40" customHeight="1">
       <c r="A315" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.emotional.seductive[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B315" t="inlineStr" s="2">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="C315" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D315" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.emotional.seductive[1]</t>
+          <t xml:space="preserve">champion.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E315" t="inlineStr" s="2">
@@ -10383,14 +10383,14 @@
       </c>
       <c r="F315" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう身体が動かない……でも、最後に立ってたのは私よ……！ 見届けてくれた？</t>
+          <t xml:space="preserve">優勝……っ……ふふ、わたし、頂点に立ったのね……!</t>
         </is>
       </c>
     </row>
     <row r="316" ht="40" customHeight="1">
       <c r="A316" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.emotional.seductive[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B316" t="inlineStr" s="2">
@@ -10400,12 +10400,12 @@
       </c>
       <c r="C316" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D316" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.emotional.seductive[2]</t>
+          <t xml:space="preserve">champion.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E316" t="inlineStr" s="2">
@@ -10415,14 +10415,14 @@
       </c>
       <c r="F316" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何人来ても倒れなかった……！ この身体が、全部証明してるでしょ……？</t>
+          <t xml:space="preserve">この景色……っ……ふふ、忘れないわ……</t>
         </is>
       </c>
     </row>
     <row r="317" ht="40" customHeight="1">
       <c r="A317" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.emotional.seductive[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B317" t="inlineStr" s="2">
@@ -10437,7 +10437,7 @@
       </c>
       <c r="D317" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.emotional.seductive[1]</t>
+          <t xml:space="preserve">postLose.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E317" t="inlineStr" s="2">
@@ -10447,14 +10447,14 @@
       </c>
       <c r="F317" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">優勝……っ……ふふ、わたし、頂点に立ったのね……!</t>
+          <t xml:space="preserve">負けたわ……っ……悔しい……でも、いい経験だった……</t>
         </is>
       </c>
     </row>
     <row r="318" ht="40" customHeight="1">
       <c r="A318" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.emotional.seductive[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B318" t="inlineStr" s="2">
@@ -10469,7 +10469,7 @@
       </c>
       <c r="D318" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.emotional.seductive[2]</t>
+          <t xml:space="preserve">postLose.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E318" t="inlineStr" s="2">
@@ -10479,14 +10479,14 @@
       </c>
       <c r="F318" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この景色……っ……ふふ、忘れないわ……</t>
+          <t xml:space="preserve">リベンジするわ……っ……ふふ、必ず……</t>
         </is>
       </c>
     </row>
     <row r="319" ht="40" customHeight="1">
       <c r="A319" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.emotional.seductive[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B319" t="inlineStr" s="2">
@@ -10501,7 +10501,7 @@
       </c>
       <c r="D319" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.emotional.seductive[1]</t>
+          <t xml:space="preserve">postMatchWin.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E319" t="inlineStr" s="2">
@@ -10511,14 +10511,14 @@
       </c>
       <c r="F319" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けたわ……っ……悔しい……でも、いい経験だった……</t>
+          <t xml:space="preserve">勝った……っ……ふふ、まだまだ行けるわ……</t>
         </is>
       </c>
     </row>
     <row r="320" ht="40" customHeight="1">
       <c r="A320" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.emotional.seductive[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B320" t="inlineStr" s="2">
@@ -10533,7 +10533,7 @@
       </c>
       <c r="D320" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.emotional.seductive[2]</t>
+          <t xml:space="preserve">postMatchWin.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E320" t="inlineStr" s="2">
@@ -10543,14 +10543,14 @@
       </c>
       <c r="F320" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">リベンジするわ……っ……ふふ、必ず……</t>
+          <t xml:space="preserve">いい感じよ……っ……ふふ……</t>
         </is>
       </c>
     </row>
     <row r="321" ht="40" customHeight="1">
       <c r="A321" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.emotional.seductive[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B321" t="inlineStr" s="2">
@@ -10565,7 +10565,7 @@
       </c>
       <c r="D321" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.emotional.seductive[1]</t>
+          <t xml:space="preserve">postWin.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E321" t="inlineStr" s="2">
@@ -10575,14 +10575,14 @@
       </c>
       <c r="F321" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝った……っ……ふふ、まだまだ行けるわ……</t>
+          <t xml:space="preserve">勝ち上がったわ……っ……ふふ、ここまで来られたの……</t>
         </is>
       </c>
     </row>
     <row r="322" ht="40" customHeight="1">
       <c r="A322" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.emotional.seductive[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B322" t="inlineStr" s="2">
@@ -10597,7 +10597,7 @@
       </c>
       <c r="D322" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.emotional.seductive[2]</t>
+          <t xml:space="preserve">postWin.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E322" t="inlineStr" s="2">
@@ -10607,14 +10607,14 @@
       </c>
       <c r="F322" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい感じよ……っ……ふふ……</t>
+          <t xml:space="preserve">もっと上を目指すわ……っ……ふふ……</t>
         </is>
       </c>
     </row>
     <row r="323" ht="40" customHeight="1">
       <c r="A323" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.emotional.seductive[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B323" t="inlineStr" s="2">
@@ -10629,7 +10629,7 @@
       </c>
       <c r="D323" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.emotional.seductive[1]</t>
+          <t xml:space="preserve">preFinal.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E323" t="inlineStr" s="2">
@@ -10639,14 +10639,14 @@
       </c>
       <c r="F323" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ち上がったわ……っ……ふふ、ここまで来られたの……</t>
+          <t xml:space="preserve">決勝戦……っ……ふふ、ここまで来たのね……</t>
         </is>
       </c>
     </row>
     <row r="324" ht="40" customHeight="1">
       <c r="A324" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.emotional.seductive[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B324" t="inlineStr" s="2">
@@ -10661,7 +10661,7 @@
       </c>
       <c r="D324" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.emotional.seductive[2]</t>
+          <t xml:space="preserve">preFinal.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E324" t="inlineStr" s="2">
@@ -10671,14 +10671,14 @@
       </c>
       <c r="F324" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もっと上を目指すわ……っ……ふふ……</t>
+          <t xml:space="preserve">最高の舞台ね……っ……ふふ、震えてるの……</t>
         </is>
       </c>
     </row>
     <row r="325" ht="40" customHeight="1">
       <c r="A325" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.emotional.seductive[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B325" t="inlineStr" s="2">
@@ -10693,7 +10693,7 @@
       </c>
       <c r="D325" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.emotional.seductive[1]</t>
+          <t xml:space="preserve">preMatch.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E325" t="inlineStr" s="2">
@@ -10703,14 +10703,14 @@
       </c>
       <c r="F325" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決勝戦……っ……ふふ、ここまで来たのね……</t>
+          <t xml:space="preserve">試合前……っ……ふふ、心臓がドキドキしてるの……</t>
         </is>
       </c>
     </row>
     <row r="326" ht="40" customHeight="1">
       <c r="A326" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.emotional.seductive[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B326" t="inlineStr" s="2">
@@ -10725,7 +10725,7 @@
       </c>
       <c r="D326" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.emotional.seductive[2]</t>
+          <t xml:space="preserve">preMatch.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E326" t="inlineStr" s="2">
@@ -10735,14 +10735,14 @@
       </c>
       <c r="F326" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高の舞台ね……っ……ふふ、震えてるの……</t>
+          <t xml:space="preserve">楽しんでくるわね……っ……ふふ……</t>
         </is>
       </c>
     </row>
     <row r="327" ht="40" customHeight="1">
       <c r="A327" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.emotional.seductive[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B327" t="inlineStr" s="2">
@@ -10757,7 +10757,7 @@
       </c>
       <c r="D327" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.emotional.seductive[1]</t>
+          <t xml:space="preserve">summon.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E327" t="inlineStr" s="2">
@@ -10767,14 +10767,14 @@
       </c>
       <c r="F327" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">試合前……っ……ふふ、心臓がドキドキしてるの……</t>
+          <t xml:space="preserve">ジュニア大会に……っ……ふふ、わたしを選んでくれたのね、嬉しい……</t>
         </is>
       </c>
     </row>
     <row r="328" ht="40" customHeight="1">
       <c r="A328" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.emotional.seductive[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B328" t="inlineStr" s="2">
@@ -10789,7 +10789,7 @@
       </c>
       <c r="D328" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.emotional.seductive[2]</t>
+          <t xml:space="preserve">summon.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E328" t="inlineStr" s="2">
@@ -10799,14 +10799,14 @@
       </c>
       <c r="F328" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">楽しんでくるわね……っ……ふふ……</t>
+          <t xml:space="preserve">楽しみだわ……っ……ふふ、燃えてきたの……</t>
         </is>
       </c>
     </row>
     <row r="329" ht="40" customHeight="1">
       <c r="A329" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.emotional.seductive[1]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B329" t="inlineStr" s="2">
@@ -10816,12 +10816,12 @@
       </c>
       <c r="C329" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D329" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.emotional.seductive[1]</t>
+          <t xml:space="preserve">seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E329" t="inlineStr" s="2">
@@ -10831,14 +10831,14 @@
       </c>
       <c r="F329" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ジュニア大会に……っ……ふふ、わたしを選んでくれたのね、嬉しい……</t>
+          <t xml:space="preserve">あの子が相手……っ……ふふ、燃えてきたわ……</t>
         </is>
       </c>
     </row>
     <row r="330" ht="40" customHeight="1">
       <c r="A330" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.emotional.seductive[2]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B330" t="inlineStr" s="2">
@@ -10848,12 +10848,12 @@
       </c>
       <c r="C330" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D330" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.emotional.seductive[2]</t>
+          <t xml:space="preserve">seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E330" t="inlineStr" s="2">
@@ -10863,14 +10863,14 @@
       </c>
       <c r="F330" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">楽しみだわ……っ……ふふ、燃えてきたの……</t>
+          <t xml:space="preserve">嬉しい……っ……!最高の舞台で勝てた……この瞬間を、ずっと忘れないわ……!</t>
         </is>
       </c>
     </row>
     <row r="331" ht="40" customHeight="1">
       <c r="A331" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.emotional.seductive[1]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B331" t="inlineStr" s="2">
@@ -10880,12 +10880,12 @@
       </c>
       <c r="C331" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D331" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.seductive[1]</t>
+          <t xml:space="preserve">seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E331" t="inlineStr" s="2">
@@ -10895,14 +10895,14 @@
       </c>
       <c r="F331" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの子が相手……っ……ふふ、燃えてきたわ……</t>
+          <t xml:space="preserve">団体として挑むわ……っ……ふふ、燃えるわね……</t>
         </is>
       </c>
     </row>
     <row r="332" ht="40" customHeight="1">
       <c r="A332" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.emotional.seductive[1]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B332" t="inlineStr" s="2">
@@ -10912,12 +10912,12 @@
       </c>
       <c r="C332" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D332" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.seductive[1]</t>
+          <t xml:space="preserve">seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E332" t="inlineStr" s="2">
@@ -10927,14 +10927,14 @@
       </c>
       <c r="F332" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">嬉しい……っ……!最高の舞台で勝てた……この瞬間を、ずっと忘れないわ……!</t>
+          <t xml:space="preserve">みんなで戦うわ……っ……ふふ……</t>
         </is>
       </c>
     </row>
     <row r="333" ht="40" customHeight="1">
       <c r="A333" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.emotional.seductive[1]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B333" t="inlineStr" s="2">
@@ -10944,12 +10944,12 @@
       </c>
       <c r="C333" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D333" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.seductive[1]</t>
+          <t xml:space="preserve">seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E333" t="inlineStr" s="2">
@@ -10959,14 +10959,14 @@
       </c>
       <c r="F333" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">団体として挑むわ……っ……ふふ、燃えるわね……</t>
+          <t xml:space="preserve">ごめんなさい……っ……今回は遠慮するわ……</t>
         </is>
       </c>
     </row>
     <row r="334" ht="40" customHeight="1">
       <c r="A334" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.emotional.seductive[2]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B334" t="inlineStr" s="2">
@@ -10976,12 +10976,12 @@
       </c>
       <c r="C334" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D334" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.seductive[2]</t>
+          <t xml:space="preserve">seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E334" t="inlineStr" s="2">
@@ -10991,14 +10991,14 @@
       </c>
       <c r="F334" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みんなで戦うわ……っ……ふふ……</t>
+          <t xml:space="preserve">またの機会に……っ……ふふ……</t>
         </is>
       </c>
     </row>
     <row r="335" ht="40" customHeight="1">
       <c r="A335" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.emotional.seductive[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B335" t="inlineStr" s="2">
@@ -11008,12 +11008,12 @@
       </c>
       <c r="C335" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D335" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.seductive[1]</t>
+          <t xml:space="preserve">result_lose.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E335" t="inlineStr" s="2">
@@ -11023,14 +11023,14 @@
       </c>
       <c r="F335" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ごめんなさい……っ……今回は遠慮するわ……</t>
+          <t xml:space="preserve">負けたわ……っ……ふふ、悔しい……</t>
         </is>
       </c>
     </row>
     <row r="336" ht="40" customHeight="1">
       <c r="A336" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.emotional.seductive[2]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B336" t="inlineStr" s="2">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="C336" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D336" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.seductive[2]</t>
+          <t xml:space="preserve">result_lose.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E336" t="inlineStr" s="2">
@@ -11055,14 +11055,14 @@
       </c>
       <c r="F336" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">またの機会に……っ……ふふ……</t>
+          <t xml:space="preserve">次は絶対に……っ……ふふ、リベンジするわ……</t>
         </is>
       </c>
     </row>
     <row r="337" ht="40" customHeight="1">
       <c r="A337" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.emotional.seductive[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B337" t="inlineStr" s="2">
@@ -11077,7 +11077,7 @@
       </c>
       <c r="D337" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.emotional.seductive[1]</t>
+          <t xml:space="preserve">result_win.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E337" t="inlineStr" s="2">
@@ -11087,14 +11087,14 @@
       </c>
       <c r="F337" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けたわ……っ……ふふ、悔しい……</t>
+          <t xml:space="preserve">勝った……っ……ふふ、団体のために戦えて嬉しい……</t>
         </is>
       </c>
     </row>
     <row r="338" ht="40" customHeight="1">
       <c r="A338" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.emotional.seductive[2]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B338" t="inlineStr" s="2">
@@ -11109,7 +11109,7 @@
       </c>
       <c r="D338" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.emotional.seductive[2]</t>
+          <t xml:space="preserve">result_win.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E338" t="inlineStr" s="2">
@@ -11119,14 +11119,14 @@
       </c>
       <c r="F338" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次は絶対に……っ……ふふ、リベンジするわ……</t>
+          <t xml:space="preserve">みんなのおかげよ……っ……ふふ……</t>
         </is>
       </c>
     </row>
     <row r="339" ht="40" customHeight="1">
       <c r="A339" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.emotional.seductive[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B339" t="inlineStr" s="2">
@@ -11136,12 +11136,12 @@
       </c>
       <c r="C339" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D339" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.emotional.seductive[1]</t>
+          <t xml:space="preserve">seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E339" t="inlineStr" s="2">
@@ -11151,14 +11151,14 @@
       </c>
       <c r="F339" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝った……っ……ふふ、団体のために戦えて嬉しい……</t>
+          <t xml:space="preserve">勝てた…！ 団体のみんなのおかげ…嬉しい…！</t>
         </is>
       </c>
     </row>
     <row r="340" ht="40" customHeight="1">
       <c r="A340" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.emotional.seductive[2]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B340" t="inlineStr" s="2">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="C340" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D340" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.emotional.seductive[2]</t>
+          <t xml:space="preserve">seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E340" t="inlineStr" s="2">
@@ -11183,14 +11183,14 @@
       </c>
       <c r="F340" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みんなのおかげよ……っ……ふふ……</t>
+          <t xml:space="preserve">勝てた…みんなのおかげ…嬉しい…！</t>
         </is>
       </c>
     </row>
     <row r="341" ht="40" customHeight="1">
       <c r="A341" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.emotional.seductive[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.emotional[3]</t>
         </is>
       </c>
       <c r="B341" t="inlineStr" s="2">
@@ -11205,7 +11205,7 @@
       </c>
       <c r="D341" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.seductive[1]</t>
+          <t xml:space="preserve">seductive.emotional[3]</t>
         </is>
       </c>
       <c r="E341" t="inlineStr" s="2">
@@ -11215,14 +11215,14 @@
       </c>
       <c r="F341" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝てた…！ 団体のみんなのおかげ…嬉しい…！</t>
+          <t xml:space="preserve">勝てた…嬉しい…！ みんなのために頑張れた…！</t>
         </is>
       </c>
     </row>
     <row r="342" ht="40" customHeight="1">
       <c r="A342" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.emotional.seductive[2]</t>
+          <t xml:space="preserve">ENDING_LINES.fighter.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B342" t="inlineStr" s="2">
@@ -11232,29 +11232,29 @@
       </c>
       <c r="C342" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">ENDING_LINES</t>
         </is>
       </c>
       <c r="D342" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.seductive[2]</t>
+          <t xml:space="preserve">fighter.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E342" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
         </is>
       </c>
       <c r="F342" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝てた…みんなのおかげ…嬉しい…！</t>
+          <t xml:space="preserve">リングを降りるわ……っ……ふふ、ここで戦えた日々、永遠に忘れない……ありがとう……</t>
         </is>
       </c>
     </row>
     <row r="343" ht="40" customHeight="1">
       <c r="A343" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.emotional.seductive[3]</t>
+          <t xml:space="preserve">FA_GREETING_LINES.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B343" t="inlineStr" s="2">
@@ -11264,29 +11264,29 @@
       </c>
       <c r="C343" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
         </is>
       </c>
       <c r="D343" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.seductive[3]</t>
+          <t xml:space="preserve">seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E343" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
       <c r="F343" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝てた…嬉しい…！ みんなのために頑張れた…！</t>
+          <t xml:space="preserve">拾われる側になるなんて…っ…参ったわ</t>
         </is>
       </c>
     </row>
     <row r="344" ht="40" customHeight="1">
       <c r="A344" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.emotional.seductive[1]</t>
+          <t xml:space="preserve">SCOUT_GREETING_LINES.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B344" t="inlineStr" s="2">
@@ -11296,91 +11296,27 @@
       </c>
       <c r="C344" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
       <c r="D344" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.emotional.seductive[1]</t>
+          <t xml:space="preserve">seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E344" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
       <c r="F344" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">リングを降りるわ……っ……ふふ、ここで戦えた日々、永遠に忘れない……ありがとう……</t>
-        </is>
-      </c>
-    </row>
-    <row r="345" ht="40" customHeight="1">
-      <c r="A345" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">FA_GREETING_LINES.emotional.seductive[1]</t>
-        </is>
-      </c>
-      <c r="B345" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C345" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
-        </is>
-      </c>
-      <c r="D345" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">emotional.seductive[1]</t>
-        </is>
-      </c>
-      <c r="E345" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
-        </is>
-      </c>
-      <c r="F345" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">拾われる側になるなんて…っ…参ったわ</t>
-        </is>
-      </c>
-    </row>
-    <row r="346" ht="40" customHeight="1">
-      <c r="A346" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES.emotional.seductive[1]</t>
-        </is>
-      </c>
-      <c r="B346" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C346" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
-        </is>
-      </c>
-      <c r="D346" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">emotional.seductive[1]</t>
-        </is>
-      </c>
-      <c r="E346" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
-        </is>
-      </c>
-      <c r="F346" t="inlineStr" s="3">
-        <is>
           <t xml:space="preserve">うふふ♪嬉しい♪</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H346"/>
+  <autoFilter ref="A1:H344"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/蠱惑×感情的.xlsx
+++ b/セリフ編集/キャラタイプ別/蠱惑×感情的.xlsx
@@ -284,7 +284,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H344"/>
+  <dimension ref="A1:H346"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -751,7 +751,7 @@
       </c>
       <c r="F14" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ごめんなさい……っ…もっとやれたはずなのに…悔しい……!</t>
+          <t xml:space="preserve">ごめんなさい……っ…もっとやれたはずなのに…悔しい……！</t>
         </is>
       </c>
     </row>
@@ -783,7 +783,7 @@
       </c>
       <c r="F15" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みんなの声が聞こえてた……っ……ありがとう……!</t>
+          <t xml:space="preserve">みんなの声が聞こえてた……っ……ありがとう……！</t>
         </is>
       </c>
     </row>
@@ -815,7 +815,7 @@
       </c>
       <c r="F16" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたしのために争ってくれたの……っ……嬉しい、絶対期待に応えるわ……!</t>
+          <t xml:space="preserve">私のために争ってくれたの……っ……嬉しい、絶対期待に応えるわ……！</t>
         </is>
       </c>
     </row>
@@ -847,7 +847,7 @@
       </c>
       <c r="F17" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">入団できて嬉しい……っ……絶対強くなってみせるわ……!</t>
+          <t xml:space="preserve">入団できて嬉しい……っ……絶対強くなってみせるわ……！</t>
         </is>
       </c>
     </row>
@@ -879,7 +879,7 @@
       </c>
       <c r="F18" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ひとりで戦ってきたの……っ……仲間ができて、嬉しい……!</t>
+          <t xml:space="preserve">ひとりで戦ってきたの……っ……仲間ができて、嬉しい……！</t>
         </is>
       </c>
     </row>
@@ -911,7 +911,7 @@
       </c>
       <c r="F19" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここで終わったら……あの日の景色に、戻っちゃう……っ!</t>
+          <t xml:space="preserve">ここで終わったら……あの日の景色に、戻っちゃう……っ！</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F20" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">立つの……あそこに切られた、あの日の私のために……!</t>
+          <t xml:space="preserve">立つの……あそこに切られた、あの日の私のために……！</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="F21" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの日、降ろされた私が……あそこの選手を沈めたの……っ!</t>
+          <t xml:space="preserve">あの日、降ろされた私が……あそこの選手を沈めたの……っ！</t>
         </is>
       </c>
     </row>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="F22" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">見てた……? 切った女、こんなに戦えるのよ……!</t>
+          <t xml:space="preserve">見てた……？ 切った女、こんなに戦えるのよ……！</t>
         </is>
       </c>
     </row>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="F33" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お疲れさま…あとはわたしが…！</t>
+          <t xml:space="preserve">お疲れさま…あとは私が…！</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="F35" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{partner}っ…ごめんっ…わたしのせいでっ…！</t>
+          <t xml:space="preserve">{partner}っ…ごめんっ…私のせいでっ…！</t>
         </is>
       </c>
     </row>
@@ -1807,7 +1807,7 @@
       </c>
       <c r="F47" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……この日を…ずっと待ってた……っ……行くわよ……!</t>
+          <t xml:space="preserve">……この日を…ずっと待ってた……っ……行くわよ……！</t>
         </is>
       </c>
     </row>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="F48" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ええ……!来なさい、全部受け止めるわ……!</t>
+          <t xml:space="preserve">……ええ……！来なさい、全部受け止めるわ……！</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="F63" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長。あの人とやりたいの。……いいでしょ?</t>
+          <t xml:space="preserve">社長。あの人とやりたいの。……いいでしょ？</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="F70" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ほら、私の言う通り。いい報告でしょう?</t>
+          <t xml:space="preserve">ほら、私の言う通り。いい報告でしょう？</t>
         </is>
       </c>
     </row>
@@ -2607,7 +2607,7 @@
       </c>
       <c r="F72" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私を呼んだわね? …後悔させてあげる。</t>
+          <t xml:space="preserve">私を呼んだわね？ …後悔させてあげる。</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F73" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふざけてるの? …いいわ、受けるわよ。</t>
+          <t xml:space="preserve">ふざけてるの？ …いいわ、受けるわよ。</t>
         </is>
       </c>
     </row>
@@ -2735,7 +2735,7 @@
       </c>
       <c r="F76" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決めさせなさいよ! …ああ、もう。</t>
+          <t xml:space="preserve">決めさせなさいよ！ …ああ、もう。</t>
         </is>
       </c>
     </row>
@@ -2767,7 +2767,7 @@
       </c>
       <c r="F77" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">中途半端は嫌いなの。…わかるでしょ?</t>
+          <t xml:space="preserve">中途半端は嫌いなの。…わかるでしょ？</t>
         </is>
       </c>
     </row>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="F79" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しい……! 悔しいのよ、私は。</t>
+          <t xml:space="preserve">悔しい……！ 悔しいのよ、私は。</t>
         </is>
       </c>
     </row>
@@ -2895,7 +2895,7 @@
       </c>
       <c r="F81" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">分かった? 二度と私を選ばないで。</t>
+          <t xml:space="preserve">分かった？ 二度と私を選ばないで。</t>
         </is>
       </c>
     </row>
@@ -3023,7 +3023,7 @@
       </c>
       <c r="F85" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……必要としてくれるんだ。…うん、残る</t>
+          <t xml:space="preserve">……必要だって言うのね。…いいわ、残ってあげる♪</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F86" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ごめん。……でも、決めたから</t>
+          <t xml:space="preserve">……悪く思わないで。……もう、決めたことなの。</t>
         </is>
       </c>
     </row>
@@ -3407,7 +3407,7 @@
       </c>
       <c r="F97" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">どうして……っ……ふふ、わたしを切り捨てるつもり？……</t>
+          <t xml:space="preserve">どうして……っ……ふふ、私を切り捨てるつもり？……</t>
         </is>
       </c>
     </row>
@@ -3439,7 +3439,7 @@
       </c>
       <c r="F98" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ戦えるの……っ……ふふ、わたしを止めないで……</t>
+          <t xml:space="preserve">まだ戦えるの……っ……ふふ、私を止めないで……</t>
         </is>
       </c>
     </row>
@@ -3567,7 +3567,7 @@
       </c>
       <c r="F102" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悪役のまま消えるわ……っ……ふふ、それがわたしらしいの……</t>
+          <t xml:space="preserve">悪役のまま消えるわ……っ……ふふ、それが私らしいの……</t>
         </is>
       </c>
     </row>
@@ -3631,7 +3631,7 @@
       </c>
       <c r="F104" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ若いけど……っ……ふふ、わたしには無理だったの……</t>
+          <t xml:space="preserve">まだ若いけど……っ……ふふ、私には無理だったの……</t>
         </is>
       </c>
     </row>
@@ -3759,7 +3759,7 @@
       </c>
       <c r="F108" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">残るわ…っ…ここが、わたしの…大切な場所だから…</t>
+          <t xml:space="preserve">残るわ…っ…ここが、私の…大切な場所だから…</t>
         </is>
       </c>
     </row>
@@ -4911,7 +4911,7 @@
       </c>
       <c r="F144" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。</t>
+          <t xml:space="preserve">…嬉しい。ありがとうございます。</t>
         </is>
       </c>
     </row>
@@ -5231,7 +5231,7 @@
       </c>
       <c r="F154" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長、ありがとうございます。</t>
+          <t xml:space="preserve">…社長。ありがとうございます……ふふ。</t>
         </is>
       </c>
     </row>
@@ -5647,7 +5647,7 @@
       </c>
       <c r="F167" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……っ……変わったの、わたし……ふふ、自分でも信じられないくらい……</t>
+          <t xml:space="preserve">……っ……変わったの、私……ふふ、自分でも信じられないくらい……</t>
         </is>
       </c>
     </row>
@@ -6102,7 +6102,7 @@
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.seductive.emotional[1]</t>
+          <t xml:space="preserve">AWARD_LINES.autumnWarChampion.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6117,7 +6117,7 @@
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.seductive.emotional[1]</t>
+          <t xml:space="preserve">autumnWarChampion.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
@@ -6127,14 +6127,14 @@
       </c>
       <c r="F182" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高の試合だった…涙が止まらないわ</t>
+          <t xml:space="preserve">みんなと分かち合える優勝だから、こんなに胸がいっぱいなの。</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.seductive.emotional[1]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6149,7 +6149,7 @@
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.seductive.emotional[1]</t>
+          <t xml:space="preserve">bestMatch.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
@@ -6159,14 +6159,14 @@
       </c>
       <c r="F183" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオン……っ……ふふ、この重み……愛おしくてたまらないわ……</t>
+          <t xml:space="preserve">最高の試合だった…涙が止まらないわ</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.seductive.emotional[1]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6181,7 +6181,7 @@
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.seductive.emotional[1]</t>
+          <t xml:space="preserve">champion.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
@@ -6191,14 +6191,14 @@
       </c>
       <c r="F184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">殿堂入り…もう言葉にならないわ…（涙を堪える）</t>
+          <t xml:space="preserve">チャンピオン……っ……ふふ、この重み……愛おしくてたまらないわ……</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mediaAward.seductive.emotional[1]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6213,7 +6213,7 @@
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mediaAward.seductive.emotional[1]</t>
+          <t xml:space="preserve">hallOfFame.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
@@ -6223,14 +6223,14 @@
       </c>
       <c r="F185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">メディア功労賞……っ……みんなに見てもらえてた証ね、嬉しいわ……</t>
+          <t xml:space="preserve">殿堂入り…もう言葉にならないわ…（涙を堪える）</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.seductive.emotional[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mediaAward.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6245,7 +6245,7 @@
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.seductive.emotional[1]</t>
+          <t xml:space="preserve">mediaAward.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
@@ -6255,14 +6255,14 @@
       </c>
       <c r="F186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">MVP……っ……ふふ、わたしが一番輝いてたって、そう言ってもらえるのね……</t>
+          <t xml:space="preserve">メディア功労賞……っ……みんなに見てもらえてた証ね、嬉しいわ……</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.seductive.emotional[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6277,7 +6277,7 @@
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.seductive.emotional[1]</t>
+          <t xml:space="preserve">mvp.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
@@ -6287,14 +6287,14 @@
       </c>
       <c r="F187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">新人王……っ……無我夢中だったの……認めてもらえて嬉しいわ……</t>
+          <t xml:space="preserve">MVP……っ……ふふ、私が一番輝いてたって、そう言ってもらえるのね……</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.seductive.emotional[1]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6304,12 +6304,12 @@
       </c>
       <c r="C188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.emotional[1]</t>
+          <t xml:space="preserve">rookie.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
@@ -6319,14 +6319,14 @@
       </c>
       <c r="F188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ドームで、あなた方の前で戦える幸せよ…</t>
+          <t xml:space="preserve">新人王……っ……無我夢中だったの……認めてもらえて嬉しいわ……</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.seductive.emotional[2]</t>
+          <t xml:space="preserve">AWARD_LINES.springTagChampion.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6336,12 +6336,12 @@
       </c>
       <c r="C189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.emotional[2]</t>
+          <t xml:space="preserve">springTagChampion.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
@@ -6351,14 +6351,14 @@
       </c>
       <c r="F189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">熱い試合を…必ず、約束する</t>
+          <t xml:space="preserve">相棒と笑えるこの瞬間が、何よりうれしいの。</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.seductive.emotional[3]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6373,7 +6373,7 @@
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.emotional[3]</t>
+          <t xml:space="preserve">seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
@@ -6383,14 +6383,14 @@
       </c>
       <c r="F190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この胸の高鳴り…試合で発散させてね</t>
+          <t xml:space="preserve">…ドームで、あなた方の前で戦える幸せよ…</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.seductive.emotional[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6400,12 +6400,12 @@
       </c>
       <c r="C191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.emotional[1]</t>
+          <t xml:space="preserve">seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
@@ -6415,14 +6415,14 @@
       </c>
       <c r="F191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…満員、お客様の熱気…忘れられない</t>
+          <t xml:space="preserve">熱い試合を…必ず、約束する</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.seductive.emotional[2]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.seductive.emotional[3]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6432,12 +6432,12 @@
       </c>
       <c r="C192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.emotional[2]</t>
+          <t xml:space="preserve">seductive.emotional[3]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
@@ -6447,14 +6447,14 @@
       </c>
       <c r="F192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">胸が熱くて、震えが止まらないの</t>
+          <t xml:space="preserve">この胸の高鳴り…試合で発散させてね</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.seductive.emotional[3]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6469,7 +6469,7 @@
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.emotional[3]</t>
+          <t xml:space="preserve">seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
@@ -6479,14 +6479,14 @@
       </c>
       <c r="F193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんな素敵な夜、生涯忘れない</t>
+          <t xml:space="preserve">…満員、お客様の熱気…忘れられない</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.seductive.emotional[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6496,29 +6496,29 @@
       </c>
       <c r="C194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.seductive.emotional[1]</t>
+          <t xml:space="preserve">seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お知らせよ……っ……ふふ、聞いて……</t>
+          <t xml:space="preserve">胸が熱くて、震えが止まらないの</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.seductive.emotional[2]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.seductive.emotional[3]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6528,29 +6528,29 @@
       </c>
       <c r="C195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.seductive.emotional[2]</t>
+          <t xml:space="preserve">seductive.emotional[3]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ねえ、聞いて……っ……ふふ……</t>
+          <t xml:space="preserve">こんな素敵な夜、生涯忘れない</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.seductive.emotional[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6565,7 +6565,7 @@
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.seductive.emotional[1]</t>
+          <t xml:space="preserve">N1.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
@@ -6575,14 +6575,14 @@
       </c>
       <c r="F196" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ちょっといいかしら……っ……ふふ……</t>
+          <t xml:space="preserve">お知らせよ……っ……ふふ、聞いて……</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.seductive.emotional[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6597,7 +6597,7 @@
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.seductive.emotional[1]</t>
+          <t xml:space="preserve">N1.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
@@ -6607,14 +6607,14 @@
       </c>
       <c r="F197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">はぁ……体が、言うこときかないの……ごめんなさい……</t>
+          <t xml:space="preserve">ねえ、聞いて……っ……ふふ……</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.seductive.emotional[2]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6629,7 +6629,7 @@
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.seductive.emotional[2]</t>
+          <t xml:space="preserve">N2.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
@@ -6639,14 +6639,14 @@
       </c>
       <c r="F198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふぅ……ちょっと、休ませて……すぐ、戻るから……</t>
+          <t xml:space="preserve">ちょっといいかしら……っ……ふふ……</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.seductive.emotional[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6661,7 +6661,7 @@
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.seductive.emotional[1]</t>
+          <t xml:space="preserve">N3.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
@@ -6671,14 +6671,14 @@
       </c>
       <c r="F199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">大事な話よ……っ……ふふ、しっかり聞いて……</t>
+          <t xml:space="preserve">はぁ……体が、言うこときかないの……ごめんなさい……</t>
         </is>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.seductive.emotional[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6693,7 +6693,7 @@
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.seductive.emotional[1]</t>
+          <t xml:space="preserve">N3.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
@@ -6703,14 +6703,14 @@
       </c>
       <c r="F200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ちょっと心配なの……っ……ふふ……</t>
+          <t xml:space="preserve">ふぅ……ちょっと、休ませて……すぐ、戻るから……</t>
         </is>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.seductive.emotional[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_warning.seductive.emotional[1]</t>
+          <t xml:space="preserve">N4.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
@@ -6735,14 +6735,14 @@
       </c>
       <c r="F201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">緊急よ……っ……ふふ、よく聞いて……</t>
+          <t xml:space="preserve">大事な話よ……っ……ふふ、しっかり聞いて……</t>
         </is>
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.breakthrough.voice.seductive.emotional[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6752,12 +6752,12 @@
       </c>
       <c r="C202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">breakthrough.voice.seductive.emotional[1]</t>
+          <t xml:space="preserve">N5_low.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
@@ -6767,14 +6767,14 @@
       </c>
       <c r="F202" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何かが変わった……っ……ふふ……</t>
+          <t xml:space="preserve">ちょっと心配なの……っ……ふふ……</t>
         </is>
       </c>
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.seductive.emotional[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6784,12 +6784,12 @@
       </c>
       <c r="C203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G1.voice.seductive.emotional[1]</t>
+          <t xml:space="preserve">N5_warning.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
@@ -6799,14 +6799,14 @@
       </c>
       <c r="F203" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう少し稼ぎたいわね……っ……</t>
+          <t xml:space="preserve">緊急よ……っ……ふふ、よく聞いて……</t>
         </is>
       </c>
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice.seductive.emotional[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.breakthrough.voice.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6821,7 +6821,7 @@
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G2.voice.seductive.emotional[1]</t>
+          <t xml:space="preserve">breakthrough.voice.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
@@ -6831,14 +6831,14 @@
       </c>
       <c r="F204" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ひとりは、ちょっと寂しいの……っ……</t>
+          <t xml:space="preserve">何かが変わった……っ……ふふ……</t>
         </is>
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice.seductive.emotional[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6853,7 +6853,7 @@
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G3.voice.seductive.emotional[1]</t>
+          <t xml:space="preserve">G1.voice.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
@@ -6863,14 +6863,14 @@
       </c>
       <c r="F205" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もう少し目立たないとダメなのかしら</t>
+          <t xml:space="preserve">もう少し稼ぎたいわね……っ……</t>
         </is>
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G4.voice.seductive.emotional[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6885,7 +6885,7 @@
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G4.voice.seductive.emotional[1]</t>
+          <t xml:space="preserve">G2.voice.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
@@ -6895,14 +6895,14 @@
       </c>
       <c r="F206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もっと強くなりたいの……っ……</t>
+          <t xml:space="preserve">ひとりは、ちょっと寂しいの……っ……</t>
         </is>
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice.seductive.emotional[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R2.voice.seductive.emotional[1]</t>
+          <t xml:space="preserve">G3.voice.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
@@ -6927,14 +6927,14 @@
       </c>
       <c r="F207" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの子と、もっと話したい……っ……</t>
+          <t xml:space="preserve">…もう少し目立たないとダメなのかしら</t>
         </is>
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice.seductive.emotional[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G4.voice.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6949,7 +6949,7 @@
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R4.voice.seductive.emotional[1]</t>
+          <t xml:space="preserve">G4.voice.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
@@ -6959,14 +6959,14 @@
       </c>
       <c r="F208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの子とは、ちょっと距離を置きたいの……っ……</t>
+          <t xml:space="preserve">もっと強くなりたいの……っ……</t>
         </is>
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice.seductive.emotional[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -6981,7 +6981,7 @@
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R5.voice.seductive.emotional[1]</t>
+          <t xml:space="preserve">R2.voice.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
@@ -6991,14 +6991,14 @@
       </c>
       <c r="F209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けたくないの……っ……ふふ……</t>
+          <t xml:space="preserve">あの子と、もっと話したい……っ……</t>
         </is>
       </c>
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.warVictory.voice.seductive.emotional[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -7013,7 +7013,7 @@
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">warVictory.voice.seductive.emotional[1]</t>
+          <t xml:space="preserve">R4.voice.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
@@ -7023,14 +7023,14 @@
       </c>
       <c r="F210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝てた……っ……ふふ、最高の気分……</t>
+          <t xml:space="preserve">あの子とは、ちょっと距離を置きたいの……っ……</t>
         </is>
       </c>
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_repeat.seductive.emotional[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7040,29 +7040,29 @@
       </c>
       <c r="C211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus_repeat.seductive.emotional[1]</t>
+          <t xml:space="preserve">R5.voice.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">また……っ……ふふ、こんなに優しくされたら、応えないわけにはいかないわ……</t>
+          <t xml:space="preserve">負けたくないの……っ……ふふ……</t>
         </is>
       </c>
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.seductive.emotional[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.warVictory.voice.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7072,29 +7072,29 @@
       </c>
       <c r="C212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.seductive.emotional[1]</t>
+          <t xml:space="preserve">warVictory.voice.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F212" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ボーナス……っ……気にかけてくれてたのね、嬉しい……ふふ、ありがとう……</t>
+          <t xml:space="preserve">勝てた……っ……ふふ、最高の気分……</t>
         </is>
       </c>
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.seductive.emotional[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_repeat.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7109,7 +7109,7 @@
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.seductive.emotional[1]</t>
+          <t xml:space="preserve">bonus_repeat.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
@@ -7119,14 +7119,14 @@
       </c>
       <c r="F213" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">合宿……っ……ふふ、みんなと一緒に過ごせるのね、楽しみ……</t>
+          <t xml:space="preserve">また……っ……ふふ、こんなに優しくされたら、応えないわけにはいかないわ……</t>
         </is>
       </c>
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.seductive.emotional[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7141,7 +7141,7 @@
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage_high_trust.seductive.emotional[1]</t>
+          <t xml:space="preserve">bonus.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
@@ -7151,14 +7151,14 @@
       </c>
       <c r="F214" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あなたの言葉だけで……っ……わたし、何でもできちゃいそうなの……ふふ……</t>
+          <t xml:space="preserve">ボーナス……っ……気にかけてくれてたのね、嬉しい……ふふ、ありがとう……</t>
         </is>
       </c>
     </row>
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.seductive.emotional[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7173,7 +7173,7 @@
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.seductive.emotional[1]</t>
+          <t xml:space="preserve">camp.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
@@ -7183,14 +7183,14 @@
       </c>
       <c r="F215" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">励まし……っ……ふふ、その言葉だけで、力が湧いてくるの……</t>
+          <t xml:space="preserve">合宿……っ……ふふ、みんなと一緒に過ごせるのね、楽しみ……</t>
         </is>
       </c>
     </row>
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.seductive.emotional[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7205,7 +7205,7 @@
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.seductive.emotional[1]</t>
+          <t xml:space="preserve">encourage_high_trust.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
@@ -7215,14 +7215,14 @@
       </c>
       <c r="F216" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">メディアに……っ……ふふ、わたしを世間に見せたいのね、いいわ……</t>
+          <t xml:space="preserve">あなたの言葉だけで……っ……私、何でもできちゃいそうなの……ふふ……</t>
         </is>
       </c>
     </row>
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.seductive.emotional[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7237,7 +7237,7 @@
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.seductive.emotional[1]</t>
+          <t xml:space="preserve">encourage.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
@@ -7247,14 +7247,14 @@
       </c>
       <c r="F217" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">パーティー……っ……ふふ、今夜は思いっきり楽しませてもらうわ……</t>
+          <t xml:space="preserve">励まし……っ……ふふ、その言葉だけで、力が湧いてくるの……</t>
         </is>
       </c>
     </row>
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.seductive.emotional[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7269,7 +7269,7 @@
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.seductive.emotional[1]</t>
+          <t xml:space="preserve">media.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
@@ -7279,14 +7279,14 @@
       </c>
       <c r="F218" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">休暇……っ……気を遣ってくれたのね、ふふ、嬉しいわ……</t>
+          <t xml:space="preserve">メディアに……っ……ふふ、私を世間に見せたいのね、いいわ……</t>
         </is>
       </c>
     </row>
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.seductive.emotional[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7301,7 +7301,7 @@
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.seductive.emotional[1]</t>
+          <t xml:space="preserve">party.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
@@ -7311,14 +7311,14 @@
       </c>
       <c r="F219" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">そこまで…してくれるの…っ、嬉しい……早く戻るわ……</t>
+          <t xml:space="preserve">パーティー……っ……ふふ、今夜は思いっきり楽しませてもらうわ……</t>
         </is>
       </c>
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.seductive.emotional[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7333,7 +7333,7 @@
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.seductive.emotional[1]</t>
+          <t xml:space="preserve">refresh_leave.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
@@ -7343,14 +7343,14 @@
       </c>
       <c r="F220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">トレーナーをつけてくれるの……っ……ふふ、本気で育ててくれるのね……</t>
+          <t xml:space="preserve">休暇……っ……気を遣ってくれたのね、ふふ、嬉しいわ……</t>
         </is>
       </c>
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.seductive.emotional[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7360,12 +7360,12 @@
       </c>
       <c r="C221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.seductive.emotional[1]</t>
+          <t xml:space="preserve">special_treatment.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
@@ -7375,14 +7375,14 @@
       </c>
       <c r="F221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……っ……どうしようかしら、ふふ、迷っちゃうわね……</t>
+          <t xml:space="preserve">そこまで…してくれるの…っ、嬉しい……早く戻るわ……</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.seductive.emotional[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="C222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.seductive.emotional[1]</t>
+          <t xml:space="preserve">trainer.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
@@ -7407,14 +7407,14 @@
       </c>
       <c r="F222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いいわよ……っ……ふふ、やってみせるわ……</t>
+          <t xml:space="preserve">トレーナーをつけてくれるの……っ……ふふ、本気で育ててくれるのね……</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.seductive.emotional[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7429,7 +7429,7 @@
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.seductive.emotional[1]</t>
+          <t xml:space="preserve">E1.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
@@ -7439,14 +7439,14 @@
       </c>
       <c r="F223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……っ……これは認められないわ、悪いけど……</t>
+          <t xml:space="preserve">……っ……どうしようかしら、ふふ、迷っちゃうわね……</t>
         </is>
       </c>
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.seductive.emotional[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7461,7 +7461,7 @@
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_grumble.seductive.emotional[1]</t>
+          <t xml:space="preserve">E6.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
@@ -7471,14 +7471,14 @@
       </c>
       <c r="F224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">正直に言うわね……っ……ちょっと不満なの……</t>
+          <t xml:space="preserve">いいわよ……っ……ふふ、やってみせるわ……</t>
         </is>
       </c>
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.seductive.emotional[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7493,7 +7493,7 @@
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_sns.seductive.emotional[1]</t>
+          <t xml:space="preserve">S_boycott.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
@@ -7503,14 +7503,14 @@
       </c>
       <c r="F225" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">SNS見たわ……っ……ふふ、勝手な人たちね……</t>
+          <t xml:space="preserve">……っ……これは認められないわ、悪いけど……</t>
         </is>
       </c>
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.seductive.emotional[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.seductive.emotional[1]</t>
+          <t xml:space="preserve">S_grumble.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
@@ -7535,14 +7535,14 @@
       </c>
       <c r="F226" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ねえ……っ……ちょっと、聞いてほしいの……</t>
+          <t xml:space="preserve">正直に言うわね……っ……ちょっと不満なの……</t>
         </is>
       </c>
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.seductive.emotional[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7557,7 +7557,7 @@
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.seductive.emotional[1]</t>
+          <t xml:space="preserve">S_sns.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
@@ -7567,14 +7567,14 @@
       </c>
       <c r="F227" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">時間、ある……っ……ふふ、ちょっとだけ付き合って……</t>
+          <t xml:space="preserve">SNS見たわ……っ……ふふ、勝手な人たちね……</t>
         </is>
       </c>
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.seductive.emotional[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7589,7 +7589,7 @@
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.seductive.emotional[1]</t>
+          <t xml:space="preserve">S1.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
@@ -7599,14 +7599,14 @@
       </c>
       <c r="F228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……っ……どう答えるのが正解なのかしら、ふふ……</t>
+          <t xml:space="preserve">ねえ……っ……ちょっと、聞いてほしいの……</t>
         </is>
       </c>
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.seductive.emotional[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7621,7 +7621,7 @@
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.seductive.emotional[1]</t>
+          <t xml:space="preserve">S2.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
@@ -7631,14 +7631,14 @@
       </c>
       <c r="F229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">はっきり言うわ……っ……わたしの気持ちは……</t>
+          <t xml:space="preserve">時間、ある……っ……ふふ、ちょっとだけ付き合って……</t>
         </is>
       </c>
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.seductive.emotional[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7653,7 +7653,7 @@
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_silent.seductive.emotional[1]</t>
+          <t xml:space="preserve">S3.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
@@ -7663,14 +7663,14 @@
       </c>
       <c r="F230" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………っ……言葉にならないの……ふふ……</t>
+          <t xml:space="preserve">……っ……どう答えるのが正解なのかしら、ふふ……</t>
         </is>
       </c>
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.seductive.emotional[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7685,7 +7685,7 @@
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.seductive.emotional[1]</t>
+          <t xml:space="preserve">S4_direct.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
@@ -7695,14 +7695,14 @@
       </c>
       <c r="F231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">少し考えさせて……っ……ふふ、すぐには決められないの……</t>
+          <t xml:space="preserve">はっきり言うわ……っ……私の気持ちは……</t>
         </is>
       </c>
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.seductive.emotional[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7717,7 +7717,7 @@
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.seductive.emotional[1]</t>
+          <t xml:space="preserve">S4_silent.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
@@ -7727,14 +7727,14 @@
       </c>
       <c r="F232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決めたわ……っ……ふふ、これがわたしの答えよ……</t>
+          <t xml:space="preserve">………っ……言葉にならないの……ふふ……</t>
         </is>
       </c>
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.seductive.emotional[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="C233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.seductive.emotional[1]</t>
+          <t xml:space="preserve">S5.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
@@ -7759,14 +7759,14 @@
       </c>
       <c r="F233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">これから……っ……やりたいこと、いっぱいあるの……</t>
+          <t xml:space="preserve">少し考えさせて……っ……ふふ、すぐには決められないの……</t>
         </is>
       </c>
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.seductive.emotional[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7776,12 +7776,12 @@
       </c>
       <c r="C234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.seductive.emotional[1]</t>
+          <t xml:space="preserve">S6.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
@@ -7791,14 +7791,14 @@
       </c>
       <c r="F234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ねえ……っ……ちょっと話、聞いてくれる？</t>
+          <t xml:space="preserve">決めたわ……っ……ふふ、これが私の答えよ……</t>
         </is>
       </c>
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.seductive.emotional[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7813,7 +7813,7 @@
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.seductive.emotional[1]</t>
+          <t xml:space="preserve">B1.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
@@ -7823,14 +7823,14 @@
       </c>
       <c r="F235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いいわよ……っ……話してみて……</t>
+          <t xml:space="preserve">これから……っ……やりたいこと、いっぱいあるの……</t>
         </is>
       </c>
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.seductive.emotional[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.seductive.emotional[1]</t>
+          <t xml:space="preserve">B2_fighter1.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
@@ -7855,14 +7855,14 @@
       </c>
       <c r="F236" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ブランドのお話……っ……ふふ、素敵ね……</t>
+          <t xml:space="preserve">ねえ……っ……ちょっと話、聞いてくれる？</t>
         </is>
       </c>
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.seductive.emotional[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -7877,7 +7877,7 @@
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.seductive.emotional[1]</t>
+          <t xml:space="preserve">B2_fighter2.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
@@ -7887,14 +7887,14 @@
       </c>
       <c r="F237" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">CMに出るの……っ……ふふ、世間に顔を売るチャンスね……</t>
+          <t xml:space="preserve">いいわよ……っ……話してみて……</t>
         </is>
       </c>
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.seductive.emotional[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -7909,7 +7909,7 @@
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.seductive.emotional[1]</t>
+          <t xml:space="preserve">B4_brand.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
@@ -7919,14 +7919,14 @@
       </c>
       <c r="F238" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ファンに会えるの……っ……ふふ、みんなに直接ありがとうって言えるのね……</t>
+          <t xml:space="preserve">ブランドのお話……っ……ふふ、素敵ね……</t>
         </is>
       </c>
     </row>
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.seductive.emotional[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -7941,7 +7941,7 @@
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.seductive.emotional[1]</t>
+          <t xml:space="preserve">B4_cm.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
@@ -7951,14 +7951,14 @@
       </c>
       <c r="F239" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ファッションのお仕事……っ……ふふ、おしゃれするのは好きよ……</t>
+          <t xml:space="preserve">CMに出るの……っ……ふふ、世間に顔を売るチャンスね……</t>
         </is>
       </c>
     </row>
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.seductive.emotional[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -7973,7 +7973,7 @@
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.seductive.emotional[1]</t>
+          <t xml:space="preserve">B4_fan.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
@@ -7983,14 +7983,14 @@
       </c>
       <c r="F240" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">グラビア……っ……ふふ、見られるのは嫌いじゃないの……</t>
+          <t xml:space="preserve">ファンに会えるの……っ……ふふ、みんなに直接ありがとうって言えるのね……</t>
         </is>
       </c>
     </row>
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.seductive.emotional[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -8005,7 +8005,7 @@
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.seductive.emotional[1]</t>
+          <t xml:space="preserve">B4_fashion.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
@@ -8015,14 +8015,14 @@
       </c>
       <c r="F241" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">バラエティに出るの……っ……ふふ、楽しんでくるわね……</t>
+          <t xml:space="preserve">ファッションのお仕事……っ……ふふ、おしゃれするのは好きよ……</t>
         </is>
       </c>
     </row>
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.seductive.emotional[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8037,7 +8037,7 @@
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.seductive.emotional[1]</t>
+          <t xml:space="preserve">B4_gravure.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
@@ -8047,14 +8047,14 @@
       </c>
       <c r="F242" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このお仕事……っ……ふふ、面白そうね……</t>
+          <t xml:space="preserve">グラビア……っ……ふふ、見られるのは嫌いじゃないの……</t>
         </is>
       </c>
     </row>
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.seductive.emotional[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8064,29 +8064,29 @@
       </c>
       <c r="C243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.emotional[1]</t>
+          <t xml:space="preserve">B4_variety.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F243" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">選んでくれたら…全力で…全力でやるから…！</t>
+          <t xml:space="preserve">バラエティに出るの……っ……ふふ、楽しんでくるわね……</t>
         </is>
       </c>
     </row>
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.seductive.emotional[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8096,29 +8096,29 @@
       </c>
       <c r="C244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.emotional[1]</t>
+          <t xml:space="preserve">B4.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F244" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…夢みたい。精一杯頑張るわ…</t>
+          <t xml:space="preserve">このお仕事……っ……ふふ、面白そうね……</t>
         </is>
       </c>
     </row>
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.seductive.emotional[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8128,7 +8128,7 @@
       </c>
       <c r="C245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D245" t="inlineStr" s="12">
@@ -8143,14 +8143,14 @@
       </c>
       <c r="F245" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとう…っ…嬉しい…。全力で、やるから…</t>
+          <t xml:space="preserve">選んでくれたら…全力で…全力でやるから…！</t>
         </is>
       </c>
     </row>
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.seductive.emotional[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8160,7 +8160,7 @@
       </c>
       <c r="C246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D246" t="inlineStr" s="12">
@@ -8175,14 +8175,14 @@
       </c>
       <c r="F246" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">嬉しい…っ…よろしくね…。頑張るから…</t>
+          <t xml:space="preserve">…っ…夢みたい。精一杯頑張るわ…</t>
         </is>
       </c>
     </row>
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.seductive.emotional[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8192,7 +8192,7 @@
       </c>
       <c r="C247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D247" t="inlineStr" s="12">
@@ -8207,14 +8207,14 @@
       </c>
       <c r="F247" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…悔しい…必ず戻ってやる…</t>
+          <t xml:space="preserve">ありがとう…っ…嬉しい…。全力で、やるから…</t>
         </is>
       </c>
     </row>
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.seductive.emotional[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="C248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.ahead.seductive.emotional[1]</t>
+          <t xml:space="preserve">seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E248" t="inlineStr" s="2">
@@ -8239,14 +8239,14 @@
       </c>
       <c r="F248" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">済んだ話よ……っ……なのに、まだ手が震えるの</t>
+          <t xml:space="preserve">嬉しい…っ…よろしくね…。頑張るから…</t>
         </is>
       </c>
     </row>
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.seductive.emotional[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8256,12 +8256,12 @@
       </c>
       <c r="C249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.behind.seductive.emotional[1]</t>
+          <t xml:space="preserve">seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E249" t="inlineStr" s="2">
@@ -8271,14 +8271,14 @@
       </c>
       <c r="F249" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">終わったの……？ ……嘘よ。まだ、疼いてる</t>
+          <t xml:space="preserve">…っ…悔しい…必ず戻ってやる…</t>
         </is>
       </c>
     </row>
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.seductive.emotional[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.seductive.emotional[1]</t>
+          <t xml:space="preserve">bitterPrematch.ahead.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
@@ -8303,14 +8303,14 @@
       </c>
       <c r="F250" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">選んでくれたら…全力で…全力でやるから…！</t>
+          <t xml:space="preserve">済んだ話よ……っ……なのに、まだ手が震えるの</t>
         </is>
       </c>
     </row>
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.seductive.emotional[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8325,7 +8325,7 @@
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.seductive.emotional[1]</t>
+          <t xml:space="preserve">bitterPrematch.behind.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
@@ -8335,14 +8335,14 @@
       </c>
       <c r="F251" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…夢みたい。精一杯頑張るわ…</t>
+          <t xml:space="preserve">終わったの……？ ……嘘よ。まだ、疼いてる</t>
         </is>
       </c>
     </row>
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.seductive.emotional[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8357,7 +8357,7 @@
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.seductive.emotional[1]</t>
+          <t xml:space="preserve">draftInterest.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
@@ -8367,14 +8367,14 @@
       </c>
       <c r="F252" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">拾われる側になるなんて…っ…参ったわ</t>
+          <t xml:space="preserve">選んでくれたら…全力で…全力でやるから…！</t>
         </is>
       </c>
     </row>
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.seductive.emotional[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8389,7 +8389,7 @@
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.seductive.emotional[1]</t>
+          <t xml:space="preserve">draftJoin.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
@@ -8399,14 +8399,14 @@
       </c>
       <c r="F253" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとう…っ…嬉しい…。全力で、やるから…</t>
+          <t xml:space="preserve">…っ…夢みたい。精一杯頑張るわ…</t>
         </is>
       </c>
     </row>
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.seductive.emotional[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8421,7 +8421,7 @@
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.seductive.emotional[1]</t>
+          <t xml:space="preserve">faGreeting.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
@@ -8431,14 +8431,14 @@
       </c>
       <c r="F254" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">嬉しい…っ…よろしくね…。頑張るから…</t>
+          <t xml:space="preserve">口説かれる側になるなんて…っ…ふふ、いい度胸ね</t>
         </is>
       </c>
     </row>
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.seductive.emotional[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8453,7 +8453,7 @@
       </c>
       <c r="D255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.seductive.emotional[1]</t>
+          <t xml:space="preserve">faSigning.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E255" t="inlineStr" s="2">
@@ -8463,14 +8463,14 @@
       </c>
       <c r="F255" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…悔しい…必ず戻ってやる…</t>
+          <t xml:space="preserve">ありがとう…っ…嬉しい…。全力で、やるから…</t>
         </is>
       </c>
     </row>
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.seductive.emotional[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8485,7 +8485,7 @@
       </c>
       <c r="D256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.seductive.emotional[1]</t>
+          <t xml:space="preserve">faWelcome.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E256" t="inlineStr" s="2">
@@ -8495,14 +8495,14 @@
       </c>
       <c r="F256" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…ありがとう…忘れないわ…</t>
+          <t xml:space="preserve">嬉しい…っ…よろしくね…。頑張るから…</t>
         </is>
       </c>
     </row>
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.seductive.emotional[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8517,7 +8517,7 @@
       </c>
       <c r="D257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.seductive.emotional[1]</t>
+          <t xml:space="preserve">injury.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E257" t="inlineStr" s="2">
@@ -8527,14 +8527,14 @@
       </c>
       <c r="F257" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくね…っ…短い間だけど…全力で、やるから…</t>
+          <t xml:space="preserve">…っ…悔しい…必ず戻ってやる…</t>
         </is>
       </c>
     </row>
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.seductive.emotional[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="D258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.seductive.emotional[1]</t>
+          <t xml:space="preserve">release.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E258" t="inlineStr" s="2">
@@ -8559,14 +8559,14 @@
       </c>
       <c r="F258" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うふふ♪嬉しい♪</t>
+          <t xml:space="preserve">…っ…ありがとう…忘れないわ…</t>
         </is>
       </c>
     </row>
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.seductive.emotional[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8581,7 +8581,7 @@
       </c>
       <c r="D259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.seductive.emotional[1]</t>
+          <t xml:space="preserve">rentalGreeting.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E259" t="inlineStr" s="2">
@@ -8591,14 +8591,14 @@
       </c>
       <c r="F259" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しい…っ…悔しい…。でも…絶対に、諦めない…</t>
+          <t xml:space="preserve">よろしくね…っ…短い間だけど…全力で、やるから…</t>
         </is>
       </c>
     </row>
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.seductive.emotional[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8613,7 +8613,7 @@
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.seductive.emotional[1]</t>
+          <t xml:space="preserve">scoutGreeting.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E260" t="inlineStr" s="2">
@@ -8623,14 +8623,14 @@
       </c>
       <c r="F260" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">守れた…っ…嬉しい…。次も、絶対に守るから…</t>
+          <t xml:space="preserve">うふふ♪嬉しい♪</t>
         </is>
       </c>
     </row>
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.seductive.emotional[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8645,7 +8645,7 @@
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.seductive.emotional[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
@@ -8655,14 +8655,14 @@
       </c>
       <c r="F261" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">嘘…っ…ベルトが…。でも…でも、諦めない…</t>
+          <t xml:space="preserve">悔しい…っ…悔しい…。でも…絶対に、諦めない…</t>
         </is>
       </c>
     </row>
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.seductive.emotional[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8677,7 +8677,7 @@
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.seductive.emotional[1]</t>
+          <t xml:space="preserve">titleDefense.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E262" t="inlineStr" s="2">
@@ -8687,14 +8687,14 @@
       </c>
       <c r="F262" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ああ…っ…チャンピオン…。嬉しい…だめ、泣いちゃう…</t>
+          <t xml:space="preserve">守れた…っ…嬉しい…。次も、絶対に守るから…</t>
         </is>
       </c>
     </row>
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.seductive.emotional[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8704,12 +8704,12 @@
       </c>
       <c r="C263" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.emotional[1]</t>
+          <t xml:space="preserve">titleLoss.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E263" t="inlineStr" s="2">
@@ -8719,14 +8719,14 @@
       </c>
       <c r="F263" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…ありがとう…忘れないわ…</t>
+          <t xml:space="preserve">嘘…っ…ベルトが…。でも…でも、諦めない…</t>
         </is>
       </c>
     </row>
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.seductive.emotional[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8736,12 +8736,12 @@
       </c>
       <c r="C264" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.emotional[1]</t>
+          <t xml:space="preserve">titleWin.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E264" t="inlineStr" s="2">
@@ -8751,14 +8751,14 @@
       </c>
       <c r="F264" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくね…っ…短い間だけど…全力で、やるから…</t>
+          <t xml:space="preserve">ああ…っ…チャンピオン…。嬉しい…だめ、泣いちゃう…</t>
         </is>
       </c>
     </row>
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.seductive.emotional[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8768,7 +8768,7 @@
       </c>
       <c r="C265" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D265" t="inlineStr" s="12">
@@ -8783,14 +8783,14 @@
       </c>
       <c r="F265" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しい…っ…悔しい…。でも…絶対に、諦めない…</t>
+          <t xml:space="preserve">…っ…ありがとう…忘れないわ…</t>
         </is>
       </c>
     </row>
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.seductive.emotional[1]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8800,7 +8800,7 @@
       </c>
       <c r="C266" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D266" t="inlineStr" s="12">
@@ -8815,14 +8815,14 @@
       </c>
       <c r="F266" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">守れた…っ…嬉しい…。次も、絶対に守るから…</t>
+          <t xml:space="preserve">よろしくね…っ…短い間だけど…全力で、やるから…</t>
         </is>
       </c>
     </row>
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.seductive.emotional[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -8832,7 +8832,7 @@
       </c>
       <c r="C267" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D267" t="inlineStr" s="12">
@@ -8847,14 +8847,14 @@
       </c>
       <c r="F267" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">嘘…っ…ベルトが…。でも…でも、諦めない…</t>
+          <t xml:space="preserve">悔しい…っ…悔しい…。でも…絶対に、諦めない…</t>
         </is>
       </c>
     </row>
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.seductive.emotional[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -8864,7 +8864,7 @@
       </c>
       <c r="C268" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D268" t="inlineStr" s="12">
@@ -8879,14 +8879,14 @@
       </c>
       <c r="F268" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ああ…っ…チャンピオン…。嬉しい…だめ、泣いちゃう…</t>
+          <t xml:space="preserve">守れた…っ…嬉しい…。次も、絶対に守るから…</t>
         </is>
       </c>
     </row>
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.emotional.seductive[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -8896,29 +8896,29 @@
       </c>
       <c r="C269" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D269" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.emotional.seductive[1]</t>
+          <t xml:space="preserve">seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E269" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F269" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">考えると苦しいの…もう無理…</t>
+          <t xml:space="preserve">嘘…っ…ベルトが…。でも…でも、諦めない…</t>
         </is>
       </c>
     </row>
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.emotional.seductive[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -8928,29 +8928,29 @@
       </c>
       <c r="C270" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D270" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.emotional.seductive[1]</t>
+          <t xml:space="preserve">seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E270" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F270" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">離れていく…嫌よ…こんなの…</t>
+          <t xml:space="preserve">ああ…っ…チャンピオン…。嬉しい…だめ、泣いちゃう…</t>
         </is>
       </c>
     </row>
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.emotional.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -8965,7 +8965,7 @@
       </c>
       <c r="D271" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.emotional.seductive[2]</t>
+          <t xml:space="preserve">bond_39_down.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E271" t="inlineStr" s="2">
@@ -8975,14 +8975,14 @@
       </c>
       <c r="F271" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">どうして…以前のように言葉をくれないの…</t>
+          <t xml:space="preserve">考えると苦しいの…もう無理…</t>
         </is>
       </c>
     </row>
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.emotional.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -8997,7 +8997,7 @@
       </c>
       <c r="D272" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.emotional.seductive[1]</t>
+          <t xml:space="preserve">bond_59_down.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E272" t="inlineStr" s="2">
@@ -9007,14 +9007,14 @@
       </c>
       <c r="F272" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">放っておけないの…もう</t>
+          <t xml:space="preserve">離れていく…嫌よ…こんなの…</t>
         </is>
       </c>
     </row>
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.emotional.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.emotional.seductive[2]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -9029,7 +9029,7 @@
       </c>
       <c r="D273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.emotional.seductive[1]</t>
+          <t xml:space="preserve">bond_59_down.emotional.seductive[2]</t>
         </is>
       </c>
       <c r="E273" t="inlineStr" s="2">
@@ -9039,14 +9039,14 @@
       </c>
       <c r="F273" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この人のためなら何でもできるの…！ 絶対に守るわ…！</t>
+          <t xml:space="preserve">どうして…以前のように言葉をくれないの…</t>
         </is>
       </c>
     </row>
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.emotional.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -9061,7 +9061,7 @@
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.emotional.seductive[2]</t>
+          <t xml:space="preserve">bond_60_up.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E274" t="inlineStr" s="2">
@@ -9071,14 +9071,14 @@
       </c>
       <c r="F274" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">巡り合えたこと、心から幸せなの…！</t>
+          <t xml:space="preserve">放っておけないの…もう</t>
         </is>
       </c>
     </row>
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.emotional.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -9093,7 +9093,7 @@
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.emotional.seductive[1]</t>
+          <t xml:space="preserve">bond_80_up.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E275" t="inlineStr" s="2">
@@ -9103,14 +9103,14 @@
       </c>
       <c r="F275" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">因縁…終わっちゃったのね…少し寂しい…</t>
+          <t xml:space="preserve">この人のためなら何でもできるの…！ 絶対に守るわ…！</t>
         </is>
       </c>
     </row>
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.emotional.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.emotional.seductive[2]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -9125,7 +9125,7 @@
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.emotional.seductive[2]</t>
+          <t xml:space="preserve">bond_80_up.emotional.seductive[2]</t>
         </is>
       </c>
       <c r="E276" t="inlineStr" s="2">
@@ -9135,14 +9135,14 @@
       </c>
       <c r="F276" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……あの熱さが消えていくわ。これでいいのかしら…</t>
+          <t xml:space="preserve">巡り合えたこと、心から幸せなの…！</t>
         </is>
       </c>
     </row>
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.emotional.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9157,7 +9157,7 @@
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.emotional.seductive[1]</t>
+          <t xml:space="preserve">rivalry_29_down.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="2">
@@ -9167,14 +9167,14 @@
       </c>
       <c r="F277" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">絶対に負けないわ…！ 絶対に…！</t>
+          <t xml:space="preserve">因縁…終わっちゃったのね…少し寂しい…</t>
         </is>
       </c>
     </row>
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.emotional.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.emotional.seductive[2]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9189,7 +9189,7 @@
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.emotional.seductive[2]</t>
+          <t xml:space="preserve">rivalry_29_down.emotional.seductive[2]</t>
         </is>
       </c>
       <c r="E278" t="inlineStr" s="2">
@@ -9199,14 +9199,14 @@
       </c>
       <c r="F278" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">考えるだけで胸が熱くなるの…！</t>
+          <t xml:space="preserve">……あの熱さが消えていくわ。これでいいのかしら…</t>
         </is>
       </c>
     </row>
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.emotional.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9221,7 +9221,7 @@
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.emotional.seductive[1]</t>
+          <t xml:space="preserve">rivalry_30_up.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E279" t="inlineStr" s="2">
@@ -9231,14 +9231,14 @@
       </c>
       <c r="F279" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くっ…考えると熱くなるの…！</t>
+          <t xml:space="preserve">絶対に負けないわ…！ 絶対に…！</t>
         </is>
       </c>
     </row>
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.emotional.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.emotional.seductive[2]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9253,7 +9253,7 @@
       </c>
       <c r="D280" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.emotional.seductive[2]</t>
+          <t xml:space="preserve">rivalry_30_up.emotional.seductive[2]</t>
         </is>
       </c>
       <c r="E280" t="inlineStr" s="2">
@@ -9263,14 +9263,14 @@
       </c>
       <c r="F280" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">絶対に…超えてみせるわ…！！</t>
+          <t xml:space="preserve">考えるだけで胸が熱くなるの…！</t>
         </is>
       </c>
     </row>
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.emotional.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9285,7 +9285,7 @@
       </c>
       <c r="D281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.emotional.seductive[1]</t>
+          <t xml:space="preserve">rivalry_50_up.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E281" t="inlineStr" s="2">
@@ -9295,14 +9295,14 @@
       </c>
       <c r="F281" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの出会いがなければ今の私はいなかった…！</t>
+          <t xml:space="preserve">くっ…考えると熱くなるの…！</t>
         </is>
       </c>
     </row>
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.emotional.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.emotional.seductive[2]</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -9317,7 +9317,7 @@
       </c>
       <c r="D282" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.emotional.seductive[2]</t>
+          <t xml:space="preserve">rivalry_50_up.emotional.seductive[2]</t>
         </is>
       </c>
       <c r="E282" t="inlineStr" s="2">
@@ -9327,14 +9327,14 @@
       </c>
       <c r="F282" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この因縁に終わりなんてないわ…！ 永遠に戦い続けるの…！</t>
+          <t xml:space="preserve">絶対に…超えてみせるわ…！！</t>
         </is>
       </c>
     </row>
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.emotional.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -9349,7 +9349,7 @@
       </c>
       <c r="D283" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.emotional.seductive[1]</t>
+          <t xml:space="preserve">rivalry_70_up.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E283" t="inlineStr" s="2">
@@ -9359,14 +9359,14 @@
       </c>
       <c r="F283" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みんなのこと…大好きよ…！ この団体のために全力を尽くすわ…！</t>
+          <t xml:space="preserve">あの出会いがなければ今の私はいなかった…！</t>
         </is>
       </c>
     </row>
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.emotional.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.emotional.seductive[2]</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -9381,7 +9381,7 @@
       </c>
       <c r="D284" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.emotional.seductive[2]</t>
+          <t xml:space="preserve">rivalry_70_up.emotional.seductive[2]</t>
         </is>
       </c>
       <c r="E284" t="inlineStr" s="2">
@@ -9391,14 +9391,14 @@
       </c>
       <c r="F284" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここで出会えた仲間は宝物なの…絶対に裏切らないわ…！</t>
+          <t xml:space="preserve">この因縁に終わりなんてないわ…！ 永遠に戦い続けるの…！</t>
         </is>
       </c>
     </row>
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.emotional.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -9413,7 +9413,7 @@
       </c>
       <c r="D285" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.emotional.seductive[1]</t>
+          <t xml:space="preserve">trust_above_75.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E285" t="inlineStr" s="2">
@@ -9423,14 +9423,14 @@
       </c>
       <c r="F285" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう…信じられないわ…！ どうして…！</t>
+          <t xml:space="preserve">みんなのこと…大好きよ…！ この団体のために全力を尽くすわ…！</t>
         </is>
       </c>
     </row>
     <row r="286" ht="40" customHeight="1">
       <c r="A286" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.emotional.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.emotional.seductive[2]</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -9445,7 +9445,7 @@
       </c>
       <c r="D286" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.emotional.seductive[2]</t>
+          <t xml:space="preserve">trust_above_75.emotional.seductive[2]</t>
         </is>
       </c>
       <c r="E286" t="inlineStr" s="2">
@@ -9455,14 +9455,14 @@
       </c>
       <c r="F286" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">裏切られたのね…全部…偽りだったの…？</t>
+          <t xml:space="preserve">ここで出会えた仲間は宝物なの…絶対に裏切らないわ…！</t>
         </is>
       </c>
     </row>
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.emotional.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -9477,7 +9477,7 @@
       </c>
       <c r="D287" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.emotional.seductive[1]</t>
+          <t xml:space="preserve">trust_below_20.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E287" t="inlineStr" s="2">
@@ -9487,14 +9487,14 @@
       </c>
       <c r="F287" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">不安なの…これでいいのかしら…？ 私、忘れられてない…？</t>
+          <t xml:space="preserve">もう…信じられないわ…！ どうして…！</t>
         </is>
       </c>
     </row>
     <row r="288" ht="40" customHeight="1">
       <c r="A288" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.seductive.emotional[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.emotional.seductive[2]</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
@@ -9504,12 +9504,12 @@
       </c>
       <c r="C288" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D288" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.goodLoss.seductive.emotional[1]</t>
+          <t xml:space="preserve">trust_below_20.emotional.seductive[2]</t>
         </is>
       </c>
       <c r="E288" t="inlineStr" s="2">
@@ -9519,14 +9519,14 @@
       </c>
       <c r="F288" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けたけど……っ……ふふ、出し切れたの……</t>
+          <t xml:space="preserve">裏切られたのね…全部…偽りだったの…？</t>
         </is>
       </c>
     </row>
     <row r="289" ht="40" customHeight="1">
       <c r="A289" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.seductive.emotional[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
@@ -9536,12 +9536,12 @@
       </c>
       <c r="C289" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D289" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.greatWin.seductive.emotional[1]</t>
+          <t xml:space="preserve">trust_below_35.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E289" t="inlineStr" s="2">
@@ -9551,14 +9551,14 @@
       </c>
       <c r="F289" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高の勝利……っ……ふふ、震えてるの……</t>
+          <t xml:space="preserve">不安なの…これでいいのかしら…？ 私、忘れられてない…？</t>
         </is>
       </c>
     </row>
     <row r="290" ht="40" customHeight="1">
       <c r="A290" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.seductive.emotional[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
@@ -9573,7 +9573,7 @@
       </c>
       <c r="D290" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.loss.seductive.emotional[1]</t>
+          <t xml:space="preserve">GL-01.goodLoss.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E290" t="inlineStr" s="2">
@@ -9583,14 +9583,14 @@
       </c>
       <c r="F290" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けた……っ……悔しい……</t>
+          <t xml:space="preserve">負けたけど……っ……ふふ、出し切れたの……</t>
         </is>
       </c>
     </row>
     <row r="291" ht="40" customHeight="1">
       <c r="A291" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.seductive.emotional[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
@@ -9605,7 +9605,7 @@
       </c>
       <c r="D291" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.win.seductive.emotional[1]</t>
+          <t xml:space="preserve">GL-01.greatWin.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E291" t="inlineStr" s="2">
@@ -9615,14 +9615,14 @@
       </c>
       <c r="F291" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ったわ……っ……ふふ、嬉しい……</t>
+          <t xml:space="preserve">最高の勝利……っ……ふふ、震えてるの……</t>
         </is>
       </c>
     </row>
     <row r="292" ht="40" customHeight="1">
       <c r="A292" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.seductive.emotional[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
@@ -9637,7 +9637,7 @@
       </c>
       <c r="D292" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.seductive.emotional[1]</t>
+          <t xml:space="preserve">GL-01.loss.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E292" t="inlineStr" s="2">
@@ -9647,14 +9647,14 @@
       </c>
       <c r="F292" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日は……っ……ふふ、よろしくね……</t>
+          <t xml:space="preserve">負けた……っ……悔しい……</t>
         </is>
       </c>
     </row>
     <row r="293" ht="40" customHeight="1">
       <c r="A293" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.seductive.emotional[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
@@ -9669,7 +9669,7 @@
       </c>
       <c r="D293" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.down.seductive.emotional[1]</t>
+          <t xml:space="preserve">GL-01.win.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E293" t="inlineStr" s="2">
@@ -9679,14 +9679,14 @@
       </c>
       <c r="F293" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うまくいかない……っ……どうしてかしら……</t>
+          <t xml:space="preserve">勝ったわ……っ……ふふ、嬉しい……</t>
         </is>
       </c>
     </row>
     <row r="294" ht="40" customHeight="1">
       <c r="A294" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.seductive.emotional[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
@@ -9701,7 +9701,7 @@
       </c>
       <c r="D294" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.up.seductive.emotional[1]</t>
+          <t xml:space="preserve">GL-02.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E294" t="inlineStr" s="2">
@@ -9711,14 +9711,14 @@
       </c>
       <c r="F294" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">なんだか調子いいの……っ……ふふ……</t>
+          <t xml:space="preserve">今日は……っ……ふふ、よろしくね……</t>
         </is>
       </c>
     </row>
     <row r="295" ht="40" customHeight="1">
       <c r="A295" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.seductive.emotional[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="2">
@@ -9733,7 +9733,7 @@
       </c>
       <c r="D295" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-04.seductive.emotional[1]</t>
+          <t xml:space="preserve">GL-03.down.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E295" t="inlineStr" s="2">
@@ -9743,14 +9743,14 @@
       </c>
       <c r="F295" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習するわ……っ……ふふ……</t>
+          <t xml:space="preserve">うまくいかない……っ……どうしてかしら……</t>
         </is>
       </c>
     </row>
     <row r="296" ht="40" customHeight="1">
       <c r="A296" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.seductive.emotional[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B296" t="inlineStr" s="2">
@@ -9765,7 +9765,7 @@
       </c>
       <c r="D296" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-05.seductive.emotional[1]</t>
+          <t xml:space="preserve">GL-03.up.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E296" t="inlineStr" s="2">
@@ -9775,14 +9775,14 @@
       </c>
       <c r="F296" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">大丈夫よ……っ……ふふ、心配しないで……</t>
+          <t xml:space="preserve">なんだか調子いいの……っ……ふふ……</t>
         </is>
       </c>
     </row>
     <row r="297" ht="40" customHeight="1">
       <c r="A297" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.seductive.emotional[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B297" t="inlineStr" s="2">
@@ -9797,7 +9797,7 @@
       </c>
       <c r="D297" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.seductive.emotional[1]</t>
+          <t xml:space="preserve">GL-04.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E297" t="inlineStr" s="2">
@@ -9807,14 +9807,14 @@
       </c>
       <c r="F297" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みんなと一緒だと……っ……ふふ、安心するの……</t>
+          <t xml:space="preserve">練習するわ……っ……ふふ……</t>
         </is>
       </c>
     </row>
     <row r="298" ht="40" customHeight="1">
       <c r="A298" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.seductive.emotional[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B298" t="inlineStr" s="2">
@@ -9829,7 +9829,7 @@
       </c>
       <c r="D298" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-07.seductive.emotional[1]</t>
+          <t xml:space="preserve">GL-05.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E298" t="inlineStr" s="2">
@@ -9839,14 +9839,14 @@
       </c>
       <c r="F298" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お客さんがいっぱい……っ……ふふ、燃えるわね……</t>
+          <t xml:space="preserve">大丈夫よ……っ……ふふ、心配しないで……</t>
         </is>
       </c>
     </row>
     <row r="299" ht="40" customHeight="1">
       <c r="A299" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.seductive.emotional[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B299" t="inlineStr" s="2">
@@ -9861,7 +9861,7 @@
       </c>
       <c r="D299" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.seductive.emotional[1]</t>
+          <t xml:space="preserve">GL-06.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E299" t="inlineStr" s="2">
@@ -9871,14 +9871,14 @@
       </c>
       <c r="F299" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">体調は大丈夫よ……っ……ふふ、心配いらない……</t>
+          <t xml:space="preserve">みんなと一緒だと……っ……ふふ、安心するの……</t>
         </is>
       </c>
     </row>
     <row r="300" ht="40" customHeight="1">
       <c r="A300" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.seductive.emotional[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B300" t="inlineStr" s="2">
@@ -9893,7 +9893,7 @@
       </c>
       <c r="D300" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-09.seductive.emotional[1]</t>
+          <t xml:space="preserve">GL-07.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E300" t="inlineStr" s="2">
@@ -9903,14 +9903,14 @@
       </c>
       <c r="F300" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次の試合……っ……ふふ、楽しみだわ……</t>
+          <t xml:space="preserve">お客さんがいっぱい……っ……ふふ、燃えるわね……</t>
         </is>
       </c>
     </row>
     <row r="301" ht="40" customHeight="1">
       <c r="A301" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.seductive.emotional[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B301" t="inlineStr" s="2">
@@ -9925,7 +9925,7 @@
       </c>
       <c r="D301" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.seductive.emotional[1]</t>
+          <t xml:space="preserve">GL-08.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E301" t="inlineStr" s="2">
@@ -9935,14 +9935,14 @@
       </c>
       <c r="F301" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとう……っ……ふふ、嬉しい……</t>
+          <t xml:space="preserve">体調は大丈夫よ……っ……ふふ、心配いらない……</t>
         </is>
       </c>
     </row>
     <row r="302" ht="40" customHeight="1">
       <c r="A302" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.seductive.emotional[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B302" t="inlineStr" s="2">
@@ -9952,12 +9952,12 @@
       </c>
       <c r="C302" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D302" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.emotional[1]</t>
+          <t xml:space="preserve">GL-09.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E302" t="inlineStr" s="2">
@@ -9967,14 +9967,14 @@
       </c>
       <c r="F302" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勢いが止まったわ……っ……ふふ、また始めればいいのよ……</t>
+          <t xml:space="preserve">次の試合……っ……ふふ、楽しみだわ……</t>
         </is>
       </c>
     </row>
     <row r="303" ht="40" customHeight="1">
       <c r="A303" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.seductive.emotional[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B303" t="inlineStr" s="2">
@@ -9984,29 +9984,29 @@
       </c>
       <c r="C303" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D303" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.seductive.emotional[1]</t>
+          <t xml:space="preserve">GL-10.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E303" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F303" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">身体、もう震えてるの…っ…ふふ、でも最後まで立つわ</t>
+          <t xml:space="preserve">ありがとう……っ……ふふ、嬉しい……</t>
         </is>
       </c>
     </row>
     <row r="304" ht="40" customHeight="1">
       <c r="A304" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.seductive.emotional[2]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B304" t="inlineStr" s="2">
@@ -10016,29 +10016,29 @@
       </c>
       <c r="C304" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D304" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.seductive.emotional[2]</t>
+          <t xml:space="preserve">seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E304" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F304" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで来たのね…っ…最後の舞台、全部ぶつけるわ</t>
+          <t xml:space="preserve">勢いが止まったわ……っ……ふふ、また始めればいいのよ……</t>
         </is>
       </c>
     </row>
     <row r="305" ht="40" customHeight="1">
       <c r="A305" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.seductive.emotional[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B305" t="inlineStr" s="2">
@@ -10053,7 +10053,7 @@
       </c>
       <c r="D305" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.seductive.emotional[1]</t>
+          <t xml:space="preserve">preFinal.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E305" t="inlineStr" s="2">
@@ -10063,14 +10063,14 @@
       </c>
       <c r="F305" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お相手は誰かしら…っ…ふふ、もう身体が疼いてるの</t>
+          <t xml:space="preserve">身体、もう震えてるの…っ…ふふ、でも最後まで立つわ</t>
         </is>
       </c>
     </row>
     <row r="306" ht="40" customHeight="1">
       <c r="A306" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.seductive.emotional[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B306" t="inlineStr" s="2">
@@ -10085,7 +10085,7 @@
       </c>
       <c r="D306" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.seductive.emotional[2]</t>
+          <t xml:space="preserve">preFinal.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E306" t="inlineStr" s="2">
@@ -10095,14 +10095,14 @@
       </c>
       <c r="F306" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">早く来てよ…! この昂り、ぶつける相手が欲しいの…!</t>
+          <t xml:space="preserve">ここまで来たのね…っ…最後の舞台、全部ぶつけるわ</t>
         </is>
       </c>
     </row>
     <row r="307" ht="40" customHeight="1">
       <c r="A307" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.seductive.emotional[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B307" t="inlineStr" s="2">
@@ -10117,7 +10117,7 @@
       </c>
       <c r="D307" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.seductive.emotional[1]</t>
+          <t xml:space="preserve">preMatch.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E307" t="inlineStr" s="2">
@@ -10127,14 +10127,14 @@
       </c>
       <c r="F307" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人、落としたわ…っ…はぁ…まだ疼いてるの。次、早く出してよ</t>
+          <t xml:space="preserve">お相手は誰かしら…っ…ふふ、もう身体が疼いてるの</t>
         </is>
       </c>
     </row>
     <row r="308" ht="40" customHeight="1">
       <c r="A308" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.seductive.emotional[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B308" t="inlineStr" s="2">
@@ -10149,7 +10149,7 @@
       </c>
       <c r="D308" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.seductive.emotional[2]</t>
+          <t xml:space="preserve">preMatch.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E308" t="inlineStr" s="2">
@@ -10159,14 +10159,14 @@
       </c>
       <c r="F308" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ立ってる…! この身体、まだ終わってないの…! 次、来なさい…!</t>
+          <t xml:space="preserve">早く来てよ…！ この昂り、ぶつける相手が欲しいの…！</t>
         </is>
       </c>
     </row>
     <row r="309" ht="40" customHeight="1">
       <c r="A309" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.seductive.emotional[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B309" t="inlineStr" s="2">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="C309" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D309" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.seductive.emotional[1]</t>
+          <t xml:space="preserve">survivor.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E309" t="inlineStr" s="2">
@@ -10191,14 +10191,14 @@
       </c>
       <c r="F309" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">三人で勝ったの……！ この感動は……一人じゃ味わえないわ……</t>
+          <t xml:space="preserve">一人、落としたわ…っ…はぁ…まだ疼いてるの。次、早く出してよ</t>
         </is>
       </c>
     </row>
     <row r="310" ht="40" customHeight="1">
       <c r="A310" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.seductive.emotional[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B310" t="inlineStr" s="2">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="C310" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D310" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.seductive.emotional[2]</t>
+          <t xml:space="preserve">survivor.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E310" t="inlineStr" s="2">
@@ -10223,14 +10223,14 @@
       </c>
       <c r="F310" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲間が繋いでくれた想い……最後まで、手放さなかったよ……！</t>
+          <t xml:space="preserve">まだ立ってる…！ この身体、まだ終わってないの…！ 次、来なさい…！</t>
         </is>
       </c>
     </row>
     <row r="311" ht="40" customHeight="1">
       <c r="A311" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.seductive.emotional[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B311" t="inlineStr" s="2">
@@ -10245,7 +10245,7 @@
       </c>
       <c r="D311" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.seductive.emotional[1]</t>
+          <t xml:space="preserve">champion.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E311" t="inlineStr" s="2">
@@ -10255,14 +10255,14 @@
       </c>
       <c r="F311" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この賞じゃ……心は満たされないのよ……！ 次は全部、奪い返すから……</t>
+          <t xml:space="preserve">三人で勝ったの……！ この感動は……一人じゃ味わえないわ……</t>
         </is>
       </c>
     </row>
     <row r="312" ht="40" customHeight="1">
       <c r="A312" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.seductive.emotional[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B312" t="inlineStr" s="2">
@@ -10277,7 +10277,7 @@
       </c>
       <c r="D312" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.seductive.emotional[2]</t>
+          <t xml:space="preserve">champion.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E312" t="inlineStr" s="2">
@@ -10287,14 +10287,14 @@
       </c>
       <c r="F312" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人で輝いても寂しいだけ……！ 次は……三人で、ね……！</t>
+          <t xml:space="preserve">仲間が繋いでくれた想い……最後まで、手放さなかったよ……！</t>
         </is>
       </c>
     </row>
     <row r="313" ht="40" customHeight="1">
       <c r="A313" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.seductive.emotional[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B313" t="inlineStr" s="2">
@@ -10309,7 +10309,7 @@
       </c>
       <c r="D313" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.seductive.emotional[1]</t>
+          <t xml:space="preserve">defiant.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E313" t="inlineStr" s="2">
@@ -10319,14 +10319,14 @@
       </c>
       <c r="F313" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう身体が動かない……でも、最後に立ってたのは私よ……！ 見届けてくれた？</t>
+          <t xml:space="preserve">この賞じゃ……心は満たされないのよ……！ 次は全部、奪い返すから……</t>
         </is>
       </c>
     </row>
     <row r="314" ht="40" customHeight="1">
       <c r="A314" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.seductive.emotional[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B314" t="inlineStr" s="2">
@@ -10341,7 +10341,7 @@
       </c>
       <c r="D314" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.seductive.emotional[2]</t>
+          <t xml:space="preserve">defiant.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E314" t="inlineStr" s="2">
@@ -10351,14 +10351,14 @@
       </c>
       <c r="F314" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何人来ても倒れなかった……！ この身体が、全部証明してるでしょ……？</t>
+          <t xml:space="preserve">一人で輝いても寂しいだけ……！ 次は……三人で、ね……！</t>
         </is>
       </c>
     </row>
     <row r="315" ht="40" customHeight="1">
       <c r="A315" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.seductive.emotional[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B315" t="inlineStr" s="2">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="C315" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D315" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.seductive.emotional[1]</t>
+          <t xml:space="preserve">gauntlet.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E315" t="inlineStr" s="2">
@@ -10383,14 +10383,14 @@
       </c>
       <c r="F315" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">優勝……っ……ふふ、わたし、頂点に立ったのね……!</t>
+          <t xml:space="preserve">もう身体が動かない……でも、最後に立ってたのは私よ……！ 見届けてくれた？</t>
         </is>
       </c>
     </row>
     <row r="316" ht="40" customHeight="1">
       <c r="A316" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.seductive.emotional[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B316" t="inlineStr" s="2">
@@ -10400,12 +10400,12 @@
       </c>
       <c r="C316" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D316" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.seductive.emotional[2]</t>
+          <t xml:space="preserve">gauntlet.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E316" t="inlineStr" s="2">
@@ -10415,14 +10415,14 @@
       </c>
       <c r="F316" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この景色……っ……ふふ、忘れないわ……</t>
+          <t xml:space="preserve">何人来ても倒れなかった……！ この身体が、全部証明してるでしょ……？</t>
         </is>
       </c>
     </row>
     <row r="317" ht="40" customHeight="1">
       <c r="A317" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.seductive.emotional[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B317" t="inlineStr" s="2">
@@ -10437,7 +10437,7 @@
       </c>
       <c r="D317" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.seductive.emotional[1]</t>
+          <t xml:space="preserve">champion.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E317" t="inlineStr" s="2">
@@ -10447,14 +10447,14 @@
       </c>
       <c r="F317" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けたわ……っ……悔しい……でも、いい経験だった……</t>
+          <t xml:space="preserve">優勝……っ……ふふ、私、頂点に立ったのね……！</t>
         </is>
       </c>
     </row>
     <row r="318" ht="40" customHeight="1">
       <c r="A318" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.seductive.emotional[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B318" t="inlineStr" s="2">
@@ -10469,7 +10469,7 @@
       </c>
       <c r="D318" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.seductive.emotional[2]</t>
+          <t xml:space="preserve">champion.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E318" t="inlineStr" s="2">
@@ -10479,14 +10479,14 @@
       </c>
       <c r="F318" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">リベンジするわ……っ……ふふ、必ず……</t>
+          <t xml:space="preserve">この景色……っ……ふふ、忘れないわ……</t>
         </is>
       </c>
     </row>
     <row r="319" ht="40" customHeight="1">
       <c r="A319" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.seductive.emotional[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B319" t="inlineStr" s="2">
@@ -10501,7 +10501,7 @@
       </c>
       <c r="D319" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.seductive.emotional[1]</t>
+          <t xml:space="preserve">postLose.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E319" t="inlineStr" s="2">
@@ -10511,14 +10511,14 @@
       </c>
       <c r="F319" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝った……っ……ふふ、まだまだ行けるわ……</t>
+          <t xml:space="preserve">負けたわ……っ……悔しい……でも、いい経験だった……</t>
         </is>
       </c>
     </row>
     <row r="320" ht="40" customHeight="1">
       <c r="A320" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.seductive.emotional[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B320" t="inlineStr" s="2">
@@ -10533,7 +10533,7 @@
       </c>
       <c r="D320" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.seductive.emotional[2]</t>
+          <t xml:space="preserve">postLose.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E320" t="inlineStr" s="2">
@@ -10543,14 +10543,14 @@
       </c>
       <c r="F320" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい感じよ……っ……ふふ……</t>
+          <t xml:space="preserve">リベンジするわ……っ……ふふ、必ず……</t>
         </is>
       </c>
     </row>
     <row r="321" ht="40" customHeight="1">
       <c r="A321" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.seductive.emotional[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B321" t="inlineStr" s="2">
@@ -10565,7 +10565,7 @@
       </c>
       <c r="D321" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.seductive.emotional[1]</t>
+          <t xml:space="preserve">postMatchWin.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E321" t="inlineStr" s="2">
@@ -10575,14 +10575,14 @@
       </c>
       <c r="F321" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ち上がったわ……っ……ふふ、ここまで来られたの……</t>
+          <t xml:space="preserve">勝った……っ……ふふ、まだまだ行けるわ……</t>
         </is>
       </c>
     </row>
     <row r="322" ht="40" customHeight="1">
       <c r="A322" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.seductive.emotional[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B322" t="inlineStr" s="2">
@@ -10597,7 +10597,7 @@
       </c>
       <c r="D322" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.seductive.emotional[2]</t>
+          <t xml:space="preserve">postMatchWin.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E322" t="inlineStr" s="2">
@@ -10607,14 +10607,14 @@
       </c>
       <c r="F322" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もっと上を目指すわ……っ……ふふ……</t>
+          <t xml:space="preserve">いい感じよ……っ……ふふ……</t>
         </is>
       </c>
     </row>
     <row r="323" ht="40" customHeight="1">
       <c r="A323" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.seductive.emotional[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B323" t="inlineStr" s="2">
@@ -10629,7 +10629,7 @@
       </c>
       <c r="D323" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.seductive.emotional[1]</t>
+          <t xml:space="preserve">postWin.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E323" t="inlineStr" s="2">
@@ -10639,14 +10639,14 @@
       </c>
       <c r="F323" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決勝戦……っ……ふふ、ここまで来たのね……</t>
+          <t xml:space="preserve">勝ち上がったわ……っ……ふふ、ここまで来られたの……</t>
         </is>
       </c>
     </row>
     <row r="324" ht="40" customHeight="1">
       <c r="A324" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.seductive.emotional[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B324" t="inlineStr" s="2">
@@ -10661,7 +10661,7 @@
       </c>
       <c r="D324" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.seductive.emotional[2]</t>
+          <t xml:space="preserve">postWin.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E324" t="inlineStr" s="2">
@@ -10671,14 +10671,14 @@
       </c>
       <c r="F324" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高の舞台ね……っ……ふふ、震えてるの……</t>
+          <t xml:space="preserve">もっと上を目指すわ……っ……ふふ……</t>
         </is>
       </c>
     </row>
     <row r="325" ht="40" customHeight="1">
       <c r="A325" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.seductive.emotional[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B325" t="inlineStr" s="2">
@@ -10693,7 +10693,7 @@
       </c>
       <c r="D325" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.seductive.emotional[1]</t>
+          <t xml:space="preserve">preFinal.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E325" t="inlineStr" s="2">
@@ -10703,14 +10703,14 @@
       </c>
       <c r="F325" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">試合前……っ……ふふ、心臓がドキドキしてるの……</t>
+          <t xml:space="preserve">決勝戦……っ……ふふ、ここまで来たのね……</t>
         </is>
       </c>
     </row>
     <row r="326" ht="40" customHeight="1">
       <c r="A326" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.seductive.emotional[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B326" t="inlineStr" s="2">
@@ -10725,7 +10725,7 @@
       </c>
       <c r="D326" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.seductive.emotional[2]</t>
+          <t xml:space="preserve">preFinal.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E326" t="inlineStr" s="2">
@@ -10735,14 +10735,14 @@
       </c>
       <c r="F326" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">楽しんでくるわね……っ……ふふ……</t>
+          <t xml:space="preserve">最高の舞台ね……っ……ふふ、震えてるの……</t>
         </is>
       </c>
     </row>
     <row r="327" ht="40" customHeight="1">
       <c r="A327" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.seductive.emotional[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B327" t="inlineStr" s="2">
@@ -10757,7 +10757,7 @@
       </c>
       <c r="D327" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.seductive.emotional[1]</t>
+          <t xml:space="preserve">preMatch.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E327" t="inlineStr" s="2">
@@ -10767,14 +10767,14 @@
       </c>
       <c r="F327" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ジュニア大会に……っ……ふふ、わたしを選んでくれたのね、嬉しい……</t>
+          <t xml:space="preserve">試合前……っ……ふふ、心臓がドキドキしてるの……</t>
         </is>
       </c>
     </row>
     <row r="328" ht="40" customHeight="1">
       <c r="A328" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.seductive.emotional[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B328" t="inlineStr" s="2">
@@ -10789,7 +10789,7 @@
       </c>
       <c r="D328" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.seductive.emotional[2]</t>
+          <t xml:space="preserve">preMatch.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E328" t="inlineStr" s="2">
@@ -10799,14 +10799,14 @@
       </c>
       <c r="F328" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">楽しみだわ……っ……ふふ、燃えてきたの……</t>
+          <t xml:space="preserve">楽しんでくるわね……っ……ふふ……</t>
         </is>
       </c>
     </row>
     <row r="329" ht="40" customHeight="1">
       <c r="A329" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.seductive.emotional[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B329" t="inlineStr" s="2">
@@ -10816,12 +10816,12 @@
       </c>
       <c r="C329" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D329" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.emotional[1]</t>
+          <t xml:space="preserve">summon.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E329" t="inlineStr" s="2">
@@ -10831,14 +10831,14 @@
       </c>
       <c r="F329" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの子が相手……っ……ふふ、燃えてきたわ……</t>
+          <t xml:space="preserve">ジュニア大会に……っ……ふふ、私を選んでくれたのね、嬉しい……</t>
         </is>
       </c>
     </row>
     <row r="330" ht="40" customHeight="1">
       <c r="A330" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.seductive.emotional[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B330" t="inlineStr" s="2">
@@ -10848,12 +10848,12 @@
       </c>
       <c r="C330" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D330" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.emotional[1]</t>
+          <t xml:space="preserve">summon.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E330" t="inlineStr" s="2">
@@ -10863,14 +10863,14 @@
       </c>
       <c r="F330" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">嬉しい……っ……!最高の舞台で勝てた……この瞬間を、ずっと忘れないわ……!</t>
+          <t xml:space="preserve">楽しみだわ……っ……ふふ、燃えてきたの……</t>
         </is>
       </c>
     </row>
     <row r="331" ht="40" customHeight="1">
       <c r="A331" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.seductive.emotional[1]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B331" t="inlineStr" s="2">
@@ -10880,7 +10880,7 @@
       </c>
       <c r="C331" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D331" t="inlineStr" s="12">
@@ -10895,14 +10895,14 @@
       </c>
       <c r="F331" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">団体として挑むわ……っ……ふふ、燃えるわね……</t>
+          <t xml:space="preserve">あの子が相手……っ……ふふ、燃えてきたわ……</t>
         </is>
       </c>
     </row>
     <row r="332" ht="40" customHeight="1">
       <c r="A332" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.seductive.emotional[2]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B332" t="inlineStr" s="2">
@@ -10912,12 +10912,12 @@
       </c>
       <c r="C332" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D332" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.emotional[2]</t>
+          <t xml:space="preserve">seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E332" t="inlineStr" s="2">
@@ -10927,14 +10927,14 @@
       </c>
       <c r="F332" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みんなで戦うわ……っ……ふふ……</t>
+          <t xml:space="preserve">嬉しい……っ……！最高の舞台で勝てた……この瞬間を、ずっと忘れないわ……！</t>
         </is>
       </c>
     </row>
     <row r="333" ht="40" customHeight="1">
       <c r="A333" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.seductive.emotional[1]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B333" t="inlineStr" s="2">
@@ -10944,7 +10944,7 @@
       </c>
       <c r="C333" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D333" t="inlineStr" s="12">
@@ -10959,14 +10959,14 @@
       </c>
       <c r="F333" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ごめんなさい……っ……今回は遠慮するわ……</t>
+          <t xml:space="preserve">団体として挑むわ……っ……ふふ、燃えるわね……</t>
         </is>
       </c>
     </row>
     <row r="334" ht="40" customHeight="1">
       <c r="A334" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.seductive.emotional[2]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B334" t="inlineStr" s="2">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C334" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D334" t="inlineStr" s="12">
@@ -10991,14 +10991,14 @@
       </c>
       <c r="F334" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">またの機会に……っ……ふふ……</t>
+          <t xml:space="preserve">みんなで戦うわ……っ……ふふ……</t>
         </is>
       </c>
     </row>
     <row r="335" ht="40" customHeight="1">
       <c r="A335" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.seductive.emotional[1]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B335" t="inlineStr" s="2">
@@ -11008,12 +11008,12 @@
       </c>
       <c r="C335" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D335" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.seductive.emotional[1]</t>
+          <t xml:space="preserve">seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E335" t="inlineStr" s="2">
@@ -11023,14 +11023,14 @@
       </c>
       <c r="F335" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けたわ……っ……ふふ、悔しい……</t>
+          <t xml:space="preserve">ごめんなさい……っ……今回は遠慮するわ……</t>
         </is>
       </c>
     </row>
     <row r="336" ht="40" customHeight="1">
       <c r="A336" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.seductive.emotional[2]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B336" t="inlineStr" s="2">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="C336" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D336" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.seductive.emotional[2]</t>
+          <t xml:space="preserve">seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E336" t="inlineStr" s="2">
@@ -11055,14 +11055,14 @@
       </c>
       <c r="F336" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次は絶対に……っ……ふふ、リベンジするわ……</t>
+          <t xml:space="preserve">またの機会に……っ……ふふ……</t>
         </is>
       </c>
     </row>
     <row r="337" ht="40" customHeight="1">
       <c r="A337" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.seductive.emotional[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B337" t="inlineStr" s="2">
@@ -11077,7 +11077,7 @@
       </c>
       <c r="D337" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.seductive.emotional[1]</t>
+          <t xml:space="preserve">result_lose.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E337" t="inlineStr" s="2">
@@ -11087,14 +11087,14 @@
       </c>
       <c r="F337" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝った……っ……ふふ、団体のために戦えて嬉しい……</t>
+          <t xml:space="preserve">負けたわ……っ……ふふ、悔しい……</t>
         </is>
       </c>
     </row>
     <row r="338" ht="40" customHeight="1">
       <c r="A338" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.seductive.emotional[2]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B338" t="inlineStr" s="2">
@@ -11109,7 +11109,7 @@
       </c>
       <c r="D338" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.seductive.emotional[2]</t>
+          <t xml:space="preserve">result_lose.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E338" t="inlineStr" s="2">
@@ -11119,14 +11119,14 @@
       </c>
       <c r="F338" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みんなのおかげよ……っ……ふふ……</t>
+          <t xml:space="preserve">次は絶対に……っ……ふふ、リベンジするわ……</t>
         </is>
       </c>
     </row>
     <row r="339" ht="40" customHeight="1">
       <c r="A339" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.emotional[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B339" t="inlineStr" s="2">
@@ -11136,12 +11136,12 @@
       </c>
       <c r="C339" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D339" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.emotional[1]</t>
+          <t xml:space="preserve">result_win.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E339" t="inlineStr" s="2">
@@ -11151,14 +11151,14 @@
       </c>
       <c r="F339" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝てた…！ 団体のみんなのおかげ…嬉しい…！</t>
+          <t xml:space="preserve">勝った……っ……ふふ、団体のために戦えて嬉しい……</t>
         </is>
       </c>
     </row>
     <row r="340" ht="40" customHeight="1">
       <c r="A340" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.emotional[2]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B340" t="inlineStr" s="2">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="C340" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D340" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.emotional[2]</t>
+          <t xml:space="preserve">result_win.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E340" t="inlineStr" s="2">
@@ -11183,14 +11183,14 @@
       </c>
       <c r="F340" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝てた…みんなのおかげ…嬉しい…！</t>
+          <t xml:space="preserve">みんなのおかげよ……っ……ふふ……</t>
         </is>
       </c>
     </row>
     <row r="341" ht="40" customHeight="1">
       <c r="A341" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.emotional[3]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B341" t="inlineStr" s="2">
@@ -11205,7 +11205,7 @@
       </c>
       <c r="D341" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.emotional[3]</t>
+          <t xml:space="preserve">seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E341" t="inlineStr" s="2">
@@ -11215,14 +11215,14 @@
       </c>
       <c r="F341" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝てた…嬉しい…！ みんなのために頑張れた…！</t>
+          <t xml:space="preserve">勝てた…！ 団体のみんなのおかげ…嬉しい…！</t>
         </is>
       </c>
     </row>
     <row r="342" ht="40" customHeight="1">
       <c r="A342" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.seductive.emotional[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B342" t="inlineStr" s="2">
@@ -11232,29 +11232,29 @@
       </c>
       <c r="C342" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D342" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.seductive.emotional[1]</t>
+          <t xml:space="preserve">seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E342" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F342" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">リングを降りるわ……っ……ふふ、ここで戦えた日々、永遠に忘れない……ありがとう……</t>
+          <t xml:space="preserve">勝てた…みんなのおかげ…嬉しい…！</t>
         </is>
       </c>
     </row>
     <row r="343" ht="40" customHeight="1">
       <c r="A343" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.seductive.emotional[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.emotional[3]</t>
         </is>
       </c>
       <c r="B343" t="inlineStr" s="2">
@@ -11264,59 +11264,123 @@
       </c>
       <c r="C343" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D343" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.emotional[1]</t>
+          <t xml:space="preserve">seductive.emotional[3]</t>
         </is>
       </c>
       <c r="E343" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F343" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">拾われる側になるなんて…っ…参ったわ</t>
+          <t xml:space="preserve">勝てた…嬉しい…！ みんなのために頑張れた…！</t>
         </is>
       </c>
     </row>
     <row r="344" ht="40" customHeight="1">
       <c r="A344" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">ENDING_LINES.fighter.seductive.emotional[1]</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ENDING_LINES</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">fighter.seductive.emotional[1]</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">リングを降りるわ……っ……ふふ、ここで戦えた日々、永遠に忘れない……ありがとう……</t>
+        </is>
+      </c>
+    </row>
+    <row r="345" ht="40" customHeight="1">
+      <c r="A345" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.seductive.emotional[1]</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">seductive.emotional[1]</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">口説かれる側になるなんて…っ…ふふ、いい度胸ね</t>
+        </is>
+      </c>
+    </row>
+    <row r="346" ht="40" customHeight="1">
+      <c r="A346" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES.seductive.emotional[1]</t>
         </is>
       </c>
-      <c r="B344" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C344" t="inlineStr" s="2">
+      <c r="B346" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D344" t="inlineStr" s="12">
+      <c r="D346" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">seductive.emotional[1]</t>
         </is>
       </c>
-      <c r="E344" t="inlineStr" s="2">
+      <c r="E346" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F344" t="inlineStr" s="3">
+      <c r="F346" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">うふふ♪嬉しい♪</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H344"/>
+  <autoFilter ref="A1:H346"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/蠱惑×感情的.xlsx
+++ b/セリフ編集/キャラタイプ別/蠱惑×感情的.xlsx
@@ -284,7 +284,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H346"/>
+  <dimension ref="A1:H353"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -3766,7 +3766,7 @@
     <row r="109" ht="40" customHeight="1">
       <c r="A109" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.seductive.emotional[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_accept.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B109" t="inlineStr" s="2">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="D109" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_accept.seductive.emotional[1]</t>
+          <t xml:space="preserve">decline_accept.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E109" t="inlineStr" s="2">
@@ -3791,14 +3791,14 @@
       </c>
       <c r="F109" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">受けるわ……っ……ふふ、こんなに評価してくれて、嬉しい……</t>
+          <t xml:space="preserve">受けて立つわ。……その数字、来年こちらから塗り替えてあげる。</t>
         </is>
       </c>
     </row>
     <row r="110" ht="40" customHeight="1">
       <c r="A110" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.seductive.emotional[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_hold.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B110" t="inlineStr" s="2">
@@ -3813,7 +3813,7 @@
       </c>
       <c r="D110" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_accept.seductive.emotional[1]</t>
+          <t xml:space="preserve">decline_hold.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E110" t="inlineStr" s="2">
@@ -3823,14 +3823,14 @@
       </c>
       <c r="F110" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">その条件なら……っ……ふふ、いいわよ、受けてあげる……</t>
+          <t xml:space="preserve">……っ……据え置きですって……？　……泣かせないでよ。牙が疼くじゃない。</t>
         </is>
       </c>
     </row>
     <row r="111" ht="40" customHeight="1">
       <c r="A111" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.seductive.emotional[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_open.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B111" t="inlineStr" s="2">
@@ -3845,7 +3845,7 @@
       </c>
       <c r="D111" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_refuse.seductive.emotional[1]</t>
+          <t xml:space="preserve">decline_open.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E111" t="inlineStr" s="2">
@@ -3855,14 +3855,14 @@
       </c>
       <c r="F111" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">考えたけれど……っ……やっぱり、難しいわ、ごめんなさい……</t>
+          <t xml:space="preserve">……そう、もう若い子に回すのね。……その子たちの前で証明してあげる。見ていて。</t>
         </is>
       </c>
     </row>
     <row r="112" ht="40" customHeight="1">
       <c r="A112" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.seductive.emotional[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_strict.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B112" t="inlineStr" s="2">
@@ -3877,7 +3877,7 @@
       </c>
       <c r="D112" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.seductive.emotional[1]</t>
+          <t xml:space="preserve">decline_strict.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E112" t="inlineStr" s="2">
@@ -3887,14 +3887,14 @@
       </c>
       <c r="F112" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">契約の話……っ……聞いてもらいたいことがあるの……</t>
+          <t xml:space="preserve">……ふうん。そこまでやるの。……こっちも遠慮はしないから。覚悟してね。</t>
         </is>
       </c>
     </row>
     <row r="113" ht="40" customHeight="1">
       <c r="A113" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.seductive.emotional[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_voluntary_accept.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B113" t="inlineStr" s="2">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="D113" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_refuse.seductive.emotional[1]</t>
+          <t xml:space="preserve">decline_voluntary_accept.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E113" t="inlineStr" s="2">
@@ -3919,14 +3919,14 @@
       </c>
       <c r="F113" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……っ……ごめんなさい、その条件では納得できないの……</t>
+          <t xml:space="preserve">ええ、そうこなくちゃ。……哀れまれるより、よっぽど気持ちいいわ。</t>
         </is>
       </c>
     </row>
     <row r="114" ht="40" customHeight="1">
       <c r="A114" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.seductive.emotional[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_voluntary_hold.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B114" t="inlineStr" s="2">
@@ -3941,7 +3941,7 @@
       </c>
       <c r="D114" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.seductive.emotional[1]</t>
+          <t xml:space="preserve">decline_voluntary_hold.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E114" t="inlineStr" s="2">
@@ -3951,14 +3951,14 @@
       </c>
       <c r="F114" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もういいわ。何も言いたくないの。……さよなら。</t>
+          <t xml:space="preserve">……っ……そこまで買いかぶるの。……後悔はさせない。覚えておいて。</t>
         </is>
       </c>
     </row>
     <row r="115" ht="40" customHeight="1">
       <c r="A115" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.seductive.emotional[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_voluntary_open.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B115" t="inlineStr" s="2">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="D115" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.seductive.emotional[2]</t>
+          <t xml:space="preserve">decline_voluntary_open.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E115" t="inlineStr" s="2">
@@ -3983,14 +3983,14 @@
       </c>
       <c r="F115" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">どうして……どうしてこんなことになったの。もう無理よ、辞めるわ。</t>
+          <t xml:space="preserve">先に言わせてもらうわ。……盛りは過ぎた。下げていい。……惨めに値切られるのは、ごめんだから。</t>
         </is>
       </c>
     </row>
     <row r="116" ht="40" customHeight="1">
       <c r="A116" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.seductive.emotional[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B116" t="inlineStr" s="2">
@@ -4005,7 +4005,7 @@
       </c>
       <c r="D116" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_listen.seductive.emotional[1]</t>
+          <t xml:space="preserve">raise_accept.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E116" t="inlineStr" s="2">
@@ -4015,14 +4015,14 @@
       </c>
       <c r="F116" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">話だけは聞くわ……っ……それで決めるから……</t>
+          <t xml:space="preserve">受けるわ……っ……ふふ、こんなに評価してくれて、嬉しい……</t>
         </is>
       </c>
     </row>
     <row r="117" ht="40" customHeight="1">
       <c r="A117" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.seductive.emotional[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B117" t="inlineStr" s="2">
@@ -4037,7 +4037,7 @@
       </c>
       <c r="D117" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.seductive.emotional[1]</t>
+          <t xml:space="preserve">raise_negotiate_accept.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E117" t="inlineStr" s="2">
@@ -4047,14 +4047,14 @@
       </c>
       <c r="F117" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">他から声がかかってるの……っ……ふふ、どうしようかしら……</t>
+          <t xml:space="preserve">その条件なら……っ……ふふ、いいわよ、受けてあげる……</t>
         </is>
       </c>
     </row>
     <row r="118" ht="40" customHeight="1">
       <c r="A118" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.seductive.emotional[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B118" t="inlineStr" s="2">
@@ -4069,7 +4069,7 @@
       </c>
       <c r="D118" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_release.seductive.emotional[1]</t>
+          <t xml:space="preserve">raise_negotiate_refuse.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E118" t="inlineStr" s="2">
@@ -4079,14 +4079,14 @@
       </c>
       <c r="F118" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">移籍させて……っ……ふふ、新しい場所で輝きたいの……</t>
+          <t xml:space="preserve">考えたけれど……っ……やっぱり、難しいわ、ごめんなさい……</t>
         </is>
       </c>
     </row>
     <row r="119" ht="40" customHeight="1">
       <c r="A119" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.seductive.emotional[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B119" t="inlineStr" s="2">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="D119" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_fail.seductive.emotional[1]</t>
+          <t xml:space="preserve">raise_open.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E119" t="inlineStr" s="2">
@@ -4111,14 +4111,14 @@
       </c>
       <c r="F119" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ごめんなさい……っ……気持ちはもう決まってるの……</t>
+          <t xml:space="preserve">契約の話……っ……聞いてもらいたいことがあるの……</t>
         </is>
       </c>
     </row>
     <row r="120" ht="40" customHeight="1">
       <c r="A120" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.seductive.emotional[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B120" t="inlineStr" s="2">
@@ -4133,7 +4133,7 @@
       </c>
       <c r="D120" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_success.seductive.emotional[1]</t>
+          <t xml:space="preserve">raise_refuse.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E120" t="inlineStr" s="2">
@@ -4143,14 +4143,14 @@
       </c>
       <c r="F120" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">残るわ……っ……ふふ、こんなに引き止められたら、行けないでしょう……</t>
+          <t xml:space="preserve">……っ……ごめんなさい、その条件では納得できないの……</t>
         </is>
       </c>
     </row>
     <row r="121" ht="40" customHeight="1">
       <c r="A121" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.blocked.seductive.emotional[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B121" t="inlineStr" s="2">
@@ -4160,12 +4160,12 @@
       </c>
       <c r="C121" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D121" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">blocked.seductive.emotional[1]</t>
+          <t xml:space="preserve">sudden_departure.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E121" t="inlineStr" s="2">
@@ -4175,14 +4175,14 @@
       </c>
       <c r="F121" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">その話は……っ……ふふ、できないの、ごめんなさい……</t>
+          <t xml:space="preserve">もういいわ。何も言いたくないの。……さよなら。</t>
         </is>
       </c>
     </row>
     <row r="122" ht="40" customHeight="1">
       <c r="A122" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.fail.seductive.emotional[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B122" t="inlineStr" s="2">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="C122" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D122" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fail.seductive.emotional[1]</t>
+          <t xml:space="preserve">sudden_departure.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E122" t="inlineStr" s="2">
@@ -4207,14 +4207,14 @@
       </c>
       <c r="F122" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">残念だけど……っ……今回は無理ね、ごめんなさい……</t>
+          <t xml:space="preserve">どうして……どうしてこんなことになったの。もう無理よ、辞めるわ。</t>
         </is>
       </c>
     </row>
     <row r="123" ht="40" customHeight="1">
       <c r="A123" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.start.seductive.emotional[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B123" t="inlineStr" s="2">
@@ -4224,12 +4224,12 @@
       </c>
       <c r="C123" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D123" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">start.seductive.emotional[1]</t>
+          <t xml:space="preserve">transfer_listen.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E123" t="inlineStr" s="2">
@@ -4239,14 +4239,14 @@
       </c>
       <c r="F123" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">交渉を始めるわ……っ……ふふ、よろしくね……</t>
+          <t xml:space="preserve">話だけは聞くわ……っ……それで決めるから……</t>
         </is>
       </c>
     </row>
     <row r="124" ht="40" customHeight="1">
       <c r="A124" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.success.seductive.emotional[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B124" t="inlineStr" s="2">
@@ -4256,12 +4256,12 @@
       </c>
       <c r="C124" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D124" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">success.seductive.emotional[1]</t>
+          <t xml:space="preserve">transfer_open.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E124" t="inlineStr" s="2">
@@ -4271,14 +4271,14 @@
       </c>
       <c r="F124" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">これで決まりね……っ……ふふ、いい話し合いだったわ……</t>
+          <t xml:space="preserve">他から声がかかってるの……っ……ふふ、どうしようかしら……</t>
         </is>
       </c>
     </row>
     <row r="125" ht="40" customHeight="1">
       <c r="A125" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_ABSTRACT.seductive.emotional[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B125" t="inlineStr" s="2">
@@ -4288,29 +4288,29 @@
       </c>
       <c r="C125" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D125" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_ABSTRACT.seductive.emotional[1]</t>
+          <t xml:space="preserve">transfer_release.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E125" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F125" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、お願い、私たちの子たちを置き去りにしないで。</t>
+          <t xml:space="preserve">移籍させて……っ……ふふ、新しい場所で輝きたいの……</t>
         </is>
       </c>
     </row>
     <row r="126" ht="40" customHeight="1">
       <c r="A126" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MAIN.seductive.emotional[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B126" t="inlineStr" s="2">
@@ -4320,29 +4320,29 @@
       </c>
       <c r="C126" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D126" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_MAIN.seductive.emotional[1]</t>
+          <t xml:space="preserve">transfer_retain_fail.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E126" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F126" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、次のメインは私たちに任せて。中途半端じゃ嫌なの、お願い。</t>
+          <t xml:space="preserve">ごめんなさい……っ……気持ちはもう決まってるの……</t>
         </is>
       </c>
     </row>
     <row r="127" ht="40" customHeight="1">
       <c r="A127" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MONEY.seductive.emotional[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B127" t="inlineStr" s="2">
@@ -4352,29 +4352,29 @@
       </c>
       <c r="C127" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D127" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_MONEY.seductive.emotional[1]</t>
+          <t xml:space="preserve">transfer_retain_success.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E127" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F127" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、お願い、私たちが何を受け取ってるか、もう一度見て。</t>
+          <t xml:space="preserve">残るわ……っ……ふふ、こんなに引き止められたら、行けないでしょう……</t>
         </is>
       </c>
     </row>
     <row r="128" ht="40" customHeight="1">
       <c r="A128" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_RECOGNITION.seductive.emotional[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.blocked.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B128" t="inlineStr" s="2">
@@ -4384,29 +4384,29 @@
       </c>
       <c r="C128" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
       <c r="D128" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_RECOGNITION.seductive.emotional[1]</t>
+          <t xml:space="preserve">blocked.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E128" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F128" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、私たちが何をしてきたか、ちゃんと見てくれないと寂しいじゃない。</t>
+          <t xml:space="preserve">その話は……っ……ふふ、できないの、ごめんなさい……</t>
         </is>
       </c>
     </row>
     <row r="129" ht="40" customHeight="1">
       <c r="A129" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.A.seductive.emotional[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.fail.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B129" t="inlineStr" s="2">
@@ -4416,29 +4416,29 @@
       </c>
       <c r="C129" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
       <c r="D129" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.A.seductive.emotional[1]</t>
+          <t xml:space="preserve">fail.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E129" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F129" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長…その一言、ずっと欲しかったの。ありがとう。</t>
+          <t xml:space="preserve">残念だけど……っ……今回は無理ね、ごめんなさい……</t>
         </is>
       </c>
     </row>
     <row r="130" ht="40" customHeight="1">
       <c r="A130" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.B.seductive.emotional[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.start.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B130" t="inlineStr" s="2">
@@ -4448,29 +4448,29 @@
       </c>
       <c r="C130" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
       <c r="D130" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.B.seductive.emotional[1]</t>
+          <t xml:space="preserve">start.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E130" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F130" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そう、ですか。…ちょっと、寂しい。</t>
+          <t xml:space="preserve">交渉を始めるわ……っ……ふふ、よろしくね……</t>
         </is>
       </c>
     </row>
     <row r="131" ht="40" customHeight="1">
       <c r="A131" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.C.seductive.emotional[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.success.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B131" t="inlineStr" s="2">
@@ -4480,29 +4480,29 @@
       </c>
       <c r="C131" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
       <c r="D131" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.C.seductive.emotional[1]</t>
+          <t xml:space="preserve">success.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E131" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F131" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長…そういう形ですか。…嬉しい、です。</t>
+          <t xml:space="preserve">これで決まりね……っ……ふふ、いい話し合いだったわ……</t>
         </is>
       </c>
     </row>
     <row r="132" ht="40" customHeight="1">
       <c r="A132" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.A.seductive.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_ABSTRACT.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B132" t="inlineStr" s="2">
@@ -4517,7 +4517,7 @@
       </c>
       <c r="D132" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.A.seductive.emotional[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_ABSTRACT.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E132" t="inlineStr" s="2">
@@ -4527,14 +4527,14 @@
       </c>
       <c r="F132" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長…ありがとう。胸が熱いの、忘れないから。</t>
+          <t xml:space="preserve">社長、お願い、私たちの子たちを置き去りにしないで。</t>
         </is>
       </c>
     </row>
     <row r="133" ht="40" customHeight="1">
       <c r="A133" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.B.seductive.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MAIN.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B133" t="inlineStr" s="2">
@@ -4549,7 +4549,7 @@
       </c>
       <c r="D133" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.B.seductive.emotional[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_MAIN.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E133" t="inlineStr" s="2">
@@ -4559,14 +4559,14 @@
       </c>
       <c r="F133" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そうですか。…ちょっと、寂しいな。</t>
+          <t xml:space="preserve">社長、次のメインは私たちに任せて。中途半端じゃ嫌なの、お願い。</t>
         </is>
       </c>
     </row>
     <row r="134" ht="40" customHeight="1">
       <c r="A134" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.C.seductive.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MONEY.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B134" t="inlineStr" s="2">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="D134" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.C.seductive.emotional[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_MONEY.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E134" t="inlineStr" s="2">
@@ -4591,14 +4591,14 @@
       </c>
       <c r="F134" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長…そういう形ですか。…ありがとう。</t>
+          <t xml:space="preserve">社長、お願い、私たちが何を受け取ってるか、もう一度見て。</t>
         </is>
       </c>
     </row>
     <row r="135" ht="40" customHeight="1">
       <c r="A135" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.A.seductive.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_RECOGNITION.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B135" t="inlineStr" s="2">
@@ -4613,7 +4613,7 @@
       </c>
       <c r="D135" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.A.seductive.emotional[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_RECOGNITION.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E135" t="inlineStr" s="2">
@@ -4623,14 +4623,14 @@
       </c>
       <c r="F135" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長…ありがとう。この嬉しさ、忘れない。</t>
+          <t xml:space="preserve">社長、私たちが何をしてきたか、ちゃんと見てくれないと寂しいじゃない。</t>
         </is>
       </c>
     </row>
     <row r="136" ht="40" customHeight="1">
       <c r="A136" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.B.seductive.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.A.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B136" t="inlineStr" s="2">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="D136" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.B.seductive.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.A.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E136" t="inlineStr" s="2">
@@ -4655,14 +4655,14 @@
       </c>
       <c r="F136" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そう、ですか。…ちょっと、寂しいけど。</t>
+          <t xml:space="preserve">社長…その一言、ずっと欲しかったの。ありがとう。</t>
         </is>
       </c>
     </row>
     <row r="137" ht="40" customHeight="1">
       <c r="A137" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.C.seductive.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.B.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B137" t="inlineStr" s="2">
@@ -4677,7 +4677,7 @@
       </c>
       <c r="D137" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.C.seductive.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.B.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E137" t="inlineStr" s="2">
@@ -4687,14 +4687,14 @@
       </c>
       <c r="F137" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長…そういう形ですか。…嬉しいです。</t>
+          <t xml:space="preserve">…そう、ですか。…ちょっと、寂しい。</t>
         </is>
       </c>
     </row>
     <row r="138" ht="40" customHeight="1">
       <c r="A138" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.A.seductive.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.C.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B138" t="inlineStr" s="2">
@@ -4709,7 +4709,7 @@
       </c>
       <c r="D138" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.A.seductive.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.C.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E138" t="inlineStr" s="2">
@@ -4719,14 +4719,14 @@
       </c>
       <c r="F138" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長…その一言、ずっと欲しかったの。ありがとう。</t>
+          <t xml:space="preserve">…社長…そういう形ですか。…嬉しい、です。</t>
         </is>
       </c>
     </row>
     <row r="139" ht="40" customHeight="1">
       <c r="A139" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.B.seductive.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.A.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B139" t="inlineStr" s="2">
@@ -4741,7 +4741,7 @@
       </c>
       <c r="D139" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.B.seductive.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.A.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E139" t="inlineStr" s="2">
@@ -4751,14 +4751,14 @@
       </c>
       <c r="F139" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そう、ですか。…ちょっと、寂しい。</t>
+          <t xml:space="preserve">社長…ありがとう。胸が熱いの、忘れないから。</t>
         </is>
       </c>
     </row>
     <row r="140" ht="40" customHeight="1">
       <c r="A140" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.C.seductive.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.B.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B140" t="inlineStr" s="2">
@@ -4773,7 +4773,7 @@
       </c>
       <c r="D140" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.C.seductive.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.B.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E140" t="inlineStr" s="2">
@@ -4783,14 +4783,14 @@
       </c>
       <c r="F140" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長…そういう答え方、好き。ありがとう。</t>
+          <t xml:space="preserve">…そうですか。…ちょっと、寂しいな。</t>
         </is>
       </c>
     </row>
     <row r="141" ht="40" customHeight="1">
       <c r="A141" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.A.seductive.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.C.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B141" t="inlineStr" s="2">
@@ -4805,7 +4805,7 @@
       </c>
       <c r="D141" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.A.seductive.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.C.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E141" t="inlineStr" s="2">
@@ -4815,14 +4815,14 @@
       </c>
       <c r="F141" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ああ、…そう、だったんですね。…悪いことをした。</t>
+          <t xml:space="preserve">…社長…そういう形ですか。…ありがとう。</t>
         </is>
       </c>
     </row>
     <row r="142" ht="40" customHeight="1">
       <c r="A142" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.B.seductive.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.A.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B142" t="inlineStr" s="2">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="D142" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.B.seductive.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.A.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E142" t="inlineStr" s="2">
@@ -4847,14 +4847,14 @@
       </c>
       <c r="F142" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。…でも、誰かを置いてけぼりにはしたくないな。</t>
+          <t xml:space="preserve">社長…ありがとう。この嬉しさ、忘れない。</t>
         </is>
       </c>
     </row>
     <row r="143" ht="40" customHeight="1">
       <c r="A143" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.A.seductive.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.B.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B143" t="inlineStr" s="2">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="D143" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.A.seductive.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.B.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E143" t="inlineStr" s="2">
@@ -4879,14 +4879,14 @@
       </c>
       <c r="F143" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そうね、…悪かった。</t>
+          <t xml:space="preserve">…そう、ですか。…ちょっと、寂しいけど。</t>
         </is>
       </c>
     </row>
     <row r="144" ht="40" customHeight="1">
       <c r="A144" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.B.seductive.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.C.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B144" t="inlineStr" s="2">
@@ -4901,7 +4901,7 @@
       </c>
       <c r="D144" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.B.seductive.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.C.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E144" t="inlineStr" s="2">
@@ -4911,14 +4911,14 @@
       </c>
       <c r="F144" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…嬉しい。ありがとうございます。</t>
+          <t xml:space="preserve">…社長…そういう形ですか。…嬉しいです。</t>
         </is>
       </c>
     </row>
     <row r="145" ht="40" customHeight="1">
       <c r="A145" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.A.seductive.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.A.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B145" t="inlineStr" s="2">
@@ -4933,7 +4933,7 @@
       </c>
       <c r="D145" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.A.seductive.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.A.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E145" t="inlineStr" s="2">
@@ -4943,14 +4943,14 @@
       </c>
       <c r="F145" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そう、ですか。…私の熱、しまいます。</t>
+          <t xml:space="preserve">社長…その一言、ずっと欲しかったの。ありがとう。</t>
         </is>
       </c>
     </row>
     <row r="146" ht="40" customHeight="1">
       <c r="A146" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.B.seductive.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.B.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B146" t="inlineStr" s="2">
@@ -4965,7 +4965,7 @@
       </c>
       <c r="D146" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.B.seductive.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.B.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E146" t="inlineStr" s="2">
@@ -4975,14 +4975,14 @@
       </c>
       <c r="F146" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。…私、止まれないから。</t>
+          <t xml:space="preserve">…そう、ですか。…ちょっと、寂しい。</t>
         </is>
       </c>
     </row>
     <row r="147" ht="40" customHeight="1">
       <c r="A147" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.A.seductive.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.C.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="2">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="D147" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.A.seductive.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.C.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E147" t="inlineStr" s="2">
@@ -5007,14 +5007,14 @@
       </c>
       <c r="F147" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長…ごめんなさい。…言い訳、しないから。</t>
+          <t xml:space="preserve">…社長…そういう答え方、好き。ありがとう。</t>
         </is>
       </c>
     </row>
     <row r="148" ht="40" customHeight="1">
       <c r="A148" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.B.seductive.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.A.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B148" t="inlineStr" s="2">
@@ -5029,7 +5029,7 @@
       </c>
       <c r="D148" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.B.seductive.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.A.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E148" t="inlineStr" s="2">
@@ -5039,14 +5039,14 @@
       </c>
       <c r="F148" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長…ありがとう、本当に優しい。</t>
+          <t xml:space="preserve">…ああ、…そう、だったんですね。…悪いことをした。</t>
         </is>
       </c>
     </row>
     <row r="149" ht="40" customHeight="1">
       <c r="A149" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.C.seductive.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.B.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="2">
@@ -5061,7 +5061,7 @@
       </c>
       <c r="D149" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.C.seductive.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.B.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E149" t="inlineStr" s="2">
@@ -5071,14 +5071,14 @@
       </c>
       <c r="F149" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長…そういう形ですか。…ありがたい、です。</t>
+          <t xml:space="preserve">…ありがとうございます。…でも、誰かを置いてけぼりにはしたくないな。</t>
         </is>
       </c>
     </row>
     <row r="150" ht="40" customHeight="1">
       <c r="A150" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.A.seductive.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.A.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="2">
@@ -5093,7 +5093,7 @@
       </c>
       <c r="D150" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.A.seductive.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.A.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E150" t="inlineStr" s="2">
@@ -5103,14 +5103,14 @@
       </c>
       <c r="F150" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長…見ててくれたんですね。嬉しい。</t>
+          <t xml:space="preserve">…そうね、…悪かった。</t>
         </is>
       </c>
     </row>
     <row r="151" ht="40" customHeight="1">
       <c r="A151" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.B.seductive.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.B.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="2">
@@ -5125,7 +5125,7 @@
       </c>
       <c r="D151" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.B.seductive.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.B.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E151" t="inlineStr" s="2">
@@ -5135,14 +5135,14 @@
       </c>
       <c r="F151" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…大丈夫です。…まだ、やれる。</t>
+          <t xml:space="preserve">…嬉しい。ありがとうございます。</t>
         </is>
       </c>
     </row>
     <row r="152" ht="40" customHeight="1">
       <c r="A152" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.C.seductive.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.A.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="2">
@@ -5157,7 +5157,7 @@
       </c>
       <c r="D152" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.C.seductive.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.A.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E152" t="inlineStr" s="2">
@@ -5167,14 +5167,14 @@
       </c>
       <c r="F152" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長…一人じゃなくていいんだね。ありがとう。</t>
+          <t xml:space="preserve">…そう、ですか。…私の熱、しまいます。</t>
         </is>
       </c>
     </row>
     <row r="153" ht="40" customHeight="1">
       <c r="A153" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.A.seductive.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.B.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="2">
@@ -5189,7 +5189,7 @@
       </c>
       <c r="D153" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.A.seductive.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.B.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E153" t="inlineStr" s="2">
@@ -5199,14 +5199,14 @@
       </c>
       <c r="F153" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そう、ですか。…私のせいだね。</t>
+          <t xml:space="preserve">…ありがとうございます。…私、止まれないから。</t>
         </is>
       </c>
     </row>
     <row r="154" ht="40" customHeight="1">
       <c r="A154" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.B.seductive.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.A.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="2">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="D154" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.B.seductive.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.A.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E154" t="inlineStr" s="2">
@@ -5231,14 +5231,14 @@
       </c>
       <c r="F154" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長。ありがとうございます……ふふ。</t>
+          <t xml:space="preserve">…社長…ごめんなさい。…言い訳、しないから。</t>
         </is>
       </c>
     </row>
     <row r="155" ht="40" customHeight="1">
       <c r="A155" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.C.seductive.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.B.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="2">
@@ -5253,7 +5253,7 @@
       </c>
       <c r="D155" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.C.seductive.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.B.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E155" t="inlineStr" s="2">
@@ -5263,14 +5263,14 @@
       </c>
       <c r="F155" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長…そういう形で気にかけてくれるの、嬉しい。</t>
+          <t xml:space="preserve">…社長…ありがとう、本当に優しい。</t>
         </is>
       </c>
     </row>
     <row r="156" ht="40" customHeight="1">
       <c r="A156" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.A.seductive.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.C.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="2">
@@ -5285,7 +5285,7 @@
       </c>
       <c r="D156" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.A.seductive.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.C.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E156" t="inlineStr" s="2">
@@ -5295,14 +5295,14 @@
       </c>
       <c r="F156" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そう、ですか。…私、出ちゃってましたね。</t>
+          <t xml:space="preserve">…社長…そういう形ですか。…ありがたい、です。</t>
         </is>
       </c>
     </row>
     <row r="157" ht="40" customHeight="1">
       <c r="A157" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.B.seductive.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.A.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
@@ -5317,7 +5317,7 @@
       </c>
       <c r="D157" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.B.seductive.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.A.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E157" t="inlineStr" s="2">
@@ -5327,14 +5327,14 @@
       </c>
       <c r="F157" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（…睫毛が震えたが、口は開かなかった）</t>
+          <t xml:space="preserve">…社長…見ててくれたんですね。嬉しい。</t>
         </is>
       </c>
     </row>
     <row r="158" ht="40" customHeight="1">
       <c r="A158" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.C.seductive.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.B.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="2">
@@ -5349,7 +5349,7 @@
       </c>
       <c r="D158" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.C.seductive.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.B.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E158" t="inlineStr" s="2">
@@ -5359,14 +5359,14 @@
       </c>
       <c r="F158" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長…そういう形ですか。…嬉しい、です。</t>
+          <t xml:space="preserve">…大丈夫です。…まだ、やれる。</t>
         </is>
       </c>
     </row>
     <row r="159" ht="40" customHeight="1">
       <c r="A159" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.A.seductive.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.C.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="D159" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.A.seductive.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.C.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E159" t="inlineStr" s="2">
@@ -5391,14 +5391,14 @@
       </c>
       <c r="F159" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長…そう、ですか。…私が追い込みすぎてた。</t>
+          <t xml:space="preserve">…社長…一人じゃなくていいんだね。ありがとう。</t>
         </is>
       </c>
     </row>
     <row r="160" ht="40" customHeight="1">
       <c r="A160" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.B.seductive.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.A.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="D160" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.B.seductive.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.A.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E160" t="inlineStr" s="2">
@@ -5423,14 +5423,14 @@
       </c>
       <c r="F160" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長…ありがとう。やり切らせてください。</t>
+          <t xml:space="preserve">…そう、ですか。…私のせいだね。</t>
         </is>
       </c>
     </row>
     <row r="161" ht="40" customHeight="1">
       <c r="A161" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.C.seductive.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.B.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
@@ -5445,7 +5445,7 @@
       </c>
       <c r="D161" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.C.seductive.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.B.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E161" t="inlineStr" s="2">
@@ -5455,14 +5455,14 @@
       </c>
       <c r="F161" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長…ありがとう。私、見えてなかった。</t>
+          <t xml:space="preserve">…社長。ありがとうございます……ふふ。</t>
         </is>
       </c>
     </row>
     <row r="162" ht="40" customHeight="1">
       <c r="A162" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES.emotional.attack.seductive</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.C.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
@@ -5472,12 +5472,12 @@
       </c>
       <c r="C162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D162" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.attack.seductive</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.C.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E162" t="inlineStr" s="2">
@@ -5487,14 +5487,14 @@
       </c>
       <c r="F162" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">許せないのよ、あの子のやり方</t>
+          <t xml:space="preserve">…社長…そういう形で気にかけてくれるの、嬉しい。</t>
         </is>
       </c>
     </row>
     <row r="163" ht="40" customHeight="1">
       <c r="A163" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES.emotional.defend.seductive</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.A.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
@@ -5504,12 +5504,12 @@
       </c>
       <c r="C163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D163" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.defend.seductive</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.A.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E163" t="inlineStr" s="2">
@@ -5519,29 +5519,29 @@
       </c>
       <c r="F163" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こっちだって、引けないのよ</t>
+          <t xml:space="preserve">…そう、ですか。…私、出ちゃってましたね。</t>
         </is>
       </c>
     </row>
     <row r="164" ht="40" customHeight="1">
       <c r="A164" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES.seductive.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.B.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D164" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.B.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E164" t="inlineStr" s="2">
@@ -5551,29 +5551,29 @@
       </c>
       <c r="F164" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">冷めちゃったのよ、すっかりね……。</t>
+          <t xml:space="preserve">（…睫毛が震えたが、口は開かなかった）</t>
         </is>
       </c>
     </row>
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F06_AMBIENT_LINES.seductive.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.C.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F06_AMBIENT_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D165" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.C.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E165" t="inlineStr" s="2">
@@ -5583,29 +5583,29 @@
       </c>
       <c r="F165" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、仲直り……いいものね。</t>
+          <t xml:space="preserve">…社長…そういう形ですか。…嬉しい、です。</t>
         </is>
       </c>
     </row>
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F08_LEADER_LINES.seductive.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.A.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F08_LEADER_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.A.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E166" t="inlineStr" s="2">
@@ -5615,14 +5615,14 @@
       </c>
       <c r="F166" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……リングでなら、本音で話せるでしょ？</t>
+          <t xml:space="preserve">…社長…そう、ですか。…私が追い込みすぎてた。</t>
         </is>
       </c>
     </row>
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES.seductive.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.B.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -5632,29 +5632,29 @@
       </c>
       <c r="C167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.B.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F167" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……っ……変わったの、私……ふふ、自分でも信じられないくらい……</t>
+          <t xml:space="preserve">…社長…ありがとう。やり切らせてください。</t>
         </is>
       </c>
     </row>
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES.seductive.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.C.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -5664,29 +5664,29 @@
       </c>
       <c r="C168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.C.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F168" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……っ……何か、来そうな予感がするの……ふふ、楽しみだわ……</t>
+          <t xml:space="preserve">…社長…ありがとう。私、見えてなかった。</t>
         </is>
       </c>
     </row>
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.cap_reached.seductive.emotional[1]</t>
+          <t xml:space="preserve">FACTION_F02_LINES.emotional.attack.seductive</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5696,29 +5696,29 @@
       </c>
       <c r="C169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
         </is>
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cap_reached.seductive.emotional[1]</t>
+          <t xml:space="preserve">emotional.attack.seductive</t>
         </is>
       </c>
       <c r="E169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F169" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまでなのね…少し寂しいけど…胸を張れるわ</t>
+          <t xml:space="preserve">許せないのよ、あの子のやり方</t>
         </is>
       </c>
     </row>
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.seductive.emotional[1]</t>
+          <t xml:space="preserve">FACTION_F02_LINES.emotional.defend.seductive</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -5728,125 +5728,125 @@
       </c>
       <c r="C170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
         </is>
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_elite.seductive.emotional[1]</t>
+          <t xml:space="preserve">emotional.defend.seductive</t>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F170" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ここまで来ちゃったの…嬉しくて…ちょっと泣きそう</t>
+          <t xml:space="preserve">こっちだって、引けないのよ</t>
         </is>
       </c>
     </row>
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.seductive.emotional[1]</t>
+          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
       <c r="C171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES</t>
         </is>
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_growth.seductive.emotional[1]</t>
+          <t xml:space="preserve">seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F171" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ふふっ、強くなっちゃった。嬉しいわ</t>
+          <t xml:space="preserve">冷めちゃったのよ、すっかりね……。</t>
         </is>
       </c>
     </row>
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.seductive.emotional[1]</t>
+          <t xml:space="preserve">FACTION_F06_AMBIENT_LINES.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
       <c r="C172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">FACTION_F06_AMBIENT_LINES</t>
         </is>
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_legend.seductive.emotional[1]</t>
+          <t xml:space="preserve">seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F172" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで来ちゃった…もう…涙が止まらないわ…</t>
+          <t xml:space="preserve">ふふ、仲直り……いいものね。</t>
         </is>
       </c>
     </row>
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_growth.seductive.emotional[1]</t>
+          <t xml:space="preserve">FACTION_F08_LEADER_LINES.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
       <c r="C173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">FACTION_F08_LEADER_LINES</t>
         </is>
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_growth.seductive.emotional[1]</t>
+          <t xml:space="preserve">seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F173" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">応援してくれる人が…嬉しいわ…ふふ</t>
+          <t xml:space="preserve">……リングでなら、本音で話せるでしょ？</t>
         </is>
       </c>
     </row>
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_star.seductive.emotional[1]</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="C174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
         </is>
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_star.seductive.emotional[1]</t>
+          <t xml:space="preserve">seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E174" t="inlineStr" s="2">
@@ -5871,14 +5871,14 @@
       </c>
       <c r="F174" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんなに…嬉しくて…もう言葉にならないの…</t>
+          <t xml:space="preserve">……っ……変わったの、私……ふふ、自分でも信じられないくらい……</t>
         </is>
       </c>
     </row>
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES.seductive.emotional[1]</t>
+          <t xml:space="preserve">BT_HINT_LINES.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="C175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
+          <t xml:space="preserve">BT_HINT_LINES</t>
         </is>
       </c>
       <c r="D175" t="inlineStr" s="12">
@@ -5903,14 +5903,14 @@
       </c>
       <c r="F175" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……っ……どうしてかしら、力が湧かないの……</t>
+          <t xml:space="preserve">……っ……何か、来そうな予感がするの……ふふ、楽しみだわ……</t>
         </is>
       </c>
     </row>
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.seductive.emotional[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.cap_reached.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="C176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.emotional[1]</t>
+          <t xml:space="preserve">cap_reached.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
@@ -5935,14 +5935,14 @@
       </c>
       <c r="F176" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……っ……ふふ、また燃えてきたの……</t>
+          <t xml:space="preserve">ここまでなのね…少し寂しいけど…胸を張れるわ</t>
         </is>
       </c>
     </row>
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES.seductive.emotional[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="C177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.emotional[1]</t>
+          <t xml:space="preserve">ovr_elite.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
@@ -5967,14 +5967,14 @@
       </c>
       <c r="F177" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">調子が戻ってきたわ……っ……ふふ、ようやくね……</t>
+          <t xml:space="preserve">…ここまで来ちゃったの…嬉しくて…ちょっと泣きそう</t>
         </is>
       </c>
     </row>
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.defeat.seductive.emotional[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -5984,12 +5984,12 @@
       </c>
       <c r="C178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defeat.seductive.emotional[1]</t>
+          <t xml:space="preserve">ovr_growth.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
@@ -5999,14 +5999,14 @@
       </c>
       <c r="F178" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けが続いて……っ……ふふ、自分が分からなくなりそう……</t>
+          <t xml:space="preserve">…ふふっ、強くなっちゃった。嬉しいわ</t>
         </is>
       </c>
     </row>
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.seductive.emotional[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="C179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_moderate_recovery.seductive.emotional[1]</t>
+          <t xml:space="preserve">ovr_legend.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
@@ -6031,14 +6031,14 @@
       </c>
       <c r="F179" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">怪我は治ったけど……っ……ふふ、感覚が戻らないの……</t>
+          <t xml:space="preserve">ここまで来ちゃった…もう…涙が止まらないわ…</t>
         </is>
       </c>
     </row>
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.seductive.emotional[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_growth.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="C180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_severe_recovery.seductive.emotional[1]</t>
+          <t xml:space="preserve">pop_growth.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
@@ -6063,14 +6063,14 @@
       </c>
       <c r="F180" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">大怪我から戻ったわ……っ……でも、まだ怖いの……</t>
+          <t xml:space="preserve">応援してくれる人が…嬉しいわ…ふふ</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.seductive.emotional[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_star.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -6080,12 +6080,12 @@
       </c>
       <c r="C181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">penalty_end.seductive.emotional[1]</t>
+          <t xml:space="preserve">pop_star.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
@@ -6095,14 +6095,14 @@
       </c>
       <c r="F181" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">謹慎が明けたわ……っ……ふふ、戻ってきたわよ……</t>
+          <t xml:space="preserve">こんなに…嬉しくて…もう言葉にならないの…</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.autumnWarChampion.seductive.emotional[1]</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6112,29 +6112,29 @@
       </c>
       <c r="C182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
         </is>
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">autumnWarChampion.seductive.emotional[1]</t>
+          <t xml:space="preserve">seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F182" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みんなと分かち合える優勝だから、こんなに胸がいっぱいなの。</t>
+          <t xml:space="preserve">……っ……どうしてかしら、力が湧かないの……</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.seductive.emotional[1]</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6144,29 +6144,29 @@
       </c>
       <c r="C183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
         </is>
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.seductive.emotional[1]</t>
+          <t xml:space="preserve">seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F183" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高の試合だった…涙が止まらないわ</t>
+          <t xml:space="preserve">……っ……ふふ、また燃えてきたの……</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.seductive.emotional[1]</t>
+          <t xml:space="preserve">SLUMP_END_LINES.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6176,29 +6176,29 @@
       </c>
       <c r="C184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_END_LINES</t>
         </is>
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.seductive.emotional[1]</t>
+          <t xml:space="preserve">seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオン……っ……ふふ、この重み……愛おしくてたまらないわ……</t>
+          <t xml:space="preserve">調子が戻ってきたわ……っ……ふふ、ようやくね……</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.seductive.emotional[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.defeat.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6208,29 +6208,29 @@
       </c>
       <c r="C185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.seductive.emotional[1]</t>
+          <t xml:space="preserve">defeat.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">殿堂入り…もう言葉にならないわ…（涙を堪える）</t>
+          <t xml:space="preserve">負けが続いて……っ……ふふ、自分が分からなくなりそう……</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mediaAward.seductive.emotional[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6240,29 +6240,29 @@
       </c>
       <c r="C186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mediaAward.seductive.emotional[1]</t>
+          <t xml:space="preserve">injury_moderate_recovery.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">メディア功労賞……っ……みんなに見てもらえてた証ね、嬉しいわ……</t>
+          <t xml:space="preserve">怪我は治ったけど……っ……ふふ、感覚が戻らないの……</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.seductive.emotional[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6272,29 +6272,29 @@
       </c>
       <c r="C187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.seductive.emotional[1]</t>
+          <t xml:space="preserve">injury_severe_recovery.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">MVP……っ……ふふ、私が一番輝いてたって、そう言ってもらえるのね……</t>
+          <t xml:space="preserve">大怪我から戻ったわ……っ……でも、まだ怖いの……</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.seductive.emotional[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6304,29 +6304,29 @@
       </c>
       <c r="C188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.seductive.emotional[1]</t>
+          <t xml:space="preserve">penalty_end.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">新人王……っ……無我夢中だったの……認めてもらえて嬉しいわ……</t>
+          <t xml:space="preserve">謹慎が明けたわ……っ……ふふ、戻ってきたわよ……</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.springTagChampion.seductive.emotional[1]</t>
+          <t xml:space="preserve">AWARD_LINES.autumnWarChampion.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">springTagChampion.seductive.emotional[1]</t>
+          <t xml:space="preserve">autumnWarChampion.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
@@ -6351,14 +6351,14 @@
       </c>
       <c r="F189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">相棒と笑えるこの瞬間が、何よりうれしいの。</t>
+          <t xml:space="preserve">みんなと分かち合える優勝だから、こんなに胸がいっぱいなの。</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.seductive.emotional[1]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6368,12 +6368,12 @@
       </c>
       <c r="C190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.emotional[1]</t>
+          <t xml:space="preserve">bestMatch.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
@@ -6383,14 +6383,14 @@
       </c>
       <c r="F190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ドームで、あなた方の前で戦える幸せよ…</t>
+          <t xml:space="preserve">最高の試合だった…涙が止まらないわ</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.seductive.emotional[2]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6400,12 +6400,12 @@
       </c>
       <c r="C191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.emotional[2]</t>
+          <t xml:space="preserve">champion.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
@@ -6415,14 +6415,14 @@
       </c>
       <c r="F191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">熱い試合を…必ず、約束する</t>
+          <t xml:space="preserve">チャンピオン……っ……ふふ、この重み……愛おしくてたまらないわ……</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.seductive.emotional[3]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6432,12 +6432,12 @@
       </c>
       <c r="C192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.emotional[3]</t>
+          <t xml:space="preserve">hallOfFame.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
@@ -6447,14 +6447,14 @@
       </c>
       <c r="F192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この胸の高鳴り…試合で発散させてね</t>
+          <t xml:space="preserve">殿堂入り…もう言葉にならないわ…（涙を堪える）</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.seductive.emotional[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mediaAward.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="C193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.emotional[1]</t>
+          <t xml:space="preserve">mediaAward.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
@@ -6479,14 +6479,14 @@
       </c>
       <c r="F193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…満員、お客様の熱気…忘れられない</t>
+          <t xml:space="preserve">メディア功労賞……っ……みんなに見てもらえてた証ね、嬉しいわ……</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.seductive.emotional[2]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6496,12 +6496,12 @@
       </c>
       <c r="C194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.emotional[2]</t>
+          <t xml:space="preserve">mvp.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
@@ -6511,14 +6511,14 @@
       </c>
       <c r="F194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">胸が熱くて、震えが止まらないの</t>
+          <t xml:space="preserve">MVP……っ……ふふ、私が一番輝いてたって、そう言ってもらえるのね……</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.seductive.emotional[3]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6528,12 +6528,12 @@
       </c>
       <c r="C195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.emotional[3]</t>
+          <t xml:space="preserve">rookie.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
@@ -6543,14 +6543,14 @@
       </c>
       <c r="F195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんな素敵な夜、生涯忘れない</t>
+          <t xml:space="preserve">新人王……っ……無我夢中だったの……認めてもらえて嬉しいわ……</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.seductive.emotional[1]</t>
+          <t xml:space="preserve">AWARD_LINES.springTagChampion.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6560,29 +6560,29 @@
       </c>
       <c r="C196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.seductive.emotional[1]</t>
+          <t xml:space="preserve">springTagChampion.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F196" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お知らせよ……っ……ふふ、聞いて……</t>
+          <t xml:space="preserve">相棒と笑えるこの瞬間が、何よりうれしいの。</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.seductive.emotional[2]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6592,29 +6592,29 @@
       </c>
       <c r="C197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.seductive.emotional[2]</t>
+          <t xml:space="preserve">seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ねえ、聞いて……っ……ふふ……</t>
+          <t xml:space="preserve">…ドームで、あなた方の前で戦える幸せよ…</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.seductive.emotional[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6624,29 +6624,29 @@
       </c>
       <c r="C198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.seductive.emotional[1]</t>
+          <t xml:space="preserve">seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ちょっといいかしら……っ……ふふ……</t>
+          <t xml:space="preserve">熱い試合を…必ず、約束する</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.seductive.emotional[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.seductive.emotional[3]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6656,29 +6656,29 @@
       </c>
       <c r="C199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.seductive.emotional[1]</t>
+          <t xml:space="preserve">seductive.emotional[3]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">はぁ……体が、言うこときかないの……ごめんなさい……</t>
+          <t xml:space="preserve">この胸の高鳴り…試合で発散させてね</t>
         </is>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.seductive.emotional[2]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6688,29 +6688,29 @@
       </c>
       <c r="C200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.seductive.emotional[2]</t>
+          <t xml:space="preserve">seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふぅ……ちょっと、休ませて……すぐ、戻るから……</t>
+          <t xml:space="preserve">…満員、お客様の熱気…忘れられない</t>
         </is>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.seductive.emotional[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6720,29 +6720,29 @@
       </c>
       <c r="C201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.seductive.emotional[1]</t>
+          <t xml:space="preserve">seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">大事な話よ……っ……ふふ、しっかり聞いて……</t>
+          <t xml:space="preserve">胸が熱くて、震えが止まらないの</t>
         </is>
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.seductive.emotional[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.seductive.emotional[3]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6752,29 +6752,29 @@
       </c>
       <c r="C202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.seductive.emotional[1]</t>
+          <t xml:space="preserve">seductive.emotional[3]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F202" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ちょっと心配なの……っ……ふふ……</t>
+          <t xml:space="preserve">こんな素敵な夜、生涯忘れない</t>
         </is>
       </c>
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.seductive.emotional[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6789,7 +6789,7 @@
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_warning.seductive.emotional[1]</t>
+          <t xml:space="preserve">N1.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
@@ -6799,14 +6799,14 @@
       </c>
       <c r="F203" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">緊急よ……っ……ふふ、よく聞いて……</t>
+          <t xml:space="preserve">お知らせよ……っ……ふふ、聞いて……</t>
         </is>
       </c>
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.breakthrough.voice.seductive.emotional[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6816,12 +6816,12 @@
       </c>
       <c r="C204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">breakthrough.voice.seductive.emotional[1]</t>
+          <t xml:space="preserve">N1.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
@@ -6831,14 +6831,14 @@
       </c>
       <c r="F204" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何かが変わった……っ……ふふ……</t>
+          <t xml:space="preserve">ねえ、聞いて……っ……ふふ……</t>
         </is>
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.seductive.emotional[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="C205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G1.voice.seductive.emotional[1]</t>
+          <t xml:space="preserve">N2.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
@@ -6863,14 +6863,14 @@
       </c>
       <c r="F205" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう少し稼ぎたいわね……っ……</t>
+          <t xml:space="preserve">ちょっといいかしら……っ……ふふ……</t>
         </is>
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice.seductive.emotional[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6880,12 +6880,12 @@
       </c>
       <c r="C206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G2.voice.seductive.emotional[1]</t>
+          <t xml:space="preserve">N3.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
@@ -6895,14 +6895,14 @@
       </c>
       <c r="F206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ひとりは、ちょっと寂しいの……っ……</t>
+          <t xml:space="preserve">はぁ……体が、言うこときかないの……ごめんなさい……</t>
         </is>
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice.seductive.emotional[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G3.voice.seductive.emotional[1]</t>
+          <t xml:space="preserve">N3.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
@@ -6927,14 +6927,14 @@
       </c>
       <c r="F207" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もう少し目立たないとダメなのかしら</t>
+          <t xml:space="preserve">ふぅ……ちょっと、休ませて……すぐ、戻るから……</t>
         </is>
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G4.voice.seductive.emotional[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="C208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G4.voice.seductive.emotional[1]</t>
+          <t xml:space="preserve">N4.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
@@ -6959,14 +6959,14 @@
       </c>
       <c r="F208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もっと強くなりたいの……っ……</t>
+          <t xml:space="preserve">大事な話よ……っ……ふふ、しっかり聞いて……</t>
         </is>
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice.seductive.emotional[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -6976,12 +6976,12 @@
       </c>
       <c r="C209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R2.voice.seductive.emotional[1]</t>
+          <t xml:space="preserve">N5_low.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
@@ -6991,14 +6991,14 @@
       </c>
       <c r="F209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの子と、もっと話したい……っ……</t>
+          <t xml:space="preserve">ちょっと心配なの……っ……ふふ……</t>
         </is>
       </c>
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice.seductive.emotional[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -7008,12 +7008,12 @@
       </c>
       <c r="C210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R4.voice.seductive.emotional[1]</t>
+          <t xml:space="preserve">N5_warning.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
@@ -7023,14 +7023,14 @@
       </c>
       <c r="F210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの子とは、ちょっと距離を置きたいの……っ……</t>
+          <t xml:space="preserve">緊急よ……っ……ふふ、よく聞いて……</t>
         </is>
       </c>
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice.seductive.emotional[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.breakthrough.voice.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7045,7 +7045,7 @@
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R5.voice.seductive.emotional[1]</t>
+          <t xml:space="preserve">breakthrough.voice.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
@@ -7055,14 +7055,14 @@
       </c>
       <c r="F211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けたくないの……っ……ふふ……</t>
+          <t xml:space="preserve">何かが変わった……っ……ふふ……</t>
         </is>
       </c>
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.warVictory.voice.seductive.emotional[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7077,7 +7077,7 @@
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">warVictory.voice.seductive.emotional[1]</t>
+          <t xml:space="preserve">G1.voice.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
@@ -7087,14 +7087,14 @@
       </c>
       <c r="F212" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝てた……っ……ふふ、最高の気分……</t>
+          <t xml:space="preserve">もう少し稼ぎたいわね……っ……</t>
         </is>
       </c>
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_repeat.seductive.emotional[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7104,29 +7104,29 @@
       </c>
       <c r="C213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus_repeat.seductive.emotional[1]</t>
+          <t xml:space="preserve">G2.voice.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F213" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">また……っ……ふふ、こんなに優しくされたら、応えないわけにはいかないわ……</t>
+          <t xml:space="preserve">ひとりは、ちょっと寂しいの……っ……</t>
         </is>
       </c>
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.seductive.emotional[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7136,29 +7136,29 @@
       </c>
       <c r="C214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.seductive.emotional[1]</t>
+          <t xml:space="preserve">G3.voice.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F214" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ボーナス……っ……気にかけてくれてたのね、嬉しい……ふふ、ありがとう……</t>
+          <t xml:space="preserve">…もう少し目立たないとダメなのかしら</t>
         </is>
       </c>
     </row>
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.seductive.emotional[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G4.voice.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7168,29 +7168,29 @@
       </c>
       <c r="C215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.seductive.emotional[1]</t>
+          <t xml:space="preserve">G4.voice.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F215" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">合宿……っ……ふふ、みんなと一緒に過ごせるのね、楽しみ……</t>
+          <t xml:space="preserve">もっと強くなりたいの……っ……</t>
         </is>
       </c>
     </row>
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.seductive.emotional[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7200,29 +7200,29 @@
       </c>
       <c r="C216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage_high_trust.seductive.emotional[1]</t>
+          <t xml:space="preserve">R2.voice.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F216" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あなたの言葉だけで……っ……私、何でもできちゃいそうなの……ふふ……</t>
+          <t xml:space="preserve">あの子と、もっと話したい……っ……</t>
         </is>
       </c>
     </row>
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.seductive.emotional[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7232,29 +7232,29 @@
       </c>
       <c r="C217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.seductive.emotional[1]</t>
+          <t xml:space="preserve">R4.voice.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F217" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">励まし……っ……ふふ、その言葉だけで、力が湧いてくるの……</t>
+          <t xml:space="preserve">あの子とは、ちょっと距離を置きたいの……っ……</t>
         </is>
       </c>
     </row>
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.seductive.emotional[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7264,29 +7264,29 @@
       </c>
       <c r="C218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.seductive.emotional[1]</t>
+          <t xml:space="preserve">R5.voice.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F218" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">メディアに……っ……ふふ、私を世間に見せたいのね、いいわ……</t>
+          <t xml:space="preserve">負けたくないの……っ……ふふ……</t>
         </is>
       </c>
     </row>
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.seductive.emotional[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.warVictory.voice.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7296,29 +7296,29 @@
       </c>
       <c r="C219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.seductive.emotional[1]</t>
+          <t xml:space="preserve">warVictory.voice.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F219" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">パーティー……っ……ふふ、今夜は思いっきり楽しませてもらうわ……</t>
+          <t xml:space="preserve">勝てた……っ……ふふ、最高の気分……</t>
         </is>
       </c>
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.seductive.emotional[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_repeat.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7333,7 +7333,7 @@
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.seductive.emotional[1]</t>
+          <t xml:space="preserve">bonus_repeat.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
@@ -7343,14 +7343,14 @@
       </c>
       <c r="F220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">休暇……っ……気を遣ってくれたのね、ふふ、嬉しいわ……</t>
+          <t xml:space="preserve">また……っ……ふふ、こんなに優しくされたら、応えないわけにはいかないわ……</t>
         </is>
       </c>
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.seductive.emotional[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7365,7 +7365,7 @@
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.seductive.emotional[1]</t>
+          <t xml:space="preserve">bonus.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
@@ -7375,14 +7375,14 @@
       </c>
       <c r="F221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">そこまで…してくれるの…っ、嬉しい……早く戻るわ……</t>
+          <t xml:space="preserve">ボーナス……っ……気にかけてくれてたのね、嬉しい……ふふ、ありがとう……</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.seductive.emotional[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7397,7 +7397,7 @@
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.seductive.emotional[1]</t>
+          <t xml:space="preserve">camp.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
@@ -7407,14 +7407,14 @@
       </c>
       <c r="F222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">トレーナーをつけてくれるの……っ……ふふ、本気で育ててくれるのね……</t>
+          <t xml:space="preserve">合宿……っ……ふふ、みんなと一緒に過ごせるのね、楽しみ……</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.seductive.emotional[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="C223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.seductive.emotional[1]</t>
+          <t xml:space="preserve">encourage_high_trust.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
@@ -7439,14 +7439,14 @@
       </c>
       <c r="F223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……っ……どうしようかしら、ふふ、迷っちゃうわね……</t>
+          <t xml:space="preserve">あなたの言葉だけで……っ……私、何でもできちゃいそうなの……ふふ……</t>
         </is>
       </c>
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.seductive.emotional[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="C224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.seductive.emotional[1]</t>
+          <t xml:space="preserve">encourage.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
@@ -7471,14 +7471,14 @@
       </c>
       <c r="F224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いいわよ……っ……ふふ、やってみせるわ……</t>
+          <t xml:space="preserve">励まし……っ……ふふ、その言葉だけで、力が湧いてくるの……</t>
         </is>
       </c>
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.seductive.emotional[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7488,12 +7488,12 @@
       </c>
       <c r="C225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.seductive.emotional[1]</t>
+          <t xml:space="preserve">media.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
@@ -7503,14 +7503,14 @@
       </c>
       <c r="F225" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……っ……これは認められないわ、悪いけど……</t>
+          <t xml:space="preserve">メディアに……っ……ふふ、私を世間に見せたいのね、いいわ……</t>
         </is>
       </c>
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.seductive.emotional[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7520,12 +7520,12 @@
       </c>
       <c r="C226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_grumble.seductive.emotional[1]</t>
+          <t xml:space="preserve">party.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
@@ -7535,14 +7535,14 @@
       </c>
       <c r="F226" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">正直に言うわね……っ……ちょっと不満なの……</t>
+          <t xml:space="preserve">パーティー……っ……ふふ、今夜は思いっきり楽しませてもらうわ……</t>
         </is>
       </c>
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.seductive.emotional[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7552,12 +7552,12 @@
       </c>
       <c r="C227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_sns.seductive.emotional[1]</t>
+          <t xml:space="preserve">refresh_leave.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
@@ -7567,14 +7567,14 @@
       </c>
       <c r="F227" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">SNS見たわ……っ……ふふ、勝手な人たちね……</t>
+          <t xml:space="preserve">休暇……っ……気を遣ってくれたのね、ふふ、嬉しいわ……</t>
         </is>
       </c>
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.seductive.emotional[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7584,12 +7584,12 @@
       </c>
       <c r="C228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.seductive.emotional[1]</t>
+          <t xml:space="preserve">special_treatment.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
@@ -7599,14 +7599,14 @@
       </c>
       <c r="F228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ねえ……っ……ちょっと、聞いてほしいの……</t>
+          <t xml:space="preserve">そこまで…してくれるの…っ、嬉しい……早く戻るわ……</t>
         </is>
       </c>
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.seductive.emotional[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="C229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.seductive.emotional[1]</t>
+          <t xml:space="preserve">trainer.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
@@ -7631,14 +7631,14 @@
       </c>
       <c r="F229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">時間、ある……っ……ふふ、ちょっとだけ付き合って……</t>
+          <t xml:space="preserve">トレーナーをつけてくれるの……っ……ふふ、本気で育ててくれるのね……</t>
         </is>
       </c>
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.seductive.emotional[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7653,7 +7653,7 @@
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.seductive.emotional[1]</t>
+          <t xml:space="preserve">E1.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
@@ -7663,14 +7663,14 @@
       </c>
       <c r="F230" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……っ……どう答えるのが正解なのかしら、ふふ……</t>
+          <t xml:space="preserve">……っ……どうしようかしら、ふふ、迷っちゃうわね……</t>
         </is>
       </c>
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.seductive.emotional[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7685,7 +7685,7 @@
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.seductive.emotional[1]</t>
+          <t xml:space="preserve">E6.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
@@ -7695,14 +7695,14 @@
       </c>
       <c r="F231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">はっきり言うわ……っ……私の気持ちは……</t>
+          <t xml:space="preserve">いいわよ……っ……ふふ、やってみせるわ……</t>
         </is>
       </c>
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.seductive.emotional[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7717,7 +7717,7 @@
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_silent.seductive.emotional[1]</t>
+          <t xml:space="preserve">S_boycott.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
@@ -7727,14 +7727,14 @@
       </c>
       <c r="F232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………っ……言葉にならないの……ふふ……</t>
+          <t xml:space="preserve">……っ……これは認められないわ、悪いけど……</t>
         </is>
       </c>
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.seductive.emotional[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7749,7 +7749,7 @@
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.seductive.emotional[1]</t>
+          <t xml:space="preserve">S_grumble.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
@@ -7759,14 +7759,14 @@
       </c>
       <c r="F233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">少し考えさせて……っ……ふふ、すぐには決められないの……</t>
+          <t xml:space="preserve">正直に言うわね……っ……ちょっと不満なの……</t>
         </is>
       </c>
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.seductive.emotional[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7781,7 +7781,7 @@
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.seductive.emotional[1]</t>
+          <t xml:space="preserve">S_sns.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
@@ -7791,14 +7791,14 @@
       </c>
       <c r="F234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決めたわ……っ……ふふ、これが私の答えよ……</t>
+          <t xml:space="preserve">SNS見たわ……っ……ふふ、勝手な人たちね……</t>
         </is>
       </c>
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.seductive.emotional[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7808,12 +7808,12 @@
       </c>
       <c r="C235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.seductive.emotional[1]</t>
+          <t xml:space="preserve">S1.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
@@ -7823,14 +7823,14 @@
       </c>
       <c r="F235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">これから……っ……やりたいこと、いっぱいあるの……</t>
+          <t xml:space="preserve">ねえ……っ……ちょっと、聞いてほしいの……</t>
         </is>
       </c>
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.seductive.emotional[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7840,12 +7840,12 @@
       </c>
       <c r="C236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.seductive.emotional[1]</t>
+          <t xml:space="preserve">S2.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
@@ -7855,14 +7855,14 @@
       </c>
       <c r="F236" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ねえ……っ……ちょっと話、聞いてくれる？</t>
+          <t xml:space="preserve">時間、ある……っ……ふふ、ちょっとだけ付き合って……</t>
         </is>
       </c>
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.seductive.emotional[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -7872,12 +7872,12 @@
       </c>
       <c r="C237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.seductive.emotional[1]</t>
+          <t xml:space="preserve">S3.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
@@ -7887,14 +7887,14 @@
       </c>
       <c r="F237" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いいわよ……っ……話してみて……</t>
+          <t xml:space="preserve">……っ……どう答えるのが正解なのかしら、ふふ……</t>
         </is>
       </c>
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.seductive.emotional[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -7904,12 +7904,12 @@
       </c>
       <c r="C238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.seductive.emotional[1]</t>
+          <t xml:space="preserve">S4_direct.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
@@ -7919,14 +7919,14 @@
       </c>
       <c r="F238" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ブランドのお話……っ……ふふ、素敵ね……</t>
+          <t xml:space="preserve">はっきり言うわ……っ……私の気持ちは……</t>
         </is>
       </c>
     </row>
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.seductive.emotional[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -7936,12 +7936,12 @@
       </c>
       <c r="C239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.seductive.emotional[1]</t>
+          <t xml:space="preserve">S4_silent.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
@@ -7951,14 +7951,14 @@
       </c>
       <c r="F239" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">CMに出るの……っ……ふふ、世間に顔を売るチャンスね……</t>
+          <t xml:space="preserve">………っ……言葉にならないの……ふふ……</t>
         </is>
       </c>
     </row>
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.seductive.emotional[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -7968,12 +7968,12 @@
       </c>
       <c r="C240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.seductive.emotional[1]</t>
+          <t xml:space="preserve">S5.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
@@ -7983,14 +7983,14 @@
       </c>
       <c r="F240" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ファンに会えるの……っ……ふふ、みんなに直接ありがとうって言えるのね……</t>
+          <t xml:space="preserve">少し考えさせて……っ……ふふ、すぐには決められないの……</t>
         </is>
       </c>
     </row>
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.seductive.emotional[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -8000,12 +8000,12 @@
       </c>
       <c r="C241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.seductive.emotional[1]</t>
+          <t xml:space="preserve">S6.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
@@ -8015,14 +8015,14 @@
       </c>
       <c r="F241" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ファッションのお仕事……っ……ふふ、おしゃれするのは好きよ……</t>
+          <t xml:space="preserve">決めたわ……っ……ふふ、これが私の答えよ……</t>
         </is>
       </c>
     </row>
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.seductive.emotional[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8037,7 +8037,7 @@
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.seductive.emotional[1]</t>
+          <t xml:space="preserve">B1.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
@@ -8047,14 +8047,14 @@
       </c>
       <c r="F242" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">グラビア……っ……ふふ、見られるのは嫌いじゃないの……</t>
+          <t xml:space="preserve">これから……っ……やりたいこと、いっぱいあるの……</t>
         </is>
       </c>
     </row>
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.seductive.emotional[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8069,7 +8069,7 @@
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.seductive.emotional[1]</t>
+          <t xml:space="preserve">B2_fighter1.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E243" t="inlineStr" s="2">
@@ -8079,14 +8079,14 @@
       </c>
       <c r="F243" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">バラエティに出るの……っ……ふふ、楽しんでくるわね……</t>
+          <t xml:space="preserve">ねえ……っ……ちょっと話、聞いてくれる？</t>
         </is>
       </c>
     </row>
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.seductive.emotional[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8101,7 +8101,7 @@
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.seductive.emotional[1]</t>
+          <t xml:space="preserve">B2_fighter2.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
@@ -8111,14 +8111,14 @@
       </c>
       <c r="F244" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このお仕事……っ……ふふ、面白そうね……</t>
+          <t xml:space="preserve">いいわよ……っ……話してみて……</t>
         </is>
       </c>
     </row>
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.seductive.emotional[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8128,29 +8128,29 @@
       </c>
       <c r="C245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.emotional[1]</t>
+          <t xml:space="preserve">B4_brand.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F245" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">選んでくれたら…全力で…全力でやるから…！</t>
+          <t xml:space="preserve">ブランドのお話……っ……ふふ、素敵ね……</t>
         </is>
       </c>
     </row>
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.seductive.emotional[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8160,29 +8160,29 @@
       </c>
       <c r="C246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.emotional[1]</t>
+          <t xml:space="preserve">B4_cm.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F246" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…夢みたい。精一杯頑張るわ…</t>
+          <t xml:space="preserve">CMに出るの……っ……ふふ、世間に顔を売るチャンスね……</t>
         </is>
       </c>
     </row>
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.seductive.emotional[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8192,29 +8192,29 @@
       </c>
       <c r="C247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.emotional[1]</t>
+          <t xml:space="preserve">B4_fan.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F247" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとう…っ…嬉しい…。全力で、やるから…</t>
+          <t xml:space="preserve">ファンに会えるの……っ……ふふ、みんなに直接ありがとうって言えるのね……</t>
         </is>
       </c>
     </row>
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.seductive.emotional[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8224,29 +8224,29 @@
       </c>
       <c r="C248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.emotional[1]</t>
+          <t xml:space="preserve">B4_fashion.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F248" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">嬉しい…っ…よろしくね…。頑張るから…</t>
+          <t xml:space="preserve">ファッションのお仕事……っ……ふふ、おしゃれするのは好きよ……</t>
         </is>
       </c>
     </row>
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.seductive.emotional[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8256,29 +8256,29 @@
       </c>
       <c r="C249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.emotional[1]</t>
+          <t xml:space="preserve">B4_gravure.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F249" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…悔しい…必ず戻ってやる…</t>
+          <t xml:space="preserve">グラビア……っ……ふふ、見られるのは嫌いじゃないの……</t>
         </is>
       </c>
     </row>
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.seductive.emotional[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8288,29 +8288,29 @@
       </c>
       <c r="C250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.ahead.seductive.emotional[1]</t>
+          <t xml:space="preserve">B4_variety.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F250" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">済んだ話よ……っ……なのに、まだ手が震えるの</t>
+          <t xml:space="preserve">バラエティに出るの……っ……ふふ、楽しんでくるわね……</t>
         </is>
       </c>
     </row>
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.seductive.emotional[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8320,29 +8320,29 @@
       </c>
       <c r="C251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.behind.seductive.emotional[1]</t>
+          <t xml:space="preserve">B4.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F251" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">終わったの……？ ……嘘よ。まだ、疼いてる</t>
+          <t xml:space="preserve">このお仕事……っ……ふふ、面白そうね……</t>
         </is>
       </c>
     </row>
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.seductive.emotional[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8352,12 +8352,12 @@
       </c>
       <c r="C252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.seductive.emotional[1]</t>
+          <t xml:space="preserve">seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
@@ -8374,7 +8374,7 @@
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.seductive.emotional[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8384,12 +8384,12 @@
       </c>
       <c r="C253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.seductive.emotional[1]</t>
+          <t xml:space="preserve">seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
@@ -8406,7 +8406,7 @@
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.seductive.emotional[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8416,12 +8416,12 @@
       </c>
       <c r="C254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.seductive.emotional[1]</t>
+          <t xml:space="preserve">seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
@@ -8431,14 +8431,14 @@
       </c>
       <c r="F254" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">口説かれる側になるなんて…っ…ふふ、いい度胸ね</t>
+          <t xml:space="preserve">ありがとう…っ…嬉しい…。全力で、やるから…</t>
         </is>
       </c>
     </row>
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.seductive.emotional[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8448,12 +8448,12 @@
       </c>
       <c r="C255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.seductive.emotional[1]</t>
+          <t xml:space="preserve">seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E255" t="inlineStr" s="2">
@@ -8463,14 +8463,14 @@
       </c>
       <c r="F255" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとう…っ…嬉しい…。全力で、やるから…</t>
+          <t xml:space="preserve">嬉しい…っ…よろしくね…。頑張るから…</t>
         </is>
       </c>
     </row>
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.seductive.emotional[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8480,12 +8480,12 @@
       </c>
       <c r="C256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.seductive.emotional[1]</t>
+          <t xml:space="preserve">seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E256" t="inlineStr" s="2">
@@ -8495,14 +8495,14 @@
       </c>
       <c r="F256" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">嬉しい…っ…よろしくね…。頑張るから…</t>
+          <t xml:space="preserve">…っ…悔しい…必ず戻ってやる…</t>
         </is>
       </c>
     </row>
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.seductive.emotional[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8517,7 +8517,7 @@
       </c>
       <c r="D257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.seductive.emotional[1]</t>
+          <t xml:space="preserve">bitterPrematch.ahead.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E257" t="inlineStr" s="2">
@@ -8527,14 +8527,14 @@
       </c>
       <c r="F257" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…悔しい…必ず戻ってやる…</t>
+          <t xml:space="preserve">済んだ話よ……っ……なのに、まだ手が震えるの</t>
         </is>
       </c>
     </row>
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.seductive.emotional[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="D258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.seductive.emotional[1]</t>
+          <t xml:space="preserve">bitterPrematch.behind.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E258" t="inlineStr" s="2">
@@ -8559,14 +8559,14 @@
       </c>
       <c r="F258" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…ありがとう…忘れないわ…</t>
+          <t xml:space="preserve">終わったの……？ ……嘘よ。まだ、疼いてる</t>
         </is>
       </c>
     </row>
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.seductive.emotional[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8581,7 +8581,7 @@
       </c>
       <c r="D259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.seductive.emotional[1]</t>
+          <t xml:space="preserve">draftInterest.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E259" t="inlineStr" s="2">
@@ -8591,14 +8591,14 @@
       </c>
       <c r="F259" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくね…っ…短い間だけど…全力で、やるから…</t>
+          <t xml:space="preserve">選んでくれたら…全力で…全力でやるから…！</t>
         </is>
       </c>
     </row>
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.seductive.emotional[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8613,7 +8613,7 @@
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.seductive.emotional[1]</t>
+          <t xml:space="preserve">draftJoin.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E260" t="inlineStr" s="2">
@@ -8623,14 +8623,14 @@
       </c>
       <c r="F260" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うふふ♪嬉しい♪</t>
+          <t xml:space="preserve">…っ…夢みたい。精一杯頑張るわ…</t>
         </is>
       </c>
     </row>
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.seductive.emotional[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8645,7 +8645,7 @@
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.seductive.emotional[1]</t>
+          <t xml:space="preserve">faGreeting.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
@@ -8655,14 +8655,14 @@
       </c>
       <c r="F261" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しい…っ…悔しい…。でも…絶対に、諦めない…</t>
+          <t xml:space="preserve">口説かれる側になるなんて…っ…ふふ、いい度胸ね</t>
         </is>
       </c>
     </row>
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.seductive.emotional[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8677,7 +8677,7 @@
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.seductive.emotional[1]</t>
+          <t xml:space="preserve">faSigning.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E262" t="inlineStr" s="2">
@@ -8687,14 +8687,14 @@
       </c>
       <c r="F262" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">守れた…っ…嬉しい…。次も、絶対に守るから…</t>
+          <t xml:space="preserve">ありがとう…っ…嬉しい…。全力で、やるから…</t>
         </is>
       </c>
     </row>
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.seductive.emotional[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8709,7 +8709,7 @@
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.seductive.emotional[1]</t>
+          <t xml:space="preserve">faWelcome.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E263" t="inlineStr" s="2">
@@ -8719,14 +8719,14 @@
       </c>
       <c r="F263" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">嘘…っ…ベルトが…。でも…でも、諦めない…</t>
+          <t xml:space="preserve">嬉しい…っ…よろしくね…。頑張るから…</t>
         </is>
       </c>
     </row>
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.seductive.emotional[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.seductive.emotional[1]</t>
+          <t xml:space="preserve">injury.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E264" t="inlineStr" s="2">
@@ -8751,14 +8751,14 @@
       </c>
       <c r="F264" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ああ…っ…チャンピオン…。嬉しい…だめ、泣いちゃう…</t>
+          <t xml:space="preserve">…っ…悔しい…必ず戻ってやる…</t>
         </is>
       </c>
     </row>
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.seductive.emotional[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="C265" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.emotional[1]</t>
+          <t xml:space="preserve">release.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E265" t="inlineStr" s="2">
@@ -8790,7 +8790,7 @@
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.seductive.emotional[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8800,12 +8800,12 @@
       </c>
       <c r="C266" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.emotional[1]</t>
+          <t xml:space="preserve">rentalGreeting.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E266" t="inlineStr" s="2">
@@ -8822,7 +8822,7 @@
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.seductive.emotional[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -8832,12 +8832,12 @@
       </c>
       <c r="C267" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.emotional[1]</t>
+          <t xml:space="preserve">scoutGreeting.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E267" t="inlineStr" s="2">
@@ -8847,14 +8847,14 @@
       </c>
       <c r="F267" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しい…っ…悔しい…。でも…絶対に、諦めない…</t>
+          <t xml:space="preserve">うふふ♪嬉しい♪</t>
         </is>
       </c>
     </row>
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.seductive.emotional[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -8864,12 +8864,12 @@
       </c>
       <c r="C268" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D268" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.emotional[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E268" t="inlineStr" s="2">
@@ -8879,14 +8879,14 @@
       </c>
       <c r="F268" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">守れた…っ…嬉しい…。次も、絶対に守るから…</t>
+          <t xml:space="preserve">悔しい…っ…悔しい…。でも…絶対に、諦めない…</t>
         </is>
       </c>
     </row>
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.seductive.emotional[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="C269" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D269" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.emotional[1]</t>
+          <t xml:space="preserve">titleDefense.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E269" t="inlineStr" s="2">
@@ -8911,14 +8911,14 @@
       </c>
       <c r="F269" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">嘘…っ…ベルトが…。でも…でも、諦めない…</t>
+          <t xml:space="preserve">守れた…っ…嬉しい…。次も、絶対に守るから…</t>
         </is>
       </c>
     </row>
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.seductive.emotional[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -8928,12 +8928,12 @@
       </c>
       <c r="C270" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D270" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.emotional[1]</t>
+          <t xml:space="preserve">titleLoss.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E270" t="inlineStr" s="2">
@@ -8943,14 +8943,14 @@
       </c>
       <c r="F270" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ああ…っ…チャンピオン…。嬉しい…だめ、泣いちゃう…</t>
+          <t xml:space="preserve">嘘…っ…ベルトが…。でも…でも、諦めない…</t>
         </is>
       </c>
     </row>
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.emotional.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -8960,29 +8960,29 @@
       </c>
       <c r="C271" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D271" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.emotional.seductive[1]</t>
+          <t xml:space="preserve">titleWin.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E271" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F271" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">考えると苦しいの…もう無理…</t>
+          <t xml:space="preserve">ああ…っ…チャンピオン…。嬉しい…だめ、泣いちゃう…</t>
         </is>
       </c>
     </row>
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.emotional.seductive[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -8992,29 +8992,29 @@
       </c>
       <c r="C272" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D272" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.emotional.seductive[1]</t>
+          <t xml:space="preserve">seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E272" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F272" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">離れていく…嫌よ…こんなの…</t>
+          <t xml:space="preserve">…っ…ありがとう…忘れないわ…</t>
         </is>
       </c>
     </row>
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.emotional.seductive[2]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -9024,29 +9024,29 @@
       </c>
       <c r="C273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.emotional.seductive[2]</t>
+          <t xml:space="preserve">seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F273" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">どうして…以前のように言葉をくれないの…</t>
+          <t xml:space="preserve">よろしくね…っ…短い間だけど…全力で、やるから…</t>
         </is>
       </c>
     </row>
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.emotional.seductive[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -9056,29 +9056,29 @@
       </c>
       <c r="C274" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.emotional.seductive[1]</t>
+          <t xml:space="preserve">seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E274" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F274" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">放っておけないの…もう</t>
+          <t xml:space="preserve">悔しい…っ…悔しい…。でも…絶対に、諦めない…</t>
         </is>
       </c>
     </row>
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.emotional.seductive[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -9088,29 +9088,29 @@
       </c>
       <c r="C275" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.emotional.seductive[1]</t>
+          <t xml:space="preserve">seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E275" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F275" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この人のためなら何でもできるの…！ 絶対に守るわ…！</t>
+          <t xml:space="preserve">守れた…っ…嬉しい…。次も、絶対に守るから…</t>
         </is>
       </c>
     </row>
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.emotional.seductive[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -9120,29 +9120,29 @@
       </c>
       <c r="C276" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.emotional.seductive[2]</t>
+          <t xml:space="preserve">seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E276" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F276" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">巡り合えたこと、心から幸せなの…！</t>
+          <t xml:space="preserve">嘘…っ…ベルトが…。でも…でも、諦めない…</t>
         </is>
       </c>
     </row>
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.emotional.seductive[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9152,29 +9152,29 @@
       </c>
       <c r="C277" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.emotional.seductive[1]</t>
+          <t xml:space="preserve">seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F277" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">因縁…終わっちゃったのね…少し寂しい…</t>
+          <t xml:space="preserve">ああ…っ…チャンピオン…。嬉しい…だめ、泣いちゃう…</t>
         </is>
       </c>
     </row>
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.emotional.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9189,7 +9189,7 @@
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.emotional.seductive[2]</t>
+          <t xml:space="preserve">bond_39_down.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E278" t="inlineStr" s="2">
@@ -9199,14 +9199,14 @@
       </c>
       <c r="F278" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……あの熱さが消えていくわ。これでいいのかしら…</t>
+          <t xml:space="preserve">考えると苦しいの…もう無理…</t>
         </is>
       </c>
     </row>
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.emotional.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9221,7 +9221,7 @@
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.emotional.seductive[1]</t>
+          <t xml:space="preserve">bond_59_down.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E279" t="inlineStr" s="2">
@@ -9231,14 +9231,14 @@
       </c>
       <c r="F279" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">絶対に負けないわ…！ 絶対に…！</t>
+          <t xml:space="preserve">離れていく…嫌よ…こんなの…</t>
         </is>
       </c>
     </row>
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.emotional.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.emotional.seductive[2]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9253,7 +9253,7 @@
       </c>
       <c r="D280" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.emotional.seductive[2]</t>
+          <t xml:space="preserve">bond_59_down.emotional.seductive[2]</t>
         </is>
       </c>
       <c r="E280" t="inlineStr" s="2">
@@ -9263,14 +9263,14 @@
       </c>
       <c r="F280" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">考えるだけで胸が熱くなるの…！</t>
+          <t xml:space="preserve">どうして…以前のように言葉をくれないの…</t>
         </is>
       </c>
     </row>
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.emotional.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9285,7 +9285,7 @@
       </c>
       <c r="D281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.emotional.seductive[1]</t>
+          <t xml:space="preserve">bond_60_up.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E281" t="inlineStr" s="2">
@@ -9295,14 +9295,14 @@
       </c>
       <c r="F281" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くっ…考えると熱くなるの…！</t>
+          <t xml:space="preserve">放っておけないの…もう</t>
         </is>
       </c>
     </row>
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.emotional.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -9317,7 +9317,7 @@
       </c>
       <c r="D282" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.emotional.seductive[2]</t>
+          <t xml:space="preserve">bond_80_up.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E282" t="inlineStr" s="2">
@@ -9327,14 +9327,14 @@
       </c>
       <c r="F282" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">絶対に…超えてみせるわ…！！</t>
+          <t xml:space="preserve">この人のためなら何でもできるの…！ 絶対に守るわ…！</t>
         </is>
       </c>
     </row>
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.emotional.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.emotional.seductive[2]</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -9349,7 +9349,7 @@
       </c>
       <c r="D283" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.emotional.seductive[1]</t>
+          <t xml:space="preserve">bond_80_up.emotional.seductive[2]</t>
         </is>
       </c>
       <c r="E283" t="inlineStr" s="2">
@@ -9359,14 +9359,14 @@
       </c>
       <c r="F283" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの出会いがなければ今の私はいなかった…！</t>
+          <t xml:space="preserve">巡り合えたこと、心から幸せなの…！</t>
         </is>
       </c>
     </row>
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.emotional.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -9381,7 +9381,7 @@
       </c>
       <c r="D284" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.emotional.seductive[2]</t>
+          <t xml:space="preserve">rivalry_29_down.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E284" t="inlineStr" s="2">
@@ -9391,14 +9391,14 @@
       </c>
       <c r="F284" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この因縁に終わりなんてないわ…！ 永遠に戦い続けるの…！</t>
+          <t xml:space="preserve">因縁…終わっちゃったのね…少し寂しい…</t>
         </is>
       </c>
     </row>
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.emotional.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.emotional.seductive[2]</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -9413,7 +9413,7 @@
       </c>
       <c r="D285" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.emotional.seductive[1]</t>
+          <t xml:space="preserve">rivalry_29_down.emotional.seductive[2]</t>
         </is>
       </c>
       <c r="E285" t="inlineStr" s="2">
@@ -9423,14 +9423,14 @@
       </c>
       <c r="F285" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みんなのこと…大好きよ…！ この団体のために全力を尽くすわ…！</t>
+          <t xml:space="preserve">……あの熱さが消えていくわ。これでいいのかしら…</t>
         </is>
       </c>
     </row>
     <row r="286" ht="40" customHeight="1">
       <c r="A286" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.emotional.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -9445,7 +9445,7 @@
       </c>
       <c r="D286" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.emotional.seductive[2]</t>
+          <t xml:space="preserve">rivalry_30_up.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E286" t="inlineStr" s="2">
@@ -9455,14 +9455,14 @@
       </c>
       <c r="F286" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここで出会えた仲間は宝物なの…絶対に裏切らないわ…！</t>
+          <t xml:space="preserve">絶対に負けないわ…！ 絶対に…！</t>
         </is>
       </c>
     </row>
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.emotional.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.emotional.seductive[2]</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -9477,7 +9477,7 @@
       </c>
       <c r="D287" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.emotional.seductive[1]</t>
+          <t xml:space="preserve">rivalry_30_up.emotional.seductive[2]</t>
         </is>
       </c>
       <c r="E287" t="inlineStr" s="2">
@@ -9487,14 +9487,14 @@
       </c>
       <c r="F287" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう…信じられないわ…！ どうして…！</t>
+          <t xml:space="preserve">考えるだけで胸が熱くなるの…！</t>
         </is>
       </c>
     </row>
     <row r="288" ht="40" customHeight="1">
       <c r="A288" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.emotional.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
@@ -9509,7 +9509,7 @@
       </c>
       <c r="D288" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.emotional.seductive[2]</t>
+          <t xml:space="preserve">rivalry_50_up.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E288" t="inlineStr" s="2">
@@ -9519,14 +9519,14 @@
       </c>
       <c r="F288" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">裏切られたのね…全部…偽りだったの…？</t>
+          <t xml:space="preserve">くっ…考えると熱くなるの…！</t>
         </is>
       </c>
     </row>
     <row r="289" ht="40" customHeight="1">
       <c r="A289" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.emotional.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.emotional.seductive[2]</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
@@ -9541,7 +9541,7 @@
       </c>
       <c r="D289" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.emotional.seductive[1]</t>
+          <t xml:space="preserve">rivalry_50_up.emotional.seductive[2]</t>
         </is>
       </c>
       <c r="E289" t="inlineStr" s="2">
@@ -9551,14 +9551,14 @@
       </c>
       <c r="F289" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">不安なの…これでいいのかしら…？ 私、忘れられてない…？</t>
+          <t xml:space="preserve">絶対に…超えてみせるわ…！！</t>
         </is>
       </c>
     </row>
     <row r="290" ht="40" customHeight="1">
       <c r="A290" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.seductive.emotional[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="C290" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D290" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.goodLoss.seductive.emotional[1]</t>
+          <t xml:space="preserve">rivalry_70_up.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E290" t="inlineStr" s="2">
@@ -9583,14 +9583,14 @@
       </c>
       <c r="F290" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けたけど……っ……ふふ、出し切れたの……</t>
+          <t xml:space="preserve">あの出会いがなければ今の私はいなかった…！</t>
         </is>
       </c>
     </row>
     <row r="291" ht="40" customHeight="1">
       <c r="A291" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.seductive.emotional[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.emotional.seductive[2]</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="C291" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D291" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.greatWin.seductive.emotional[1]</t>
+          <t xml:space="preserve">rivalry_70_up.emotional.seductive[2]</t>
         </is>
       </c>
       <c r="E291" t="inlineStr" s="2">
@@ -9615,14 +9615,14 @@
       </c>
       <c r="F291" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高の勝利……っ……ふふ、震えてるの……</t>
+          <t xml:space="preserve">この因縁に終わりなんてないわ…！ 永遠に戦い続けるの…！</t>
         </is>
       </c>
     </row>
     <row r="292" ht="40" customHeight="1">
       <c r="A292" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.seductive.emotional[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
@@ -9632,12 +9632,12 @@
       </c>
       <c r="C292" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D292" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.loss.seductive.emotional[1]</t>
+          <t xml:space="preserve">trust_above_75.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E292" t="inlineStr" s="2">
@@ -9647,14 +9647,14 @@
       </c>
       <c r="F292" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けた……っ……悔しい……</t>
+          <t xml:space="preserve">みんなのこと…大好きよ…！ この団体のために全力を尽くすわ…！</t>
         </is>
       </c>
     </row>
     <row r="293" ht="40" customHeight="1">
       <c r="A293" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.seductive.emotional[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.emotional.seductive[2]</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
@@ -9664,12 +9664,12 @@
       </c>
       <c r="C293" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D293" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.win.seductive.emotional[1]</t>
+          <t xml:space="preserve">trust_above_75.emotional.seductive[2]</t>
         </is>
       </c>
       <c r="E293" t="inlineStr" s="2">
@@ -9679,14 +9679,14 @@
       </c>
       <c r="F293" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ったわ……っ……ふふ、嬉しい……</t>
+          <t xml:space="preserve">ここで出会えた仲間は宝物なの…絶対に裏切らないわ…！</t>
         </is>
       </c>
     </row>
     <row r="294" ht="40" customHeight="1">
       <c r="A294" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.seductive.emotional[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
@@ -9696,12 +9696,12 @@
       </c>
       <c r="C294" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D294" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.seductive.emotional[1]</t>
+          <t xml:space="preserve">trust_below_20.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E294" t="inlineStr" s="2">
@@ -9711,14 +9711,14 @@
       </c>
       <c r="F294" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日は……っ……ふふ、よろしくね……</t>
+          <t xml:space="preserve">もう…信じられないわ…！ どうして…！</t>
         </is>
       </c>
     </row>
     <row r="295" ht="40" customHeight="1">
       <c r="A295" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.seductive.emotional[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.emotional.seductive[2]</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="2">
@@ -9728,12 +9728,12 @@
       </c>
       <c r="C295" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D295" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.down.seductive.emotional[1]</t>
+          <t xml:space="preserve">trust_below_20.emotional.seductive[2]</t>
         </is>
       </c>
       <c r="E295" t="inlineStr" s="2">
@@ -9743,14 +9743,14 @@
       </c>
       <c r="F295" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うまくいかない……っ……どうしてかしら……</t>
+          <t xml:space="preserve">裏切られたのね…全部…偽りだったの…？</t>
         </is>
       </c>
     </row>
     <row r="296" ht="40" customHeight="1">
       <c r="A296" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.seductive.emotional[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="B296" t="inlineStr" s="2">
@@ -9760,12 +9760,12 @@
       </c>
       <c r="C296" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D296" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.up.seductive.emotional[1]</t>
+          <t xml:space="preserve">trust_below_35.emotional.seductive[1]</t>
         </is>
       </c>
       <c r="E296" t="inlineStr" s="2">
@@ -9775,14 +9775,14 @@
       </c>
       <c r="F296" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">なんだか調子いいの……っ……ふふ……</t>
+          <t xml:space="preserve">不安なの…これでいいのかしら…？ 私、忘れられてない…？</t>
         </is>
       </c>
     </row>
     <row r="297" ht="40" customHeight="1">
       <c r="A297" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.seductive.emotional[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B297" t="inlineStr" s="2">
@@ -9797,7 +9797,7 @@
       </c>
       <c r="D297" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-04.seductive.emotional[1]</t>
+          <t xml:space="preserve">GL-01.goodLoss.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E297" t="inlineStr" s="2">
@@ -9807,14 +9807,14 @@
       </c>
       <c r="F297" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習するわ……っ……ふふ……</t>
+          <t xml:space="preserve">負けたけど……っ……ふふ、出し切れたの……</t>
         </is>
       </c>
     </row>
     <row r="298" ht="40" customHeight="1">
       <c r="A298" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.seductive.emotional[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B298" t="inlineStr" s="2">
@@ -9829,7 +9829,7 @@
       </c>
       <c r="D298" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-05.seductive.emotional[1]</t>
+          <t xml:space="preserve">GL-01.greatWin.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E298" t="inlineStr" s="2">
@@ -9839,14 +9839,14 @@
       </c>
       <c r="F298" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">大丈夫よ……っ……ふふ、心配しないで……</t>
+          <t xml:space="preserve">最高の勝利……っ……ふふ、震えてるの……</t>
         </is>
       </c>
     </row>
     <row r="299" ht="40" customHeight="1">
       <c r="A299" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.seductive.emotional[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B299" t="inlineStr" s="2">
@@ -9861,7 +9861,7 @@
       </c>
       <c r="D299" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.seductive.emotional[1]</t>
+          <t xml:space="preserve">GL-01.loss.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E299" t="inlineStr" s="2">
@@ -9871,14 +9871,14 @@
       </c>
       <c r="F299" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みんなと一緒だと……っ……ふふ、安心するの……</t>
+          <t xml:space="preserve">負けた……っ……悔しい……</t>
         </is>
       </c>
     </row>
     <row r="300" ht="40" customHeight="1">
       <c r="A300" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.seductive.emotional[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B300" t="inlineStr" s="2">
@@ -9893,7 +9893,7 @@
       </c>
       <c r="D300" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-07.seductive.emotional[1]</t>
+          <t xml:space="preserve">GL-01.win.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E300" t="inlineStr" s="2">
@@ -9903,14 +9903,14 @@
       </c>
       <c r="F300" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お客さんがいっぱい……っ……ふふ、燃えるわね……</t>
+          <t xml:space="preserve">勝ったわ……っ……ふふ、嬉しい……</t>
         </is>
       </c>
     </row>
     <row r="301" ht="40" customHeight="1">
       <c r="A301" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.seductive.emotional[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B301" t="inlineStr" s="2">
@@ -9925,7 +9925,7 @@
       </c>
       <c r="D301" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.seductive.emotional[1]</t>
+          <t xml:space="preserve">GL-02.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E301" t="inlineStr" s="2">
@@ -9935,14 +9935,14 @@
       </c>
       <c r="F301" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">体調は大丈夫よ……っ……ふふ、心配いらない……</t>
+          <t xml:space="preserve">今日は……っ……ふふ、よろしくね……</t>
         </is>
       </c>
     </row>
     <row r="302" ht="40" customHeight="1">
       <c r="A302" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.seductive.emotional[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B302" t="inlineStr" s="2">
@@ -9957,7 +9957,7 @@
       </c>
       <c r="D302" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-09.seductive.emotional[1]</t>
+          <t xml:space="preserve">GL-03.down.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E302" t="inlineStr" s="2">
@@ -9967,14 +9967,14 @@
       </c>
       <c r="F302" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次の試合……っ……ふふ、楽しみだわ……</t>
+          <t xml:space="preserve">うまくいかない……っ……どうしてかしら……</t>
         </is>
       </c>
     </row>
     <row r="303" ht="40" customHeight="1">
       <c r="A303" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.seductive.emotional[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B303" t="inlineStr" s="2">
@@ -9989,7 +9989,7 @@
       </c>
       <c r="D303" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.seductive.emotional[1]</t>
+          <t xml:space="preserve">GL-03.up.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E303" t="inlineStr" s="2">
@@ -9999,14 +9999,14 @@
       </c>
       <c r="F303" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとう……っ……ふふ、嬉しい……</t>
+          <t xml:space="preserve">なんだか調子いいの……っ……ふふ……</t>
         </is>
       </c>
     </row>
     <row r="304" ht="40" customHeight="1">
       <c r="A304" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.seductive.emotional[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B304" t="inlineStr" s="2">
@@ -10016,12 +10016,12 @@
       </c>
       <c r="C304" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D304" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.emotional[1]</t>
+          <t xml:space="preserve">GL-04.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E304" t="inlineStr" s="2">
@@ -10031,14 +10031,14 @@
       </c>
       <c r="F304" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勢いが止まったわ……っ……ふふ、また始めればいいのよ……</t>
+          <t xml:space="preserve">練習するわ……っ……ふふ……</t>
         </is>
       </c>
     </row>
     <row r="305" ht="40" customHeight="1">
       <c r="A305" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.seductive.emotional[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B305" t="inlineStr" s="2">
@@ -10048,29 +10048,29 @@
       </c>
       <c r="C305" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D305" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.seductive.emotional[1]</t>
+          <t xml:space="preserve">GL-05.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E305" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F305" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">身体、もう震えてるの…っ…ふふ、でも最後まで立つわ</t>
+          <t xml:space="preserve">大丈夫よ……っ……ふふ、心配しないで……</t>
         </is>
       </c>
     </row>
     <row r="306" ht="40" customHeight="1">
       <c r="A306" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.seductive.emotional[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B306" t="inlineStr" s="2">
@@ -10080,29 +10080,29 @@
       </c>
       <c r="C306" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D306" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.seductive.emotional[2]</t>
+          <t xml:space="preserve">GL-06.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E306" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F306" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで来たのね…っ…最後の舞台、全部ぶつけるわ</t>
+          <t xml:space="preserve">みんなと一緒だと……っ……ふふ、安心するの……</t>
         </is>
       </c>
     </row>
     <row r="307" ht="40" customHeight="1">
       <c r="A307" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.seductive.emotional[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B307" t="inlineStr" s="2">
@@ -10112,29 +10112,29 @@
       </c>
       <c r="C307" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D307" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.seductive.emotional[1]</t>
+          <t xml:space="preserve">GL-07.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E307" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F307" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お相手は誰かしら…っ…ふふ、もう身体が疼いてるの</t>
+          <t xml:space="preserve">お客さんがいっぱい……っ……ふふ、燃えるわね……</t>
         </is>
       </c>
     </row>
     <row r="308" ht="40" customHeight="1">
       <c r="A308" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.seductive.emotional[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B308" t="inlineStr" s="2">
@@ -10144,29 +10144,29 @@
       </c>
       <c r="C308" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D308" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.seductive.emotional[2]</t>
+          <t xml:space="preserve">GL-08.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E308" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F308" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">早く来てよ…！ この昂り、ぶつける相手が欲しいの…！</t>
+          <t xml:space="preserve">体調は大丈夫よ……っ……ふふ、心配いらない……</t>
         </is>
       </c>
     </row>
     <row r="309" ht="40" customHeight="1">
       <c r="A309" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.seductive.emotional[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B309" t="inlineStr" s="2">
@@ -10176,29 +10176,29 @@
       </c>
       <c r="C309" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D309" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.seductive.emotional[1]</t>
+          <t xml:space="preserve">GL-09.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E309" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F309" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人、落としたわ…っ…はぁ…まだ疼いてるの。次、早く出してよ</t>
+          <t xml:space="preserve">次の試合……っ……ふふ、楽しみだわ……</t>
         </is>
       </c>
     </row>
     <row r="310" ht="40" customHeight="1">
       <c r="A310" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.seductive.emotional[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B310" t="inlineStr" s="2">
@@ -10208,29 +10208,29 @@
       </c>
       <c r="C310" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D310" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.seductive.emotional[2]</t>
+          <t xml:space="preserve">GL-10.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E310" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F310" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ立ってる…！ この身体、まだ終わってないの…！ 次、来なさい…！</t>
+          <t xml:space="preserve">ありがとう……っ……ふふ、嬉しい……</t>
         </is>
       </c>
     </row>
     <row r="311" ht="40" customHeight="1">
       <c r="A311" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.seductive.emotional[1]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B311" t="inlineStr" s="2">
@@ -10240,29 +10240,29 @@
       </c>
       <c r="C311" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D311" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.seductive.emotional[1]</t>
+          <t xml:space="preserve">seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E311" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F311" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">三人で勝ったの……！ この感動は……一人じゃ味わえないわ……</t>
+          <t xml:space="preserve">勢いが止まったわ……っ……ふふ、また始めればいいのよ……</t>
         </is>
       </c>
     </row>
     <row r="312" ht="40" customHeight="1">
       <c r="A312" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.seductive.emotional[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B312" t="inlineStr" s="2">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="C312" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D312" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.seductive.emotional[2]</t>
+          <t xml:space="preserve">preFinal.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E312" t="inlineStr" s="2">
@@ -10287,14 +10287,14 @@
       </c>
       <c r="F312" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲間が繋いでくれた想い……最後まで、手放さなかったよ……！</t>
+          <t xml:space="preserve">身体、もう震えてるの…っ…ふふ、でも最後まで立つわ</t>
         </is>
       </c>
     </row>
     <row r="313" ht="40" customHeight="1">
       <c r="A313" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.seductive.emotional[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B313" t="inlineStr" s="2">
@@ -10304,12 +10304,12 @@
       </c>
       <c r="C313" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D313" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.seductive.emotional[1]</t>
+          <t xml:space="preserve">preFinal.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E313" t="inlineStr" s="2">
@@ -10319,14 +10319,14 @@
       </c>
       <c r="F313" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この賞じゃ……心は満たされないのよ……！ 次は全部、奪い返すから……</t>
+          <t xml:space="preserve">ここまで来たのね…っ…最後の舞台、全部ぶつけるわ</t>
         </is>
       </c>
     </row>
     <row r="314" ht="40" customHeight="1">
       <c r="A314" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.seductive.emotional[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B314" t="inlineStr" s="2">
@@ -10336,12 +10336,12 @@
       </c>
       <c r="C314" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D314" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.seductive.emotional[2]</t>
+          <t xml:space="preserve">preMatch.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E314" t="inlineStr" s="2">
@@ -10351,14 +10351,14 @@
       </c>
       <c r="F314" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人で輝いても寂しいだけ……！ 次は……三人で、ね……！</t>
+          <t xml:space="preserve">お相手は誰かしら…っ…ふふ、もう身体が疼いてるの</t>
         </is>
       </c>
     </row>
     <row r="315" ht="40" customHeight="1">
       <c r="A315" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.seductive.emotional[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B315" t="inlineStr" s="2">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="C315" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D315" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.seductive.emotional[1]</t>
+          <t xml:space="preserve">preMatch.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E315" t="inlineStr" s="2">
@@ -10383,14 +10383,14 @@
       </c>
       <c r="F315" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう身体が動かない……でも、最後に立ってたのは私よ……！ 見届けてくれた？</t>
+          <t xml:space="preserve">早く来てよ…！ この昂り、ぶつける相手が欲しいの…！</t>
         </is>
       </c>
     </row>
     <row r="316" ht="40" customHeight="1">
       <c r="A316" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.seductive.emotional[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B316" t="inlineStr" s="2">
@@ -10400,12 +10400,12 @@
       </c>
       <c r="C316" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D316" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.seductive.emotional[2]</t>
+          <t xml:space="preserve">survivor.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E316" t="inlineStr" s="2">
@@ -10415,14 +10415,14 @@
       </c>
       <c r="F316" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何人来ても倒れなかった……！ この身体が、全部証明してるでしょ……？</t>
+          <t xml:space="preserve">一人、落としたわ…っ…はぁ…まだ疼いてるの。次、早く出してよ</t>
         </is>
       </c>
     </row>
     <row r="317" ht="40" customHeight="1">
       <c r="A317" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.seductive.emotional[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B317" t="inlineStr" s="2">
@@ -10432,12 +10432,12 @@
       </c>
       <c r="C317" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D317" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.seductive.emotional[1]</t>
+          <t xml:space="preserve">survivor.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E317" t="inlineStr" s="2">
@@ -10447,14 +10447,14 @@
       </c>
       <c r="F317" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">優勝……っ……ふふ、私、頂点に立ったのね……！</t>
+          <t xml:space="preserve">まだ立ってる…！ この身体、まだ終わってないの…！ 次、来なさい…！</t>
         </is>
       </c>
     </row>
     <row r="318" ht="40" customHeight="1">
       <c r="A318" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.seductive.emotional[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B318" t="inlineStr" s="2">
@@ -10464,12 +10464,12 @@
       </c>
       <c r="C318" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D318" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.seductive.emotional[2]</t>
+          <t xml:space="preserve">champion.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E318" t="inlineStr" s="2">
@@ -10479,14 +10479,14 @@
       </c>
       <c r="F318" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この景色……っ……ふふ、忘れないわ……</t>
+          <t xml:space="preserve">三人で勝ったの……！ この感動は……一人じゃ味わえないわ……</t>
         </is>
       </c>
     </row>
     <row r="319" ht="40" customHeight="1">
       <c r="A319" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.seductive.emotional[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B319" t="inlineStr" s="2">
@@ -10496,12 +10496,12 @@
       </c>
       <c r="C319" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D319" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.seductive.emotional[1]</t>
+          <t xml:space="preserve">champion.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E319" t="inlineStr" s="2">
@@ -10511,14 +10511,14 @@
       </c>
       <c r="F319" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けたわ……っ……悔しい……でも、いい経験だった……</t>
+          <t xml:space="preserve">仲間が繋いでくれた想い……最後まで、手放さなかったよ……！</t>
         </is>
       </c>
     </row>
     <row r="320" ht="40" customHeight="1">
       <c r="A320" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.seductive.emotional[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B320" t="inlineStr" s="2">
@@ -10528,12 +10528,12 @@
       </c>
       <c r="C320" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D320" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.seductive.emotional[2]</t>
+          <t xml:space="preserve">defiant.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E320" t="inlineStr" s="2">
@@ -10543,14 +10543,14 @@
       </c>
       <c r="F320" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">リベンジするわ……っ……ふふ、必ず……</t>
+          <t xml:space="preserve">この賞じゃ……心は満たされないのよ……！ 次は全部、奪い返すから……</t>
         </is>
       </c>
     </row>
     <row r="321" ht="40" customHeight="1">
       <c r="A321" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.seductive.emotional[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B321" t="inlineStr" s="2">
@@ -10560,12 +10560,12 @@
       </c>
       <c r="C321" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D321" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.seductive.emotional[1]</t>
+          <t xml:space="preserve">defiant.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E321" t="inlineStr" s="2">
@@ -10575,14 +10575,14 @@
       </c>
       <c r="F321" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝った……っ……ふふ、まだまだ行けるわ……</t>
+          <t xml:space="preserve">一人で輝いても寂しいだけ……！ 次は……三人で、ね……！</t>
         </is>
       </c>
     </row>
     <row r="322" ht="40" customHeight="1">
       <c r="A322" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.seductive.emotional[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B322" t="inlineStr" s="2">
@@ -10592,12 +10592,12 @@
       </c>
       <c r="C322" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D322" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.seductive.emotional[2]</t>
+          <t xml:space="preserve">gauntlet.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E322" t="inlineStr" s="2">
@@ -10607,14 +10607,14 @@
       </c>
       <c r="F322" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい感じよ……っ……ふふ……</t>
+          <t xml:space="preserve">もう身体が動かない……でも、最後に立ってたのは私よ……！ 見届けてくれた？</t>
         </is>
       </c>
     </row>
     <row r="323" ht="40" customHeight="1">
       <c r="A323" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.seductive.emotional[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B323" t="inlineStr" s="2">
@@ -10624,12 +10624,12 @@
       </c>
       <c r="C323" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D323" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.seductive.emotional[1]</t>
+          <t xml:space="preserve">gauntlet.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E323" t="inlineStr" s="2">
@@ -10639,14 +10639,14 @@
       </c>
       <c r="F323" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ち上がったわ……っ……ふふ、ここまで来られたの……</t>
+          <t xml:space="preserve">何人来ても倒れなかった……！ この身体が、全部証明してるでしょ……？</t>
         </is>
       </c>
     </row>
     <row r="324" ht="40" customHeight="1">
       <c r="A324" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.seductive.emotional[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B324" t="inlineStr" s="2">
@@ -10661,7 +10661,7 @@
       </c>
       <c r="D324" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.seductive.emotional[2]</t>
+          <t xml:space="preserve">champion.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E324" t="inlineStr" s="2">
@@ -10671,14 +10671,14 @@
       </c>
       <c r="F324" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もっと上を目指すわ……っ……ふふ……</t>
+          <t xml:space="preserve">優勝……っ……ふふ、私、頂点に立ったのね……！</t>
         </is>
       </c>
     </row>
     <row r="325" ht="40" customHeight="1">
       <c r="A325" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.seductive.emotional[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B325" t="inlineStr" s="2">
@@ -10693,7 +10693,7 @@
       </c>
       <c r="D325" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.seductive.emotional[1]</t>
+          <t xml:space="preserve">champion.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E325" t="inlineStr" s="2">
@@ -10703,14 +10703,14 @@
       </c>
       <c r="F325" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決勝戦……っ……ふふ、ここまで来たのね……</t>
+          <t xml:space="preserve">この景色……っ……ふふ、忘れないわ……</t>
         </is>
       </c>
     </row>
     <row r="326" ht="40" customHeight="1">
       <c r="A326" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.seductive.emotional[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B326" t="inlineStr" s="2">
@@ -10725,7 +10725,7 @@
       </c>
       <c r="D326" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.seductive.emotional[2]</t>
+          <t xml:space="preserve">postLose.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E326" t="inlineStr" s="2">
@@ -10735,14 +10735,14 @@
       </c>
       <c r="F326" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高の舞台ね……っ……ふふ、震えてるの……</t>
+          <t xml:space="preserve">負けたわ……っ……悔しい……でも、いい経験だった……</t>
         </is>
       </c>
     </row>
     <row r="327" ht="40" customHeight="1">
       <c r="A327" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.seductive.emotional[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B327" t="inlineStr" s="2">
@@ -10757,7 +10757,7 @@
       </c>
       <c r="D327" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.seductive.emotional[1]</t>
+          <t xml:space="preserve">postLose.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E327" t="inlineStr" s="2">
@@ -10767,14 +10767,14 @@
       </c>
       <c r="F327" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">試合前……っ……ふふ、心臓がドキドキしてるの……</t>
+          <t xml:space="preserve">リベンジするわ……っ……ふふ、必ず……</t>
         </is>
       </c>
     </row>
     <row r="328" ht="40" customHeight="1">
       <c r="A328" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.seductive.emotional[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B328" t="inlineStr" s="2">
@@ -10789,7 +10789,7 @@
       </c>
       <c r="D328" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.seductive.emotional[2]</t>
+          <t xml:space="preserve">postMatchWin.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E328" t="inlineStr" s="2">
@@ -10799,14 +10799,14 @@
       </c>
       <c r="F328" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">楽しんでくるわね……っ……ふふ……</t>
+          <t xml:space="preserve">勝った……っ……ふふ、まだまだ行けるわ……</t>
         </is>
       </c>
     </row>
     <row r="329" ht="40" customHeight="1">
       <c r="A329" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.seductive.emotional[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B329" t="inlineStr" s="2">
@@ -10821,7 +10821,7 @@
       </c>
       <c r="D329" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.seductive.emotional[1]</t>
+          <t xml:space="preserve">postMatchWin.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E329" t="inlineStr" s="2">
@@ -10831,14 +10831,14 @@
       </c>
       <c r="F329" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ジュニア大会に……っ……ふふ、私を選んでくれたのね、嬉しい……</t>
+          <t xml:space="preserve">いい感じよ……っ……ふふ……</t>
         </is>
       </c>
     </row>
     <row r="330" ht="40" customHeight="1">
       <c r="A330" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.seductive.emotional[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B330" t="inlineStr" s="2">
@@ -10853,7 +10853,7 @@
       </c>
       <c r="D330" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.seductive.emotional[2]</t>
+          <t xml:space="preserve">postWin.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E330" t="inlineStr" s="2">
@@ -10863,14 +10863,14 @@
       </c>
       <c r="F330" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">楽しみだわ……っ……ふふ、燃えてきたの……</t>
+          <t xml:space="preserve">勝ち上がったわ……っ……ふふ、ここまで来られたの……</t>
         </is>
       </c>
     </row>
     <row r="331" ht="40" customHeight="1">
       <c r="A331" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.seductive.emotional[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B331" t="inlineStr" s="2">
@@ -10880,12 +10880,12 @@
       </c>
       <c r="C331" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D331" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.emotional[1]</t>
+          <t xml:space="preserve">postWin.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E331" t="inlineStr" s="2">
@@ -10895,14 +10895,14 @@
       </c>
       <c r="F331" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの子が相手……っ……ふふ、燃えてきたわ……</t>
+          <t xml:space="preserve">もっと上を目指すわ……っ……ふふ……</t>
         </is>
       </c>
     </row>
     <row r="332" ht="40" customHeight="1">
       <c r="A332" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.seductive.emotional[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B332" t="inlineStr" s="2">
@@ -10912,12 +10912,12 @@
       </c>
       <c r="C332" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D332" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.emotional[1]</t>
+          <t xml:space="preserve">preFinal.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E332" t="inlineStr" s="2">
@@ -10927,14 +10927,14 @@
       </c>
       <c r="F332" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">嬉しい……っ……！最高の舞台で勝てた……この瞬間を、ずっと忘れないわ……！</t>
+          <t xml:space="preserve">決勝戦……っ……ふふ、ここまで来たのね……</t>
         </is>
       </c>
     </row>
     <row r="333" ht="40" customHeight="1">
       <c r="A333" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.seductive.emotional[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B333" t="inlineStr" s="2">
@@ -10944,12 +10944,12 @@
       </c>
       <c r="C333" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D333" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.emotional[1]</t>
+          <t xml:space="preserve">preFinal.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E333" t="inlineStr" s="2">
@@ -10959,14 +10959,14 @@
       </c>
       <c r="F333" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">団体として挑むわ……っ……ふふ、燃えるわね……</t>
+          <t xml:space="preserve">最高の舞台ね……っ……ふふ、震えてるの……</t>
         </is>
       </c>
     </row>
     <row r="334" ht="40" customHeight="1">
       <c r="A334" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.seductive.emotional[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B334" t="inlineStr" s="2">
@@ -10976,12 +10976,12 @@
       </c>
       <c r="C334" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D334" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.emotional[2]</t>
+          <t xml:space="preserve">preMatch.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E334" t="inlineStr" s="2">
@@ -10991,14 +10991,14 @@
       </c>
       <c r="F334" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みんなで戦うわ……っ……ふふ……</t>
+          <t xml:space="preserve">試合前……っ……ふふ、心臓がドキドキしてるの……</t>
         </is>
       </c>
     </row>
     <row r="335" ht="40" customHeight="1">
       <c r="A335" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.seductive.emotional[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B335" t="inlineStr" s="2">
@@ -11008,12 +11008,12 @@
       </c>
       <c r="C335" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D335" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.emotional[1]</t>
+          <t xml:space="preserve">preMatch.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E335" t="inlineStr" s="2">
@@ -11023,14 +11023,14 @@
       </c>
       <c r="F335" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ごめんなさい……っ……今回は遠慮するわ……</t>
+          <t xml:space="preserve">楽しんでくるわね……っ……ふふ……</t>
         </is>
       </c>
     </row>
     <row r="336" ht="40" customHeight="1">
       <c r="A336" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.seductive.emotional[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B336" t="inlineStr" s="2">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="C336" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D336" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.emotional[2]</t>
+          <t xml:space="preserve">summon.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E336" t="inlineStr" s="2">
@@ -11055,14 +11055,14 @@
       </c>
       <c r="F336" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">またの機会に……っ……ふふ……</t>
+          <t xml:space="preserve">ジュニア大会に……っ……ふふ、私を選んでくれたのね、嬉しい……</t>
         </is>
       </c>
     </row>
     <row r="337" ht="40" customHeight="1">
       <c r="A337" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.seductive.emotional[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B337" t="inlineStr" s="2">
@@ -11072,12 +11072,12 @@
       </c>
       <c r="C337" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D337" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.seductive.emotional[1]</t>
+          <t xml:space="preserve">summon.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E337" t="inlineStr" s="2">
@@ -11087,14 +11087,14 @@
       </c>
       <c r="F337" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けたわ……っ……ふふ、悔しい……</t>
+          <t xml:space="preserve">楽しみだわ……っ……ふふ、燃えてきたの……</t>
         </is>
       </c>
     </row>
     <row r="338" ht="40" customHeight="1">
       <c r="A338" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.seductive.emotional[2]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B338" t="inlineStr" s="2">
@@ -11104,12 +11104,12 @@
       </c>
       <c r="C338" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D338" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.seductive.emotional[2]</t>
+          <t xml:space="preserve">seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E338" t="inlineStr" s="2">
@@ -11119,14 +11119,14 @@
       </c>
       <c r="F338" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次は絶対に……っ……ふふ、リベンジするわ……</t>
+          <t xml:space="preserve">あの子が相手……っ……ふふ、燃えてきたわ……</t>
         </is>
       </c>
     </row>
     <row r="339" ht="40" customHeight="1">
       <c r="A339" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.seductive.emotional[1]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B339" t="inlineStr" s="2">
@@ -11136,12 +11136,12 @@
       </c>
       <c r="C339" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D339" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.seductive.emotional[1]</t>
+          <t xml:space="preserve">seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E339" t="inlineStr" s="2">
@@ -11151,14 +11151,14 @@
       </c>
       <c r="F339" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝った……っ……ふふ、団体のために戦えて嬉しい……</t>
+          <t xml:space="preserve">嬉しい……っ……！最高の舞台で勝てた……この瞬間を、ずっと忘れないわ……！</t>
         </is>
       </c>
     </row>
     <row r="340" ht="40" customHeight="1">
       <c r="A340" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.seductive.emotional[2]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B340" t="inlineStr" s="2">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="C340" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D340" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.seductive.emotional[2]</t>
+          <t xml:space="preserve">seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E340" t="inlineStr" s="2">
@@ -11183,14 +11183,14 @@
       </c>
       <c r="F340" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みんなのおかげよ……っ……ふふ……</t>
+          <t xml:space="preserve">団体として挑むわ……っ……ふふ、燃えるわね……</t>
         </is>
       </c>
     </row>
     <row r="341" ht="40" customHeight="1">
       <c r="A341" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.emotional[1]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B341" t="inlineStr" s="2">
@@ -11200,12 +11200,12 @@
       </c>
       <c r="C341" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D341" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.emotional[1]</t>
+          <t xml:space="preserve">seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E341" t="inlineStr" s="2">
@@ -11215,14 +11215,14 @@
       </c>
       <c r="F341" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝てた…！ 団体のみんなのおかげ…嬉しい…！</t>
+          <t xml:space="preserve">みんなで戦うわ……っ……ふふ……</t>
         </is>
       </c>
     </row>
     <row r="342" ht="40" customHeight="1">
       <c r="A342" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.emotional[2]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B342" t="inlineStr" s="2">
@@ -11232,12 +11232,12 @@
       </c>
       <c r="C342" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D342" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.emotional[2]</t>
+          <t xml:space="preserve">seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E342" t="inlineStr" s="2">
@@ -11247,14 +11247,14 @@
       </c>
       <c r="F342" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝てた…みんなのおかげ…嬉しい…！</t>
+          <t xml:space="preserve">ごめんなさい……っ……今回は遠慮するわ……</t>
         </is>
       </c>
     </row>
     <row r="343" ht="40" customHeight="1">
       <c r="A343" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.emotional[3]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B343" t="inlineStr" s="2">
@@ -11264,12 +11264,12 @@
       </c>
       <c r="C343" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D343" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.emotional[3]</t>
+          <t xml:space="preserve">seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E343" t="inlineStr" s="2">
@@ -11279,14 +11279,14 @@
       </c>
       <c r="F343" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝てた…嬉しい…！ みんなのために頑張れた…！</t>
+          <t xml:space="preserve">またの機会に……っ……ふふ……</t>
         </is>
       </c>
     </row>
     <row r="344" ht="40" customHeight="1">
       <c r="A344" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.seductive.emotional[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B344" t="inlineStr" s="2">
@@ -11296,29 +11296,29 @@
       </c>
       <c r="C344" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D344" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.seductive.emotional[1]</t>
+          <t xml:space="preserve">result_lose.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E344" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F344" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">リングを降りるわ……っ……ふふ、ここで戦えた日々、永遠に忘れない……ありがとう……</t>
+          <t xml:space="preserve">負けたわ……っ……ふふ、悔しい……</t>
         </is>
       </c>
     </row>
     <row r="345" ht="40" customHeight="1">
       <c r="A345" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.seductive.emotional[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B345" t="inlineStr" s="2">
@@ -11328,59 +11328,283 @@
       </c>
       <c r="C345" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D345" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.emotional[1]</t>
+          <t xml:space="preserve">result_lose.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E345" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F345" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">口説かれる側になるなんて…っ…ふふ、いい度胸ね</t>
+          <t xml:space="preserve">次は絶対に……っ……ふふ、リベンジするわ……</t>
         </is>
       </c>
     </row>
     <row r="346" ht="40" customHeight="1">
       <c r="A346" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.seductive.emotional[1]</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_win.seductive.emotional[1]</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">勝った……っ……ふふ、団体のために戦えて嬉しい……</t>
+        </is>
+      </c>
+    </row>
+    <row r="347" ht="40" customHeight="1">
+      <c r="A347" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.seductive.emotional[2]</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_win.seductive.emotional[2]</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">みんなのおかげよ……っ……ふふ……</t>
+        </is>
+      </c>
+    </row>
+    <row r="348" ht="40" customHeight="1">
+      <c r="A348" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.emotional[1]</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">seductive.emotional[1]</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">勝てた…！ 団体のみんなのおかげ…嬉しい…！</t>
+        </is>
+      </c>
+    </row>
+    <row r="349" ht="40" customHeight="1">
+      <c r="A349" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.emotional[2]</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">seductive.emotional[2]</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">勝てた…みんなのおかげ…嬉しい…！</t>
+        </is>
+      </c>
+    </row>
+    <row r="350" ht="40" customHeight="1">
+      <c r="A350" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.emotional[3]</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">seductive.emotional[3]</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">勝てた…嬉しい…！ みんなのために頑張れた…！</t>
+        </is>
+      </c>
+    </row>
+    <row r="351" ht="40" customHeight="1">
+      <c r="A351" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">ENDING_LINES.fighter.seductive.emotional[1]</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ENDING_LINES</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">fighter.seductive.emotional[1]</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">リングを降りるわ……っ……ふふ、ここで戦えた日々、永遠に忘れない……ありがとう……</t>
+        </is>
+      </c>
+    </row>
+    <row r="352" ht="40" customHeight="1">
+      <c r="A352" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.seductive.emotional[1]</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">seductive.emotional[1]</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">口説かれる側になるなんて…っ…ふふ、いい度胸ね</t>
+        </is>
+      </c>
+    </row>
+    <row r="353" ht="40" customHeight="1">
+      <c r="A353" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES.seductive.emotional[1]</t>
         </is>
       </c>
-      <c r="B346" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C346" t="inlineStr" s="2">
+      <c r="B353" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D346" t="inlineStr" s="12">
+      <c r="D353" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">seductive.emotional[1]</t>
         </is>
       </c>
-      <c r="E346" t="inlineStr" s="2">
+      <c r="E353" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F346" t="inlineStr" s="3">
+      <c r="F353" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">うふふ♪嬉しい♪</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H346"/>
+  <autoFilter ref="A1:H353"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/蠱惑×感情的.xlsx
+++ b/セリフ編集/キャラタイプ別/蠱惑×感情的.xlsx
@@ -284,7 +284,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H346"/>
+  <dimension ref="A1:H336"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -9686,7 +9686,7 @@
     <row r="294" ht="40" customHeight="1">
       <c r="A294" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.seductive.emotional[1]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
@@ -9696,12 +9696,12 @@
       </c>
       <c r="C294" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D294" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.seductive.emotional[1]</t>
+          <t xml:space="preserve">seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E294" t="inlineStr" s="2">
@@ -9711,14 +9711,14 @@
       </c>
       <c r="F294" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日は……っ……ふふ、よろしくね……</t>
+          <t xml:space="preserve">勢いが止まったわ……っ……ふふ、また始めればいいのよ……</t>
         </is>
       </c>
     </row>
     <row r="295" ht="40" customHeight="1">
       <c r="A295" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.seductive.emotional[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="2">
@@ -9728,29 +9728,29 @@
       </c>
       <c r="C295" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D295" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.down.seductive.emotional[1]</t>
+          <t xml:space="preserve">preFinal.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E295" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F295" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うまくいかない……っ……どうしてかしら……</t>
+          <t xml:space="preserve">身体、もう震えてるの…っ…ふふ、でも最後まで立つわ</t>
         </is>
       </c>
     </row>
     <row r="296" ht="40" customHeight="1">
       <c r="A296" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.seductive.emotional[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B296" t="inlineStr" s="2">
@@ -9760,29 +9760,29 @@
       </c>
       <c r="C296" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D296" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.up.seductive.emotional[1]</t>
+          <t xml:space="preserve">preFinal.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E296" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F296" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">なんだか調子いいの……っ……ふふ……</t>
+          <t xml:space="preserve">ここまで来たのね…っ…最後の舞台、全部ぶつけるわ</t>
         </is>
       </c>
     </row>
     <row r="297" ht="40" customHeight="1">
       <c r="A297" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.seductive.emotional[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B297" t="inlineStr" s="2">
@@ -9792,29 +9792,29 @@
       </c>
       <c r="C297" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D297" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-04.seductive.emotional[1]</t>
+          <t xml:space="preserve">preMatch.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E297" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F297" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習するわ……っ……ふふ……</t>
+          <t xml:space="preserve">お相手は誰かしら…っ…ふふ、もう身体が疼いてるの</t>
         </is>
       </c>
     </row>
     <row r="298" ht="40" customHeight="1">
       <c r="A298" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.seductive.emotional[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B298" t="inlineStr" s="2">
@@ -9824,29 +9824,29 @@
       </c>
       <c r="C298" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D298" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-05.seductive.emotional[1]</t>
+          <t xml:space="preserve">preMatch.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E298" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F298" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">大丈夫よ……っ……ふふ、心配しないで……</t>
+          <t xml:space="preserve">早く来てよ…！ この昂り、ぶつける相手が欲しいの…！</t>
         </is>
       </c>
     </row>
     <row r="299" ht="40" customHeight="1">
       <c r="A299" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.seductive.emotional[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B299" t="inlineStr" s="2">
@@ -9856,29 +9856,29 @@
       </c>
       <c r="C299" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D299" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.seductive.emotional[1]</t>
+          <t xml:space="preserve">survivor.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E299" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F299" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みんなと一緒だと……っ……ふふ、安心するの……</t>
+          <t xml:space="preserve">一人、落としたわ…っ…はぁ…まだ疼いてるの。次、早く出してよ</t>
         </is>
       </c>
     </row>
     <row r="300" ht="40" customHeight="1">
       <c r="A300" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.seductive.emotional[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B300" t="inlineStr" s="2">
@@ -9888,29 +9888,29 @@
       </c>
       <c r="C300" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D300" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-07.seductive.emotional[1]</t>
+          <t xml:space="preserve">survivor.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E300" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F300" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お客さんがいっぱい……っ……ふふ、燃えるわね……</t>
+          <t xml:space="preserve">まだ立ってる…！ この身体、まだ終わってないの…！ 次、来なさい…！</t>
         </is>
       </c>
     </row>
     <row r="301" ht="40" customHeight="1">
       <c r="A301" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.seductive.emotional[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B301" t="inlineStr" s="2">
@@ -9920,29 +9920,29 @@
       </c>
       <c r="C301" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D301" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.seductive.emotional[1]</t>
+          <t xml:space="preserve">champion.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E301" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F301" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">体調は大丈夫よ……っ……ふふ、心配いらない……</t>
+          <t xml:space="preserve">三人で勝ったの……！ この感動は……一人じゃ味わえないわ……</t>
         </is>
       </c>
     </row>
     <row r="302" ht="40" customHeight="1">
       <c r="A302" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.seductive.emotional[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B302" t="inlineStr" s="2">
@@ -9952,29 +9952,29 @@
       </c>
       <c r="C302" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D302" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-09.seductive.emotional[1]</t>
+          <t xml:space="preserve">champion.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E302" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F302" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次の試合……っ……ふふ、楽しみだわ……</t>
+          <t xml:space="preserve">仲間が繋いでくれた想い……最後まで、手放さなかったよ……！</t>
         </is>
       </c>
     </row>
     <row r="303" ht="40" customHeight="1">
       <c r="A303" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.seductive.emotional[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B303" t="inlineStr" s="2">
@@ -9984,29 +9984,29 @@
       </c>
       <c r="C303" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D303" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.seductive.emotional[1]</t>
+          <t xml:space="preserve">defiant.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E303" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F303" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとう……っ……ふふ、嬉しい……</t>
+          <t xml:space="preserve">この賞じゃ……心は満たされないのよ……！ 次は全部、奪い返すから……</t>
         </is>
       </c>
     </row>
     <row r="304" ht="40" customHeight="1">
       <c r="A304" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.seductive.emotional[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B304" t="inlineStr" s="2">
@@ -10016,29 +10016,29 @@
       </c>
       <c r="C304" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D304" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.emotional[1]</t>
+          <t xml:space="preserve">defiant.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E304" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F304" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勢いが止まったわ……っ……ふふ、また始めればいいのよ……</t>
+          <t xml:space="preserve">一人で輝いても寂しいだけ……！ 次は……三人で、ね……！</t>
         </is>
       </c>
     </row>
     <row r="305" ht="40" customHeight="1">
       <c r="A305" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.seductive.emotional[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B305" t="inlineStr" s="2">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="C305" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D305" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.seductive.emotional[1]</t>
+          <t xml:space="preserve">gauntlet.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E305" t="inlineStr" s="2">
@@ -10063,14 +10063,14 @@
       </c>
       <c r="F305" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">身体、もう震えてるの…っ…ふふ、でも最後まで立つわ</t>
+          <t xml:space="preserve">もう身体が動かない……でも、最後に立ってたのは私よ……！ 見届けてくれた？</t>
         </is>
       </c>
     </row>
     <row r="306" ht="40" customHeight="1">
       <c r="A306" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.seductive.emotional[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B306" t="inlineStr" s="2">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="C306" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D306" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.seductive.emotional[2]</t>
+          <t xml:space="preserve">gauntlet.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E306" t="inlineStr" s="2">
@@ -10095,14 +10095,14 @@
       </c>
       <c r="F306" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで来たのね…っ…最後の舞台、全部ぶつけるわ</t>
+          <t xml:space="preserve">何人来ても倒れなかった……！ この身体が、全部証明してるでしょ……？</t>
         </is>
       </c>
     </row>
     <row r="307" ht="40" customHeight="1">
       <c r="A307" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.seductive.emotional[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B307" t="inlineStr" s="2">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="C307" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D307" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.seductive.emotional[1]</t>
+          <t xml:space="preserve">champion.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E307" t="inlineStr" s="2">
@@ -10127,14 +10127,14 @@
       </c>
       <c r="F307" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お相手は誰かしら…っ…ふふ、もう身体が疼いてるの</t>
+          <t xml:space="preserve">優勝……っ……ふふ、私、頂点に立ったのね……！</t>
         </is>
       </c>
     </row>
     <row r="308" ht="40" customHeight="1">
       <c r="A308" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.seductive.emotional[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B308" t="inlineStr" s="2">
@@ -10144,12 +10144,12 @@
       </c>
       <c r="C308" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D308" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.seductive.emotional[2]</t>
+          <t xml:space="preserve">champion.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E308" t="inlineStr" s="2">
@@ -10159,14 +10159,14 @@
       </c>
       <c r="F308" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">早く来てよ…！ この昂り、ぶつける相手が欲しいの…！</t>
+          <t xml:space="preserve">この景色……っ……ふふ、忘れないわ……</t>
         </is>
       </c>
     </row>
     <row r="309" ht="40" customHeight="1">
       <c r="A309" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.seductive.emotional[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B309" t="inlineStr" s="2">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="C309" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D309" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.seductive.emotional[1]</t>
+          <t xml:space="preserve">postLose.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E309" t="inlineStr" s="2">
@@ -10191,14 +10191,14 @@
       </c>
       <c r="F309" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人、落としたわ…っ…はぁ…まだ疼いてるの。次、早く出してよ</t>
+          <t xml:space="preserve">負けたわ……っ……悔しい……でも、いい経験だった……</t>
         </is>
       </c>
     </row>
     <row r="310" ht="40" customHeight="1">
       <c r="A310" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.seductive.emotional[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B310" t="inlineStr" s="2">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="C310" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D310" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.seductive.emotional[2]</t>
+          <t xml:space="preserve">postLose.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E310" t="inlineStr" s="2">
@@ -10223,14 +10223,14 @@
       </c>
       <c r="F310" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ立ってる…！ この身体、まだ終わってないの…！ 次、来なさい…！</t>
+          <t xml:space="preserve">リベンジするわ……っ……ふふ、必ず……</t>
         </is>
       </c>
     </row>
     <row r="311" ht="40" customHeight="1">
       <c r="A311" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.seductive.emotional[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B311" t="inlineStr" s="2">
@@ -10240,12 +10240,12 @@
       </c>
       <c r="C311" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D311" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.seductive.emotional[1]</t>
+          <t xml:space="preserve">postMatchWin.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E311" t="inlineStr" s="2">
@@ -10255,14 +10255,14 @@
       </c>
       <c r="F311" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">三人で勝ったの……！ この感動は……一人じゃ味わえないわ……</t>
+          <t xml:space="preserve">勝った……っ……ふふ、まだまだ行けるわ……</t>
         </is>
       </c>
     </row>
     <row r="312" ht="40" customHeight="1">
       <c r="A312" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.seductive.emotional[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B312" t="inlineStr" s="2">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="C312" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D312" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.seductive.emotional[2]</t>
+          <t xml:space="preserve">postMatchWin.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E312" t="inlineStr" s="2">
@@ -10287,14 +10287,14 @@
       </c>
       <c r="F312" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲間が繋いでくれた想い……最後まで、手放さなかったよ……！</t>
+          <t xml:space="preserve">いい感じよ……っ……ふふ……</t>
         </is>
       </c>
     </row>
     <row r="313" ht="40" customHeight="1">
       <c r="A313" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.seductive.emotional[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B313" t="inlineStr" s="2">
@@ -10304,12 +10304,12 @@
       </c>
       <c r="C313" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D313" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.seductive.emotional[1]</t>
+          <t xml:space="preserve">postWin.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E313" t="inlineStr" s="2">
@@ -10319,14 +10319,14 @@
       </c>
       <c r="F313" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この賞じゃ……心は満たされないのよ……！ 次は全部、奪い返すから……</t>
+          <t xml:space="preserve">勝ち上がったわ……っ……ふふ、ここまで来られたの……</t>
         </is>
       </c>
     </row>
     <row r="314" ht="40" customHeight="1">
       <c r="A314" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.seductive.emotional[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B314" t="inlineStr" s="2">
@@ -10336,12 +10336,12 @@
       </c>
       <c r="C314" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D314" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.seductive.emotional[2]</t>
+          <t xml:space="preserve">postWin.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E314" t="inlineStr" s="2">
@@ -10351,14 +10351,14 @@
       </c>
       <c r="F314" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人で輝いても寂しいだけ……！ 次は……三人で、ね……！</t>
+          <t xml:space="preserve">もっと上を目指すわ……っ……ふふ……</t>
         </is>
       </c>
     </row>
     <row r="315" ht="40" customHeight="1">
       <c r="A315" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.seductive.emotional[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B315" t="inlineStr" s="2">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="C315" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D315" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.seductive.emotional[1]</t>
+          <t xml:space="preserve">preFinal.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E315" t="inlineStr" s="2">
@@ -10383,14 +10383,14 @@
       </c>
       <c r="F315" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう身体が動かない……でも、最後に立ってたのは私よ……！ 見届けてくれた？</t>
+          <t xml:space="preserve">決勝戦……っ……ふふ、ここまで来たのね……</t>
         </is>
       </c>
     </row>
     <row r="316" ht="40" customHeight="1">
       <c r="A316" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.seductive.emotional[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B316" t="inlineStr" s="2">
@@ -10400,12 +10400,12 @@
       </c>
       <c r="C316" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D316" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.seductive.emotional[2]</t>
+          <t xml:space="preserve">preFinal.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E316" t="inlineStr" s="2">
@@ -10415,14 +10415,14 @@
       </c>
       <c r="F316" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何人来ても倒れなかった……！ この身体が、全部証明してるでしょ……？</t>
+          <t xml:space="preserve">最高の舞台ね……っ……ふふ、震えてるの……</t>
         </is>
       </c>
     </row>
     <row r="317" ht="40" customHeight="1">
       <c r="A317" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.seductive.emotional[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B317" t="inlineStr" s="2">
@@ -10437,7 +10437,7 @@
       </c>
       <c r="D317" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.seductive.emotional[1]</t>
+          <t xml:space="preserve">preMatch.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E317" t="inlineStr" s="2">
@@ -10447,14 +10447,14 @@
       </c>
       <c r="F317" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">優勝……っ……ふふ、私、頂点に立ったのね……！</t>
+          <t xml:space="preserve">試合前……っ……ふふ、心臓がドキドキしてるの……</t>
         </is>
       </c>
     </row>
     <row r="318" ht="40" customHeight="1">
       <c r="A318" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.seductive.emotional[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B318" t="inlineStr" s="2">
@@ -10469,7 +10469,7 @@
       </c>
       <c r="D318" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.seductive.emotional[2]</t>
+          <t xml:space="preserve">preMatch.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E318" t="inlineStr" s="2">
@@ -10479,14 +10479,14 @@
       </c>
       <c r="F318" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この景色……っ……ふふ、忘れないわ……</t>
+          <t xml:space="preserve">楽しんでくるわね……っ……ふふ……</t>
         </is>
       </c>
     </row>
     <row r="319" ht="40" customHeight="1">
       <c r="A319" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.seductive.emotional[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B319" t="inlineStr" s="2">
@@ -10501,7 +10501,7 @@
       </c>
       <c r="D319" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.seductive.emotional[1]</t>
+          <t xml:space="preserve">summon.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E319" t="inlineStr" s="2">
@@ -10511,14 +10511,14 @@
       </c>
       <c r="F319" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けたわ……っ……悔しい……でも、いい経験だった……</t>
+          <t xml:space="preserve">ジュニア大会に……っ……ふふ、私を選んでくれたのね、嬉しい……</t>
         </is>
       </c>
     </row>
     <row r="320" ht="40" customHeight="1">
       <c r="A320" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.seductive.emotional[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B320" t="inlineStr" s="2">
@@ -10533,7 +10533,7 @@
       </c>
       <c r="D320" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.seductive.emotional[2]</t>
+          <t xml:space="preserve">summon.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E320" t="inlineStr" s="2">
@@ -10543,14 +10543,14 @@
       </c>
       <c r="F320" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">リベンジするわ……っ……ふふ、必ず……</t>
+          <t xml:space="preserve">楽しみだわ……っ……ふふ、燃えてきたの……</t>
         </is>
       </c>
     </row>
     <row r="321" ht="40" customHeight="1">
       <c r="A321" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.seductive.emotional[1]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B321" t="inlineStr" s="2">
@@ -10560,12 +10560,12 @@
       </c>
       <c r="C321" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D321" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.seductive.emotional[1]</t>
+          <t xml:space="preserve">seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E321" t="inlineStr" s="2">
@@ -10575,14 +10575,14 @@
       </c>
       <c r="F321" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝った……っ……ふふ、まだまだ行けるわ……</t>
+          <t xml:space="preserve">あの子が相手……っ……ふふ、燃えてきたわ……</t>
         </is>
       </c>
     </row>
     <row r="322" ht="40" customHeight="1">
       <c r="A322" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.seductive.emotional[2]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B322" t="inlineStr" s="2">
@@ -10592,12 +10592,12 @@
       </c>
       <c r="C322" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D322" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.seductive.emotional[2]</t>
+          <t xml:space="preserve">seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E322" t="inlineStr" s="2">
@@ -10607,14 +10607,14 @@
       </c>
       <c r="F322" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい感じよ……っ……ふふ……</t>
+          <t xml:space="preserve">嬉しい……っ……！最高の舞台で勝てた……この瞬間を、ずっと忘れないわ……！</t>
         </is>
       </c>
     </row>
     <row r="323" ht="40" customHeight="1">
       <c r="A323" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.seductive.emotional[1]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B323" t="inlineStr" s="2">
@@ -10624,12 +10624,12 @@
       </c>
       <c r="C323" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D323" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.seductive.emotional[1]</t>
+          <t xml:space="preserve">seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E323" t="inlineStr" s="2">
@@ -10639,14 +10639,14 @@
       </c>
       <c r="F323" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ち上がったわ……っ……ふふ、ここまで来られたの……</t>
+          <t xml:space="preserve">団体として挑むわ……っ……ふふ、燃えるわね……</t>
         </is>
       </c>
     </row>
     <row r="324" ht="40" customHeight="1">
       <c r="A324" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.seductive.emotional[2]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B324" t="inlineStr" s="2">
@@ -10656,12 +10656,12 @@
       </c>
       <c r="C324" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D324" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.seductive.emotional[2]</t>
+          <t xml:space="preserve">seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E324" t="inlineStr" s="2">
@@ -10671,14 +10671,14 @@
       </c>
       <c r="F324" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もっと上を目指すわ……っ……ふふ……</t>
+          <t xml:space="preserve">みんなで戦うわ……っ……ふふ……</t>
         </is>
       </c>
     </row>
     <row r="325" ht="40" customHeight="1">
       <c r="A325" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.seductive.emotional[1]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B325" t="inlineStr" s="2">
@@ -10688,12 +10688,12 @@
       </c>
       <c r="C325" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D325" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.seductive.emotional[1]</t>
+          <t xml:space="preserve">seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E325" t="inlineStr" s="2">
@@ -10703,14 +10703,14 @@
       </c>
       <c r="F325" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決勝戦……っ……ふふ、ここまで来たのね……</t>
+          <t xml:space="preserve">ごめんなさい……っ……今回は遠慮するわ……</t>
         </is>
       </c>
     </row>
     <row r="326" ht="40" customHeight="1">
       <c r="A326" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.seductive.emotional[2]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B326" t="inlineStr" s="2">
@@ -10720,12 +10720,12 @@
       </c>
       <c r="C326" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D326" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.seductive.emotional[2]</t>
+          <t xml:space="preserve">seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E326" t="inlineStr" s="2">
@@ -10735,14 +10735,14 @@
       </c>
       <c r="F326" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高の舞台ね……っ……ふふ、震えてるの……</t>
+          <t xml:space="preserve">またの機会に……っ……ふふ……</t>
         </is>
       </c>
     </row>
     <row r="327" ht="40" customHeight="1">
       <c r="A327" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.seductive.emotional[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B327" t="inlineStr" s="2">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="C327" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D327" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.seductive.emotional[1]</t>
+          <t xml:space="preserve">result_lose.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E327" t="inlineStr" s="2">
@@ -10767,14 +10767,14 @@
       </c>
       <c r="F327" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">試合前……っ……ふふ、心臓がドキドキしてるの……</t>
+          <t xml:space="preserve">負けたわ……っ……ふふ、悔しい……</t>
         </is>
       </c>
     </row>
     <row r="328" ht="40" customHeight="1">
       <c r="A328" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.seductive.emotional[2]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B328" t="inlineStr" s="2">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="C328" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D328" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.seductive.emotional[2]</t>
+          <t xml:space="preserve">result_lose.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E328" t="inlineStr" s="2">
@@ -10799,14 +10799,14 @@
       </c>
       <c r="F328" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">楽しんでくるわね……っ……ふふ……</t>
+          <t xml:space="preserve">次は絶対に……っ……ふふ、リベンジするわ……</t>
         </is>
       </c>
     </row>
     <row r="329" ht="40" customHeight="1">
       <c r="A329" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.seductive.emotional[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B329" t="inlineStr" s="2">
@@ -10816,12 +10816,12 @@
       </c>
       <c r="C329" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D329" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.seductive.emotional[1]</t>
+          <t xml:space="preserve">result_win.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E329" t="inlineStr" s="2">
@@ -10831,14 +10831,14 @@
       </c>
       <c r="F329" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ジュニア大会に……っ……ふふ、私を選んでくれたのね、嬉しい……</t>
+          <t xml:space="preserve">勝った……っ……ふふ、団体のために戦えて嬉しい……</t>
         </is>
       </c>
     </row>
     <row r="330" ht="40" customHeight="1">
       <c r="A330" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.seductive.emotional[2]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B330" t="inlineStr" s="2">
@@ -10848,12 +10848,12 @@
       </c>
       <c r="C330" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D330" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.seductive.emotional[2]</t>
+          <t xml:space="preserve">result_win.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E330" t="inlineStr" s="2">
@@ -10863,14 +10863,14 @@
       </c>
       <c r="F330" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">楽しみだわ……っ……ふふ、燃えてきたの……</t>
+          <t xml:space="preserve">みんなのおかげよ……っ……ふふ……</t>
         </is>
       </c>
     </row>
     <row r="331" ht="40" customHeight="1">
       <c r="A331" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.seductive.emotional[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B331" t="inlineStr" s="2">
@@ -10880,7 +10880,7 @@
       </c>
       <c r="C331" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D331" t="inlineStr" s="12">
@@ -10895,14 +10895,14 @@
       </c>
       <c r="F331" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの子が相手……っ……ふふ、燃えてきたわ……</t>
+          <t xml:space="preserve">勝てた…！ 団体のみんなのおかげ…嬉しい…！</t>
         </is>
       </c>
     </row>
     <row r="332" ht="40" customHeight="1">
       <c r="A332" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.seductive.emotional[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.emotional[2]</t>
         </is>
       </c>
       <c r="B332" t="inlineStr" s="2">
@@ -10912,12 +10912,12 @@
       </c>
       <c r="C332" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D332" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.emotional[1]</t>
+          <t xml:space="preserve">seductive.emotional[2]</t>
         </is>
       </c>
       <c r="E332" t="inlineStr" s="2">
@@ -10927,14 +10927,14 @@
       </c>
       <c r="F332" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">嬉しい……っ……！最高の舞台で勝てた……この瞬間を、ずっと忘れないわ……！</t>
+          <t xml:space="preserve">勝てた…みんなのおかげ…嬉しい…！</t>
         </is>
       </c>
     </row>
     <row r="333" ht="40" customHeight="1">
       <c r="A333" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.seductive.emotional[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.emotional[3]</t>
         </is>
       </c>
       <c r="B333" t="inlineStr" s="2">
@@ -10944,12 +10944,12 @@
       </c>
       <c r="C333" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D333" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.emotional[1]</t>
+          <t xml:space="preserve">seductive.emotional[3]</t>
         </is>
       </c>
       <c r="E333" t="inlineStr" s="2">
@@ -10959,14 +10959,14 @@
       </c>
       <c r="F333" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">団体として挑むわ……っ……ふふ、燃えるわね……</t>
+          <t xml:space="preserve">勝てた…嬉しい…！ みんなのために頑張れた…！</t>
         </is>
       </c>
     </row>
     <row r="334" ht="40" customHeight="1">
       <c r="A334" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.seductive.emotional[2]</t>
+          <t xml:space="preserve">ENDING_LINES.fighter.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B334" t="inlineStr" s="2">
@@ -10976,29 +10976,29 @@
       </c>
       <c r="C334" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">ENDING_LINES</t>
         </is>
       </c>
       <c r="D334" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.emotional[2]</t>
+          <t xml:space="preserve">fighter.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E334" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
         </is>
       </c>
       <c r="F334" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みんなで戦うわ……っ……ふふ……</t>
+          <t xml:space="preserve">リングを降りるわ……っ……ふふ、ここで戦えた日々、永遠に忘れない……ありがとう……</t>
         </is>
       </c>
     </row>
     <row r="335" ht="40" customHeight="1">
       <c r="A335" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.seductive.emotional[1]</t>
+          <t xml:space="preserve">FA_GREETING_LINES.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B335" t="inlineStr" s="2">
@@ -11008,7 +11008,7 @@
       </c>
       <c r="C335" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
         </is>
       </c>
       <c r="D335" t="inlineStr" s="12">
@@ -11018,19 +11018,19 @@
       </c>
       <c r="E335" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
       <c r="F335" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ごめんなさい……っ……今回は遠慮するわ……</t>
+          <t xml:space="preserve">口説かれる側になるなんて…っ…ふふ、いい度胸ね</t>
         </is>
       </c>
     </row>
     <row r="336" ht="40" customHeight="1">
       <c r="A336" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.seductive.emotional[2]</t>
+          <t xml:space="preserve">SCOUT_GREETING_LINES.seductive.emotional[1]</t>
         </is>
       </c>
       <c r="B336" t="inlineStr" s="2">
@@ -11040,347 +11040,27 @@
       </c>
       <c r="C336" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
       <c r="D336" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.emotional[2]</t>
+          <t xml:space="preserve">seductive.emotional[1]</t>
         </is>
       </c>
       <c r="E336" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
       <c r="F336" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">またの機会に……っ……ふふ……</t>
-        </is>
-      </c>
-    </row>
-    <row r="337" ht="40" customHeight="1">
-      <c r="A337" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.seductive.emotional[1]</t>
-        </is>
-      </c>
-      <c r="B337" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C337" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
-        </is>
-      </c>
-      <c r="D337" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">result_lose.seductive.emotional[1]</t>
-        </is>
-      </c>
-      <c r="E337" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
-        </is>
-      </c>
-      <c r="F337" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">負けたわ……っ……ふふ、悔しい……</t>
-        </is>
-      </c>
-    </row>
-    <row r="338" ht="40" customHeight="1">
-      <c r="A338" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.seductive.emotional[2]</t>
-        </is>
-      </c>
-      <c r="B338" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C338" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
-        </is>
-      </c>
-      <c r="D338" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">result_lose.seductive.emotional[2]</t>
-        </is>
-      </c>
-      <c r="E338" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
-        </is>
-      </c>
-      <c r="F338" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">次は絶対に……っ……ふふ、リベンジするわ……</t>
-        </is>
-      </c>
-    </row>
-    <row r="339" ht="40" customHeight="1">
-      <c r="A339" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.seductive.emotional[1]</t>
-        </is>
-      </c>
-      <c r="B339" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C339" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
-        </is>
-      </c>
-      <c r="D339" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">result_win.seductive.emotional[1]</t>
-        </is>
-      </c>
-      <c r="E339" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
-        </is>
-      </c>
-      <c r="F339" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">勝った……っ……ふふ、団体のために戦えて嬉しい……</t>
-        </is>
-      </c>
-    </row>
-    <row r="340" ht="40" customHeight="1">
-      <c r="A340" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.seductive.emotional[2]</t>
-        </is>
-      </c>
-      <c r="B340" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C340" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
-        </is>
-      </c>
-      <c r="D340" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">result_win.seductive.emotional[2]</t>
-        </is>
-      </c>
-      <c r="E340" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
-        </is>
-      </c>
-      <c r="F340" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">みんなのおかげよ……っ……ふふ……</t>
-        </is>
-      </c>
-    </row>
-    <row r="341" ht="40" customHeight="1">
-      <c r="A341" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.emotional[1]</t>
-        </is>
-      </c>
-      <c r="B341" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C341" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
-        </is>
-      </c>
-      <c r="D341" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">seductive.emotional[1]</t>
-        </is>
-      </c>
-      <c r="E341" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
-        </is>
-      </c>
-      <c r="F341" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">勝てた…！ 団体のみんなのおかげ…嬉しい…！</t>
-        </is>
-      </c>
-    </row>
-    <row r="342" ht="40" customHeight="1">
-      <c r="A342" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.emotional[2]</t>
-        </is>
-      </c>
-      <c r="B342" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C342" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
-        </is>
-      </c>
-      <c r="D342" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">seductive.emotional[2]</t>
-        </is>
-      </c>
-      <c r="E342" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
-        </is>
-      </c>
-      <c r="F342" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">勝てた…みんなのおかげ…嬉しい…！</t>
-        </is>
-      </c>
-    </row>
-    <row r="343" ht="40" customHeight="1">
-      <c r="A343" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.emotional[3]</t>
-        </is>
-      </c>
-      <c r="B343" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C343" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
-        </is>
-      </c>
-      <c r="D343" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">seductive.emotional[3]</t>
-        </is>
-      </c>
-      <c r="E343" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
-        </is>
-      </c>
-      <c r="F343" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">勝てた…嬉しい…！ みんなのために頑張れた…！</t>
-        </is>
-      </c>
-    </row>
-    <row r="344" ht="40" customHeight="1">
-      <c r="A344" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.seductive.emotional[1]</t>
-        </is>
-      </c>
-      <c r="B344" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C344" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">ENDING_LINES</t>
-        </is>
-      </c>
-      <c r="D344" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">fighter.seductive.emotional[1]</t>
-        </is>
-      </c>
-      <c r="E344" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
-        </is>
-      </c>
-      <c r="F344" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">リングを降りるわ……っ……ふふ、ここで戦えた日々、永遠に忘れない……ありがとう……</t>
-        </is>
-      </c>
-    </row>
-    <row r="345" ht="40" customHeight="1">
-      <c r="A345" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">FA_GREETING_LINES.seductive.emotional[1]</t>
-        </is>
-      </c>
-      <c r="B345" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C345" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
-        </is>
-      </c>
-      <c r="D345" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">seductive.emotional[1]</t>
-        </is>
-      </c>
-      <c r="E345" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
-        </is>
-      </c>
-      <c r="F345" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">口説かれる側になるなんて…っ…ふふ、いい度胸ね</t>
-        </is>
-      </c>
-    </row>
-    <row r="346" ht="40" customHeight="1">
-      <c r="A346" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES.seductive.emotional[1]</t>
-        </is>
-      </c>
-      <c r="B346" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C346" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
-        </is>
-      </c>
-      <c r="D346" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">seductive.emotional[1]</t>
-        </is>
-      </c>
-      <c r="E346" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
-        </is>
-      </c>
-      <c r="F346" t="inlineStr" s="3">
-        <is>
           <t xml:space="preserve">うふふ♪嬉しい♪</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H346"/>
+  <autoFilter ref="A1:H336"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/蠱惑×感情的.xlsx
+++ b/セリフ編集/キャラタイプ別/蠱惑×感情的.xlsx
@@ -2319,7 +2319,7 @@
       </c>
       <c r="F63" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長。あの人とやりたいの。……いいでしょ？</t>
+          <t xml:space="preserve">社長。三人であちらへ行きたいの。……いいでしょ？</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="F64" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">我慢が切れたの。あの人と、やらせて。</t>
+          <t xml:space="preserve">我慢が切れたの。三人で、乗り込ませて。</t>
         </is>
       </c>
     </row>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="F65" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">言うだけ言うわ。あの人と当てて。</t>
+          <t xml:space="preserve">言うだけ言うわ。三人であの団体に当てて。</t>
         </is>
       </c>
     </row>
